--- a/GearSage-client/pkgGear/data_raw/dstyle_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/dstyle_rod_import.xlsx
@@ -59,8 +59,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -448,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,50 +521,55 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>fit_style_tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>images</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>series_positioning</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>main_selling_points</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>official_reference_price</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>market_status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>player_positioning</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>player_selling_points</t>
         </is>
@@ -564,20 +601,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/dstyle_rods/DSR1000_DEHIGHRO_GRANDEE_Spec.png</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>DEHIGHRO GRANDEE Spec（ディハイロ グランディースペック） DEHIGHRO GRANDEE Spec</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>淡水 Bass 竿系</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>以 Bass 路亞作釣為核心，覆蓋精細、泛用、游動與強力障礙等細分場景</t>
         </is>
@@ -609,20 +651,25 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/dstyle_rods/DSR1001_DEHIGHRO.jpg</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>DEHIGHRO / ディハイロ DEHIGHRO / HIGH-END SERIES</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>淡水 Bass 竿系</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>以 Bass 路亞作釣為核心，覆蓋精細、泛用、游動與強力障礙等細分場景</t>
         </is>
@@ -654,20 +701,25 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/dstyle_rods/DSR1002_BLUE_TREK_SABER_SERIES.png</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>BLUE TREK SABER SERIES (ブルートレック サーベルシリーズ) 琵琶湖ガイド”にっしぃ”こと『西平守良プロデュースロッド』 BLUE TREKの生まれた個性派SABER SERIES(サーベルシリーズ）が登場。 BLUE TREKをベースにブランクとグリップ周りを見直し。西平守良の描く理想のヘビーデューティー仕様に生まれ変わりました。 特徴としてはブランクはより粘り＆パワーを持たせてブランク仕様に変更。グリップはダークグレー＆ブラックのEVA仕様。グリップエンドはパワーフッキング時のダメージを軽減するべくコルクエンドキャップを採用。ベイトはラウンドタイプを採用。</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>淡水 Bass 竿系</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>以 Bass 路亞作釣為核心，覆蓋精細、泛用、游動與強力障礙等細分場景</t>
         </is>
@@ -699,20 +751,25 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/dstyle_rods/DSR1003_BLUE_TREK_2_Piece.png</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>BLUE TREK 2ピースモデル 【クイック、モバイル、２ピースレボリューション】 DSTYLEが考えるBLUE TREKの2ピースのカタチ!! 車内でも気軽に収納・クイックに持ち出せる!! ワンピースモデルに引けを取らない操作性</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>淡水 Bass 竿系</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>以 Bass 路亞作釣為核心，覆蓋精細、泛用、游動與強力障礙等細分場景</t>
         </is>
@@ -744,20 +801,25 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/dstyle_rods/DSR1004_BLUE_TREK_10th_Anniversary_Model.png</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>BLUE TREK 10th Anniversary Model 10th Anniversary Model DSTYLE創業10周年に相応しい究極のフィネスロッドモデル。</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>淡水 Bass 竿系</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>以 Bass 路亞作釣為核心，覆蓋精細、泛用、游動與強力障礙等細分場景</t>
         </is>
@@ -789,20 +851,25 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/dstyle_rods/DSR1005_BLUE_TREK.jpg</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>BLUE TREK ブルートレック フィールドを駆け回れ！！ 青木大介のジャパントレイル経験をフィードバック。それが『BLUE TREK』 アメリカへ舞台を移すまでに日本のあらゆるフィールドでトーナメントや取材などで足を運んだ青木大介。その経験の元に本当に必要なパフォーマンスをアングラーに感じて欲しいという思いがロッドに込められています。 本当に求める性能とは 青木大介の代名詞【早いフィネス】それをおこなうには正確に投げれるキャスト性能、操作性、バスのバイトを感じる感度、掛けてからのパワーなどが必要不可欠です。それはフィネスに限った話ではなくあらゆるジャンルのルアー、メソッドに必要となります。 勿論フィールドの状況は刻々と変化をしていきます。その変化のスピードに柔軟に対応できるだけの懐の広さと必要とする動作を最大限アシストできる性能を求めたのが『BLUE TREK』 そんなアングラーに優しいロッドを目指しました。 不必要の削除 開発する上でコスト面は必ず直面をする壁。プロトサンプル制作する過程で不必要な箇所を徹底的に削ぎ落し、本当に必要とする性能にフォーカスをする事で性能の向上とコストの削減にも成功。</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>淡水 Bass 竿系</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>以 Bass 路亞作釣為核心，覆蓋精細、泛用、游動與強力障礙等細分場景</t>
         </is>
@@ -1045,6618 +1112,6618 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>DSRD10000</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>DSR1000</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C2" s="53" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>DHRS-GD-64L</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F2" s="19" t="inlineStr">
+      <c r="F2" s="53" t="inlineStr">
         <is>
           <t>6’4″</t>
         </is>
       </c>
-      <c r="G2" s="19" t="inlineStr">
+      <c r="G2" s="53" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H2" s="19" t="inlineStr"/>
-      <c r="I2" s="19" t="inlineStr"/>
-      <c r="J2" s="19" t="inlineStr">
+      <c r="H2" s="53" t="inlineStr"/>
+      <c r="I2" s="53" t="inlineStr"/>
+      <c r="J2" s="53" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K2" s="19" t="inlineStr"/>
-      <c r="L2" s="19" t="inlineStr"/>
-      <c r="M2" s="19" t="inlineStr">
+      <c r="K2" s="53" t="inlineStr"/>
+      <c r="L2" s="53" t="inlineStr"/>
+      <c r="M2" s="53" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N2" s="19" t="inlineStr"/>
-      <c r="O2" s="19" t="inlineStr"/>
-      <c r="P2" s="19" t="inlineStr"/>
-      <c r="Q2" s="19" t="inlineStr"/>
-      <c r="R2" s="19" t="inlineStr">
+      <c r="N2" s="53" t="inlineStr"/>
+      <c r="O2" s="53" t="inlineStr"/>
+      <c r="P2" s="53" t="inlineStr"/>
+      <c r="Q2" s="53" t="inlineStr"/>
+      <c r="R2" s="53" t="inlineStr">
         <is>
           <t>¥60,000 （税込￥66,000）</t>
         </is>
       </c>
-      <c r="S2" s="19" t="inlineStr"/>
-      <c r="T2" s="19" t="inlineStr"/>
-      <c r="U2" s="19" t="inlineStr"/>
-      <c r="V2" s="19" t="inlineStr"/>
-      <c r="W2" s="19" t="inlineStr"/>
-      <c r="X2" s="19" t="inlineStr"/>
-      <c r="Y2" s="19" t="inlineStr"/>
-      <c r="Z2" s="19" t="inlineStr">
+      <c r="S2" s="53" t="inlineStr"/>
+      <c r="T2" s="53" t="inlineStr"/>
+      <c r="U2" s="53" t="inlineStr"/>
+      <c r="V2" s="53" t="inlineStr"/>
+      <c r="W2" s="53" t="inlineStr"/>
+      <c r="X2" s="53" t="inlineStr"/>
+      <c r="Y2" s="53" t="inlineStr"/>
+      <c r="Z2" s="53" t="inlineStr">
         <is>
           <t>1/32〜3/16</t>
         </is>
       </c>
-      <c r="AA2" s="19" t="inlineStr"/>
-      <c r="AB2" s="19" t="inlineStr"/>
-      <c r="AC2" s="19" t="inlineStr">
+      <c r="AA2" s="53" t="inlineStr"/>
+      <c r="AB2" s="53" t="inlineStr"/>
+      <c r="AC2" s="53" t="inlineStr">
         <is>
           <t>RIKU Mk-01</t>
         </is>
       </c>
-      <c r="AD2" s="19" t="inlineStr"/>
-      <c r="AE2" s="19" t="inlineStr"/>
-      <c r="AF2" s="19" t="inlineStr"/>
-      <c r="AG2" s="19" t="inlineStr">
+      <c r="AD2" s="53" t="inlineStr"/>
+      <c r="AE2" s="53" t="inlineStr"/>
+      <c r="AF2" s="53" t="inlineStr"/>
+      <c r="AG2" s="53" t="inlineStr">
         <is>
           <t>不鏽鋼 SiC 導環：兼顧耐用與出線穩定，Bass 多技法拋投和控線更可靠</t>
         </is>
       </c>
-      <c r="AH2" s="19" t="inlineStr">
+      <c r="AH2" s="53" t="inlineStr">
         <is>
           <t>RIKU 是轻量泛用 spinning：先以 Neko、Down Shot、No Sinker 做精细操作，需要搜索时再切到小型 Plug；温和 Fast 调性兼顾远投、控线和中鱼后的牵制。</t>
         </is>
       </c>
-      <c r="AI2" s="19" t="inlineStr">
+      <c r="AI2" s="53" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Plug</t>
         </is>
       </c>
-      <c r="AJ2" s="19" t="inlineStr"/>
-      <c r="AK2" s="19" t="inlineStr"/>
-      <c r="AL2" s="19" t="inlineStr"/>
-      <c r="AM2" s="19" t="inlineStr">
+      <c r="AJ2" s="53" t="inlineStr"/>
+      <c r="AK2" s="53" t="inlineStr"/>
+      <c r="AL2" s="53" t="inlineStr"/>
+      <c r="AM2" s="53" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓与船钓 / 近中距离精细到小型硬饵搜索</t>
         </is>
       </c>
-      <c r="AN2" s="19" t="inlineStr">
+      <c r="AN2" s="53" t="inlineStr">
         <is>
           <t>轻量精细泛用 spinning</t>
         </is>
       </c>
-      <c r="AO2" s="19" t="inlineStr">
+      <c r="AO2" s="53" t="inlineStr">
         <is>
           <t>Neko、Down Shot 和 No Sinker 的控线手感比较自然，小型 Plug 搜索也能兼顾，适合只带一支 spinning 应对高压场。</t>
         </is>
       </c>
-      <c r="AP2" s="19" t="inlineStr">
+      <c r="AP2" s="53" t="inlineStr">
         <is>
           <t>RIKU Mk-01 「RIKU」 ■ 青木大介 × ダイワの融合から生まれた次世代スピニングロッド トップトーナメンター青木大介の理論と経験、そしてダイワの最先端テクノロジーが融合した1本。 それがスピニングロッド 「RIKU」 です。 ■ 届く・操る・獲るを高次元で実現 軽量かつ高強度のブランクス設計により、繊細な近距離アプローチからロングキャストまで対応。 さらに、掛けた魚を確実に寄せ切るバットパワーを備え、アングラーの操作を確実に成果へとつなげます。 ■ 幅広い戦略を支えるマイルドなファストテーパー 極端に用途を限定しないマイルドなファストテーパーを採用。 ライトリグを駆使した繊細な釣りから、小型プラグを用いた巻きの釣りまで柔軟にこなします。 1本で幅広い状況に対応できる懐の深さが、大きなアドバンテージとなります。 ■ 新しい可能性を拓くスピニングロッド 青木大介のこだわりとダイワのテクノロジーが融合した「RIKU」。 多様化する現代フィールドにおいて、次世代の可能性を切り拓くスピニングロッドです。</t>
         </is>
       </c>
-      <c r="AQ2" s="19" t="inlineStr">
+      <c r="AQ2" s="53" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="AR2" s="19" t="inlineStr"/>
+      <c r="AR2" s="53" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>DSRD10001</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>DSR1000</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="53" t="inlineStr">
         <is>
           <t>DHRC-GD-68M-LM</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>M-LM</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="53" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="53" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr"/>
-      <c r="I3" s="19" t="inlineStr"/>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="H3" s="53" t="inlineStr"/>
+      <c r="I3" s="53" t="inlineStr"/>
+      <c r="J3" s="53" t="inlineStr">
         <is>
           <t>101g</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr"/>
-      <c r="L3" s="19" t="inlineStr"/>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="K3" s="53" t="inlineStr"/>
+      <c r="L3" s="53" t="inlineStr"/>
+      <c r="M3" s="53" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr"/>
-      <c r="O3" s="19" t="inlineStr"/>
-      <c r="P3" s="19" t="inlineStr"/>
-      <c r="Q3" s="19" t="inlineStr"/>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="N3" s="53" t="inlineStr"/>
+      <c r="O3" s="53" t="inlineStr"/>
+      <c r="P3" s="53" t="inlineStr"/>
+      <c r="Q3" s="53" t="inlineStr"/>
+      <c r="R3" s="53" t="inlineStr">
         <is>
           <t>¥62,000 （税込￥68,200）</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr"/>
-      <c r="T3" s="19" t="inlineStr"/>
-      <c r="U3" s="19" t="inlineStr"/>
-      <c r="V3" s="19" t="inlineStr"/>
-      <c r="W3" s="19" t="inlineStr"/>
-      <c r="X3" s="19" t="inlineStr"/>
-      <c r="Y3" s="19" t="inlineStr"/>
-      <c r="Z3" s="19" t="inlineStr">
+      <c r="S3" s="53" t="inlineStr"/>
+      <c r="T3" s="53" t="inlineStr"/>
+      <c r="U3" s="53" t="inlineStr"/>
+      <c r="V3" s="53" t="inlineStr"/>
+      <c r="W3" s="53" t="inlineStr"/>
+      <c r="X3" s="53" t="inlineStr"/>
+      <c r="Y3" s="53" t="inlineStr"/>
+      <c r="Z3" s="53" t="inlineStr">
         <is>
           <t>3/16〜5/8</t>
         </is>
       </c>
-      <c r="AA3" s="19" t="inlineStr"/>
-      <c r="AB3" s="19" t="inlineStr"/>
-      <c r="AC3" s="19" t="inlineStr">
+      <c r="AA3" s="53" t="inlineStr"/>
+      <c r="AB3" s="53" t="inlineStr"/>
+      <c r="AC3" s="53" t="inlineStr">
         <is>
           <t>THE SUTO Mk-01</t>
         </is>
       </c>
-      <c r="AD3" s="19" t="inlineStr"/>
-      <c r="AE3" s="19" t="inlineStr"/>
-      <c r="AF3" s="19" t="inlineStr"/>
-      <c r="AG3" s="19" t="inlineStr">
+      <c r="AD3" s="53" t="inlineStr"/>
+      <c r="AE3" s="53" t="inlineStr"/>
+      <c r="AF3" s="53" t="inlineStr"/>
+      <c r="AG3" s="53" t="inlineStr">
         <is>
           <t>不鏽鋼 SiC 導環：兼顧耐用與出線穩定，Bass 多技法拋投和控線更可靠</t>
         </is>
       </c>
-      <c r="AH3" s="19" t="inlineStr">
+      <c r="AH3" s="53" t="inlineStr">
         <is>
           <t>THE SUTO 以 bait mid-strolling 为主轴：Jighead 或 Football Jig 自然游动放首位，低弹性碳布让短咬更容易黏住；硬饵和 wire bait 只是副线用途。</t>
         </is>
       </c>
-      <c r="AI3" s="19" t="inlineStr">
+      <c r="AI3" s="53" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Swimming Football Jig / Hover Strolling / Spinnerbait / Crankbait</t>
         </is>
       </c>
-      <c r="AJ3" s="19" t="inlineStr"/>
-      <c r="AK3" s="19" t="inlineStr"/>
-      <c r="AL3" s="19" t="inlineStr"/>
-      <c r="AM3" s="19" t="inlineStr">
+      <c r="AJ3" s="53" t="inlineStr"/>
+      <c r="AK3" s="53" t="inlineStr"/>
+      <c r="AL3" s="53" t="inlineStr"/>
+      <c r="AM3" s="53" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水域・船钓 / 中层游动与轻移动饵</t>
         </is>
       </c>
-      <c r="AN3" s="19" t="inlineStr">
+      <c r="AN3" s="53" t="inlineStr">
         <is>
           <t>Bait mid-strolling 兼轻移动饵</t>
         </is>
       </c>
-      <c r="AO3" s="19" t="inlineStr">
+      <c r="AO3" s="53" t="inlineStr">
         <is>
           <t>用枪柄系统做 Mid Strolling 时更好控线，Swimming Football Jig 也能维持泳姿；需要时可切 Spinnerbait、Crankbait 做弱搜索。</t>
         </is>
       </c>
-      <c r="AP3" s="19" t="inlineStr">
+      <c r="AP3" s="53" t="inlineStr">
         <is>
           <t>THE SUTO Mk-01 『THE SUTO』 ベイトで操る、新時代のミドストロッド。 青木大介が培ってきたミドスト理論と、ダイワの最先端テクノロジーが融合した1本。 その名も 『THE SUTO』。 従来はスピニングでしか実現できなかった繊細な揺らぎを、ベイトタックルで正確かつ快適に再現できるよう設計されています。 ■ オリジナルテーパーが生む操作性と感度 独自のテーパー設計によるしなやかなティップが、ジグヘッドやフットボールジグを自然にスイミング。 ルアーの微細な振動やショートバイトも逃さず、確実に手元へと伝えます。 一方でベリーからバットにかけてはしっかりとした張りを備え、フッキングからランディングまで安定したやり取りを可能にします。 ■ Low Modulusカーボン採用による懐の深さ しなやかさと粘りを兼ね備えた低弾性カーボン“Low Modulus”を採用。 ミドスト専用機としての性能はもちろん、副次的にハードベイトやワイヤーベイトにも幅広く対応。 1本で様々なアプローチを可能にする汎用性を手にしました。 ■ 青木大介 × ダイワの答え 青木大介のこだわりとダイワテクノロジーの融合から生まれた、ベイトミドストという新たな可能性を切り拓くロッド。 それが DHRC-GD-68M-LM “THE SUTO” です。</t>
         </is>
       </c>
-      <c r="AQ3" s="19" t="inlineStr">
+      <c r="AQ3" s="53" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR3" s="19" t="inlineStr"/>
+      <c r="AR3" s="53" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="52" t="inlineStr">
         <is>
           <t>DSRD10002</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="52" t="inlineStr">
         <is>
           <t>DHRS-511UL</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="52" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="52" t="inlineStr">
         <is>
           <t>5’11”</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="G4" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr"/>
-      <c r="I4" s="22" t="inlineStr"/>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="H4" s="52" t="inlineStr"/>
+      <c r="I4" s="52" t="inlineStr"/>
+      <c r="J4" s="52" t="inlineStr">
         <is>
           <t>70g</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr"/>
-      <c r="L4" s="22" t="inlineStr"/>
-      <c r="M4" s="22" t="inlineStr">
+      <c r="K4" s="52" t="inlineStr"/>
+      <c r="L4" s="52" t="inlineStr"/>
+      <c r="M4" s="52" t="inlineStr">
         <is>
           <t>2~6</t>
         </is>
       </c>
-      <c r="N4" s="22" t="inlineStr"/>
-      <c r="O4" s="22" t="inlineStr"/>
-      <c r="P4" s="22" t="inlineStr"/>
-      <c r="Q4" s="22" t="inlineStr"/>
-      <c r="R4" s="22" t="inlineStr">
+      <c r="N4" s="52" t="inlineStr"/>
+      <c r="O4" s="52" t="inlineStr"/>
+      <c r="P4" s="52" t="inlineStr"/>
+      <c r="Q4" s="52" t="inlineStr"/>
+      <c r="R4" s="52" t="inlineStr">
         <is>
           <t>￥50,000 （￥55,000）</t>
         </is>
       </c>
-      <c r="S4" s="22" t="inlineStr">
+      <c r="S4" s="52" t="inlineStr">
         <is>
           <t>4571527865183</t>
         </is>
       </c>
-      <c r="T4" s="22" t="inlineStr"/>
-      <c r="U4" s="22" t="inlineStr"/>
-      <c r="V4" s="22" t="inlineStr"/>
-      <c r="W4" s="22" t="inlineStr"/>
-      <c r="X4" s="22" t="inlineStr"/>
-      <c r="Y4" s="22" t="inlineStr"/>
-      <c r="Z4" s="22" t="inlineStr">
+      <c r="T4" s="52" t="inlineStr"/>
+      <c r="U4" s="52" t="inlineStr"/>
+      <c r="V4" s="52" t="inlineStr"/>
+      <c r="W4" s="52" t="inlineStr"/>
+      <c r="X4" s="52" t="inlineStr"/>
+      <c r="Y4" s="52" t="inlineStr"/>
+      <c r="Z4" s="52" t="inlineStr">
         <is>
           <t>1/48～3/16</t>
         </is>
       </c>
-      <c r="AA4" s="22" t="inlineStr"/>
-      <c r="AB4" s="22" t="inlineStr"/>
-      <c r="AC4" s="22" t="inlineStr">
+      <c r="AA4" s="52" t="inlineStr"/>
+      <c r="AB4" s="52" t="inlineStr"/>
+      <c r="AC4" s="52" t="inlineStr">
         <is>
           <t>Finesse Shake 1</t>
         </is>
       </c>
-      <c r="AD4" s="22" t="inlineStr"/>
-      <c r="AE4" s="22" t="inlineStr"/>
-      <c r="AF4" s="22" t="inlineStr"/>
-      <c r="AG4" s="22" t="inlineStr">
+      <c r="AD4" s="52" t="inlineStr"/>
+      <c r="AE4" s="52" t="inlineStr"/>
+      <c r="AF4" s="52" t="inlineStr"/>
+      <c r="AG4" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH4" s="22" t="inlineStr">
+      <c r="AH4" s="52" t="inlineStr">
         <is>
           <t>短竿超精细定位，适合高压近距离用 Neko、Down Shot、No Sinker 和 Small Rubber Jig 做精准落点与细抖；小型 Plug 属补充搜索。</t>
         </is>
       </c>
-      <c r="AI4" s="22" t="inlineStr">
+      <c r="AI4" s="52" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Plug</t>
         </is>
       </c>
-      <c r="AJ4" s="22" t="inlineStr"/>
-      <c r="AK4" s="22" t="inlineStr"/>
-      <c r="AL4" s="22" t="inlineStr"/>
-      <c r="AM4" s="22" t="inlineStr">
+      <c r="AJ4" s="52" t="inlineStr"/>
+      <c r="AK4" s="52" t="inlineStr"/>
+      <c r="AL4" s="52" t="inlineStr"/>
+      <c r="AM4" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压野池・近岸标点 / 短距超精细</t>
         </is>
       </c>
-      <c r="AN4" s="22" t="inlineStr">
+      <c r="AN4" s="52" t="inlineStr">
         <is>
           <t>近距离超精细食わせ</t>
         </is>
       </c>
-      <c r="AO4" s="22" t="inlineStr">
+      <c r="AO4" s="52" t="inlineStr">
         <is>
           <t>短竿在狭小标点更容易压低弹道，Neko、Down Shot、Small Rubber Jig 的轻抖和短咬反馈更直接。</t>
         </is>
       </c>
-      <c r="AP4" s="22" t="inlineStr">
+      <c r="AP4" s="52" t="inlineStr">
         <is>
           <t>Finesse SHAKE 1 Finesse Shake 1 過去の自分を超える為のスーパーフィネスロッド。青木大介が新たに考えた『ショートグリップコンセプト』を色濃く反映させ、正確なキャスト性能とルアーをより繊細に扱える操作性と感度が向上。 ６ft以下まで下げる事で極限のプレッシャーでも攻撃的フィネス展開。よりタイト、よりシビアに進化したウルトラフィネスロッド。 伝統の食わせのファストテーパーからバスの引きに負けないバットパワーを持ち合わせ、ネコリグ、ダウンショットリグ、ノーシンカーリグ、スモラバなどのフィネス全般からスモールプラグまで幅広く対応。</t>
         </is>
       </c>
-      <c r="AQ4" s="22" t="inlineStr">
+      <c r="AQ4" s="52" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="AR4" s="22" t="inlineStr">
+      <c r="AR4" s="52" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>DSRD10003</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="52" t="inlineStr">
         <is>
           <t>DHRS-60L</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="52" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="52" t="inlineStr">
         <is>
           <t>6’0″</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr"/>
-      <c r="I5" s="22" t="inlineStr"/>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="H5" s="52" t="inlineStr"/>
+      <c r="I5" s="52" t="inlineStr"/>
+      <c r="J5" s="52" t="inlineStr">
         <is>
           <t>74g</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr"/>
-      <c r="L5" s="22" t="inlineStr"/>
-      <c r="M5" s="22" t="inlineStr">
+      <c r="K5" s="52" t="inlineStr"/>
+      <c r="L5" s="52" t="inlineStr"/>
+      <c r="M5" s="52" t="inlineStr">
         <is>
           <t>2.5~8</t>
         </is>
       </c>
-      <c r="N5" s="22" t="inlineStr"/>
-      <c r="O5" s="22" t="inlineStr"/>
-      <c r="P5" s="22" t="inlineStr"/>
-      <c r="Q5" s="22" t="inlineStr"/>
-      <c r="R5" s="22" t="inlineStr">
+      <c r="N5" s="52" t="inlineStr"/>
+      <c r="O5" s="52" t="inlineStr"/>
+      <c r="P5" s="52" t="inlineStr"/>
+      <c r="Q5" s="52" t="inlineStr"/>
+      <c r="R5" s="52" t="inlineStr">
         <is>
           <t>￥50,000 （￥55,000）</t>
         </is>
       </c>
-      <c r="S5" s="22" t="inlineStr">
+      <c r="S5" s="52" t="inlineStr">
         <is>
           <t>4571527865190</t>
         </is>
       </c>
-      <c r="T5" s="22" t="inlineStr"/>
-      <c r="U5" s="22" t="inlineStr"/>
-      <c r="V5" s="22" t="inlineStr"/>
-      <c r="W5" s="22" t="inlineStr"/>
-      <c r="X5" s="22" t="inlineStr"/>
-      <c r="Y5" s="22" t="inlineStr"/>
-      <c r="Z5" s="22" t="inlineStr">
+      <c r="T5" s="52" t="inlineStr"/>
+      <c r="U5" s="52" t="inlineStr"/>
+      <c r="V5" s="52" t="inlineStr"/>
+      <c r="W5" s="52" t="inlineStr"/>
+      <c r="X5" s="52" t="inlineStr"/>
+      <c r="Y5" s="52" t="inlineStr"/>
+      <c r="Z5" s="52" t="inlineStr">
         <is>
           <t>1/32〜1/4</t>
         </is>
       </c>
-      <c r="AA5" s="22" t="inlineStr"/>
-      <c r="AB5" s="22" t="inlineStr"/>
-      <c r="AC5" s="22" t="inlineStr">
+      <c r="AA5" s="52" t="inlineStr"/>
+      <c r="AB5" s="52" t="inlineStr"/>
+      <c r="AC5" s="52" t="inlineStr">
         <is>
           <t>Finesse Shake 2</t>
         </is>
       </c>
-      <c r="AD5" s="22" t="inlineStr"/>
-      <c r="AE5" s="22" t="inlineStr"/>
-      <c r="AF5" s="22" t="inlineStr"/>
-      <c r="AG5" s="22" t="inlineStr">
+      <c r="AD5" s="52" t="inlineStr"/>
+      <c r="AE5" s="52" t="inlineStr"/>
+      <c r="AF5" s="52" t="inlineStr"/>
+      <c r="AG5" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH5" s="22" t="inlineStr">
+      <c r="AH5" s="52" t="inlineStr">
         <is>
           <t>Finesse Shake 2 仍以食わせ系 Fast taper 为核心，Neko、Down Shot、No Sinker 和 Small Rubber Jig 是主场；需要拉开距离时可兼顾小型 Plug。</t>
         </is>
       </c>
-      <c r="AI5" s="22" t="inlineStr">
+      <c r="AI5" s="52" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Plug</t>
         </is>
       </c>
-      <c r="AJ5" s="22" t="inlineStr"/>
-      <c r="AK5" s="22" t="inlineStr"/>
-      <c r="AL5" s="22" t="inlineStr"/>
-      <c r="AM5" s="22" t="inlineStr">
+      <c r="AJ5" s="52" t="inlineStr"/>
+      <c r="AK5" s="52" t="inlineStr"/>
+      <c r="AL5" s="52" t="inlineStr"/>
+      <c r="AM5" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压湖库・野池 / 精细软饵到小型 Plug</t>
         </is>
       </c>
-      <c r="AN5" s="22" t="inlineStr">
+      <c r="AN5" s="52" t="inlineStr">
         <is>
           <t>精细食わせ泛用 spinning</t>
         </is>
       </c>
-      <c r="AO5" s="22" t="inlineStr">
+      <c r="AO5" s="52" t="inlineStr">
         <is>
           <t>比 XUL/UL 更有余量，细线软饵仍然好操作，遇到鱼追但不咬时可换小型 Plug 做慢速搜索。</t>
         </is>
       </c>
-      <c r="AP5" s="22" t="inlineStr">
+      <c r="AP5" s="52" t="inlineStr">
         <is>
           <t>Finesse SHAKE 2 Finesse Shake 2 過去の自分を超える為のスーパーフィネスロッド。青木大介が新たに考えた『ショートグリップコンセプト』を色濃く反映させ、正確なキャスト性能とルアーをより繊細に扱える操作性と感度が向上。 伝統の食わせのファストテーパーからバスの引きに負けないバットパワーを持ち合わせ、ネコリグ、ダウンショットリグ、ノーシンカーリグ、スモラバなどのフィネス全般からスモールプラグまで幅広く対応。</t>
         </is>
       </c>
-      <c r="AQ5" s="22" t="inlineStr">
+      <c r="AQ5" s="52" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="AR5" s="22" t="inlineStr">
+      <c r="AR5" s="52" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>DSRD10004</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="52" t="inlineStr">
         <is>
           <t>DHRS-63L</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="52" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="52" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr"/>
-      <c r="I6" s="22" t="inlineStr"/>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="H6" s="52" t="inlineStr"/>
+      <c r="I6" s="52" t="inlineStr"/>
+      <c r="J6" s="52" t="inlineStr">
         <is>
           <t>74g</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="22" t="inlineStr"/>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="K6" s="52" t="inlineStr"/>
+      <c r="L6" s="52" t="inlineStr"/>
+      <c r="M6" s="52" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N6" s="22" t="inlineStr"/>
-      <c r="O6" s="22" t="inlineStr"/>
-      <c r="P6" s="22" t="inlineStr"/>
-      <c r="Q6" s="22" t="inlineStr"/>
-      <c r="R6" s="22" t="inlineStr">
+      <c r="N6" s="52" t="inlineStr"/>
+      <c r="O6" s="52" t="inlineStr"/>
+      <c r="P6" s="52" t="inlineStr"/>
+      <c r="Q6" s="52" t="inlineStr"/>
+      <c r="R6" s="52" t="inlineStr">
         <is>
           <t>￥50,000 （￥55,000）</t>
         </is>
       </c>
-      <c r="S6" s="22" t="inlineStr">
+      <c r="S6" s="52" t="inlineStr">
         <is>
           <t>4571527863790</t>
         </is>
       </c>
-      <c r="T6" s="22" t="inlineStr"/>
-      <c r="U6" s="22" t="inlineStr"/>
-      <c r="V6" s="22" t="inlineStr"/>
-      <c r="W6" s="22" t="inlineStr"/>
-      <c r="X6" s="22" t="inlineStr"/>
-      <c r="Y6" s="22" t="inlineStr"/>
-      <c r="Z6" s="22" t="inlineStr">
+      <c r="T6" s="52" t="inlineStr"/>
+      <c r="U6" s="52" t="inlineStr"/>
+      <c r="V6" s="52" t="inlineStr"/>
+      <c r="W6" s="52" t="inlineStr"/>
+      <c r="X6" s="52" t="inlineStr"/>
+      <c r="Y6" s="52" t="inlineStr"/>
+      <c r="Z6" s="52" t="inlineStr">
         <is>
           <t>1/32〜3/16</t>
         </is>
       </c>
-      <c r="AA6" s="22" t="inlineStr"/>
-      <c r="AB6" s="22" t="inlineStr"/>
-      <c r="AC6" s="22" t="inlineStr">
+      <c r="AA6" s="52" t="inlineStr"/>
+      <c r="AB6" s="52" t="inlineStr"/>
+      <c r="AC6" s="52" t="inlineStr">
         <is>
           <t>Finesse Versatile</t>
         </is>
       </c>
-      <c r="AD6" s="22" t="inlineStr"/>
-      <c r="AE6" s="22" t="inlineStr"/>
-      <c r="AF6" s="22" t="inlineStr"/>
-      <c r="AG6" s="22" t="inlineStr">
+      <c r="AD6" s="52" t="inlineStr"/>
+      <c r="AE6" s="52" t="inlineStr"/>
+      <c r="AF6" s="52" t="inlineStr"/>
+      <c r="AG6" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH6" s="22" t="inlineStr">
+      <c r="AH6" s="52" t="inlineStr">
         <is>
           <t>Finesse Versatile 覆盖 spinning light-rig 全段：底层 Neko/Down Shot、无铅软饵、表层 Plug、Shad 和虫系都能切换，重点是轻量多用途而不是强障碍。</t>
         </is>
       </c>
-      <c r="AI6" s="22" t="inlineStr">
+      <c r="AI6" s="52" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Surface Plug / Shad / Bug Lure</t>
         </is>
       </c>
-      <c r="AJ6" s="22" t="inlineStr"/>
-      <c r="AK6" s="22" t="inlineStr"/>
-      <c r="AL6" s="22" t="inlineStr"/>
-      <c r="AM6" s="22" t="inlineStr">
+      <c r="AJ6" s="52" t="inlineStr"/>
+      <c r="AK6" s="52" t="inlineStr"/>
+      <c r="AL6" s="52" t="inlineStr"/>
+      <c r="AM6" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓中距离 / 轻量软饵・表层・Shad 切换</t>
         </is>
       </c>
-      <c r="AN6" s="22" t="inlineStr">
+      <c r="AN6" s="52" t="inlineStr">
         <is>
           <t>轻量多用途 spinning</t>
         </is>
       </c>
-      <c r="AO6" s="22" t="inlineStr">
+      <c r="AO6" s="52" t="inlineStr">
         <is>
           <t>Neko、Down Shot、No Sinker 是主轴，表层 Plug、Shad 和虫系可补搜索；适合一支竿覆盖高压轻量路线。</t>
         </is>
       </c>
-      <c r="AP6" s="22" t="inlineStr">
+      <c r="AP6" s="52" t="inlineStr">
         <is>
           <t>Finesse Versatile Finesse Versatile 癖のないファーストテーパーデザインにより、スピニングにおけるあらゆるライトリグをカバーするフィネスバーサタイルスピン。6’3″で近距離の繊細攻めから中距離の少しディスタンスが必要な釣りまでをこなす。ライトリグ全般から表層系プラグ、シャッド、虫系など幅広く対応。１本であらゆる状況にアジャストできる至高の１本。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ6" s="22" t="inlineStr">
+      <c r="AQ6" s="52" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="AR6" s="22" t="inlineStr"/>
+      <c r="AR6" s="52" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>DSRD10005</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="52" t="inlineStr">
         <is>
           <t>DHRS-63UL-FS</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="52" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="52" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr"/>
-      <c r="I7" s="22" t="inlineStr"/>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="H7" s="52" t="inlineStr"/>
+      <c r="I7" s="52" t="inlineStr"/>
+      <c r="J7" s="52" t="inlineStr">
         <is>
           <t>71g</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr"/>
-      <c r="L7" s="22" t="inlineStr"/>
-      <c r="M7" s="22" t="inlineStr">
+      <c r="K7" s="52" t="inlineStr"/>
+      <c r="L7" s="52" t="inlineStr"/>
+      <c r="M7" s="52" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N7" s="22" t="inlineStr"/>
-      <c r="O7" s="22" t="inlineStr"/>
-      <c r="P7" s="22" t="inlineStr"/>
-      <c r="Q7" s="22" t="inlineStr"/>
-      <c r="R7" s="22" t="inlineStr">
+      <c r="N7" s="52" t="inlineStr"/>
+      <c r="O7" s="52" t="inlineStr"/>
+      <c r="P7" s="52" t="inlineStr"/>
+      <c r="Q7" s="52" t="inlineStr"/>
+      <c r="R7" s="52" t="inlineStr">
         <is>
           <t>￥51,000 (￥56,100)</t>
         </is>
       </c>
-      <c r="S7" s="22" t="inlineStr">
+      <c r="S7" s="52" t="inlineStr">
         <is>
           <t>4571527863806</t>
         </is>
       </c>
-      <c r="T7" s="22" t="inlineStr"/>
-      <c r="U7" s="22" t="inlineStr"/>
-      <c r="V7" s="22" t="inlineStr"/>
-      <c r="W7" s="22" t="inlineStr"/>
-      <c r="X7" s="22" t="inlineStr"/>
-      <c r="Y7" s="22" t="inlineStr"/>
-      <c r="Z7" s="22" t="inlineStr">
+      <c r="T7" s="52" t="inlineStr"/>
+      <c r="U7" s="52" t="inlineStr"/>
+      <c r="V7" s="52" t="inlineStr"/>
+      <c r="W7" s="52" t="inlineStr"/>
+      <c r="X7" s="52" t="inlineStr"/>
+      <c r="Y7" s="52" t="inlineStr"/>
+      <c r="Z7" s="52" t="inlineStr">
         <is>
           <t>1/32〜3/16</t>
         </is>
       </c>
-      <c r="AA7" s="22" t="inlineStr"/>
-      <c r="AB7" s="22" t="inlineStr"/>
-      <c r="AC7" s="22" t="inlineStr">
+      <c r="AA7" s="52" t="inlineStr"/>
+      <c r="AB7" s="52" t="inlineStr"/>
+      <c r="AC7" s="52" t="inlineStr">
         <is>
           <t>Light Midstroll</t>
         </is>
       </c>
-      <c r="AD7" s="22" t="inlineStr"/>
-      <c r="AE7" s="22" t="inlineStr"/>
-      <c r="AF7" s="22" t="inlineStr"/>
-      <c r="AG7" s="22" t="inlineStr">
+      <c r="AD7" s="52" t="inlineStr"/>
+      <c r="AE7" s="52" t="inlineStr"/>
+      <c r="AF7" s="52" t="inlineStr"/>
+      <c r="AG7" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH7" s="22" t="inlineStr">
+      <c r="AH7" s="52" t="inlineStr">
         <is>
           <t>Finesse Swim 不是普通底操竿，重点是用 Jighead、Neko 或 Down Shot 做中层游动；竿尖和导环设定服务于线弧、抖动节奏和泳姿稳定。</t>
         </is>
       </c>
-      <c r="AI7" s="22" t="inlineStr">
+      <c r="AI7" s="52" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Swimming Neko Rig / Swimming Down Shot / Hover Strolling</t>
         </is>
       </c>
-      <c r="AJ7" s="22" t="inlineStr"/>
-      <c r="AK7" s="22" t="inlineStr"/>
-      <c r="AL7" s="22" t="inlineStr"/>
-      <c r="AM7" s="22" t="inlineStr">
+      <c r="AJ7" s="52" t="inlineStr"/>
+      <c r="AK7" s="52" t="inlineStr"/>
+      <c r="AL7" s="52" t="inlineStr"/>
+      <c r="AM7" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水域・缓坡 / 中层 finesse swim</t>
         </is>
       </c>
-      <c r="AN7" s="22" t="inlineStr">
+      <c r="AN7" s="52" t="inlineStr">
         <is>
           <t>轻量中层游动专向</t>
         </is>
       </c>
-      <c r="AO7" s="22" t="inlineStr">
+      <c r="AO7" s="52" t="inlineStr">
         <is>
           <t>Jighead、Swimming Neko 和 Swimming Down Shot 的线弧更容易维持，适合持续抖动和轻量软饵水平泳姿控制。</t>
         </is>
       </c>
-      <c r="AP7" s="22" t="inlineStr">
+      <c r="AP7" s="52" t="inlineStr">
         <is>
           <t>Finesse Swim Finesse Swim 近年欠かすことの出来ないテクニックの一つミッドストローリングは、より進化をした時代を迎え、ジグヘッドの釣りに限らずネコリグやダウンショットなどあらゆるライトリグでスイミングで使いやすさを求められます。よりタイトに攻める事が出来る操作性とラインスラッグを出しながらシェイクをしやすいテーパーとガイドセッティングを追求することで、最高のフィネススイミングロッドに仕上げた。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ7" s="22" t="inlineStr">
+      <c r="AQ7" s="52" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="AR7" s="22" t="inlineStr"/>
+      <c r="AR7" s="52" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>DSRD10006</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="52" t="inlineStr">
         <is>
           <t>DHRS-66ML</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="52" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="52" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr"/>
-      <c r="I8" s="22" t="inlineStr"/>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="H8" s="52" t="inlineStr"/>
+      <c r="I8" s="52" t="inlineStr"/>
+      <c r="J8" s="52" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="22" t="inlineStr"/>
-      <c r="M8" s="22" t="inlineStr">
+      <c r="K8" s="52" t="inlineStr"/>
+      <c r="L8" s="52" t="inlineStr"/>
+      <c r="M8" s="52" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N8" s="22" t="inlineStr">
+      <c r="N8" s="52" t="inlineStr">
         <is>
           <t>0.6~1.5</t>
         </is>
       </c>
-      <c r="O8" s="22" t="inlineStr"/>
-      <c r="P8" s="22" t="inlineStr"/>
-      <c r="Q8" s="22" t="inlineStr"/>
-      <c r="R8" s="22" t="inlineStr">
+      <c r="O8" s="52" t="inlineStr"/>
+      <c r="P8" s="52" t="inlineStr"/>
+      <c r="Q8" s="52" t="inlineStr"/>
+      <c r="R8" s="52" t="inlineStr">
         <is>
           <t>￥51,500 (￥56,650)</t>
         </is>
       </c>
-      <c r="S8" s="22" t="inlineStr">
+      <c r="S8" s="52" t="inlineStr">
         <is>
           <t>4571527865206</t>
         </is>
       </c>
-      <c r="T8" s="22" t="inlineStr"/>
-      <c r="U8" s="22" t="inlineStr"/>
-      <c r="V8" s="22" t="inlineStr"/>
-      <c r="W8" s="22" t="inlineStr"/>
-      <c r="X8" s="22" t="inlineStr"/>
-      <c r="Y8" s="22" t="inlineStr"/>
-      <c r="Z8" s="22" t="inlineStr">
+      <c r="T8" s="52" t="inlineStr"/>
+      <c r="U8" s="52" t="inlineStr"/>
+      <c r="V8" s="52" t="inlineStr"/>
+      <c r="W8" s="52" t="inlineStr"/>
+      <c r="X8" s="52" t="inlineStr"/>
+      <c r="Y8" s="52" t="inlineStr"/>
+      <c r="Z8" s="52" t="inlineStr">
         <is>
           <t>1/32〜3/8</t>
         </is>
       </c>
-      <c r="AA8" s="22" t="inlineStr"/>
-      <c r="AB8" s="22" t="inlineStr"/>
-      <c r="AC8" s="22" t="inlineStr">
+      <c r="AA8" s="52" t="inlineStr"/>
+      <c r="AB8" s="52" t="inlineStr"/>
+      <c r="AC8" s="52" t="inlineStr">
         <is>
           <t>MAX Finesse</t>
         </is>
       </c>
-      <c r="AD8" s="22" t="inlineStr"/>
-      <c r="AE8" s="22" t="inlineStr"/>
-      <c r="AF8" s="22" t="inlineStr"/>
-      <c r="AG8" s="22" t="inlineStr">
+      <c r="AD8" s="52" t="inlineStr"/>
+      <c r="AE8" s="52" t="inlineStr"/>
+      <c r="AF8" s="52" t="inlineStr"/>
+      <c r="AG8" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH8" s="22" t="inlineStr">
+      <c r="AH8" s="52" t="inlineStr">
         <is>
           <t>MAX Finesse 面向 PE cover power finesse：吊挂 Small Rubber Jig、Elastomer dog-walk、Power Mid Strolling 和稍重 Neko/Down Shot 都可用，重点是细致操作后把鱼带出 cover。</t>
         </is>
       </c>
-      <c r="AI8" s="22" t="inlineStr">
+      <c r="AI8" s="52" t="inlineStr">
         <is>
           <t>Power Finesse / Hanging Small Rubber Jig / Elastomer Dog Walk / Power Mid Strolling / Heavy Down Shot</t>
         </is>
       </c>
-      <c r="AJ8" s="22" t="inlineStr"/>
-      <c r="AK8" s="22" t="inlineStr"/>
-      <c r="AL8" s="22" t="inlineStr"/>
-      <c r="AM8" s="22" t="inlineStr">
+      <c r="AJ8" s="52" t="inlineStr"/>
+      <c r="AK8" s="52" t="inlineStr"/>
+      <c r="AL8" s="52" t="inlineStr"/>
+      <c r="AM8" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 边缘・码头・草洞 / PE power finesse</t>
         </is>
       </c>
-      <c r="AN8" s="22" t="inlineStr">
+      <c r="AN8" s="52" t="inlineStr">
         <is>
           <t>PE power finesse 多用途</t>
         </is>
       </c>
-      <c r="AO8" s="22" t="inlineStr">
+      <c r="AO8" s="52" t="inlineStr">
         <is>
           <t>Small Rubber Jig 吊挂、Elastomer dog-walk 和 Power Mid Strolling 都能处理，价值在细操作后仍有把鱼带出 cover 的支撑。</t>
         </is>
       </c>
-      <c r="AP8" s="22" t="inlineStr">
+      <c r="AP8" s="52" t="inlineStr">
         <is>
           <t>MAX Finesse MAX Finesse ミドルバーサタイルフィネスロッド。PEを使用したカバー周りのパワーフィネスから吊るし系、エラストマールアーのドックウォーク、パワーミドスト、やや重量のあるライトリグ全般まで幅広くカバー。 。伝統の食わせのファストテーパーからバスの引きに負けないバットパワーを持ち合わせバスを捉える。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい</t>
         </is>
       </c>
-      <c r="AQ8" s="22" t="inlineStr">
+      <c r="AQ8" s="52" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR8" s="22" t="inlineStr">
+      <c r="AR8" s="52" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>DSRD10007</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="52" t="inlineStr">
         <is>
           <t>DHRS-66L/ML-FS</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="52" t="inlineStr">
         <is>
           <t>L/ML</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="52" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr"/>
-      <c r="I9" s="22" t="inlineStr"/>
-      <c r="J9" s="22" t="inlineStr"/>
-      <c r="K9" s="22" t="inlineStr"/>
-      <c r="L9" s="22" t="inlineStr"/>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="H9" s="52" t="inlineStr"/>
+      <c r="I9" s="52" t="inlineStr"/>
+      <c r="J9" s="52" t="inlineStr"/>
+      <c r="K9" s="52" t="inlineStr"/>
+      <c r="L9" s="52" t="inlineStr"/>
+      <c r="M9" s="52" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N9" s="22" t="inlineStr">
+      <c r="N9" s="52" t="inlineStr">
         <is>
           <t>0.4~1号</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr"/>
-      <c r="P9" s="22" t="inlineStr"/>
-      <c r="Q9" s="22" t="inlineStr"/>
-      <c r="R9" s="22" t="inlineStr">
+      <c r="O9" s="52" t="inlineStr"/>
+      <c r="P9" s="52" t="inlineStr"/>
+      <c r="Q9" s="52" t="inlineStr"/>
+      <c r="R9" s="52" t="inlineStr">
         <is>
           <t>￥57,500 (￥63,250)</t>
         </is>
       </c>
-      <c r="S9" s="22" t="inlineStr">
+      <c r="S9" s="52" t="inlineStr">
         <is>
           <t>4571527869037</t>
         </is>
       </c>
-      <c r="T9" s="22" t="inlineStr"/>
-      <c r="U9" s="22" t="inlineStr"/>
-      <c r="V9" s="22" t="inlineStr"/>
-      <c r="W9" s="22" t="inlineStr"/>
-      <c r="X9" s="22" t="inlineStr"/>
-      <c r="Y9" s="22" t="inlineStr"/>
-      <c r="Z9" s="22" t="inlineStr">
+      <c r="T9" s="52" t="inlineStr"/>
+      <c r="U9" s="52" t="inlineStr"/>
+      <c r="V9" s="52" t="inlineStr"/>
+      <c r="W9" s="52" t="inlineStr"/>
+      <c r="X9" s="52" t="inlineStr"/>
+      <c r="Y9" s="52" t="inlineStr"/>
+      <c r="Z9" s="52" t="inlineStr">
         <is>
           <t>1/32〜1/4</t>
         </is>
       </c>
-      <c r="AA9" s="22" t="inlineStr"/>
-      <c r="AB9" s="22" t="inlineStr"/>
-      <c r="AC9" s="22" t="inlineStr">
+      <c r="AA9" s="52" t="inlineStr"/>
+      <c r="AB9" s="52" t="inlineStr"/>
+      <c r="AC9" s="52" t="inlineStr">
         <is>
           <t>Power Finesse Swim</t>
         </is>
       </c>
-      <c r="AD9" s="22" t="inlineStr"/>
-      <c r="AE9" s="22" t="inlineStr"/>
-      <c r="AF9" s="22" t="inlineStr"/>
-      <c r="AG9" s="22" t="inlineStr">
+      <c r="AD9" s="52" t="inlineStr"/>
+      <c r="AE9" s="52" t="inlineStr"/>
+      <c r="AF9" s="52" t="inlineStr"/>
+      <c r="AG9" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH9" s="22" t="inlineStr">
+      <c r="AH9" s="52" t="inlineStr">
         <is>
           <t>Power Finesse Swim 是 4-5 寸中型 worm 的 mid-strolling 专用向，导环给线松弛和 blank 震动传递留空间；Power Finesse 只是同一套 PE 系统下的延伸。</t>
         </is>
       </c>
-      <c r="AI9" s="22" t="inlineStr">
+      <c r="AI9" s="52" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Hover Strolling / 4-5in Worm Swim / Power Finesse</t>
         </is>
       </c>
-      <c r="AJ9" s="22" t="inlineStr"/>
-      <c r="AK9" s="22" t="inlineStr"/>
-      <c r="AL9" s="22" t="inlineStr"/>
-      <c r="AM9" s="22" t="inlineStr">
+      <c r="AJ9" s="52" t="inlineStr"/>
+      <c r="AK9" s="52" t="inlineStr"/>
+      <c r="AL9" s="52" t="inlineStr"/>
+      <c r="AM9" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水域・大型湖库 / 4-5 寸 worm 中层游动</t>
         </is>
       </c>
-      <c r="AN9" s="22" t="inlineStr">
+      <c r="AN9" s="52" t="inlineStr">
         <is>
           <t>中型软饵 Mid Strolling</t>
         </is>
       </c>
-      <c r="AO9" s="22" t="inlineStr">
+      <c r="AO9" s="52" t="inlineStr">
         <is>
           <t>4-5 寸 worm 做 Mid Strolling 时不容易被饵重拖垮，远处线弧和 roll 感更好维持，兼顾 PE power finesse。</t>
         </is>
       </c>
-      <c r="AP9" s="22" t="inlineStr">
+      <c r="AP9" s="52" t="inlineStr">
         <is>
           <t>Power Finesse Swim Power Finesse Swim 昨今のハイプレッシャーフィールドにおいて、欠かすことのできないテクニックとなったミッドストローリング。青木大介が求める「理想の振り幅」を具現化したミドスト特化型モデル。 最大の特徴は、独自のガイドセッティング。ラインの遊びを適度に持たせつつ、ブランクスの振動を効率よくルアーへ伝えることで、4〜5インチクラスの中型ワームを誰でも簡単に、かつ正確にロールさせ続けることが可能。微かなバイトを弾かずに絡め取り、ミドスト特有の「重くなるだけのバイト」を確実に手元へ伝える。現場で振り続けてきたからこそ辿り着いた、ミドストの完成形がここにある。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ9" s="22" t="inlineStr">
+      <c r="AQ9" s="52" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR9" s="22" t="inlineStr">
+      <c r="AR9" s="52" t="inlineStr">
         <is>
           <t>2026 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>DSRD10008</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="52" t="inlineStr">
         <is>
           <t>DHRS-68M</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="52" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="52" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr"/>
-      <c r="I10" s="22" t="inlineStr"/>
-      <c r="J10" s="22" t="inlineStr"/>
-      <c r="K10" s="22" t="inlineStr"/>
-      <c r="L10" s="22" t="inlineStr"/>
-      <c r="M10" s="22" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr">
+      <c r="H10" s="52" t="inlineStr"/>
+      <c r="I10" s="52" t="inlineStr"/>
+      <c r="J10" s="52" t="inlineStr"/>
+      <c r="K10" s="52" t="inlineStr"/>
+      <c r="L10" s="52" t="inlineStr"/>
+      <c r="M10" s="52" t="inlineStr"/>
+      <c r="N10" s="52" t="inlineStr">
         <is>
           <t>MAX~2号</t>
         </is>
       </c>
-      <c r="O10" s="22" t="inlineStr"/>
-      <c r="P10" s="22" t="inlineStr"/>
-      <c r="Q10" s="22" t="inlineStr"/>
-      <c r="R10" s="22" t="inlineStr">
+      <c r="O10" s="52" t="inlineStr"/>
+      <c r="P10" s="52" t="inlineStr"/>
+      <c r="Q10" s="52" t="inlineStr"/>
+      <c r="R10" s="52" t="inlineStr">
         <is>
           <t>￥58,500 (￥64,350)</t>
         </is>
       </c>
-      <c r="S10" s="22" t="inlineStr">
+      <c r="S10" s="52" t="inlineStr">
         <is>
           <t>4571527869044</t>
         </is>
       </c>
-      <c r="T10" s="22" t="inlineStr"/>
-      <c r="U10" s="22" t="inlineStr"/>
-      <c r="V10" s="22" t="inlineStr"/>
-      <c r="W10" s="22" t="inlineStr"/>
-      <c r="X10" s="22" t="inlineStr"/>
-      <c r="Y10" s="22" t="inlineStr"/>
-      <c r="Z10" s="22" t="inlineStr">
+      <c r="T10" s="52" t="inlineStr"/>
+      <c r="U10" s="52" t="inlineStr"/>
+      <c r="V10" s="52" t="inlineStr"/>
+      <c r="W10" s="52" t="inlineStr"/>
+      <c r="X10" s="52" t="inlineStr"/>
+      <c r="Y10" s="52" t="inlineStr"/>
+      <c r="Z10" s="52" t="inlineStr">
         <is>
           <t>1/8〜5/8</t>
         </is>
       </c>
-      <c r="AA10" s="22" t="inlineStr"/>
-      <c r="AB10" s="22" t="inlineStr"/>
-      <c r="AC10" s="22" t="inlineStr">
+      <c r="AA10" s="52" t="inlineStr"/>
+      <c r="AB10" s="52" t="inlineStr"/>
+      <c r="AC10" s="52" t="inlineStr">
         <is>
           <t>Power Finesse Shake</t>
         </is>
       </c>
-      <c r="AD10" s="22" t="inlineStr"/>
-      <c r="AE10" s="22" t="inlineStr"/>
-      <c r="AF10" s="22" t="inlineStr"/>
-      <c r="AG10" s="22" t="inlineStr">
+      <c r="AD10" s="52" t="inlineStr"/>
+      <c r="AE10" s="52" t="inlineStr"/>
+      <c r="AF10" s="52" t="inlineStr"/>
+      <c r="AG10" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH10" s="22" t="inlineStr">
+      <c r="AH10" s="52" t="inlineStr">
         <is>
           <t>Power Finesse Shake 以 PE spinning 远投和 cover 拖鱼为核心，Cover Neko、Small Rubber Jig、6 寸以上 worm 的 Mid Strolling 和较重无铅软饵都比普通轻量底操更匹配。</t>
         </is>
       </c>
-      <c r="AI10" s="22" t="inlineStr">
+      <c r="AI10" s="52" t="inlineStr">
         <is>
           <t>Power Finesse / Cover Neko / Small Rubber Jig / 6in+ Mid Strolling / Heavy No Sinker</t>
         </is>
       </c>
-      <c r="AJ10" s="22" t="inlineStr"/>
-      <c r="AK10" s="22" t="inlineStr"/>
-      <c r="AL10" s="22" t="inlineStr"/>
-      <c r="AM10" s="22" t="inlineStr">
+      <c r="AJ10" s="52" t="inlineStr"/>
+      <c r="AK10" s="52" t="inlineStr"/>
+      <c r="AL10" s="52" t="inlineStr"/>
+      <c r="AM10" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖库・远投 cover / 强化 spinning finesse</t>
         </is>
       </c>
-      <c r="AN10" s="22" t="inlineStr">
+      <c r="AN10" s="52" t="inlineStr">
         <is>
           <t>远投型 power finesse spinning</t>
         </is>
       </c>
-      <c r="AO10" s="22" t="inlineStr">
+      <c r="AO10" s="52" t="inlineStr">
         <is>
           <t>Cover Neko、Small Rubber Jig 和 6 寸以上 worm 的远距离操作更有底气，适合细线体系下想兼顾距离和控鱼的人。</t>
         </is>
       </c>
-      <c r="AP10" s="22" t="inlineStr">
+      <c r="AP10" s="52" t="inlineStr">
         <is>
           <t>Power Finesse Shake Power Finesse Shake スピニングタックルでのPEライン使用を前提とした、次世代のマルチフィネスモデル。フィネスロッドの枠を超えたパワーと遠投性能を兼ね備えている。 重量級ワームの抵抗に負けないバットパワーを持ちながら、ティップは繊細なアクションを殺さない。また、ライトリグ全般からカバーネコ、スモラバ、6インチ以上のルアーを使用したミドストをカバーし、PEラインの特性を最大限に活かした「遠くで掛ける」「カバーから引きずり出す」といった強気のフィネスを可能にする。 スピニングだから獲れる魚がいる。Mクラスだから挑める場所がある。青木の右腕として欠かせない、パワーフィネスの新たな基軸。屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ10" s="22" t="inlineStr">
+      <c r="AQ10" s="52" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR10" s="22" t="inlineStr">
+      <c r="AR10" s="52" t="inlineStr">
         <is>
           <t>2026 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>DSRD10009</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="52" t="inlineStr">
         <is>
           <t>DHRC-66L/ML</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="52" t="inlineStr">
         <is>
           <t>L/ML</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="52" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr"/>
-      <c r="I11" s="22" t="inlineStr"/>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="H11" s="52" t="inlineStr"/>
+      <c r="I11" s="52" t="inlineStr"/>
+      <c r="J11" s="52" t="inlineStr">
         <is>
           <t>95g</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr"/>
-      <c r="L11" s="22" t="inlineStr"/>
-      <c r="M11" s="22" t="inlineStr">
+      <c r="K11" s="52" t="inlineStr"/>
+      <c r="L11" s="52" t="inlineStr"/>
+      <c r="M11" s="52" t="inlineStr">
         <is>
           <t>6~12</t>
         </is>
       </c>
-      <c r="N11" s="22" t="inlineStr"/>
-      <c r="O11" s="22" t="inlineStr"/>
-      <c r="P11" s="22" t="inlineStr"/>
-      <c r="Q11" s="22" t="inlineStr"/>
-      <c r="R11" s="22" t="inlineStr">
+      <c r="N11" s="52" t="inlineStr"/>
+      <c r="O11" s="52" t="inlineStr"/>
+      <c r="P11" s="52" t="inlineStr"/>
+      <c r="Q11" s="52" t="inlineStr"/>
+      <c r="R11" s="52" t="inlineStr">
         <is>
           <t>￥50,500 （￥55,550）</t>
         </is>
       </c>
-      <c r="S11" s="22" t="inlineStr">
+      <c r="S11" s="52" t="inlineStr">
         <is>
           <t>4571527863813</t>
         </is>
       </c>
-      <c r="T11" s="22" t="inlineStr"/>
-      <c r="U11" s="22" t="inlineStr"/>
-      <c r="V11" s="22" t="inlineStr"/>
-      <c r="W11" s="22" t="inlineStr"/>
-      <c r="X11" s="22" t="inlineStr"/>
-      <c r="Y11" s="22" t="inlineStr"/>
-      <c r="Z11" s="22" t="inlineStr">
+      <c r="T11" s="52" t="inlineStr"/>
+      <c r="U11" s="52" t="inlineStr"/>
+      <c r="V11" s="52" t="inlineStr"/>
+      <c r="W11" s="52" t="inlineStr"/>
+      <c r="X11" s="52" t="inlineStr"/>
+      <c r="Y11" s="52" t="inlineStr"/>
+      <c r="Z11" s="52" t="inlineStr">
         <is>
           <t>1/16〜1/4</t>
         </is>
       </c>
-      <c r="AA11" s="22" t="inlineStr"/>
-      <c r="AB11" s="22" t="inlineStr"/>
-      <c r="AC11" s="22" t="inlineStr">
+      <c r="AA11" s="52" t="inlineStr"/>
+      <c r="AB11" s="52" t="inlineStr"/>
+      <c r="AC11" s="52" t="inlineStr">
         <is>
           <t>Bait Finesse Versatile</t>
         </is>
       </c>
-      <c r="AD11" s="22" t="inlineStr"/>
-      <c r="AE11" s="22" t="inlineStr"/>
-      <c r="AF11" s="22" t="inlineStr"/>
-      <c r="AG11" s="22" t="inlineStr">
+      <c r="AD11" s="52" t="inlineStr"/>
+      <c r="AE11" s="52" t="inlineStr"/>
+      <c r="AF11" s="52" t="inlineStr"/>
+      <c r="AG11" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH11" s="22" t="inlineStr">
+      <c r="AH11" s="52" t="inlineStr">
         <is>
           <t>Bait Finesse Versatile 适合在 cover 与 open water 间精准投放 No Sinker、Neko、Down Shot 和 Small Rubber Jig；优势是短中距离落点、读底和控线。</t>
         </is>
       </c>
-      <c r="AI11" s="22" t="inlineStr">
+      <c r="AI11" s="52" t="inlineStr">
         <is>
           <t>No Sinker / Neko Rig / Down Shot / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ11" s="22" t="inlineStr"/>
-      <c r="AK11" s="22" t="inlineStr"/>
-      <c r="AL11" s="22" t="inlineStr"/>
-      <c r="AM11" s="22" t="inlineStr">
+      <c r="AJ11" s="52" t="inlineStr"/>
+      <c r="AK11" s="52" t="inlineStr"/>
+      <c r="AL11" s="52" t="inlineStr"/>
+      <c r="AM11" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 边缘・浅场 / BFS 软饵精细</t>
         </is>
       </c>
-      <c r="AN11" s="22" t="inlineStr">
+      <c r="AN11" s="52" t="inlineStr">
         <is>
           <t>软饵向 bait finesse</t>
         </is>
       </c>
-      <c r="AO11" s="22" t="inlineStr">
+      <c r="AO11" s="52" t="inlineStr">
         <is>
           <t>No Sinker、Neko、Down Shot 和 Small Rubber Jig 的落点控制好，适合用枪柄在障碍边缘做低弹道精细投放。</t>
         </is>
       </c>
-      <c r="AP11" s="22" t="inlineStr">
+      <c r="AP11" s="52" t="inlineStr">
         <is>
           <t>Bait Finesse Versatile Bait Finesse Versatile LパワーティップにMLパワーのバット、繊細さと強さを兼ね備えたバーサタイルベイトフィネスロッド。 カバーでもオープンエリアでも取り回しが良い6’6″の長さはカバーへの正確なフィネスアプローチや底の変化をしっかりと感じ取るボトムの釣りでもアドバンテージをもたらします。ノーシンカー、ネコリグ、ダウンショット、スモールラバージグのフィネス系全般に活躍する１本。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ11" s="22" t="inlineStr">
+      <c r="AQ11" s="52" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR11" s="22" t="inlineStr"/>
+      <c r="AR11" s="52" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>DSRD10010</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="52" t="inlineStr">
         <is>
           <t>DHRC-69L+</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="52" t="inlineStr">
         <is>
           <t>L+</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="52" t="inlineStr">
         <is>
           <t>6’9″</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr"/>
-      <c r="I12" s="22" t="inlineStr"/>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="H12" s="52" t="inlineStr"/>
+      <c r="I12" s="52" t="inlineStr"/>
+      <c r="J12" s="52" t="inlineStr">
         <is>
           <t>95g</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr"/>
-      <c r="L12" s="22" t="inlineStr"/>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="K12" s="52" t="inlineStr"/>
+      <c r="L12" s="52" t="inlineStr"/>
+      <c r="M12" s="52" t="inlineStr">
         <is>
           <t>6~12</t>
         </is>
       </c>
-      <c r="N12" s="22" t="inlineStr"/>
-      <c r="O12" s="22" t="inlineStr"/>
-      <c r="P12" s="22" t="inlineStr"/>
-      <c r="Q12" s="22" t="inlineStr"/>
-      <c r="R12" s="22" t="inlineStr">
+      <c r="N12" s="52" t="inlineStr"/>
+      <c r="O12" s="52" t="inlineStr"/>
+      <c r="P12" s="52" t="inlineStr"/>
+      <c r="Q12" s="52" t="inlineStr"/>
+      <c r="R12" s="52" t="inlineStr">
         <is>
           <t>￥51,500 (￥56,650)</t>
         </is>
       </c>
-      <c r="S12" s="22" t="inlineStr">
+      <c r="S12" s="52" t="inlineStr">
         <is>
           <t>4571527865213</t>
         </is>
       </c>
-      <c r="T12" s="22" t="inlineStr"/>
-      <c r="U12" s="22" t="inlineStr"/>
-      <c r="V12" s="22" t="inlineStr"/>
-      <c r="W12" s="22" t="inlineStr"/>
-      <c r="X12" s="22" t="inlineStr"/>
-      <c r="Y12" s="22" t="inlineStr"/>
-      <c r="Z12" s="22" t="inlineStr">
+      <c r="T12" s="52" t="inlineStr"/>
+      <c r="U12" s="52" t="inlineStr"/>
+      <c r="V12" s="52" t="inlineStr"/>
+      <c r="W12" s="52" t="inlineStr"/>
+      <c r="X12" s="52" t="inlineStr"/>
+      <c r="Y12" s="52" t="inlineStr"/>
+      <c r="Z12" s="52" t="inlineStr">
         <is>
           <t>1/16〜1/4</t>
         </is>
       </c>
-      <c r="AA12" s="22" t="inlineStr"/>
-      <c r="AB12" s="22" t="inlineStr"/>
-      <c r="AC12" s="22" t="inlineStr">
+      <c r="AA12" s="52" t="inlineStr"/>
+      <c r="AB12" s="52" t="inlineStr"/>
+      <c r="AC12" s="52" t="inlineStr">
         <is>
           <t>Cover Finesse</t>
         </is>
       </c>
-      <c r="AD12" s="22" t="inlineStr"/>
-      <c r="AE12" s="22" t="inlineStr"/>
-      <c r="AF12" s="22" t="inlineStr"/>
-      <c r="AG12" s="22" t="inlineStr">
+      <c r="AD12" s="52" t="inlineStr"/>
+      <c r="AE12" s="52" t="inlineStr"/>
+      <c r="AF12" s="52" t="inlineStr"/>
+      <c r="AG12" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH12" s="22" t="inlineStr">
+      <c r="AH12" s="52" t="inlineStr">
         <is>
           <t>Cover Finesse 的重点是把轻量软饵送进 cover：Cover Neko 和 Small Rubber Jig 放首位，No Sinker 与 Light Texas 用于更隐蔽或更抗挂的切换。</t>
         </is>
       </c>
-      <c r="AI12" s="22" t="inlineStr">
+      <c r="AI12" s="52" t="inlineStr">
         <is>
           <t>Cover Neko / Small Rubber Jig / No Sinker / Light Texas</t>
         </is>
       </c>
-      <c r="AJ12" s="22" t="inlineStr"/>
-      <c r="AK12" s="22" t="inlineStr"/>
-      <c r="AL12" s="22" t="inlineStr"/>
-      <c r="AM12" s="22" t="inlineStr">
+      <c r="AJ12" s="52" t="inlineStr"/>
+      <c r="AK12" s="52" t="inlineStr"/>
+      <c r="AL12" s="52" t="inlineStr"/>
+      <c r="AM12" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 轻 cover・芦苇边・浮物 / cover finesse</t>
         </is>
       </c>
-      <c r="AN12" s="22" t="inlineStr">
+      <c r="AN12" s="52" t="inlineStr">
         <is>
           <t>轻 cover 精细软饵</t>
         </is>
       </c>
-      <c r="AO12" s="22" t="inlineStr">
+      <c r="AO12" s="52" t="inlineStr">
         <is>
           <t>Cover Neko 和 Small Rubber Jig 是最自然的搭配，竿长让贴 cover 投放和中鱼后导鱼更有优势。</t>
         </is>
       </c>
-      <c r="AP12" s="22" t="inlineStr">
+      <c r="AP12" s="52" t="inlineStr">
         <is>
           <t>COVER Finesse Cover Finesse 時代が変わっても必要とされる不変のカバーフィネスロッド。 6’９”の長さはカバーへのより正確なフィネスアプローチや掛けた時の優位性、カバーの釣りに必要な性能備えている。カバーネコリグ、スモールラバージグ、ノーシンカーなどフィネス系全般に活躍する１本。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ12" s="22" t="inlineStr">
+      <c r="AQ12" s="52" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="AR12" s="22" t="inlineStr">
+      <c r="AR12" s="52" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>DSRD10011</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="52" t="inlineStr">
         <is>
           <t>DHRC-68M</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="52" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="52" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr"/>
-      <c r="I13" s="22" t="inlineStr"/>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="H13" s="52" t="inlineStr"/>
+      <c r="I13" s="52" t="inlineStr"/>
+      <c r="J13" s="52" t="inlineStr">
         <is>
           <t>95g</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr"/>
-      <c r="L13" s="22" t="inlineStr"/>
-      <c r="M13" s="22" t="inlineStr">
+      <c r="K13" s="52" t="inlineStr"/>
+      <c r="L13" s="52" t="inlineStr"/>
+      <c r="M13" s="52" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N13" s="22" t="inlineStr"/>
-      <c r="O13" s="22" t="inlineStr"/>
-      <c r="P13" s="22" t="inlineStr"/>
-      <c r="Q13" s="22" t="inlineStr"/>
-      <c r="R13" s="22" t="inlineStr">
+      <c r="N13" s="52" t="inlineStr"/>
+      <c r="O13" s="52" t="inlineStr"/>
+      <c r="P13" s="52" t="inlineStr"/>
+      <c r="Q13" s="52" t="inlineStr"/>
+      <c r="R13" s="52" t="inlineStr">
         <is>
           <t>￥51,500 (￥56,650)</t>
         </is>
       </c>
-      <c r="S13" s="22" t="inlineStr">
+      <c r="S13" s="52" t="inlineStr">
         <is>
           <t>4571527863820</t>
         </is>
       </c>
-      <c r="T13" s="22" t="inlineStr"/>
-      <c r="U13" s="22" t="inlineStr"/>
-      <c r="V13" s="22" t="inlineStr"/>
-      <c r="W13" s="22" t="inlineStr"/>
-      <c r="X13" s="22" t="inlineStr"/>
-      <c r="Y13" s="22" t="inlineStr"/>
-      <c r="Z13" s="22" t="inlineStr">
+      <c r="T13" s="52" t="inlineStr"/>
+      <c r="U13" s="52" t="inlineStr"/>
+      <c r="V13" s="52" t="inlineStr"/>
+      <c r="W13" s="52" t="inlineStr"/>
+      <c r="X13" s="52" t="inlineStr"/>
+      <c r="Y13" s="52" t="inlineStr"/>
+      <c r="Z13" s="52" t="inlineStr">
         <is>
           <t>3/16〜5/8</t>
         </is>
       </c>
-      <c r="AA13" s="22" t="inlineStr"/>
-      <c r="AB13" s="22" t="inlineStr"/>
-      <c r="AC13" s="22" t="inlineStr">
+      <c r="AA13" s="52" t="inlineStr"/>
+      <c r="AB13" s="52" t="inlineStr"/>
+      <c r="AC13" s="52" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="AD13" s="22" t="inlineStr"/>
-      <c r="AE13" s="22" t="inlineStr"/>
-      <c r="AF13" s="22" t="inlineStr"/>
-      <c r="AG13" s="22" t="inlineStr">
+      <c r="AD13" s="52" t="inlineStr"/>
+      <c r="AE13" s="52" t="inlineStr"/>
+      <c r="AF13" s="52" t="inlineStr"/>
+      <c r="AG13" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH13" s="22" t="inlineStr">
+      <c r="AH13" s="52" t="inlineStr">
         <is>
           <t>FX 是 bait 万用核心竿，描述明确覆盖从撃ち到巻き：软饵端以 No Sinker、Texas、Down Shot、Neko、Football 为主，搜索端再接 Crankbait 和 Spinnerbait。</t>
         </is>
       </c>
-      <c r="AI13" s="22" t="inlineStr">
+      <c r="AI13" s="52" t="inlineStr">
         <is>
           <t>No Sinker / Texas Rig / Down Shot / Neko Rig / Football Jig / Crankbait / Spinnerbait</t>
         </is>
       </c>
-      <c r="AJ13" s="22" t="inlineStr"/>
-      <c r="AK13" s="22" t="inlineStr"/>
-      <c r="AL13" s="22" t="inlineStr"/>
-      <c r="AM13" s="22" t="inlineStr">
+      <c r="AJ13" s="52" t="inlineStr"/>
+      <c r="AK13" s="52" t="inlineStr"/>
+      <c r="AL13" s="52" t="inlineStr"/>
+      <c r="AM13" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓・船钓 / 软饵底操到卷物搜索</t>
         </is>
       </c>
-      <c r="AN13" s="22" t="inlineStr">
+      <c r="AN13" s="52" t="inlineStr">
         <is>
           <t>软硬饵切换型 bait versatile</t>
         </is>
       </c>
-      <c r="AO13" s="22" t="inlineStr">
+      <c r="AO13" s="52" t="inlineStr">
         <is>
           <t>No Sinker、Texas、Down Shot、Neko、Football 可以打点，Crankbait 和 Spinnerbait 可搜索，适合一支竿覆盖日常主力 bait 场景。</t>
         </is>
       </c>
-      <c r="AP13" s="22" t="inlineStr">
+      <c r="AP13" s="52" t="inlineStr">
         <is>
           <t>FX 巻きから撃ちまでマルチにこなせるスーパーバーサタイルモデル。癖のないテーパーから生み出されるキャスト性能とロッドの自由度。ベイトモデルの中核に相応しいバランスを実現。ノーシンカー、テキサス、ダウンショット、ネコリグ、フットボール、プラグ全般、ワイヤーベイトまであらゆるジャンルのタイプが使用可能。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ13" s="22" t="inlineStr">
+      <c r="AQ13" s="52" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR13" s="22" t="inlineStr"/>
+      <c r="AR13" s="52" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>DSRD10012</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="52" t="inlineStr">
         <is>
           <t>DHRC-610MH</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="52" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="52" t="inlineStr">
         <is>
           <t>6’10”</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr"/>
-      <c r="I14" s="22" t="inlineStr"/>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="H14" s="52" t="inlineStr"/>
+      <c r="I14" s="52" t="inlineStr"/>
+      <c r="J14" s="52" t="inlineStr">
         <is>
           <t>109g</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr"/>
-      <c r="L14" s="22" t="inlineStr"/>
-      <c r="M14" s="22" t="inlineStr">
+      <c r="K14" s="52" t="inlineStr"/>
+      <c r="L14" s="52" t="inlineStr"/>
+      <c r="M14" s="52" t="inlineStr">
         <is>
           <t>8~20</t>
         </is>
       </c>
-      <c r="N14" s="22" t="inlineStr"/>
-      <c r="O14" s="22" t="inlineStr"/>
-      <c r="P14" s="22" t="inlineStr"/>
-      <c r="Q14" s="22" t="inlineStr"/>
-      <c r="R14" s="22" t="inlineStr">
+      <c r="N14" s="52" t="inlineStr"/>
+      <c r="O14" s="52" t="inlineStr"/>
+      <c r="P14" s="52" t="inlineStr"/>
+      <c r="Q14" s="52" t="inlineStr"/>
+      <c r="R14" s="52" t="inlineStr">
         <is>
           <t>￥52,500 (￥57,750)</t>
         </is>
       </c>
-      <c r="S14" s="22" t="inlineStr">
+      <c r="S14" s="52" t="inlineStr">
         <is>
           <t>4571527865220</t>
         </is>
       </c>
-      <c r="T14" s="22" t="inlineStr"/>
-      <c r="U14" s="22" t="inlineStr"/>
-      <c r="V14" s="22" t="inlineStr"/>
-      <c r="W14" s="22" t="inlineStr"/>
-      <c r="X14" s="22" t="inlineStr"/>
-      <c r="Y14" s="22" t="inlineStr"/>
-      <c r="Z14" s="22" t="inlineStr">
+      <c r="T14" s="52" t="inlineStr"/>
+      <c r="U14" s="52" t="inlineStr"/>
+      <c r="V14" s="52" t="inlineStr"/>
+      <c r="W14" s="52" t="inlineStr"/>
+      <c r="X14" s="52" t="inlineStr"/>
+      <c r="Y14" s="52" t="inlineStr"/>
+      <c r="Z14" s="52" t="inlineStr">
         <is>
           <t>3/16〜3/4</t>
         </is>
       </c>
-      <c r="AA14" s="22" t="inlineStr"/>
-      <c r="AB14" s="22" t="inlineStr"/>
-      <c r="AC14" s="22" t="inlineStr">
+      <c r="AA14" s="52" t="inlineStr"/>
+      <c r="AB14" s="52" t="inlineStr"/>
+      <c r="AC14" s="52" t="inlineStr">
         <is>
           <t>FXR</t>
         </is>
       </c>
-      <c r="AD14" s="22" t="inlineStr"/>
-      <c r="AE14" s="22" t="inlineStr"/>
-      <c r="AF14" s="22" t="inlineStr"/>
-      <c r="AG14" s="22" t="inlineStr">
+      <c r="AD14" s="52" t="inlineStr"/>
+      <c r="AE14" s="52" t="inlineStr"/>
+      <c r="AF14" s="52" t="inlineStr"/>
+      <c r="AG14" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH14" s="22" t="inlineStr">
+      <c r="AH14" s="52" t="inlineStr">
         <is>
           <t>FXR 是中量级 super versatile，先承担 Texas、No Sinker、Down Shot、Neko 和 Football 这类 worm/jig 场景，再扩展到 wire bait 与中型 Big Bait。</t>
         </is>
       </c>
-      <c r="AI14" s="22" t="inlineStr">
+      <c r="AI14" s="52" t="inlineStr">
         <is>
           <t>Texas Rig / No Sinker / Down Shot / Neko Rig / Football Jig / Spinnerbait / Mid-size Big Bait</t>
         </is>
       </c>
-      <c r="AJ14" s="22" t="inlineStr"/>
-      <c r="AK14" s="22" t="inlineStr"/>
-      <c r="AL14" s="22" t="inlineStr"/>
-      <c r="AM14" s="22" t="inlineStr">
+      <c r="AJ14" s="52" t="inlineStr"/>
+      <c r="AK14" s="52" t="inlineStr"/>
+      <c r="AL14" s="52" t="inlineStr"/>
+      <c r="AM14" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 湖库・草边・硬底 / 中量软饵与移动饵</t>
         </is>
       </c>
-      <c r="AN14" s="22" t="inlineStr">
+      <c r="AN14" s="52" t="inlineStr">
         <is>
           <t>中量级强泛用 bait</t>
         </is>
       </c>
-      <c r="AO14" s="22" t="inlineStr">
+      <c r="AO14" s="52" t="inlineStr">
         <is>
           <t>Texas、Football、Neko 和 Spinnerbait 都在合理范围，Mid-size Big Bait 只是扩展用途；更适合中重钓组的连续切换。</t>
         </is>
       </c>
-      <c r="AP14" s="22" t="inlineStr">
+      <c r="AP14" s="52" t="inlineStr">
         <is>
           <t>FXR 巻きから撃ちまでマルチにこなせるスーパーミドルバーサタイルモデル。癖のないテーパーから生み出されるキャスト性能とロッドの自由度。ベイトモデルの中核に相応しいバランスを実現。ノーシンカー、テキサス、ダウンショット、ネコリグ、フットボール、プラグ全般、ワイヤーベイト、ミドルサイズビッグベイトまであらゆるジャンルのタイプが使用可能。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ14" s="22" t="inlineStr">
+      <c r="AQ14" s="52" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="AR14" s="22" t="inlineStr">
+      <c r="AR14" s="52" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>DSRD10013</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="52" t="inlineStr">
         <is>
           <t>DHRC-70H</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="52" t="inlineStr">
         <is>
           <t>7’0″</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="52" t="inlineStr">
         <is>
           <t>Regular first</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr"/>
-      <c r="I15" s="22" t="inlineStr"/>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="H15" s="52" t="inlineStr"/>
+      <c r="I15" s="52" t="inlineStr"/>
+      <c r="J15" s="52" t="inlineStr">
         <is>
           <t>112g</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr"/>
-      <c r="L15" s="22" t="inlineStr"/>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="K15" s="52" t="inlineStr"/>
+      <c r="L15" s="52" t="inlineStr"/>
+      <c r="M15" s="52" t="inlineStr">
         <is>
           <t>12~25</t>
         </is>
       </c>
-      <c r="N15" s="22" t="inlineStr"/>
-      <c r="O15" s="22" t="inlineStr"/>
-      <c r="P15" s="22" t="inlineStr"/>
-      <c r="Q15" s="22" t="inlineStr"/>
-      <c r="R15" s="22" t="inlineStr">
+      <c r="N15" s="52" t="inlineStr"/>
+      <c r="O15" s="52" t="inlineStr"/>
+      <c r="P15" s="52" t="inlineStr"/>
+      <c r="Q15" s="52" t="inlineStr"/>
+      <c r="R15" s="52" t="inlineStr">
         <is>
           <t>￥52,500 (￥57,750)</t>
         </is>
       </c>
-      <c r="S15" s="22" t="inlineStr">
+      <c r="S15" s="52" t="inlineStr">
         <is>
           <t>4571527863837</t>
         </is>
       </c>
-      <c r="T15" s="22" t="inlineStr"/>
-      <c r="U15" s="22" t="inlineStr"/>
-      <c r="V15" s="22" t="inlineStr"/>
-      <c r="W15" s="22" t="inlineStr"/>
-      <c r="X15" s="22" t="inlineStr"/>
-      <c r="Y15" s="22" t="inlineStr"/>
-      <c r="Z15" s="22" t="inlineStr">
+      <c r="T15" s="52" t="inlineStr"/>
+      <c r="U15" s="52" t="inlineStr"/>
+      <c r="V15" s="52" t="inlineStr"/>
+      <c r="W15" s="52" t="inlineStr"/>
+      <c r="X15" s="52" t="inlineStr"/>
+      <c r="Y15" s="52" t="inlineStr"/>
+      <c r="Z15" s="52" t="inlineStr">
         <is>
           <t>3/16〜1</t>
         </is>
       </c>
-      <c r="AA15" s="22" t="inlineStr"/>
-      <c r="AB15" s="22" t="inlineStr"/>
-      <c r="AC15" s="22" t="inlineStr">
+      <c r="AA15" s="52" t="inlineStr"/>
+      <c r="AB15" s="52" t="inlineStr"/>
+      <c r="AC15" s="52" t="inlineStr">
         <is>
           <t>Power Fishing Versatile</t>
         </is>
       </c>
-      <c r="AD15" s="22" t="inlineStr"/>
-      <c r="AE15" s="22" t="inlineStr"/>
-      <c r="AF15" s="22" t="inlineStr"/>
-      <c r="AG15" s="22" t="inlineStr">
+      <c r="AD15" s="52" t="inlineStr"/>
+      <c r="AE15" s="52" t="inlineStr"/>
+      <c r="AF15" s="52" t="inlineStr"/>
+      <c r="AG15" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH15" s="22" t="inlineStr">
+      <c r="AH15" s="52" t="inlineStr">
         <is>
           <t>Power Fishing Versatile 明确面向重 cover 和重系钓组：Heavy Texas、Rubber Jig、Carolina、Free Rig 是主线，Big Spoon、Big Bait 和 Heavy Spinnerbait 属强力搜索补充。</t>
         </is>
       </c>
-      <c r="AI15" s="22" t="inlineStr">
+      <c r="AI15" s="52" t="inlineStr">
         <is>
           <t>Heavy Texas / Rubber Jig / Carolina Rig / Free Rig / Big Spoon / Big Bait / Heavy Spinnerbait</t>
         </is>
       </c>
-      <c r="AJ15" s="22" t="inlineStr"/>
-      <c r="AK15" s="22" t="inlineStr"/>
-      <c r="AL15" s="22" t="inlineStr"/>
-      <c r="AM15" s="22" t="inlineStr">
+      <c r="AJ15" s="52" t="inlineStr"/>
+      <c r="AK15" s="52" t="inlineStr"/>
+      <c r="AL15" s="52" t="inlineStr"/>
+      <c r="AM15" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 重 cover・深水硬底・大型饵搜索</t>
         </is>
       </c>
-      <c r="AN15" s="22" t="inlineStr">
+      <c r="AN15" s="52" t="inlineStr">
         <is>
           <t>强力底操与重系搜索</t>
         </is>
       </c>
-      <c r="AO15" s="22" t="inlineStr">
+      <c r="AO15" s="52" t="inlineStr">
         <is>
           <t>Heavy Texas、Rubber Jig、Carolina、Free Rig 能打重 cover，Big Spoon、Big Bait 和 Heavy Spinnerbait 可做强搜索，适合需要控鱼余量的场景。</t>
         </is>
       </c>
-      <c r="AP15" s="22" t="inlineStr">
+      <c r="AP15" s="52" t="inlineStr">
         <is>
           <t>Power Fishing Versatile Power Fishing Versatile 難攻不落のカバーを制するヘビーバーサタイルロッド。強靭な強さと繊細さを合わせ持つこのロッドは軽めのリグから重めのリグまでフィールドの状況に応じて幅広い変化に対応。テキサス、ラバージグ、キャロライナリグ、フリーリグ、ビッグスプーン、ビッグベイト、ヘビースピナーベイトなど対応。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ15" s="22" t="inlineStr">
+      <c r="AQ15" s="52" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="AR15" s="22" t="inlineStr"/>
+      <c r="AR15" s="52" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>DSRD10014</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="52" t="inlineStr">
         <is>
           <t>DHRS-E-62UL-S</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="52" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="52" t="inlineStr">
         <is>
           <t>6’2″</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr"/>
-      <c r="I16" s="22" t="inlineStr"/>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="H16" s="52" t="inlineStr"/>
+      <c r="I16" s="52" t="inlineStr"/>
+      <c r="J16" s="52" t="inlineStr">
         <is>
           <t>71g</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr"/>
-      <c r="L16" s="22" t="inlineStr"/>
-      <c r="M16" s="22" t="inlineStr">
+      <c r="K16" s="52" t="inlineStr"/>
+      <c r="L16" s="52" t="inlineStr"/>
+      <c r="M16" s="52" t="inlineStr">
         <is>
           <t>2.5~8</t>
         </is>
       </c>
-      <c r="N16" s="22" t="inlineStr"/>
-      <c r="O16" s="22" t="inlineStr"/>
-      <c r="P16" s="22" t="inlineStr"/>
-      <c r="Q16" s="22" t="inlineStr"/>
-      <c r="R16" s="22" t="inlineStr">
+      <c r="N16" s="52" t="inlineStr"/>
+      <c r="O16" s="52" t="inlineStr"/>
+      <c r="P16" s="52" t="inlineStr"/>
+      <c r="Q16" s="52" t="inlineStr"/>
+      <c r="R16" s="52" t="inlineStr">
         <is>
           <t>￥62,000 (￥68,200)</t>
         </is>
       </c>
-      <c r="S16" s="22" t="inlineStr">
+      <c r="S16" s="52" t="inlineStr">
         <is>
           <t>4571527863844</t>
         </is>
       </c>
-      <c r="T16" s="22" t="inlineStr"/>
-      <c r="U16" s="22" t="inlineStr"/>
-      <c r="V16" s="22" t="inlineStr"/>
-      <c r="W16" s="22" t="inlineStr"/>
-      <c r="X16" s="22" t="inlineStr"/>
-      <c r="Y16" s="22" t="inlineStr"/>
-      <c r="Z16" s="22" t="inlineStr">
+      <c r="T16" s="52" t="inlineStr"/>
+      <c r="U16" s="52" t="inlineStr"/>
+      <c r="V16" s="52" t="inlineStr"/>
+      <c r="W16" s="52" t="inlineStr"/>
+      <c r="X16" s="52" t="inlineStr"/>
+      <c r="Y16" s="52" t="inlineStr"/>
+      <c r="Z16" s="52" t="inlineStr">
         <is>
           <t>1/32〜1/4</t>
         </is>
       </c>
-      <c r="AA16" s="22" t="inlineStr"/>
-      <c r="AB16" s="22" t="inlineStr"/>
-      <c r="AC16" s="22" t="inlineStr">
+      <c r="AA16" s="52" t="inlineStr"/>
+      <c r="AB16" s="52" t="inlineStr"/>
+      <c r="AC16" s="52" t="inlineStr">
         <is>
           <t>The Finesse Shooting</t>
         </is>
       </c>
-      <c r="AD16" s="22" t="inlineStr"/>
-      <c r="AE16" s="22" t="inlineStr"/>
-      <c r="AF16" s="22" t="inlineStr"/>
-      <c r="AG16" s="22" t="inlineStr">
+      <c r="AD16" s="52" t="inlineStr"/>
+      <c r="AE16" s="52" t="inlineStr"/>
+      <c r="AF16" s="52" t="inlineStr"/>
+      <c r="AG16" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH16" s="22" t="inlineStr">
+      <c r="AH16" s="52" t="inlineStr">
         <is>
           <t>The Finesse Shooting 用长 solid tip 和细 PE 做轻量投射与操作，No Sinker、Down Shot、Neko、Jighead、Small Rubber Jig 和 Hover Strolling 都是官网明确适用。</t>
         </is>
       </c>
-      <c r="AI16" s="22" t="inlineStr">
+      <c r="AI16" s="52" t="inlineStr">
         <is>
           <t>No Sinker / Down Shot / Neko Rig / Jighead Rig / Small Rubber Jig / Hover Strolling</t>
         </is>
       </c>
-      <c r="AJ16" s="22" t="inlineStr"/>
-      <c r="AK16" s="22" t="inlineStr"/>
-      <c r="AL16" s="22" t="inlineStr"/>
-      <c r="AM16" s="22" t="inlineStr">
+      <c r="AJ16" s="52" t="inlineStr"/>
+      <c r="AK16" s="52" t="inlineStr"/>
+      <c r="AL16" s="52" t="inlineStr"/>
+      <c r="AM16" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压开放水・清水 / PE finesse shooting</t>
         </is>
       </c>
-      <c r="AN16" s="22" t="inlineStr">
+      <c r="AN16" s="52" t="inlineStr">
         <is>
           <t>极细线轻量投射 finesse</t>
         </is>
       </c>
-      <c r="AO16" s="22" t="inlineStr">
+      <c r="AO16" s="52" t="inlineStr">
         <is>
           <t>No Sinker、Down Shot、Jighead 和 Hover Strolling 的轻量投射更稳定，长 solid tip 对短咬和细微负重变化更友好。</t>
         </is>
       </c>
-      <c r="AP16" s="22" t="inlineStr">
+      <c r="AP16" s="52" t="inlineStr">
         <is>
           <t>The Finesse Shooting EXTREME SPEC/2024 【EXTREME SPEC/2024 Limited】The Finesse Shooting 過激なまでに追求したエクストリームスペックモデル。ハイクオリティカーボンと中弾性ロングソリッドの極上なまでの操作感で軽量ルアーを意のままに飛ばし、操り、掛ける。極細PEラインに対応。ノーシンカー、ダウンショット、ネコリグ、ジグヘッド、スモラバ、ホバストまで幅広く対応。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ16" s="22" t="inlineStr">
+      <c r="AQ16" s="52" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="AR16" s="22" t="inlineStr"/>
+      <c r="AR16" s="52" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>DSRD10015</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="52" t="inlineStr">
         <is>
           <t>DHRS-E-510XUL-S</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="52" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="52" t="inlineStr">
         <is>
           <t>5’10”</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr"/>
-      <c r="I17" s="22" t="inlineStr"/>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="H17" s="52" t="inlineStr"/>
+      <c r="I17" s="52" t="inlineStr"/>
+      <c r="J17" s="52" t="inlineStr">
         <is>
           <t>67g</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr"/>
-      <c r="L17" s="22" t="inlineStr"/>
-      <c r="M17" s="22" t="inlineStr">
+      <c r="K17" s="52" t="inlineStr"/>
+      <c r="L17" s="52" t="inlineStr"/>
+      <c r="M17" s="52" t="inlineStr">
         <is>
           <t>2~4</t>
         </is>
       </c>
-      <c r="N17" s="22" t="inlineStr">
+      <c r="N17" s="52" t="inlineStr">
         <is>
           <t>0.2~0.6</t>
         </is>
       </c>
-      <c r="O17" s="22" t="inlineStr"/>
-      <c r="P17" s="22" t="inlineStr"/>
-      <c r="Q17" s="22" t="inlineStr"/>
-      <c r="R17" s="22" t="inlineStr">
+      <c r="O17" s="52" t="inlineStr"/>
+      <c r="P17" s="52" t="inlineStr"/>
+      <c r="Q17" s="52" t="inlineStr"/>
+      <c r="R17" s="52" t="inlineStr">
         <is>
           <t>￥62,000 (￥68,200)</t>
         </is>
       </c>
-      <c r="S17" s="22" t="inlineStr">
+      <c r="S17" s="52" t="inlineStr">
         <is>
           <t>4571527865237</t>
         </is>
       </c>
-      <c r="T17" s="22" t="inlineStr"/>
-      <c r="U17" s="22" t="inlineStr"/>
-      <c r="V17" s="22" t="inlineStr"/>
-      <c r="W17" s="22" t="inlineStr"/>
-      <c r="X17" s="22" t="inlineStr"/>
-      <c r="Y17" s="22" t="inlineStr"/>
-      <c r="Z17" s="22" t="inlineStr">
+      <c r="T17" s="52" t="inlineStr"/>
+      <c r="U17" s="52" t="inlineStr"/>
+      <c r="V17" s="52" t="inlineStr"/>
+      <c r="W17" s="52" t="inlineStr"/>
+      <c r="X17" s="52" t="inlineStr"/>
+      <c r="Y17" s="52" t="inlineStr"/>
+      <c r="Z17" s="52" t="inlineStr">
         <is>
           <t>1/48～1/8</t>
         </is>
       </c>
-      <c r="AA17" s="22" t="inlineStr"/>
-      <c r="AB17" s="22" t="inlineStr"/>
-      <c r="AC17" s="22" t="inlineStr">
+      <c r="AA17" s="52" t="inlineStr"/>
+      <c r="AB17" s="52" t="inlineStr"/>
+      <c r="AC17" s="52" t="inlineStr">
         <is>
           <t>Finesse Shake KIWAMI</t>
         </is>
       </c>
-      <c r="AD17" s="22" t="inlineStr"/>
-      <c r="AE17" s="22" t="inlineStr"/>
-      <c r="AF17" s="22" t="inlineStr"/>
-      <c r="AG17" s="22" t="inlineStr">
+      <c r="AD17" s="52" t="inlineStr"/>
+      <c r="AE17" s="52" t="inlineStr"/>
+      <c r="AF17" s="52" t="inlineStr"/>
+      <c r="AG17" s="52" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH17" s="22" t="inlineStr">
+      <c r="AH17" s="52" t="inlineStr">
         <is>
           <t>Finesse Shake KIWAMI 是 XUL solid 的极限食わせ竿，适合短咬明显的 No Sinker、Down Shot、Neko、Jighead 和 Hover Strolling，重点是轻量操控和瞬间挂鱼。</t>
         </is>
       </c>
-      <c r="AI17" s="22" t="inlineStr">
+      <c r="AI17" s="52" t="inlineStr">
         <is>
           <t>No Sinker / Down Shot / Neko Rig / Jighead Rig / Hover Strolling</t>
         </is>
       </c>
-      <c r="AJ17" s="22" t="inlineStr"/>
-      <c r="AK17" s="22" t="inlineStr"/>
-      <c r="AL17" s="22" t="inlineStr"/>
-      <c r="AM17" s="22" t="inlineStr">
+      <c r="AJ17" s="52" t="inlineStr"/>
+      <c r="AK17" s="52" t="inlineStr"/>
+      <c r="AL17" s="52" t="inlineStr"/>
+      <c r="AM17" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 极高压近距・ sight fishing / XUL finesse</t>
         </is>
       </c>
-      <c r="AN17" s="22" t="inlineStr">
+      <c r="AN17" s="52" t="inlineStr">
         <is>
           <t>短距极轻食わせ专向</t>
         </is>
       </c>
-      <c r="AO17" s="22" t="inlineStr">
+      <c r="AO17" s="52" t="inlineStr">
         <is>
           <t>XUL solid 更适合轻 No Sinker、Down Shot、Neko 与 Hover Strolling，优势是轻饵存在感和短咬判断。</t>
         </is>
       </c>
-      <c r="AP17" s="22" t="inlineStr">
+      <c r="AP17" s="52" t="inlineStr">
         <is>
           <t>Finesse SHAKE KIWAMI EXTREME SPEC/2025 【EXTREME SPEC/2025 Limited】 Finesse Shake KIWAMI 過激なまでに追求したエクストリームスペックモデル。ショートバイトを逃さない、瞬間的に掛けられる研ぎ澄まされたフィネスロッド。ロッドを軽量化する事で得られる感度とXULソリッドを採用する事で水中の違和感さえも把握。極上なまでの操作感で軽量ルアーを意のままに飛ばし、操り、掛ける。極細PEラインに対応。ノーシンカー、ダウンショット、ネコリグ、ジグヘッド、ホバストまで幅広く対応。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ17" s="22" t="inlineStr">
+      <c r="AQ17" s="52" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="AR17" s="22" t="inlineStr">
+      <c r="AR17" s="52" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="53" t="inlineStr">
         <is>
           <t>DSRD10016</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="53" t="inlineStr">
         <is>
           <t>DSR1002</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="53" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="53" t="inlineStr">
         <is>
           <t>DBTS-SS-63ML</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="53" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="53" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="53" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr"/>
-      <c r="I18" s="19" t="inlineStr"/>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="H18" s="53" t="inlineStr"/>
+      <c r="I18" s="53" t="inlineStr"/>
+      <c r="J18" s="53" t="inlineStr">
         <is>
           <t>93g</t>
         </is>
       </c>
-      <c r="K18" s="19" t="inlineStr"/>
-      <c r="L18" s="19" t="inlineStr"/>
-      <c r="M18" s="19" t="inlineStr">
+      <c r="K18" s="53" t="inlineStr"/>
+      <c r="L18" s="53" t="inlineStr"/>
+      <c r="M18" s="53" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N18" s="19" t="inlineStr">
+      <c r="N18" s="53" t="inlineStr">
         <is>
           <t>0.6~1.2</t>
         </is>
       </c>
-      <c r="O18" s="19" t="inlineStr"/>
-      <c r="P18" s="19" t="inlineStr"/>
-      <c r="Q18" s="19" t="inlineStr"/>
-      <c r="R18" s="19" t="inlineStr">
+      <c r="O18" s="53" t="inlineStr"/>
+      <c r="P18" s="53" t="inlineStr"/>
+      <c r="Q18" s="53" t="inlineStr"/>
+      <c r="R18" s="53" t="inlineStr">
         <is>
           <t>¥28,000 （税込み¥30,800）</t>
         </is>
       </c>
-      <c r="S18" s="19" t="inlineStr">
+      <c r="S18" s="53" t="inlineStr">
         <is>
           <t>4571527863554</t>
         </is>
       </c>
-      <c r="T18" s="19" t="inlineStr"/>
-      <c r="U18" s="19" t="inlineStr"/>
-      <c r="V18" s="19" t="inlineStr"/>
-      <c r="W18" s="19" t="inlineStr"/>
-      <c r="X18" s="19" t="inlineStr"/>
-      <c r="Y18" s="19" t="inlineStr"/>
-      <c r="Z18" s="19" t="inlineStr">
+      <c r="T18" s="53" t="inlineStr"/>
+      <c r="U18" s="53" t="inlineStr"/>
+      <c r="V18" s="53" t="inlineStr"/>
+      <c r="W18" s="53" t="inlineStr"/>
+      <c r="X18" s="53" t="inlineStr"/>
+      <c r="Y18" s="53" t="inlineStr"/>
+      <c r="Z18" s="53" t="inlineStr">
         <is>
           <t>1/16~1/4</t>
         </is>
       </c>
-      <c r="AA18" s="19" t="inlineStr"/>
-      <c r="AB18" s="19" t="inlineStr"/>
-      <c r="AC18" s="19" t="inlineStr">
+      <c r="AA18" s="53" t="inlineStr"/>
+      <c r="AB18" s="53" t="inlineStr"/>
+      <c r="AC18" s="53" t="inlineStr">
         <is>
           <t>Lightning</t>
         </is>
       </c>
-      <c r="AD18" s="19" t="inlineStr"/>
-      <c r="AE18" s="19" t="inlineStr"/>
-      <c r="AF18" s="19" t="inlineStr"/>
-      <c r="AG18" s="19" t="inlineStr"/>
-      <c r="AH18" s="19" t="inlineStr">
+      <c r="AD18" s="53" t="inlineStr"/>
+      <c r="AE18" s="53" t="inlineStr"/>
+      <c r="AF18" s="53" t="inlineStr"/>
+      <c r="AG18" s="53" t="inlineStr"/>
+      <c r="AH18" s="53" t="inlineStr">
         <is>
           <t>Lightning 为 big lake finesse pattern 设计，Neko 是核心，Down Shot、Small Rubber Jig 和 No Sinker 承接 light-rig 全般；ML power 用来补足远处中鱼后的牵制。</t>
         </is>
       </c>
-      <c r="AI18" s="19" t="inlineStr">
+      <c r="AI18" s="53" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / Small Rubber Jig / No Sinker / Power Finesse</t>
         </is>
       </c>
-      <c r="AJ18" s="19" t="inlineStr"/>
-      <c r="AK18" s="19" t="inlineStr"/>
-      <c r="AL18" s="19" t="inlineStr"/>
-      <c r="AM18" s="19" t="inlineStr">
+      <c r="AJ18" s="53" t="inlineStr"/>
+      <c r="AK18" s="53" t="inlineStr"/>
+      <c r="AL18" s="53" t="inlineStr"/>
+      <c r="AM18" s="53" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖库・风浪边 / Neko 与 power finesse</t>
         </is>
       </c>
-      <c r="AN18" s="19" t="inlineStr">
+      <c r="AN18" s="53" t="inlineStr">
         <is>
           <t>湖库 Neko power finesse</t>
         </is>
       </c>
-      <c r="AO18" s="19" t="inlineStr">
+      <c r="AO18" s="53" t="inlineStr">
         <is>
           <t>Neko Rig 放在核心，Down Shot、Small Rubber Jig 和 No Sinker 可跟进；ML power 让远处中鱼后更容易保持主动。</t>
         </is>
       </c>
-      <c r="AP18" s="19" t="inlineStr">
+      <c r="AP18" s="53" t="inlineStr">
         <is>
           <t>Lightning BLUE TREKから生まれた個性派SABER SERIES(サーベルシリーズ）。 ビッグレイクのフィネスパターン攻略に主眼を置き、ネコリグを中心としたライトリグ全般をこなせるパワー系フィネスロッド。6.3ftのレングスは操作性とパワーを両立。シェイクをしやすいテーパー設定を採用。グリップデザインはサーベルシリーズ専用設計。 異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビッグフィッシュでも逃さない粘りを実現。Lightning『タフコンディションを切り裂く剣』</t>
         </is>
       </c>
-      <c r="AQ18" s="19" t="inlineStr"/>
-      <c r="AR18" s="19" t="inlineStr"/>
+      <c r="AQ18" s="53" t="inlineStr"/>
+      <c r="AR18" s="53" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="53" t="inlineStr">
         <is>
           <t>DSRD10017</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="53" t="inlineStr">
         <is>
           <t>DSR1002</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="53" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="53" t="inlineStr">
         <is>
           <t>DBTS-SS-68L</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="53" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="53" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr"/>
-      <c r="I19" s="19" t="inlineStr"/>
-      <c r="J19" s="19" t="inlineStr">
+      <c r="H19" s="53" t="inlineStr"/>
+      <c r="I19" s="53" t="inlineStr"/>
+      <c r="J19" s="53" t="inlineStr">
         <is>
           <t>93g</t>
         </is>
       </c>
-      <c r="K19" s="19" t="inlineStr"/>
-      <c r="L19" s="19" t="inlineStr"/>
-      <c r="M19" s="19" t="inlineStr">
+      <c r="K19" s="53" t="inlineStr"/>
+      <c r="L19" s="53" t="inlineStr"/>
+      <c r="M19" s="53" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N19" s="19" t="inlineStr">
+      <c r="N19" s="53" t="inlineStr">
         <is>
           <t>0.4~0.8</t>
         </is>
       </c>
-      <c r="O19" s="19" t="inlineStr"/>
-      <c r="P19" s="19" t="inlineStr"/>
-      <c r="Q19" s="19" t="inlineStr"/>
-      <c r="R19" s="19" t="inlineStr">
+      <c r="O19" s="53" t="inlineStr"/>
+      <c r="P19" s="53" t="inlineStr"/>
+      <c r="Q19" s="53" t="inlineStr"/>
+      <c r="R19" s="53" t="inlineStr">
         <is>
           <t>¥28,500 （税込み¥31,350）</t>
         </is>
       </c>
-      <c r="S19" s="19" t="inlineStr">
+      <c r="S19" s="53" t="inlineStr">
         <is>
           <t>4571527862762</t>
         </is>
       </c>
-      <c r="T19" s="19" t="inlineStr"/>
-      <c r="U19" s="19" t="inlineStr"/>
-      <c r="V19" s="19" t="inlineStr"/>
-      <c r="W19" s="19" t="inlineStr"/>
-      <c r="X19" s="19" t="inlineStr"/>
-      <c r="Y19" s="19" t="inlineStr"/>
-      <c r="Z19" s="19" t="inlineStr">
+      <c r="T19" s="53" t="inlineStr"/>
+      <c r="U19" s="53" t="inlineStr"/>
+      <c r="V19" s="53" t="inlineStr"/>
+      <c r="W19" s="53" t="inlineStr"/>
+      <c r="X19" s="53" t="inlineStr"/>
+      <c r="Y19" s="53" t="inlineStr"/>
+      <c r="Z19" s="53" t="inlineStr">
         <is>
           <t>1/32~1/4</t>
         </is>
       </c>
-      <c r="AA19" s="19" t="inlineStr"/>
-      <c r="AB19" s="19" t="inlineStr"/>
-      <c r="AC19" s="19" t="inlineStr">
+      <c r="AA19" s="53" t="inlineStr"/>
+      <c r="AB19" s="53" t="inlineStr"/>
+      <c r="AC19" s="53" t="inlineStr">
         <is>
           <t>BM1</t>
         </is>
       </c>
-      <c r="AD19" s="19" t="inlineStr"/>
-      <c r="AE19" s="19" t="inlineStr"/>
-      <c r="AF19" s="19" t="inlineStr"/>
-      <c r="AG19" s="19" t="inlineStr"/>
-      <c r="AH19" s="19" t="inlineStr">
+      <c r="AD19" s="53" t="inlineStr"/>
+      <c r="AE19" s="53" t="inlineStr"/>
+      <c r="AF19" s="53" t="inlineStr"/>
+      <c r="AG19" s="53" t="inlineStr"/>
+      <c r="AH19" s="53" t="inlineStr">
         <is>
           <t>BM1 的主轴是 long-cast mid-strolling，6'8 长度和较粗 fluorocarbon/PE 导环设定服务于远投控线；Down Shot、No Sinker 只是 light-rig 侧向扩展。</t>
         </is>
       </c>
-      <c r="AI19" s="19" t="inlineStr">
+      <c r="AI19" s="53" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Long Cast Down Shot / No Sinker / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ19" s="19" t="inlineStr"/>
-      <c r="AK19" s="19" t="inlineStr"/>
-      <c r="AL19" s="19" t="inlineStr"/>
-      <c r="AM19" s="19" t="inlineStr">
+      <c r="AJ19" s="53" t="inlineStr"/>
+      <c r="AK19" s="53" t="inlineStr"/>
+      <c r="AL19" s="53" t="inlineStr"/>
+      <c r="AM19" s="53" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖库・远投开阔水 / long-cast mid strolling</t>
         </is>
       </c>
-      <c r="AN19" s="19" t="inlineStr">
+      <c r="AN19" s="53" t="inlineStr">
         <is>
           <t>远投中层游动 spinning</t>
         </is>
       </c>
-      <c r="AO19" s="19" t="inlineStr">
+      <c r="AO19" s="53" t="inlineStr">
         <is>
           <t>6'8 长度适合把 Jighead Mid Strolling 和 Long Cast Down Shot 送远，PE 或较粗 fluorocarbon 下仍能维持线弧。</t>
         </is>
       </c>
-      <c r="AP19" s="19" t="inlineStr">
+      <c r="AP19" s="53" t="inlineStr">
         <is>
           <t>BM1 BLUE TREKから生まれた個性派SABER SERIES(サーベルシリーズ） ミッドストローリングのロングキャストシューティングを主眼に置き、ライトリグ全般をこなせるロッド。6.8ftのレングスはキャスト性能と操作性を両立。ガイドセッティングは太めのフロロカーボンラインやPEを想定したセッティング。グリップデザインはサーベルシリーズ専用設計。 異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビックフィッシュでも逃さない粘りを実現。BM1『琵琶湖を制するミドストロッド』 https://youtu.be/KUaGHkQiQJY</t>
         </is>
       </c>
-      <c r="AQ19" s="19" t="inlineStr"/>
-      <c r="AR19" s="19" t="inlineStr"/>
+      <c r="AQ19" s="53" t="inlineStr"/>
+      <c r="AR19" s="53" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="53" t="inlineStr">
         <is>
           <t>DSRD10018</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="53" t="inlineStr">
         <is>
           <t>DSR1002</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="53" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="53" t="inlineStr">
         <is>
           <t>DBTC-SS-64MH</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="53" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="53" t="inlineStr">
         <is>
           <t>6’4″</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="53" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr"/>
-      <c r="I20" s="19" t="inlineStr"/>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="H20" s="53" t="inlineStr"/>
+      <c r="I20" s="53" t="inlineStr"/>
+      <c r="J20" s="53" t="inlineStr">
         <is>
           <t>108g</t>
         </is>
       </c>
-      <c r="K20" s="19" t="inlineStr"/>
-      <c r="L20" s="19" t="inlineStr"/>
-      <c r="M20" s="19" t="inlineStr">
+      <c r="K20" s="53" t="inlineStr"/>
+      <c r="L20" s="53" t="inlineStr"/>
+      <c r="M20" s="53" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N20" s="19" t="inlineStr"/>
-      <c r="O20" s="19" t="inlineStr"/>
-      <c r="P20" s="19" t="inlineStr"/>
-      <c r="Q20" s="19" t="inlineStr"/>
-      <c r="R20" s="19" t="inlineStr">
+      <c r="N20" s="53" t="inlineStr"/>
+      <c r="O20" s="53" t="inlineStr"/>
+      <c r="P20" s="53" t="inlineStr"/>
+      <c r="Q20" s="53" t="inlineStr"/>
+      <c r="R20" s="53" t="inlineStr">
         <is>
           <t>¥29,500 （税込み¥32,450）</t>
         </is>
       </c>
-      <c r="S20" s="19" t="inlineStr">
+      <c r="S20" s="53" t="inlineStr">
         <is>
           <t>4571527862779</t>
         </is>
       </c>
-      <c r="T20" s="19" t="inlineStr"/>
-      <c r="U20" s="19" t="inlineStr"/>
-      <c r="V20" s="19" t="inlineStr"/>
-      <c r="W20" s="19" t="inlineStr"/>
-      <c r="X20" s="19" t="inlineStr"/>
-      <c r="Y20" s="19" t="inlineStr"/>
-      <c r="Z20" s="19" t="inlineStr">
+      <c r="T20" s="53" t="inlineStr"/>
+      <c r="U20" s="53" t="inlineStr"/>
+      <c r="V20" s="53" t="inlineStr"/>
+      <c r="W20" s="53" t="inlineStr"/>
+      <c r="X20" s="53" t="inlineStr"/>
+      <c r="Y20" s="53" t="inlineStr"/>
+      <c r="Z20" s="53" t="inlineStr">
         <is>
           <t>3/16~3/4</t>
         </is>
       </c>
-      <c r="AA20" s="19" t="inlineStr"/>
-      <c r="AB20" s="19" t="inlineStr"/>
-      <c r="AC20" s="19" t="inlineStr">
+      <c r="AA20" s="53" t="inlineStr"/>
+      <c r="AB20" s="53" t="inlineStr"/>
+      <c r="AC20" s="53" t="inlineStr">
         <is>
           <t>Dagger</t>
         </is>
       </c>
-      <c r="AD20" s="19" t="inlineStr"/>
-      <c r="AE20" s="19" t="inlineStr"/>
-      <c r="AF20" s="19" t="inlineStr"/>
-      <c r="AG20" s="19" t="inlineStr"/>
-      <c r="AH20" s="19" t="inlineStr">
+      <c r="AD20" s="53" t="inlineStr"/>
+      <c r="AE20" s="53" t="inlineStr"/>
+      <c r="AF20" s="53" t="inlineStr"/>
+      <c r="AG20" s="53" t="inlineStr"/>
+      <c r="AH20" s="53" t="inlineStr">
         <is>
           <t>Dagger 明确为高比重 worm no-sinker jerking 设计，6'4 长度便于连续 jerk 和控姿；Texas、Free Rig 只是同等重量软饵的补充用法。</t>
         </is>
       </c>
-      <c r="AI20" s="19" t="inlineStr">
+      <c r="AI20" s="53" t="inlineStr">
         <is>
           <t>High-density No Sinker / Jerk Worm / Texas Rig / Free Rig</t>
         </is>
       </c>
-      <c r="AJ20" s="19" t="inlineStr"/>
-      <c r="AK20" s="19" t="inlineStr"/>
-      <c r="AL20" s="19" t="inlineStr"/>
-      <c r="AM20" s="19" t="inlineStr">
+      <c r="AJ20" s="53" t="inlineStr"/>
+      <c r="AK20" s="53" t="inlineStr"/>
+      <c r="AL20" s="53" t="inlineStr"/>
+      <c r="AM20" s="53" t="inlineStr">
         <is>
           <t>淡水 Bass / 浅草边・开口区 / 高比重 worm jerk</t>
         </is>
       </c>
-      <c r="AN20" s="19" t="inlineStr">
+      <c r="AN20" s="53" t="inlineStr">
         <is>
           <t>高比重无铅 jerking 专向</t>
         </is>
       </c>
-      <c r="AO20" s="19" t="inlineStr">
+      <c r="AO20" s="53" t="inlineStr">
         <is>
           <t>短尺 MH 让 High-density No Sinker 和 Jerk Worm 更好做连续抽停，Texas、Free Rig 可作为同重量软饵替代。</t>
         </is>
       </c>
-      <c r="AP20" s="19" t="inlineStr">
+      <c r="AP20" s="53" t="inlineStr">
         <is>
           <t>Dagger BLUE TREKから生まれた個性派SABER SERIES(サーベルシリーズ） 近年流行のノーシンカー高比重ワームのジャーキングメソッドを主眼に置いたモデル。ジャーク時のアクションを考えレングスを6.4ftにする事でジャークのし易さ向上と共に操作性もUP。ブランクはしなやかに曲がりつつもバットはしっかりとビッグバスに耐えれるタフ仕様。グリップデザインはサーベルシリーズ専用設計。異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビックフィッシュでも逃さない粘りを実現。Dagger『バスを脅かす短剣』 https://youtu.be/MVP9z1qGTFE</t>
         </is>
       </c>
-      <c r="AQ20" s="19" t="inlineStr"/>
-      <c r="AR20" s="19" t="inlineStr"/>
+      <c r="AQ20" s="53" t="inlineStr"/>
+      <c r="AR20" s="53" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="53" t="inlineStr">
         <is>
           <t>DSRD10019</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="53" t="inlineStr">
         <is>
           <t>DSR1002</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="53" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>DBTC-SS-69MH+</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="53" t="inlineStr">
         <is>
           <t>MH+</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="53" t="inlineStr">
         <is>
           <t>6’9″</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="53" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr"/>
-      <c r="I21" s="19" t="inlineStr"/>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="H21" s="53" t="inlineStr"/>
+      <c r="I21" s="53" t="inlineStr"/>
+      <c r="J21" s="53" t="inlineStr">
         <is>
           <t>131g</t>
         </is>
       </c>
-      <c r="K21" s="19" t="inlineStr"/>
-      <c r="L21" s="19" t="inlineStr"/>
-      <c r="M21" s="19" t="inlineStr">
+      <c r="K21" s="53" t="inlineStr"/>
+      <c r="L21" s="53" t="inlineStr"/>
+      <c r="M21" s="53" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N21" s="19" t="inlineStr"/>
-      <c r="O21" s="19" t="inlineStr"/>
-      <c r="P21" s="19" t="inlineStr"/>
-      <c r="Q21" s="19" t="inlineStr"/>
-      <c r="R21" s="19" t="inlineStr">
+      <c r="N21" s="53" t="inlineStr"/>
+      <c r="O21" s="53" t="inlineStr"/>
+      <c r="P21" s="53" t="inlineStr"/>
+      <c r="Q21" s="53" t="inlineStr"/>
+      <c r="R21" s="53" t="inlineStr">
         <is>
           <t>¥29,500 （税込み¥32,450）</t>
         </is>
       </c>
-      <c r="S21" s="19" t="inlineStr">
+      <c r="S21" s="53" t="inlineStr">
         <is>
           <t>4571527863561</t>
         </is>
       </c>
-      <c r="T21" s="19" t="inlineStr"/>
-      <c r="U21" s="19" t="inlineStr"/>
-      <c r="V21" s="19" t="inlineStr"/>
-      <c r="W21" s="19" t="inlineStr"/>
-      <c r="X21" s="19" t="inlineStr"/>
-      <c r="Y21" s="19" t="inlineStr"/>
-      <c r="Z21" s="19" t="inlineStr">
+      <c r="T21" s="53" t="inlineStr"/>
+      <c r="U21" s="53" t="inlineStr"/>
+      <c r="V21" s="53" t="inlineStr"/>
+      <c r="W21" s="53" t="inlineStr"/>
+      <c r="X21" s="53" t="inlineStr"/>
+      <c r="Y21" s="53" t="inlineStr"/>
+      <c r="Z21" s="53" t="inlineStr">
         <is>
           <t>3/16~3/4</t>
         </is>
       </c>
-      <c r="AA21" s="19" t="inlineStr"/>
-      <c r="AB21" s="19" t="inlineStr"/>
-      <c r="AC21" s="19" t="inlineStr">
+      <c r="AA21" s="53" t="inlineStr"/>
+      <c r="AB21" s="53" t="inlineStr"/>
+      <c r="AC21" s="53" t="inlineStr">
         <is>
           <t>Saber versatile SP</t>
         </is>
       </c>
-      <c r="AD21" s="19" t="inlineStr"/>
-      <c r="AE21" s="19" t="inlineStr"/>
-      <c r="AF21" s="19" t="inlineStr"/>
-      <c r="AG21" s="19" t="inlineStr"/>
-      <c r="AH21" s="19" t="inlineStr">
+      <c r="AD21" s="53" t="inlineStr"/>
+      <c r="AE21" s="53" t="inlineStr"/>
+      <c r="AF21" s="53" t="inlineStr"/>
+      <c r="AG21" s="53" t="inlineStr"/>
+      <c r="AH21" s="53" t="inlineStr">
         <is>
           <t>Saber versatile SP 是琵琶湖向 power versatile，先覆盖 worm 系 rig，再扩展到 wire bait、Chatterbait、Swimbait 和 Big Bait；不是单纯 heavy bottom 竿。</t>
         </is>
       </c>
-      <c r="AI21" s="19" t="inlineStr">
+      <c r="AI21" s="53" t="inlineStr">
         <is>
           <t>Texas Rig / Free Rig / No Sinker / Spinnerbait / Chatterbait / Swimbait / Big Bait</t>
         </is>
       </c>
-      <c r="AJ21" s="19" t="inlineStr"/>
-      <c r="AK21" s="19" t="inlineStr"/>
-      <c r="AL21" s="19" t="inlineStr"/>
-      <c r="AM21" s="19" t="inlineStr">
+      <c r="AJ21" s="53" t="inlineStr"/>
+      <c r="AK21" s="53" t="inlineStr"/>
+      <c r="AL21" s="53" t="inlineStr"/>
+      <c r="AM21" s="53" t="inlineStr">
         <is>
           <t>淡水 Bass / 琵琶湖型大型湖・草区边缘 / power versatile</t>
         </is>
       </c>
-      <c r="AN21" s="19" t="inlineStr">
+      <c r="AN21" s="53" t="inlineStr">
         <is>
           <t>强力软硬饵泛用</t>
         </is>
       </c>
-      <c r="AO21" s="19" t="inlineStr">
+      <c r="AO21" s="53" t="inlineStr">
         <is>
           <t>Texas、Free Rig 和 No Sinker 可打点，Spinnerbait、Chatterbait、Swimbait 和 Big Bait 可搜索，适合大水面重线组切换。</t>
         </is>
       </c>
-      <c r="AP21" s="19" t="inlineStr">
+      <c r="AP21" s="53" t="inlineStr">
         <is>
           <t>Saber versatile SP BLUE TREKから生まれた個性派SABER SERIES(サーベルシリーズ）。 あらゆるワーム系リグを全般にワイヤーベイト、ビッグベイトやスイムベイトまで幅広く対応するパワー系バーサタイルモデル。ブランクスはトルク重視のＭＨアクションを更にパワーをプラス。 グリップデザインはサーベルシリーズ専用設計。異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビッグフィッシュでも逃さない粘りを実現。Saber versatile SP『琵琶湖に求められたバーサタイルロッド』</t>
         </is>
       </c>
-      <c r="AQ21" s="19" t="inlineStr"/>
-      <c r="AR21" s="19" t="inlineStr"/>
+      <c r="AQ21" s="53" t="inlineStr"/>
+      <c r="AR21" s="53" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>DSRD10020</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="52" t="inlineStr">
         <is>
           <t>DBTS-612UL+-S</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="52" t="inlineStr">
         <is>
           <t>UL+</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="52" t="inlineStr">
         <is>
           <t>6’1″</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr"/>
-      <c r="I22" s="22" t="inlineStr"/>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="H22" s="52" t="inlineStr"/>
+      <c r="I22" s="52" t="inlineStr"/>
+      <c r="J22" s="52" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K22" s="22" t="inlineStr"/>
-      <c r="L22" s="22" t="inlineStr"/>
-      <c r="M22" s="22" t="inlineStr">
+      <c r="K22" s="52" t="inlineStr"/>
+      <c r="L22" s="52" t="inlineStr"/>
+      <c r="M22" s="52" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N22" s="22" t="inlineStr"/>
-      <c r="O22" s="22" t="inlineStr"/>
-      <c r="P22" s="22" t="inlineStr"/>
-      <c r="Q22" s="22" t="inlineStr"/>
-      <c r="R22" s="22" t="inlineStr">
+      <c r="N22" s="52" t="inlineStr"/>
+      <c r="O22" s="52" t="inlineStr"/>
+      <c r="P22" s="52" t="inlineStr"/>
+      <c r="Q22" s="52" t="inlineStr"/>
+      <c r="R22" s="52" t="inlineStr">
         <is>
           <t>¥28,000 （税込み¥30,800）</t>
         </is>
       </c>
-      <c r="S22" s="22" t="inlineStr">
+      <c r="S22" s="52" t="inlineStr">
         <is>
           <t>4571527862540</t>
         </is>
       </c>
-      <c r="T22" s="22" t="inlineStr"/>
-      <c r="U22" s="22" t="inlineStr"/>
-      <c r="V22" s="22" t="inlineStr"/>
-      <c r="W22" s="22" t="inlineStr"/>
-      <c r="X22" s="22" t="inlineStr"/>
-      <c r="Y22" s="22" t="inlineStr"/>
-      <c r="Z22" s="22" t="inlineStr">
+      <c r="T22" s="52" t="inlineStr"/>
+      <c r="U22" s="52" t="inlineStr"/>
+      <c r="V22" s="52" t="inlineStr"/>
+      <c r="W22" s="52" t="inlineStr"/>
+      <c r="X22" s="52" t="inlineStr"/>
+      <c r="Y22" s="52" t="inlineStr"/>
+      <c r="Z22" s="52" t="inlineStr">
         <is>
           <t>1/32~3/16</t>
         </is>
       </c>
-      <c r="AA22" s="22" t="inlineStr"/>
-      <c r="AB22" s="22" t="inlineStr"/>
-      <c r="AC22" s="22" t="inlineStr"/>
-      <c r="AD22" s="22" t="inlineStr"/>
-      <c r="AE22" s="22" t="inlineStr"/>
-      <c r="AF22" s="22" t="inlineStr"/>
-      <c r="AG22" s="22" t="inlineStr"/>
-      <c r="AH22" s="22" t="inlineStr">
+      <c r="AA22" s="52" t="inlineStr"/>
+      <c r="AB22" s="52" t="inlineStr"/>
+      <c r="AC22" s="52" t="inlineStr"/>
+      <c r="AD22" s="52" t="inlineStr"/>
+      <c r="AE22" s="52" t="inlineStr"/>
+      <c r="AF22" s="52" t="inlineStr"/>
+      <c r="AG22" s="52" t="inlineStr"/>
+      <c r="AH22" s="52" t="inlineStr">
         <is>
           <t>2-piece 612UL+-S 是更轻量的 super finesse，solid tip 让 No Sinker、Down Shot、Neko、Jighead、Small Rubber Jig 与 Hover Strolling 的轻咬更容易吃住。</t>
         </is>
       </c>
-      <c r="AI22" s="22" t="inlineStr">
+      <c r="AI22" s="52" t="inlineStr">
         <is>
           <t>No Sinker / Down Shot / Neko Rig / Jighead Rig / Small Rubber Jig / Hover Strolling</t>
         </is>
       </c>
-      <c r="AJ22" s="22" t="inlineStr"/>
-      <c r="AK22" s="22" t="inlineStr"/>
-      <c r="AL22" s="22" t="inlineStr"/>
-      <c r="AM22" s="22" t="inlineStr">
+      <c r="AJ22" s="52" t="inlineStr"/>
+      <c r="AK22" s="52" t="inlineStr"/>
+      <c r="AL22" s="52" t="inlineStr"/>
+      <c r="AM22" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压岸边・小型湖库 / 2pc super finesse</t>
         </is>
       </c>
-      <c r="AN22" s="22" t="inlineStr">
+      <c r="AN22" s="52" t="inlineStr">
         <is>
           <t>便携超精细 spinning</t>
         </is>
       </c>
-      <c r="AO22" s="22" t="inlineStr">
+      <c r="AO22" s="52" t="inlineStr">
         <is>
           <t>No Sinker、Down Shot、Neko、Jighead 和 Hover Strolling 都能细致操作，2pc 适合移动频繁但仍要保持轻饵手感的玩家。</t>
         </is>
       </c>
-      <c r="AP22" s="22" t="inlineStr">
+      <c r="AP22" s="52" t="inlineStr">
         <is>
           <t>時を捉える事が出来る進化したスーパーフィネスモデル DBTS-61Lをベースに、より軽量ルアーを扱えるようチューンニングしたモデル。 ソリッドティップを搭載する事でより軽量ルアーを繊細に扱えるようになり、ショートバイトでもバスを逃しません。ノーシンカー、ダウンショット、ネコリグ、ジグヘッド、スモラバ、ホバストまで幅広く対応。ナノマテリアル配合のBLUE TREKブランクスによりバットパワーでバスを浮かせ主導権を与えません。日々変化するフィールドの時を捉える事が出来る進化した攻撃的フィネスロッドに仕上げました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ22" s="22" t="inlineStr"/>
-      <c r="AR22" s="22" t="inlineStr"/>
+      <c r="AQ22" s="52" t="inlineStr"/>
+      <c r="AR22" s="52" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>DSRD10021</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="52" t="inlineStr">
         <is>
           <t>DBTS-632UL/L-S</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="52" t="inlineStr">
         <is>
           <t>UL/L</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="52" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr"/>
-      <c r="I23" s="22" t="inlineStr"/>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="H23" s="52" t="inlineStr"/>
+      <c r="I23" s="52" t="inlineStr"/>
+      <c r="J23" s="52" t="inlineStr">
         <is>
           <t>81g</t>
         </is>
       </c>
-      <c r="K23" s="22" t="inlineStr"/>
-      <c r="L23" s="22" t="inlineStr"/>
-      <c r="M23" s="22" t="inlineStr">
+      <c r="K23" s="52" t="inlineStr"/>
+      <c r="L23" s="52" t="inlineStr"/>
+      <c r="M23" s="52" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N23" s="22" t="inlineStr">
+      <c r="N23" s="52" t="inlineStr">
         <is>
           <t>0.4~1</t>
         </is>
       </c>
-      <c r="O23" s="22" t="inlineStr"/>
-      <c r="P23" s="22" t="inlineStr"/>
-      <c r="Q23" s="22" t="inlineStr"/>
-      <c r="R23" s="22" t="inlineStr">
+      <c r="O23" s="52" t="inlineStr"/>
+      <c r="P23" s="52" t="inlineStr"/>
+      <c r="Q23" s="52" t="inlineStr"/>
+      <c r="R23" s="52" t="inlineStr">
         <is>
           <t>¥28,000 （税込み¥30,800）</t>
         </is>
       </c>
-      <c r="S23" s="22" t="inlineStr">
+      <c r="S23" s="52" t="inlineStr">
         <is>
           <t>4571527863752</t>
         </is>
       </c>
-      <c r="T23" s="22" t="inlineStr"/>
-      <c r="U23" s="22" t="inlineStr"/>
-      <c r="V23" s="22" t="inlineStr"/>
-      <c r="W23" s="22" t="inlineStr"/>
-      <c r="X23" s="22" t="inlineStr"/>
-      <c r="Y23" s="22" t="inlineStr"/>
-      <c r="Z23" s="22" t="inlineStr">
+      <c r="T23" s="52" t="inlineStr"/>
+      <c r="U23" s="52" t="inlineStr"/>
+      <c r="V23" s="52" t="inlineStr"/>
+      <c r="W23" s="52" t="inlineStr"/>
+      <c r="X23" s="52" t="inlineStr"/>
+      <c r="Y23" s="52" t="inlineStr"/>
+      <c r="Z23" s="52" t="inlineStr">
         <is>
           <t>1/32~1/4</t>
         </is>
       </c>
-      <c r="AA23" s="22" t="inlineStr"/>
-      <c r="AB23" s="22" t="inlineStr"/>
-      <c r="AC23" s="22" t="inlineStr"/>
-      <c r="AD23" s="22" t="inlineStr"/>
-      <c r="AE23" s="22" t="inlineStr"/>
-      <c r="AF23" s="22" t="inlineStr"/>
-      <c r="AG23" s="22" t="inlineStr"/>
-      <c r="AH23" s="22" t="inlineStr">
+      <c r="AA23" s="52" t="inlineStr"/>
+      <c r="AB23" s="52" t="inlineStr"/>
+      <c r="AC23" s="52" t="inlineStr"/>
+      <c r="AD23" s="52" t="inlineStr"/>
+      <c r="AE23" s="52" t="inlineStr"/>
+      <c r="AF23" s="52" t="inlineStr"/>
+      <c r="AG23" s="52" t="inlineStr"/>
+      <c r="AH23" s="52" t="inlineStr">
         <is>
           <t>632UL/L-S 用 UL tip 搭配 L butt，官网明确覆盖 No Sinker、Down Shot、Neko、Jighead、Small Rubber Jig、Hover Strolling 与 Elastomer；适合食わせ和控鱼并重。</t>
         </is>
       </c>
-      <c r="AI23" s="22" t="inlineStr">
+      <c r="AI23" s="52" t="inlineStr">
         <is>
           <t>No Sinker / Down Shot / Neko Rig / Jighead Rig / Small Rubber Jig / Hover Strolling / Elastomer Softbait</t>
         </is>
       </c>
-      <c r="AJ23" s="22" t="inlineStr"/>
-      <c r="AK23" s="22" t="inlineStr"/>
-      <c r="AL23" s="22" t="inlineStr"/>
-      <c r="AM23" s="22" t="inlineStr">
+      <c r="AJ23" s="52" t="inlineStr"/>
+      <c r="AK23" s="52" t="inlineStr"/>
+      <c r="AL23" s="52" t="inlineStr"/>
+      <c r="AM23" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压开放水・轻 cover 边 / all-round finesse</t>
         </is>
       </c>
-      <c r="AN23" s="22" t="inlineStr">
+      <c r="AN23" s="52" t="inlineStr">
         <is>
           <t>食わせ与控鱼兼顾 finesse</t>
         </is>
       </c>
-      <c r="AO23" s="22" t="inlineStr">
+      <c r="AO23" s="52" t="inlineStr">
         <is>
           <t>UL tip 负责轻咬承接，L butt 负责控鱼；No Sinker、Down Shot、Small Rubber Jig、Hover 和 Elastomer 都能覆盖。</t>
         </is>
       </c>
-      <c r="AP23" s="22" t="inlineStr">
+      <c r="AP23" s="52" t="inlineStr">
         <is>
           <t>オールマイティーフィネスモデル ULパワーのソリッドティップでバイトを乗せ、Lパワーのバットで魚を制する。食わせとパワーを両立させたオールマイティーフィネスモデル。 ガイドセッティングは近年のPEラインでの使用も考慮したDSTYLEオリジナルセッティング。 ノーシンカー、ダウンショット、ネコリグ、ジグヘッド、スモラバ、ホバスト、エラストマールアーまで幅広く対応。ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビッグフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ23" s="22" t="inlineStr"/>
-      <c r="AR23" s="22" t="inlineStr"/>
+      <c r="AQ23" s="52" t="inlineStr"/>
+      <c r="AR23" s="52" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="52" t="inlineStr">
         <is>
           <t>DSRD10022</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="52" t="inlineStr">
         <is>
           <t>DBTS-642UL+-MIDSP</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="52" t="inlineStr">
         <is>
           <t>UL+</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="52" t="inlineStr">
         <is>
           <t>6’4″</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr"/>
-      <c r="I24" s="22" t="inlineStr"/>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="H24" s="52" t="inlineStr"/>
+      <c r="I24" s="52" t="inlineStr"/>
+      <c r="J24" s="52" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K24" s="22" t="inlineStr"/>
-      <c r="L24" s="22" t="inlineStr"/>
-      <c r="M24" s="22" t="inlineStr">
+      <c r="K24" s="52" t="inlineStr"/>
+      <c r="L24" s="52" t="inlineStr"/>
+      <c r="M24" s="52" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N24" s="22" t="inlineStr"/>
-      <c r="O24" s="22" t="inlineStr"/>
-      <c r="P24" s="22" t="inlineStr"/>
-      <c r="Q24" s="22" t="inlineStr"/>
-      <c r="R24" s="22" t="inlineStr">
+      <c r="N24" s="52" t="inlineStr"/>
+      <c r="O24" s="52" t="inlineStr"/>
+      <c r="P24" s="52" t="inlineStr"/>
+      <c r="Q24" s="52" t="inlineStr"/>
+      <c r="R24" s="52" t="inlineStr">
         <is>
           <t>¥28,000 （税込み¥30,800）</t>
         </is>
       </c>
-      <c r="S24" s="22" t="inlineStr">
+      <c r="S24" s="52" t="inlineStr">
         <is>
           <t>4571527863745</t>
         </is>
       </c>
-      <c r="T24" s="22" t="inlineStr"/>
-      <c r="U24" s="22" t="inlineStr"/>
-      <c r="V24" s="22" t="inlineStr"/>
-      <c r="W24" s="22" t="inlineStr"/>
-      <c r="X24" s="22" t="inlineStr"/>
-      <c r="Y24" s="22" t="inlineStr"/>
-      <c r="Z24" s="22" t="inlineStr">
+      <c r="T24" s="52" t="inlineStr"/>
+      <c r="U24" s="52" t="inlineStr"/>
+      <c r="V24" s="52" t="inlineStr"/>
+      <c r="W24" s="52" t="inlineStr"/>
+      <c r="X24" s="52" t="inlineStr"/>
+      <c r="Y24" s="52" t="inlineStr"/>
+      <c r="Z24" s="52" t="inlineStr">
         <is>
           <t>1/32~3/16</t>
         </is>
       </c>
-      <c r="AA24" s="22" t="inlineStr"/>
-      <c r="AB24" s="22" t="inlineStr"/>
-      <c r="AC24" s="22" t="inlineStr"/>
-      <c r="AD24" s="22" t="inlineStr"/>
-      <c r="AE24" s="22" t="inlineStr"/>
-      <c r="AF24" s="22" t="inlineStr"/>
-      <c r="AG24" s="22" t="inlineStr"/>
-      <c r="AH24" s="22" t="inlineStr">
+      <c r="AA24" s="52" t="inlineStr"/>
+      <c r="AB24" s="52" t="inlineStr"/>
+      <c r="AC24" s="52" t="inlineStr"/>
+      <c r="AD24" s="52" t="inlineStr"/>
+      <c r="AE24" s="52" t="inlineStr"/>
+      <c r="AF24" s="52" t="inlineStr"/>
+      <c r="AG24" s="52" t="inlineStr"/>
+      <c r="AH24" s="52" t="inlineStr">
         <is>
           <t>642UL+-MIDSP 是 mid-strolling 专门项，Jighead 与 Down Shot 的 shake 线弧是核心；Bottom Strolling 是同一调性下的底层游动延伸。</t>
         </is>
       </c>
-      <c r="AI24" s="22" t="inlineStr">
+      <c r="AI24" s="52" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Bottom Strolling / Down Shot / Jighead Rig</t>
         </is>
       </c>
-      <c r="AJ24" s="22" t="inlineStr"/>
-      <c r="AK24" s="22" t="inlineStr"/>
-      <c r="AL24" s="22" t="inlineStr"/>
-      <c r="AM24" s="22" t="inlineStr">
+      <c r="AJ24" s="52" t="inlineStr"/>
+      <c r="AK24" s="52" t="inlineStr"/>
+      <c r="AL24" s="52" t="inlineStr"/>
+      <c r="AM24" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水・缓坡・中层鱼 / 2pc mid strolling</t>
         </is>
       </c>
-      <c r="AN24" s="22" t="inlineStr">
+      <c r="AN24" s="52" t="inlineStr">
         <is>
           <t>便携 mid/bottom strolling 专向</t>
         </is>
       </c>
-      <c r="AO24" s="22" t="inlineStr">
+      <c r="AO24" s="52" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead 和 Bottom Strolling 的节奏更明确，Down Shot 也能按中层或贴底游动思路使用。</t>
         </is>
       </c>
-      <c r="AP24" s="22" t="inlineStr">
+      <c r="AP24" s="52" t="inlineStr">
         <is>
           <t>無双できるミッドストローリングロッド 近年欠かすこと出来ないテクニックの一つミッドストローリング、通称ミドスト。ラインスラッグを出しながらジグヘッドやダウンショットをシェイクしやすいテーパーとガイドセッティングを追求することで、よりミドスト、ボトストの操作性能を高めました。レングスやロッドパワーは２pc専用設計。「ミドストが苦手な方の突破口」になり得る1本。 ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビッグフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ24" s="22" t="inlineStr"/>
-      <c r="AR24" s="22" t="inlineStr"/>
+      <c r="AQ24" s="52" t="inlineStr"/>
+      <c r="AR24" s="52" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>DSRD10023</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="52" t="inlineStr">
         <is>
           <t>DBTS-662L</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="52" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="52" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr"/>
-      <c r="I25" s="22" t="inlineStr"/>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="H25" s="52" t="inlineStr"/>
+      <c r="I25" s="52" t="inlineStr"/>
+      <c r="J25" s="52" t="inlineStr">
         <is>
           <t>86g</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr"/>
-      <c r="L25" s="22" t="inlineStr"/>
-      <c r="M25" s="22" t="inlineStr">
+      <c r="K25" s="52" t="inlineStr"/>
+      <c r="L25" s="52" t="inlineStr"/>
+      <c r="M25" s="52" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N25" s="22" t="inlineStr"/>
-      <c r="O25" s="22" t="inlineStr"/>
-      <c r="P25" s="22" t="inlineStr"/>
-      <c r="Q25" s="22" t="inlineStr"/>
-      <c r="R25" s="22" t="inlineStr">
+      <c r="N25" s="52" t="inlineStr"/>
+      <c r="O25" s="52" t="inlineStr"/>
+      <c r="P25" s="52" t="inlineStr"/>
+      <c r="Q25" s="52" t="inlineStr"/>
+      <c r="R25" s="52" t="inlineStr">
         <is>
           <t>¥28,500 （税込み¥31,350）</t>
         </is>
       </c>
-      <c r="S25" s="22" t="inlineStr">
+      <c r="S25" s="52" t="inlineStr">
         <is>
           <t>4571527862557</t>
         </is>
       </c>
-      <c r="T25" s="22" t="inlineStr"/>
-      <c r="U25" s="22" t="inlineStr"/>
-      <c r="V25" s="22" t="inlineStr"/>
-      <c r="W25" s="22" t="inlineStr"/>
-      <c r="X25" s="22" t="inlineStr"/>
-      <c r="Y25" s="22" t="inlineStr"/>
-      <c r="Z25" s="22" t="inlineStr">
+      <c r="T25" s="52" t="inlineStr"/>
+      <c r="U25" s="52" t="inlineStr"/>
+      <c r="V25" s="52" t="inlineStr"/>
+      <c r="W25" s="52" t="inlineStr"/>
+      <c r="X25" s="52" t="inlineStr"/>
+      <c r="Y25" s="52" t="inlineStr"/>
+      <c r="Z25" s="52" t="inlineStr">
         <is>
           <t>1/32~1/4</t>
         </is>
       </c>
-      <c r="AA25" s="22" t="inlineStr"/>
-      <c r="AB25" s="22" t="inlineStr"/>
-      <c r="AC25" s="22" t="inlineStr"/>
-      <c r="AD25" s="22" t="inlineStr"/>
-      <c r="AE25" s="22" t="inlineStr"/>
-      <c r="AF25" s="22" t="inlineStr"/>
-      <c r="AG25" s="22" t="inlineStr"/>
-      <c r="AH25" s="22" t="inlineStr">
+      <c r="AA25" s="52" t="inlineStr"/>
+      <c r="AB25" s="52" t="inlineStr"/>
+      <c r="AC25" s="52" t="inlineStr"/>
+      <c r="AD25" s="52" t="inlineStr"/>
+      <c r="AE25" s="52" t="inlineStr"/>
+      <c r="AF25" s="52" t="inlineStr"/>
+      <c r="AG25" s="52" t="inlineStr"/>
+      <c r="AH25" s="52" t="inlineStr">
         <is>
           <t>662L 是 finesse 到小型 plug 的多用途 spinning，食わせ端以 Neko、Down Shot、No Sinker 为主；远投搜索时更适合 Small Minnow 与 Shad，而不是重 cover。</t>
         </is>
       </c>
-      <c r="AI25" s="22" t="inlineStr">
+      <c r="AI25" s="52" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Minnow / Shad</t>
         </is>
       </c>
-      <c r="AJ25" s="22" t="inlineStr"/>
-      <c r="AK25" s="22" t="inlineStr"/>
-      <c r="AL25" s="22" t="inlineStr"/>
-      <c r="AM25" s="22" t="inlineStr">
+      <c r="AJ25" s="52" t="inlineStr"/>
+      <c r="AK25" s="52" t="inlineStr"/>
+      <c r="AL25" s="52" t="inlineStr"/>
+      <c r="AM25" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓远近切换 / finesse 到小型 Minnow・Shad</t>
         </is>
       </c>
-      <c r="AN25" s="22" t="inlineStr">
+      <c r="AN25" s="52" t="inlineStr">
         <is>
           <t>轻量软饵兼小硬饵</t>
         </is>
       </c>
-      <c r="AO25" s="22" t="inlineStr">
+      <c r="AO25" s="52" t="inlineStr">
         <is>
           <t>Neko、Down Shot、No Sinker 可以食わせ，Small Minnow 和 Shad 能补搜索，适合岸边只带一支 spinning 时拉开距离。</t>
         </is>
       </c>
-      <c r="AP25" s="22" t="inlineStr">
+      <c r="AP25" s="52" t="inlineStr">
         <is>
           <t>マルチバーサタイルモデル 1本でフィネス全般からプラグ系までアングラーの求める要素を詰め込んだマルチバーサタイルモデル 食わせが必要なフィネスアプローチから距離を求められる小型プラグのロングキャストまでセッティング次第で幅広く対応する事が可能。おかっぱりでもボートでも、持ち出せるタックルが限られた条件でこそ活躍する１本。。 ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビックフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ25" s="22" t="inlineStr"/>
-      <c r="AR25" s="22" t="inlineStr"/>
+      <c r="AQ25" s="52" t="inlineStr"/>
+      <c r="AR25" s="52" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="52" t="inlineStr">
         <is>
           <t>DSRD10024</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="52" t="inlineStr">
         <is>
           <t>DBTS-662M</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="52" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="52" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr"/>
-      <c r="I26" s="22" t="inlineStr"/>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="H26" s="52" t="inlineStr"/>
+      <c r="I26" s="52" t="inlineStr"/>
+      <c r="J26" s="52" t="inlineStr">
         <is>
           <t>91g</t>
         </is>
       </c>
-      <c r="K26" s="22" t="inlineStr"/>
-      <c r="L26" s="22" t="inlineStr"/>
-      <c r="M26" s="22" t="inlineStr">
+      <c r="K26" s="52" t="inlineStr"/>
+      <c r="L26" s="52" t="inlineStr"/>
+      <c r="M26" s="52" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N26" s="22" t="inlineStr">
+      <c r="N26" s="52" t="inlineStr">
         <is>
           <t>0.6~1.5</t>
         </is>
       </c>
-      <c r="O26" s="22" t="inlineStr"/>
-      <c r="P26" s="22" t="inlineStr"/>
-      <c r="Q26" s="22" t="inlineStr"/>
-      <c r="R26" s="22" t="inlineStr">
+      <c r="O26" s="52" t="inlineStr"/>
+      <c r="P26" s="52" t="inlineStr"/>
+      <c r="Q26" s="52" t="inlineStr"/>
+      <c r="R26" s="52" t="inlineStr">
         <is>
           <t>¥28,500 （税込み¥31,350）</t>
         </is>
       </c>
-      <c r="S26" s="22" t="inlineStr">
+      <c r="S26" s="52" t="inlineStr">
         <is>
           <t>4571527862564</t>
         </is>
       </c>
-      <c r="T26" s="22" t="inlineStr"/>
-      <c r="U26" s="22" t="inlineStr"/>
-      <c r="V26" s="22" t="inlineStr"/>
-      <c r="W26" s="22" t="inlineStr"/>
-      <c r="X26" s="22" t="inlineStr"/>
-      <c r="Y26" s="22" t="inlineStr"/>
-      <c r="Z26" s="22" t="inlineStr">
+      <c r="T26" s="52" t="inlineStr"/>
+      <c r="U26" s="52" t="inlineStr"/>
+      <c r="V26" s="52" t="inlineStr"/>
+      <c r="W26" s="52" t="inlineStr"/>
+      <c r="X26" s="52" t="inlineStr"/>
+      <c r="Y26" s="52" t="inlineStr"/>
+      <c r="Z26" s="52" t="inlineStr">
         <is>
           <t>1/16~3/8</t>
         </is>
       </c>
-      <c r="AA26" s="22" t="inlineStr"/>
-      <c r="AB26" s="22" t="inlineStr"/>
-      <c r="AC26" s="22" t="inlineStr"/>
-      <c r="AD26" s="22" t="inlineStr"/>
-      <c r="AE26" s="22" t="inlineStr"/>
-      <c r="AF26" s="22" t="inlineStr"/>
-      <c r="AG26" s="22" t="inlineStr"/>
-      <c r="AH26" s="22" t="inlineStr">
+      <c r="AA26" s="52" t="inlineStr"/>
+      <c r="AB26" s="52" t="inlineStr"/>
+      <c r="AC26" s="52" t="inlineStr"/>
+      <c r="AD26" s="52" t="inlineStr"/>
+      <c r="AE26" s="52" t="inlineStr"/>
+      <c r="AF26" s="52" t="inlineStr"/>
+      <c r="AG26" s="52" t="inlineStr"/>
+      <c r="AH26" s="52" t="inlineStr">
         <is>
           <t>662M 是 PE power finesse spinning，重点是 Guarded Small Rubber Jig、Cover Neko 和虫系打浓 cover；big lake 远投 Down Shot/Neko 可用，但不是第一定位。</t>
         </is>
       </c>
-      <c r="AI26" s="22" t="inlineStr">
+      <c r="AI26" s="52" t="inlineStr">
         <is>
           <t>Cover Neko / Guarded Small Rubber Jig / Bug Lure / Power Finesse / Long Cast Down Shot</t>
         </is>
       </c>
-      <c r="AJ26" s="22" t="inlineStr"/>
-      <c r="AK26" s="22" t="inlineStr"/>
-      <c r="AL26" s="22" t="inlineStr"/>
-      <c r="AM26" s="22" t="inlineStr">
+      <c r="AJ26" s="52" t="inlineStr"/>
+      <c r="AK26" s="52" t="inlineStr"/>
+      <c r="AL26" s="52" t="inlineStr"/>
+      <c r="AM26" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 浓 cover・虫系・大型湖 light rig / PE power finesse</t>
         </is>
       </c>
-      <c r="AN26" s="22" t="inlineStr">
+      <c r="AN26" s="52" t="inlineStr">
         <is>
           <t>cover power finesse spinning</t>
         </is>
       </c>
-      <c r="AO26" s="22" t="inlineStr">
+      <c r="AO26" s="52" t="inlineStr">
         <is>
           <t>Cover Neko、Guarded Small Rubber Jig 和 Bug Lure 适合打 cover，Long Cast Down Shot 可作为大型湖远投精细补充。</t>
         </is>
       </c>
-      <c r="AP26" s="22" t="inlineStr">
+      <c r="AP26" s="52" t="inlineStr">
         <is>
           <t>キャスタビリティーとパワーを追求したパワーフィネススピン 近年の釣りで不可欠な存在になっているPEを用いたパワーフィネス。6’6″のレングスにする事でキャスタビリティー性能を重視。食わせの「間」を与える硬すぎないティップアクションとナノマテリアル配合のBLUE TREKブランクスを採用した強靭なバットがバスをカバーから引きはがします。ガード付きのスモラバやカバーネコ、濃いめのカバーを虫系で攻める場合にアドバンテージを与えてくれる仕様。また琵琶湖等のビックレイクでのライトリグにもおススメです。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ26" s="22" t="inlineStr"/>
-      <c r="AR26" s="22" t="inlineStr"/>
+      <c r="AQ26" s="52" t="inlineStr"/>
+      <c r="AR26" s="52" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="52" t="inlineStr">
         <is>
           <t>DSRD10025</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="52" t="inlineStr">
         <is>
           <t>DBTS-6102ML-S</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="52" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="52" t="inlineStr">
         <is>
           <t>6’10″</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr"/>
-      <c r="I27" s="22" t="inlineStr"/>
-      <c r="J27" s="22" t="inlineStr">
+      <c r="H27" s="52" t="inlineStr"/>
+      <c r="I27" s="52" t="inlineStr"/>
+      <c r="J27" s="52" t="inlineStr">
         <is>
           <t>85g</t>
         </is>
       </c>
-      <c r="K27" s="22" t="inlineStr"/>
-      <c r="L27" s="22" t="inlineStr"/>
-      <c r="M27" s="22" t="inlineStr">
+      <c r="K27" s="52" t="inlineStr"/>
+      <c r="L27" s="52" t="inlineStr"/>
+      <c r="M27" s="52" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N27" s="22" t="inlineStr">
+      <c r="N27" s="52" t="inlineStr">
         <is>
           <t>0.4~1</t>
         </is>
       </c>
-      <c r="O27" s="22" t="inlineStr"/>
-      <c r="P27" s="22" t="inlineStr"/>
-      <c r="Q27" s="22" t="inlineStr"/>
-      <c r="R27" s="22" t="inlineStr">
+      <c r="O27" s="52" t="inlineStr"/>
+      <c r="P27" s="52" t="inlineStr"/>
+      <c r="Q27" s="52" t="inlineStr"/>
+      <c r="R27" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込み¥31,900）</t>
         </is>
       </c>
-      <c r="S27" s="22" t="inlineStr">
+      <c r="S27" s="52" t="inlineStr">
         <is>
           <t>4571527862571</t>
         </is>
       </c>
-      <c r="T27" s="22" t="inlineStr"/>
-      <c r="U27" s="22" t="inlineStr"/>
-      <c r="V27" s="22" t="inlineStr"/>
-      <c r="W27" s="22" t="inlineStr"/>
-      <c r="X27" s="22" t="inlineStr"/>
-      <c r="Y27" s="22" t="inlineStr"/>
-      <c r="Z27" s="22" t="inlineStr">
+      <c r="T27" s="52" t="inlineStr"/>
+      <c r="U27" s="52" t="inlineStr"/>
+      <c r="V27" s="52" t="inlineStr"/>
+      <c r="W27" s="52" t="inlineStr"/>
+      <c r="X27" s="52" t="inlineStr"/>
+      <c r="Y27" s="52" t="inlineStr"/>
+      <c r="Z27" s="52" t="inlineStr">
         <is>
           <t>1/16~3/8</t>
         </is>
       </c>
-      <c r="AA27" s="22" t="inlineStr"/>
-      <c r="AB27" s="22" t="inlineStr"/>
-      <c r="AC27" s="22" t="inlineStr"/>
-      <c r="AD27" s="22" t="inlineStr"/>
-      <c r="AE27" s="22" t="inlineStr"/>
-      <c r="AF27" s="22" t="inlineStr"/>
-      <c r="AG27" s="22" t="inlineStr"/>
-      <c r="AH27" s="22" t="inlineStr">
+      <c r="AA27" s="52" t="inlineStr"/>
+      <c r="AB27" s="52" t="inlineStr"/>
+      <c r="AC27" s="52" t="inlineStr"/>
+      <c r="AD27" s="52" t="inlineStr"/>
+      <c r="AE27" s="52" t="inlineStr"/>
+      <c r="AF27" s="52" t="inlineStr"/>
+      <c r="AG27" s="52" t="inlineStr"/>
+      <c r="AH27" s="52" t="inlineStr">
         <is>
           <t>6102ML-S 是 long-shooting special，ML solid tip 和 PE 导环适合把 Down Shot/Neko、I-shaped、虫系和表层 Plug 送远；核心价值是距离下仍保留操作感。</t>
         </is>
       </c>
-      <c r="AI27" s="22" t="inlineStr">
+      <c r="AI27" s="52" t="inlineStr">
         <is>
           <t>Long Cast Down Shot / Neko Rig / I-shaped Plug / Bug Lure / Surface Plug</t>
         </is>
       </c>
-      <c r="AJ27" s="22" t="inlineStr"/>
-      <c r="AK27" s="22" t="inlineStr"/>
-      <c r="AL27" s="22" t="inlineStr"/>
-      <c r="AM27" s="22" t="inlineStr">
+      <c r="AJ27" s="52" t="inlineStr"/>
+      <c r="AK27" s="52" t="inlineStr"/>
+      <c r="AL27" s="52" t="inlineStr"/>
+      <c r="AM27" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓远投・开阔水 / light rig 与表层搜索</t>
         </is>
       </c>
-      <c r="AN27" s="22" t="inlineStr">
+      <c r="AN27" s="52" t="inlineStr">
         <is>
           <t>远投轻量泛用 spinning</t>
         </is>
       </c>
-      <c r="AO27" s="22" t="inlineStr">
+      <c r="AO27" s="52" t="inlineStr">
         <is>
           <t>Long Cast Down Shot 和 Neko 能保持距离下的操作感，I-shaped、Bug、Surface Plug 用来处理表层或清水弱波动搜索。</t>
         </is>
       </c>
-      <c r="AP27" s="22" t="inlineStr">
+      <c r="AP27" s="52" t="inlineStr">
         <is>
           <t>パワフルロングシューティングスペシャル ロングキャストが必要な状況でキャスタビリティーと操作性の両立を実現させたおかっぱりやボートで重宝するモデル。MLパワーソリッドティップを採用することでライトリグ全般から表層系プラグ、i字系、虫系など幅広く対応。ガイドもPEライン仕様の専用セッティング。ナノマテリアル配合のBLUE TREKブランクは不意なビックフィッシュでも逃さない粘りを実現しました。軽量ルアーをもっと遠くへ、未開の領域へ飛ばしたいアングラーに。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ27" s="22" t="inlineStr"/>
-      <c r="AR27" s="22" t="inlineStr"/>
+      <c r="AQ27" s="52" t="inlineStr"/>
+      <c r="AR27" s="52" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="52" t="inlineStr">
         <is>
           <t>DSRD10026</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="52" t="inlineStr">
         <is>
           <t>DBTC-662ML-BF</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="52" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="52" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr"/>
-      <c r="I28" s="22" t="inlineStr"/>
-      <c r="J28" s="22" t="inlineStr">
+      <c r="H28" s="52" t="inlineStr"/>
+      <c r="I28" s="52" t="inlineStr"/>
+      <c r="J28" s="52" t="inlineStr">
         <is>
           <t>110g</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr"/>
-      <c r="L28" s="22" t="inlineStr"/>
-      <c r="M28" s="22" t="inlineStr">
+      <c r="K28" s="52" t="inlineStr"/>
+      <c r="L28" s="52" t="inlineStr"/>
+      <c r="M28" s="52" t="inlineStr">
         <is>
           <t>6~12</t>
         </is>
       </c>
-      <c r="N28" s="22" t="inlineStr"/>
-      <c r="O28" s="22" t="inlineStr"/>
-      <c r="P28" s="22" t="inlineStr"/>
-      <c r="Q28" s="22" t="inlineStr"/>
-      <c r="R28" s="22" t="inlineStr">
+      <c r="N28" s="52" t="inlineStr"/>
+      <c r="O28" s="52" t="inlineStr"/>
+      <c r="P28" s="52" t="inlineStr"/>
+      <c r="Q28" s="52" t="inlineStr"/>
+      <c r="R28" s="52" t="inlineStr">
         <is>
           <t>¥28,500 （税込み¥31,350）</t>
         </is>
       </c>
-      <c r="S28" s="22" t="inlineStr">
+      <c r="S28" s="52" t="inlineStr">
         <is>
           <t>4571527863769</t>
         </is>
       </c>
-      <c r="T28" s="22" t="inlineStr"/>
-      <c r="U28" s="22" t="inlineStr"/>
-      <c r="V28" s="22" t="inlineStr"/>
-      <c r="W28" s="22" t="inlineStr"/>
-      <c r="X28" s="22" t="inlineStr"/>
-      <c r="Y28" s="22" t="inlineStr"/>
-      <c r="Z28" s="22" t="inlineStr">
+      <c r="T28" s="52" t="inlineStr"/>
+      <c r="U28" s="52" t="inlineStr"/>
+      <c r="V28" s="52" t="inlineStr"/>
+      <c r="W28" s="52" t="inlineStr"/>
+      <c r="X28" s="52" t="inlineStr"/>
+      <c r="Y28" s="52" t="inlineStr"/>
+      <c r="Z28" s="52" t="inlineStr">
         <is>
           <t>1/8~1/2</t>
         </is>
       </c>
-      <c r="AA28" s="22" t="inlineStr"/>
-      <c r="AB28" s="22" t="inlineStr"/>
-      <c r="AC28" s="22" t="inlineStr"/>
-      <c r="AD28" s="22" t="inlineStr"/>
-      <c r="AE28" s="22" t="inlineStr"/>
-      <c r="AF28" s="22" t="inlineStr"/>
-      <c r="AG28" s="22" t="inlineStr"/>
-      <c r="AH28" s="22" t="inlineStr">
+      <c r="AA28" s="52" t="inlineStr"/>
+      <c r="AB28" s="52" t="inlineStr"/>
+      <c r="AC28" s="52" t="inlineStr"/>
+      <c r="AD28" s="52" t="inlineStr"/>
+      <c r="AE28" s="52" t="inlineStr"/>
+      <c r="AF28" s="52" t="inlineStr"/>
+      <c r="AG28" s="52" t="inlineStr"/>
+      <c r="AH28" s="52" t="inlineStr">
         <is>
           <t>662ML-BF 是 multi bait finesse，小型 Plug 与小型 wire bait 可以搜索，Small Rubber Jig、Neko、Down Shot 用于精细投放；优势是近中距离准确和手返し。</t>
         </is>
       </c>
-      <c r="AI28" s="22" t="inlineStr">
+      <c r="AI28" s="52" t="inlineStr">
         <is>
           <t>Bait Finesse Small Plug / Small Spinnerbait / Small Rubber Jig / Neko Rig / Down Shot</t>
         </is>
       </c>
-      <c r="AJ28" s="22" t="inlineStr"/>
-      <c r="AK28" s="22" t="inlineStr"/>
-      <c r="AL28" s="22" t="inlineStr"/>
-      <c r="AM28" s="22" t="inlineStr">
+      <c r="AJ28" s="52" t="inlineStr"/>
+      <c r="AK28" s="52" t="inlineStr"/>
+      <c r="AL28" s="52" t="inlineStr"/>
+      <c r="AM28" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸边障碍・小型河川・野池 / multi BFS</t>
         </is>
       </c>
-      <c r="AN28" s="22" t="inlineStr">
+      <c r="AN28" s="52" t="inlineStr">
         <is>
           <t>小硬饵与精细软饵 BFS</t>
         </is>
       </c>
-      <c r="AO28" s="22" t="inlineStr">
+      <c r="AO28" s="52" t="inlineStr">
         <is>
           <t>Small Plug、Small Spinnerbait 能搜索，Small Rubber Jig、Neko、Down Shot 可打点；适合近中距离精准抛投和手返し。</t>
         </is>
       </c>
-      <c r="AP28" s="22" t="inlineStr">
+      <c r="AP28" s="52" t="inlineStr">
         <is>
           <t>マルチベイトフィネスモデル ベイトフィネスモデルでありながらこの１本で幅広くルアーを扱えるマルチベイトフィネスモデル。スモールプラグや小型ワイヤーベイト、スモールラバージグやネコリグ、ダウンショットまでこなせる汎用性があります。おっかぱりやボートでも重宝する１本。ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビッグフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ28" s="22" t="inlineStr"/>
-      <c r="AR28" s="22" t="inlineStr"/>
+      <c r="AQ28" s="52" t="inlineStr"/>
+      <c r="AR28" s="52" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="52" t="inlineStr">
         <is>
           <t>DSRD10027</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="52" t="inlineStr">
         <is>
           <t>DBTC-672MH-S</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="52" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="52" t="inlineStr">
         <is>
           <t>6’7″</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr"/>
-      <c r="I29" s="22" t="inlineStr"/>
-      <c r="J29" s="22" t="inlineStr">
+      <c r="H29" s="52" t="inlineStr"/>
+      <c r="I29" s="52" t="inlineStr"/>
+      <c r="J29" s="52" t="inlineStr">
         <is>
           <t>117g</t>
         </is>
       </c>
-      <c r="K29" s="22" t="inlineStr"/>
-      <c r="L29" s="22" t="inlineStr"/>
-      <c r="M29" s="22" t="inlineStr">
+      <c r="K29" s="52" t="inlineStr"/>
+      <c r="L29" s="52" t="inlineStr"/>
+      <c r="M29" s="52" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N29" s="22" t="inlineStr"/>
-      <c r="O29" s="22" t="inlineStr"/>
-      <c r="P29" s="22" t="inlineStr"/>
-      <c r="Q29" s="22" t="inlineStr"/>
-      <c r="R29" s="22" t="inlineStr">
+      <c r="N29" s="52" t="inlineStr"/>
+      <c r="O29" s="52" t="inlineStr"/>
+      <c r="P29" s="52" t="inlineStr"/>
+      <c r="Q29" s="52" t="inlineStr"/>
+      <c r="R29" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込み¥31,900）</t>
         </is>
       </c>
-      <c r="S29" s="22" t="inlineStr">
+      <c r="S29" s="52" t="inlineStr">
         <is>
           <t>4571527863776</t>
         </is>
       </c>
-      <c r="T29" s="22" t="inlineStr"/>
-      <c r="U29" s="22" t="inlineStr"/>
-      <c r="V29" s="22" t="inlineStr"/>
-      <c r="W29" s="22" t="inlineStr"/>
-      <c r="X29" s="22" t="inlineStr"/>
-      <c r="Y29" s="22" t="inlineStr"/>
-      <c r="Z29" s="22" t="inlineStr">
+      <c r="T29" s="52" t="inlineStr"/>
+      <c r="U29" s="52" t="inlineStr"/>
+      <c r="V29" s="52" t="inlineStr"/>
+      <c r="W29" s="52" t="inlineStr"/>
+      <c r="X29" s="52" t="inlineStr"/>
+      <c r="Y29" s="52" t="inlineStr"/>
+      <c r="Z29" s="52" t="inlineStr">
         <is>
           <t>3/16~3/4</t>
         </is>
       </c>
-      <c r="AA29" s="22" t="inlineStr"/>
-      <c r="AB29" s="22" t="inlineStr"/>
-      <c r="AC29" s="22" t="inlineStr"/>
-      <c r="AD29" s="22" t="inlineStr"/>
-      <c r="AE29" s="22" t="inlineStr"/>
-      <c r="AF29" s="22" t="inlineStr"/>
-      <c r="AG29" s="22" t="inlineStr"/>
-      <c r="AH29" s="22" t="inlineStr">
+      <c r="AA29" s="52" t="inlineStr"/>
+      <c r="AB29" s="52" t="inlineStr"/>
+      <c r="AC29" s="52" t="inlineStr"/>
+      <c r="AD29" s="52" t="inlineStr"/>
+      <c r="AE29" s="52" t="inlineStr"/>
+      <c r="AF29" s="52" t="inlineStr"/>
+      <c r="AG29" s="52" t="inlineStr"/>
+      <c r="AH29" s="52" t="inlineStr">
         <is>
           <t>672MH-S 描述虽短，但明确是 tough-cover rod；推荐只保守落在 Cover Neko、Heavy Down Shot、Texas 与 Rubber Jig，不外扩到 Big Bait。</t>
         </is>
       </c>
-      <c r="AI29" s="22" t="inlineStr">
+      <c r="AI29" s="52" t="inlineStr">
         <is>
           <t>Cover Neko / Heavy Down Shot / Texas Rig / Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ29" s="22" t="inlineStr"/>
-      <c r="AK29" s="22" t="inlineStr"/>
-      <c r="AL29" s="22" t="inlineStr"/>
-      <c r="AM29" s="22" t="inlineStr">
+      <c r="AJ29" s="52" t="inlineStr"/>
+      <c r="AK29" s="52" t="inlineStr"/>
+      <c r="AL29" s="52" t="inlineStr"/>
+      <c r="AM29" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / tough cover・沉木・草边 / cover soft rig</t>
         </is>
       </c>
-      <c r="AN29" s="22" t="inlineStr">
+      <c r="AN29" s="52" t="inlineStr">
         <is>
           <t>cover 底操与 heavy finesse</t>
         </is>
       </c>
-      <c r="AO29" s="22" t="inlineStr">
+      <c r="AO29" s="52" t="inlineStr">
         <is>
           <t>Cover Neko、Heavy Down Shot、Texas 和 Rubber Jig 都围绕 cover 展开，定位保守清晰，不把 MH 误扩成大型饵竿。</t>
         </is>
       </c>
-      <c r="AP29" s="22" t="inlineStr">
+      <c r="AP29" s="52" t="inlineStr">
         <is>
           <t>タフタイムを制するカバーロッド</t>
         </is>
       </c>
-      <c r="AQ29" s="22" t="inlineStr"/>
-      <c r="AR29" s="22" t="inlineStr"/>
+      <c r="AQ29" s="52" t="inlineStr"/>
+      <c r="AR29" s="52" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="52" t="inlineStr">
         <is>
           <t>DSRD10028</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="52" t="inlineStr">
         <is>
           <t>DBTC-6102M</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="52" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="52" t="inlineStr">
         <is>
           <t>6’10″</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr"/>
-      <c r="I30" s="22" t="inlineStr"/>
-      <c r="J30" s="22" t="inlineStr">
+      <c r="H30" s="52" t="inlineStr"/>
+      <c r="I30" s="52" t="inlineStr"/>
+      <c r="J30" s="52" t="inlineStr">
         <is>
           <t>113g</t>
         </is>
       </c>
-      <c r="K30" s="22" t="inlineStr"/>
-      <c r="L30" s="22" t="inlineStr"/>
-      <c r="M30" s="22" t="inlineStr">
+      <c r="K30" s="52" t="inlineStr"/>
+      <c r="L30" s="52" t="inlineStr"/>
+      <c r="M30" s="52" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N30" s="22" t="inlineStr"/>
-      <c r="O30" s="22" t="inlineStr"/>
-      <c r="P30" s="22" t="inlineStr"/>
-      <c r="Q30" s="22" t="inlineStr"/>
-      <c r="R30" s="22" t="inlineStr">
+      <c r="N30" s="52" t="inlineStr"/>
+      <c r="O30" s="52" t="inlineStr"/>
+      <c r="P30" s="52" t="inlineStr"/>
+      <c r="Q30" s="52" t="inlineStr"/>
+      <c r="R30" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込み¥31,900）</t>
         </is>
       </c>
-      <c r="S30" s="22" t="inlineStr">
+      <c r="S30" s="52" t="inlineStr">
         <is>
           <t>4571527862588</t>
         </is>
       </c>
-      <c r="T30" s="22" t="inlineStr"/>
-      <c r="U30" s="22" t="inlineStr"/>
-      <c r="V30" s="22" t="inlineStr"/>
-      <c r="W30" s="22" t="inlineStr"/>
-      <c r="X30" s="22" t="inlineStr"/>
-      <c r="Y30" s="22" t="inlineStr"/>
-      <c r="Z30" s="22" t="inlineStr">
+      <c r="T30" s="52" t="inlineStr"/>
+      <c r="U30" s="52" t="inlineStr"/>
+      <c r="V30" s="52" t="inlineStr"/>
+      <c r="W30" s="52" t="inlineStr"/>
+      <c r="X30" s="52" t="inlineStr"/>
+      <c r="Y30" s="52" t="inlineStr"/>
+      <c r="Z30" s="52" t="inlineStr">
         <is>
           <t>3/16~5/8</t>
         </is>
       </c>
-      <c r="AA30" s="22" t="inlineStr"/>
-      <c r="AB30" s="22" t="inlineStr"/>
-      <c r="AC30" s="22" t="inlineStr"/>
-      <c r="AD30" s="22" t="inlineStr"/>
-      <c r="AE30" s="22" t="inlineStr"/>
-      <c r="AF30" s="22" t="inlineStr"/>
-      <c r="AG30" s="22" t="inlineStr"/>
-      <c r="AH30" s="22" t="inlineStr">
+      <c r="AA30" s="52" t="inlineStr"/>
+      <c r="AB30" s="52" t="inlineStr"/>
+      <c r="AC30" s="52" t="inlineStr"/>
+      <c r="AD30" s="52" t="inlineStr"/>
+      <c r="AE30" s="52" t="inlineStr"/>
+      <c r="AF30" s="52" t="inlineStr"/>
+      <c r="AG30" s="52" t="inlineStr"/>
+      <c r="AH30" s="52" t="inlineStr">
         <is>
           <t>6102M 是岸钓到船钓都能带的一支 super versatile，worm 系 rig 负责撃ち，Crankbait、Spinnerbait、Chatterbait 负责巻き；适合软硬饵切换。</t>
         </is>
       </c>
-      <c r="AI30" s="22" t="inlineStr">
+      <c r="AI30" s="52" t="inlineStr">
         <is>
           <t>Texas Rig / Free Rig / No Sinker / Crankbait / Spinnerbait / Chatterbait</t>
         </is>
       </c>
-      <c r="AJ30" s="22" t="inlineStr"/>
-      <c r="AK30" s="22" t="inlineStr"/>
-      <c r="AL30" s="22" t="inlineStr"/>
-      <c r="AM30" s="22" t="inlineStr">
+      <c r="AJ30" s="52" t="inlineStr"/>
+      <c r="AK30" s="52" t="inlineStr"/>
+      <c r="AL30" s="52" t="inlineStr"/>
+      <c r="AM30" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓・船钓通用 / worm rig 到 Chatterbait</t>
         </is>
       </c>
-      <c r="AN30" s="22" t="inlineStr">
+      <c r="AN30" s="52" t="inlineStr">
         <is>
           <t>软硬饵日常主力 bait</t>
         </is>
       </c>
-      <c r="AO30" s="22" t="inlineStr">
+      <c r="AO30" s="52" t="inlineStr">
         <is>
           <t>Texas、Free Rig、No Sinker 负责打点，Crankbait、Spinnerbait、Chatterbait 负责搜索，适合一支竿快速切换路线。</t>
         </is>
       </c>
-      <c r="AP30" s="22" t="inlineStr">
+      <c r="AP30" s="52" t="inlineStr">
         <is>
           <t>スーパーバーサタイルモデル 巻きから撃ちまでマルチにこなせるスーパーバーサタイルモデル。おかっぱりからボートまでどこへ行くにも手放せない１本。癖のないレギュラーファーストテーパーにすることで投げて楽しい、掛けて楽しいロッドに仕上がっています。ワーム系リグ全般、プラグやワイヤーベイトまであらゆるジャンルのタイプが使用可能です。「迷ったら」「1本しか持ち出せないなら」この1本をおススメします。 ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビックフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ30" s="22" t="inlineStr"/>
-      <c r="AR30" s="22" t="inlineStr"/>
+      <c r="AQ30" s="52" t="inlineStr"/>
+      <c r="AR30" s="52" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="52" t="inlineStr">
         <is>
           <t>DSRD10029</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="52" t="inlineStr">
         <is>
           <t>DBTC-6102MH</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="52" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="52" t="inlineStr">
         <is>
           <t>6’10″</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr"/>
-      <c r="I31" s="22" t="inlineStr"/>
-      <c r="J31" s="22" t="inlineStr">
+      <c r="H31" s="52" t="inlineStr"/>
+      <c r="I31" s="52" t="inlineStr"/>
+      <c r="J31" s="52" t="inlineStr">
         <is>
           <t>123g</t>
         </is>
       </c>
-      <c r="K31" s="22" t="inlineStr"/>
-      <c r="L31" s="22" t="inlineStr"/>
-      <c r="M31" s="22" t="inlineStr">
+      <c r="K31" s="52" t="inlineStr"/>
+      <c r="L31" s="52" t="inlineStr"/>
+      <c r="M31" s="52" t="inlineStr">
         <is>
           <t>8~20</t>
         </is>
       </c>
-      <c r="N31" s="22" t="inlineStr"/>
-      <c r="O31" s="22" t="inlineStr"/>
-      <c r="P31" s="22" t="inlineStr"/>
-      <c r="Q31" s="22" t="inlineStr"/>
-      <c r="R31" s="22" t="inlineStr">
+      <c r="N31" s="52" t="inlineStr"/>
+      <c r="O31" s="52" t="inlineStr"/>
+      <c r="P31" s="52" t="inlineStr"/>
+      <c r="Q31" s="52" t="inlineStr"/>
+      <c r="R31" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込み¥31,900）</t>
         </is>
       </c>
-      <c r="S31" s="22" t="inlineStr">
+      <c r="S31" s="52" t="inlineStr">
         <is>
           <t>4571527862595</t>
         </is>
       </c>
-      <c r="T31" s="22" t="inlineStr"/>
-      <c r="U31" s="22" t="inlineStr"/>
-      <c r="V31" s="22" t="inlineStr"/>
-      <c r="W31" s="22" t="inlineStr"/>
-      <c r="X31" s="22" t="inlineStr"/>
-      <c r="Y31" s="22" t="inlineStr"/>
-      <c r="Z31" s="22" t="inlineStr">
+      <c r="T31" s="52" t="inlineStr"/>
+      <c r="U31" s="52" t="inlineStr"/>
+      <c r="V31" s="52" t="inlineStr"/>
+      <c r="W31" s="52" t="inlineStr"/>
+      <c r="X31" s="52" t="inlineStr"/>
+      <c r="Y31" s="52" t="inlineStr"/>
+      <c r="Z31" s="52" t="inlineStr">
         <is>
           <t>3/16~3/4</t>
         </is>
       </c>
-      <c r="AA31" s="22" t="inlineStr"/>
-      <c r="AB31" s="22" t="inlineStr"/>
-      <c r="AC31" s="22" t="inlineStr"/>
-      <c r="AD31" s="22" t="inlineStr"/>
-      <c r="AE31" s="22" t="inlineStr"/>
-      <c r="AF31" s="22" t="inlineStr"/>
-      <c r="AG31" s="22" t="inlineStr"/>
-      <c r="AH31" s="22" t="inlineStr">
+      <c r="AA31" s="52" t="inlineStr"/>
+      <c r="AB31" s="52" t="inlineStr"/>
+      <c r="AC31" s="52" t="inlineStr"/>
+      <c r="AD31" s="52" t="inlineStr"/>
+      <c r="AE31" s="52" t="inlineStr"/>
+      <c r="AF31" s="52" t="inlineStr"/>
+      <c r="AG31" s="52" t="inlineStr"/>
+      <c r="AH31" s="52" t="inlineStr">
         <is>
           <t>6102MH 只有中量级 versatile 描述，按 MH 规格保守放在 Texas、Free Rig、Rubber Jig 与中量移动饵；不因 MH 自动扩写到大型饵。</t>
         </is>
       </c>
-      <c r="AI31" s="22" t="inlineStr">
+      <c r="AI31" s="52" t="inlineStr">
         <is>
           <t>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait / Crankbait</t>
         </is>
       </c>
-      <c r="AJ31" s="22" t="inlineStr"/>
-      <c r="AK31" s="22" t="inlineStr"/>
-      <c r="AL31" s="22" t="inlineStr"/>
-      <c r="AM31" s="22" t="inlineStr">
+      <c r="AJ31" s="52" t="inlineStr"/>
+      <c r="AK31" s="52" t="inlineStr"/>
+      <c r="AL31" s="52" t="inlineStr"/>
+      <c r="AM31" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 中重 cover・硬底・浅草 / middle-heavy versatile</t>
         </is>
       </c>
-      <c r="AN31" s="22" t="inlineStr">
+      <c r="AN31" s="52" t="inlineStr">
         <is>
           <t>中重软饵与卷物泛用</t>
         </is>
       </c>
-      <c r="AO31" s="22" t="inlineStr">
+      <c r="AO31" s="52" t="inlineStr">
         <is>
           <t>Texas、Free Rig、Rubber Jig 可读底和穿 cover，Spinnerbait、Chatterbait、Crankbait 能做中量搜索；不把用途夸大到纯大饵。</t>
         </is>
       </c>
-      <c r="AP31" s="22" t="inlineStr">
+      <c r="AP31" s="52" t="inlineStr">
         <is>
           <t>ミドルスーパーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ31" s="22" t="inlineStr"/>
-      <c r="AR31" s="22" t="inlineStr"/>
+      <c r="AQ31" s="52" t="inlineStr"/>
+      <c r="AR31" s="52" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="52" t="inlineStr">
         <is>
           <t>DSRD10030</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="52" t="inlineStr">
         <is>
           <t>DBTC-6102XH</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="52" t="inlineStr">
         <is>
           <t>XH</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="52" t="inlineStr">
         <is>
           <t>6’10″</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="52" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr"/>
-      <c r="I32" s="22" t="inlineStr"/>
-      <c r="J32" s="22" t="inlineStr">
+      <c r="H32" s="52" t="inlineStr"/>
+      <c r="I32" s="52" t="inlineStr"/>
+      <c r="J32" s="52" t="inlineStr">
         <is>
           <t>172g</t>
         </is>
       </c>
-      <c r="K32" s="22" t="inlineStr"/>
-      <c r="L32" s="22" t="inlineStr"/>
-      <c r="M32" s="22" t="inlineStr">
+      <c r="K32" s="52" t="inlineStr"/>
+      <c r="L32" s="52" t="inlineStr"/>
+      <c r="M32" s="52" t="inlineStr">
         <is>
           <t>max 30</t>
         </is>
       </c>
-      <c r="N32" s="22" t="inlineStr"/>
-      <c r="O32" s="22" t="inlineStr"/>
-      <c r="P32" s="22" t="inlineStr"/>
-      <c r="Q32" s="22" t="inlineStr"/>
-      <c r="R32" s="22" t="inlineStr">
+      <c r="N32" s="52" t="inlineStr"/>
+      <c r="O32" s="52" t="inlineStr"/>
+      <c r="P32" s="52" t="inlineStr"/>
+      <c r="Q32" s="52" t="inlineStr"/>
+      <c r="R32" s="52" t="inlineStr">
         <is>
           <t>¥29,500 （税込み¥32,450）</t>
         </is>
       </c>
-      <c r="S32" s="22" t="inlineStr">
+      <c r="S32" s="52" t="inlineStr">
         <is>
           <t>4571527863783</t>
         </is>
       </c>
-      <c r="T32" s="22" t="inlineStr"/>
-      <c r="U32" s="22" t="inlineStr"/>
-      <c r="V32" s="22" t="inlineStr"/>
-      <c r="W32" s="22" t="inlineStr"/>
-      <c r="X32" s="22" t="inlineStr"/>
-      <c r="Y32" s="22" t="inlineStr"/>
-      <c r="Z32" s="22" t="inlineStr">
+      <c r="T32" s="52" t="inlineStr"/>
+      <c r="U32" s="52" t="inlineStr"/>
+      <c r="V32" s="52" t="inlineStr"/>
+      <c r="W32" s="52" t="inlineStr"/>
+      <c r="X32" s="52" t="inlineStr"/>
+      <c r="Y32" s="52" t="inlineStr"/>
+      <c r="Z32" s="52" t="inlineStr">
         <is>
           <t>max4oz</t>
         </is>
       </c>
-      <c r="AA32" s="22" t="inlineStr"/>
-      <c r="AB32" s="22" t="inlineStr"/>
-      <c r="AC32" s="22" t="inlineStr"/>
-      <c r="AD32" s="22" t="inlineStr"/>
-      <c r="AE32" s="22" t="inlineStr"/>
-      <c r="AF32" s="22" t="inlineStr"/>
-      <c r="AG32" s="22" t="inlineStr"/>
-      <c r="AH32" s="22" t="inlineStr">
+      <c r="AA32" s="52" t="inlineStr"/>
+      <c r="AB32" s="52" t="inlineStr"/>
+      <c r="AC32" s="52" t="inlineStr"/>
+      <c r="AD32" s="52" t="inlineStr"/>
+      <c r="AE32" s="52" t="inlineStr"/>
+      <c r="AF32" s="52" t="inlineStr"/>
+      <c r="AG32" s="52" t="inlineStr"/>
+      <c r="AH32" s="52" t="inlineStr">
         <is>
           <t>6102XH 的描述明确是操作系 Big Bait 竿，优先服务 Big Bait、Swimbait、Crawler 和 Glide 系的操控与承接，不再套用普通 Texas/Jig 泛用逻辑。</t>
         </is>
       </c>
-      <c r="AI32" s="22" t="inlineStr">
+      <c r="AI32" s="52" t="inlineStr">
         <is>
           <t>Big Bait / Swimbait / Crawler Bait / Glide Bait</t>
         </is>
       </c>
-      <c r="AJ32" s="22" t="inlineStr"/>
-      <c r="AK32" s="22" t="inlineStr"/>
-      <c r="AL32" s="22" t="inlineStr"/>
-      <c r="AM32" s="22" t="inlineStr">
+      <c r="AJ32" s="52" t="inlineStr"/>
+      <c r="AK32" s="52" t="inlineStr"/>
+      <c r="AL32" s="52" t="inlineStr"/>
+      <c r="AM32" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖・开阔水・大型鱼标点 / big bait 操作</t>
         </is>
       </c>
-      <c r="AN32" s="22" t="inlineStr">
+      <c r="AN32" s="52" t="inlineStr">
         <is>
           <t>操作系大型饵专向</t>
         </is>
       </c>
-      <c r="AO32" s="22" t="inlineStr">
+      <c r="AO32" s="52" t="inlineStr">
         <is>
           <t>Big Bait、Swimbait、Crawler 和 Glide Bait 的抽停与承接是核心，适合需要明确操控大型饵而不是单纯重底操的玩家。</t>
         </is>
       </c>
-      <c r="AP32" s="22" t="inlineStr">
+      <c r="AP32" s="52" t="inlineStr">
         <is>
           <t>XHパワーの操作系ビックベイトロッド</t>
         </is>
       </c>
-      <c r="AQ32" s="22" t="inlineStr"/>
-      <c r="AR32" s="22" t="inlineStr"/>
+      <c r="AQ32" s="52" t="inlineStr"/>
+      <c r="AR32" s="52" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="52" t="inlineStr">
         <is>
           <t>DSRD10031</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="52" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="52" t="inlineStr">
         <is>
           <t>DBTC-702H</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="52" t="inlineStr">
         <is>
           <t>7’0″</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr"/>
-      <c r="I33" s="22" t="inlineStr"/>
-      <c r="J33" s="22" t="inlineStr">
+      <c r="H33" s="52" t="inlineStr"/>
+      <c r="I33" s="52" t="inlineStr"/>
+      <c r="J33" s="52" t="inlineStr">
         <is>
           <t>128g</t>
         </is>
       </c>
-      <c r="K33" s="22" t="inlineStr"/>
-      <c r="L33" s="22" t="inlineStr"/>
-      <c r="M33" s="22" t="inlineStr">
+      <c r="K33" s="52" t="inlineStr"/>
+      <c r="L33" s="52" t="inlineStr"/>
+      <c r="M33" s="52" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N33" s="22" t="inlineStr"/>
-      <c r="O33" s="22" t="inlineStr"/>
-      <c r="P33" s="22" t="inlineStr"/>
-      <c r="Q33" s="22" t="inlineStr"/>
-      <c r="R33" s="22" t="inlineStr">
+      <c r="N33" s="52" t="inlineStr"/>
+      <c r="O33" s="52" t="inlineStr"/>
+      <c r="P33" s="52" t="inlineStr"/>
+      <c r="Q33" s="52" t="inlineStr"/>
+      <c r="R33" s="52" t="inlineStr">
         <is>
           <t>¥29,500 （税込み¥32,450）</t>
         </is>
       </c>
-      <c r="S33" s="22" t="inlineStr">
+      <c r="S33" s="52" t="inlineStr">
         <is>
           <t>4571527862601</t>
         </is>
       </c>
-      <c r="T33" s="22" t="inlineStr"/>
-      <c r="U33" s="22" t="inlineStr"/>
-      <c r="V33" s="22" t="inlineStr"/>
-      <c r="W33" s="22" t="inlineStr"/>
-      <c r="X33" s="22" t="inlineStr"/>
-      <c r="Y33" s="22" t="inlineStr"/>
-      <c r="Z33" s="22" t="inlineStr">
+      <c r="T33" s="52" t="inlineStr"/>
+      <c r="U33" s="52" t="inlineStr"/>
+      <c r="V33" s="52" t="inlineStr"/>
+      <c r="W33" s="52" t="inlineStr"/>
+      <c r="X33" s="52" t="inlineStr"/>
+      <c r="Y33" s="52" t="inlineStr"/>
+      <c r="Z33" s="52" t="inlineStr">
         <is>
           <t>3/16~1</t>
         </is>
       </c>
-      <c r="AA33" s="22" t="inlineStr"/>
-      <c r="AB33" s="22" t="inlineStr"/>
-      <c r="AC33" s="22" t="inlineStr"/>
-      <c r="AD33" s="22" t="inlineStr"/>
-      <c r="AE33" s="22" t="inlineStr"/>
-      <c r="AF33" s="22" t="inlineStr"/>
-      <c r="AG33" s="22" t="inlineStr"/>
-      <c r="AH33" s="22" t="inlineStr">
+      <c r="AA33" s="52" t="inlineStr"/>
+      <c r="AB33" s="52" t="inlineStr"/>
+      <c r="AC33" s="52" t="inlineStr"/>
+      <c r="AD33" s="52" t="inlineStr"/>
+      <c r="AE33" s="52" t="inlineStr"/>
+      <c r="AF33" s="52" t="inlineStr"/>
+      <c r="AG33" s="52" t="inlineStr"/>
+      <c r="AH33" s="52" t="inlineStr">
         <is>
           <t>702H 仅有 heavy super versatile 描述，按 H power 保守覆盖 Heavy Texas、Rubber Jig、Frog 与中大型移动饵；具体大型饵排序低于底操和 cover 用途。</t>
         </is>
       </c>
-      <c r="AI33" s="22" t="inlineStr">
+      <c r="AI33" s="52" t="inlineStr">
         <is>
           <t>Heavy Texas / Rubber Jig / Frog / Big Bait / Swimbait</t>
         </is>
       </c>
-      <c r="AJ33" s="22" t="inlineStr"/>
-      <c r="AK33" s="22" t="inlineStr"/>
-      <c r="AL33" s="22" t="inlineStr"/>
-      <c r="AM33" s="22" t="inlineStr">
+      <c r="AJ33" s="52" t="inlineStr"/>
+      <c r="AK33" s="52" t="inlineStr"/>
+      <c r="AL33" s="52" t="inlineStr"/>
+      <c r="AM33" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 重 cover・草区・大型饵补充搜索 / heavy versatile</t>
         </is>
       </c>
-      <c r="AN33" s="22" t="inlineStr">
+      <c r="AN33" s="52" t="inlineStr">
         <is>
           <t>强力 cover 与大型饵补充</t>
         </is>
       </c>
-      <c r="AO33" s="22" t="inlineStr">
+      <c r="AO33" s="52" t="inlineStr">
         <is>
           <t>Heavy Texas、Rubber Jig 和 Frog 是主要场景，Big Bait、Swimbait 属副线搜索；适合重线组和控鱼优先的玩家。</t>
         </is>
       </c>
-      <c r="AP33" s="22" t="inlineStr">
+      <c r="AP33" s="52" t="inlineStr">
         <is>
           <t>ヘビースーパーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ33" s="22" t="inlineStr"/>
-      <c r="AR33" s="22" t="inlineStr"/>
+      <c r="AQ33" s="52" t="inlineStr"/>
+      <c r="AR33" s="52" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="53" t="inlineStr">
         <is>
           <t>DSRD10032</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B34" s="53" t="inlineStr">
         <is>
           <t>DSR1004</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C34" s="53" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D34" s="19" t="inlineStr">
+      <c r="D34" s="53" t="inlineStr">
         <is>
           <t>DBTS-60XUL-S</t>
         </is>
       </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="E34" s="53" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F34" s="53" t="inlineStr">
         <is>
           <t>6’0″</t>
         </is>
       </c>
-      <c r="G34" s="19" t="inlineStr">
+      <c r="G34" s="53" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H34" s="19" t="inlineStr"/>
-      <c r="I34" s="19" t="inlineStr"/>
-      <c r="J34" s="19" t="inlineStr">
+      <c r="H34" s="53" t="inlineStr"/>
+      <c r="I34" s="53" t="inlineStr"/>
+      <c r="J34" s="53" t="inlineStr">
         <is>
           <t>72g</t>
         </is>
       </c>
-      <c r="K34" s="19" t="inlineStr"/>
-      <c r="L34" s="19" t="inlineStr"/>
-      <c r="M34" s="19" t="inlineStr">
+      <c r="K34" s="53" t="inlineStr"/>
+      <c r="L34" s="53" t="inlineStr"/>
+      <c r="M34" s="53" t="inlineStr">
         <is>
           <t>2~5</t>
         </is>
       </c>
-      <c r="N34" s="19" t="inlineStr"/>
-      <c r="O34" s="19" t="inlineStr"/>
-      <c r="P34" s="19" t="inlineStr"/>
-      <c r="Q34" s="19" t="inlineStr"/>
-      <c r="R34" s="19" t="inlineStr">
+      <c r="N34" s="53" t="inlineStr"/>
+      <c r="O34" s="53" t="inlineStr"/>
+      <c r="P34" s="53" t="inlineStr"/>
+      <c r="Q34" s="53" t="inlineStr"/>
+      <c r="R34" s="53" t="inlineStr">
         <is>
           <t>¥39,500 （税込み¥43,450）</t>
         </is>
       </c>
-      <c r="S34" s="19" t="inlineStr">
+      <c r="S34" s="53" t="inlineStr">
         <is>
           <t>4571527862106</t>
         </is>
       </c>
-      <c r="T34" s="19" t="inlineStr"/>
-      <c r="U34" s="19" t="inlineStr"/>
-      <c r="V34" s="19" t="inlineStr"/>
-      <c r="W34" s="19" t="inlineStr"/>
-      <c r="X34" s="19" t="inlineStr"/>
-      <c r="Y34" s="19" t="inlineStr"/>
-      <c r="Z34" s="19" t="inlineStr">
+      <c r="T34" s="53" t="inlineStr"/>
+      <c r="U34" s="53" t="inlineStr"/>
+      <c r="V34" s="53" t="inlineStr"/>
+      <c r="W34" s="53" t="inlineStr"/>
+      <c r="X34" s="53" t="inlineStr"/>
+      <c r="Y34" s="53" t="inlineStr"/>
+      <c r="Z34" s="53" t="inlineStr">
         <is>
           <t>1/48~1/8</t>
         </is>
       </c>
-      <c r="AA34" s="19" t="inlineStr"/>
-      <c r="AB34" s="19" t="inlineStr"/>
-      <c r="AC34" s="19" t="inlineStr"/>
-      <c r="AD34" s="19" t="inlineStr"/>
-      <c r="AE34" s="19" t="inlineStr"/>
-      <c r="AF34" s="19" t="inlineStr"/>
-      <c r="AG34" s="19" t="inlineStr">
+      <c r="AA34" s="53" t="inlineStr"/>
+      <c r="AB34" s="53" t="inlineStr"/>
+      <c r="AC34" s="53" t="inlineStr"/>
+      <c r="AD34" s="53" t="inlineStr"/>
+      <c r="AE34" s="53" t="inlineStr"/>
+      <c r="AF34" s="53" t="inlineStr"/>
+      <c r="AG34" s="53" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH34" s="19" t="inlineStr">
+      <c r="AH34" s="53" t="inlineStr">
         <is>
           <t>60XUL-S 是 10th ultimate finesse 的短尺 XUL solid，适合 Down Shot、Neko、Hover Strolling 和轻 No Sinker；强调极轻饵控制和短咬承接。</t>
         </is>
       </c>
-      <c r="AI34" s="19" t="inlineStr">
+      <c r="AI34" s="53" t="inlineStr">
         <is>
           <t>Down Shot / Neko Rig / Hover Strolling / No Sinker</t>
         </is>
       </c>
-      <c r="AJ34" s="19" t="inlineStr"/>
-      <c r="AK34" s="19" t="inlineStr"/>
-      <c r="AL34" s="19" t="inlineStr"/>
-      <c r="AM34" s="19" t="inlineStr">
+      <c r="AJ34" s="53" t="inlineStr"/>
+      <c r="AK34" s="53" t="inlineStr"/>
+      <c r="AL34" s="53" t="inlineStr"/>
+      <c r="AM34" s="53" t="inlineStr">
         <is>
           <t>淡水 Bass / 极高压近岸・清水 / ultimate finesse</t>
         </is>
       </c>
-      <c r="AN34" s="19" t="inlineStr">
+      <c r="AN34" s="53" t="inlineStr">
         <is>
           <t>短尺 XUL 食わせ finesse</t>
         </is>
       </c>
-      <c r="AO34" s="19" t="inlineStr">
+      <c r="AO34" s="53" t="inlineStr">
         <is>
           <t>Down Shot、Neko、Hover Strolling 和轻 No Sinker 更容易做细节动作，适合轻咬口多、鱼不愿追饵的场景。</t>
         </is>
       </c>
-      <c r="AP34" s="19" t="inlineStr">
+      <c r="AP34" s="53" t="inlineStr">
         <is>
           <t>BLUE TREK 10th Anniversary Model 10th Anniversary Model DSTYLE創業10周年に相応しい究極のフィネスロッドモデル。</t>
         </is>
       </c>
-      <c r="AQ34" s="19" t="inlineStr"/>
-      <c r="AR34" s="19" t="inlineStr"/>
+      <c r="AQ34" s="53" t="inlineStr"/>
+      <c r="AR34" s="53" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="53" t="inlineStr">
         <is>
           <t>DSRD10033</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B35" s="53" t="inlineStr">
         <is>
           <t>DSR1004</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="53" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D35" s="53" t="inlineStr">
         <is>
           <t>DBTS-67UL-S</t>
         </is>
       </c>
-      <c r="E35" s="19" t="inlineStr">
+      <c r="E35" s="53" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F35" s="53" t="inlineStr">
         <is>
           <t>6’7″</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G35" s="53" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr"/>
-      <c r="I35" s="19" t="inlineStr"/>
-      <c r="J35" s="19" t="inlineStr">
+      <c r="H35" s="53" t="inlineStr"/>
+      <c r="I35" s="53" t="inlineStr"/>
+      <c r="J35" s="53" t="inlineStr">
         <is>
           <t>78g</t>
         </is>
       </c>
-      <c r="K35" s="19" t="inlineStr"/>
-      <c r="L35" s="19" t="inlineStr"/>
-      <c r="M35" s="19" t="inlineStr">
+      <c r="K35" s="53" t="inlineStr"/>
+      <c r="L35" s="53" t="inlineStr"/>
+      <c r="M35" s="53" t="inlineStr">
         <is>
           <t>2~5</t>
         </is>
       </c>
-      <c r="N35" s="19" t="inlineStr"/>
-      <c r="O35" s="19" t="inlineStr"/>
-      <c r="P35" s="19" t="inlineStr"/>
-      <c r="Q35" s="19" t="inlineStr"/>
-      <c r="R35" s="19" t="inlineStr">
+      <c r="N35" s="53" t="inlineStr"/>
+      <c r="O35" s="53" t="inlineStr"/>
+      <c r="P35" s="53" t="inlineStr"/>
+      <c r="Q35" s="53" t="inlineStr"/>
+      <c r="R35" s="53" t="inlineStr">
         <is>
           <t>¥39,500 （税込み¥43,450）</t>
         </is>
       </c>
-      <c r="S35" s="19" t="inlineStr">
+      <c r="S35" s="53" t="inlineStr">
         <is>
           <t>4571527862113</t>
         </is>
       </c>
-      <c r="T35" s="19" t="inlineStr"/>
-      <c r="U35" s="19" t="inlineStr"/>
-      <c r="V35" s="19" t="inlineStr"/>
-      <c r="W35" s="19" t="inlineStr"/>
-      <c r="X35" s="19" t="inlineStr"/>
-      <c r="Y35" s="19" t="inlineStr"/>
-      <c r="Z35" s="19" t="inlineStr">
+      <c r="T35" s="53" t="inlineStr"/>
+      <c r="U35" s="53" t="inlineStr"/>
+      <c r="V35" s="53" t="inlineStr"/>
+      <c r="W35" s="53" t="inlineStr"/>
+      <c r="X35" s="53" t="inlineStr"/>
+      <c r="Y35" s="53" t="inlineStr"/>
+      <c r="Z35" s="53" t="inlineStr">
         <is>
           <t>1/48~1/8</t>
         </is>
       </c>
-      <c r="AA35" s="19" t="inlineStr"/>
-      <c r="AB35" s="19" t="inlineStr"/>
-      <c r="AC35" s="19" t="inlineStr"/>
-      <c r="AD35" s="19" t="inlineStr"/>
-      <c r="AE35" s="19" t="inlineStr"/>
-      <c r="AF35" s="19" t="inlineStr"/>
-      <c r="AG35" s="19" t="inlineStr">
+      <c r="AA35" s="53" t="inlineStr"/>
+      <c r="AB35" s="53" t="inlineStr"/>
+      <c r="AC35" s="53" t="inlineStr"/>
+      <c r="AD35" s="53" t="inlineStr"/>
+      <c r="AE35" s="53" t="inlineStr"/>
+      <c r="AF35" s="53" t="inlineStr"/>
+      <c r="AG35" s="53" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH35" s="19" t="inlineStr">
+      <c r="AH35" s="53" t="inlineStr">
         <is>
           <t>67UL-S 是 10th 长尺 finesse，Light Carolina 与长 leader Down Shot 放首位，No Sinker 和 I-shaped Plug 用于需要距离和弱波动搜索的场景。</t>
         </is>
       </c>
-      <c r="AI35" s="19" t="inlineStr">
+      <c r="AI35" s="53" t="inlineStr">
         <is>
           <t>Light Carolina Rig / Long Leader Down Shot / No Sinker / I-shaped Plug</t>
         </is>
       </c>
-      <c r="AJ35" s="19" t="inlineStr"/>
-      <c r="AK35" s="19" t="inlineStr"/>
-      <c r="AL35" s="19" t="inlineStr"/>
-      <c r="AM35" s="19" t="inlineStr">
+      <c r="AJ35" s="53" t="inlineStr"/>
+      <c r="AK35" s="53" t="inlineStr"/>
+      <c r="AL35" s="53" t="inlineStr"/>
+      <c r="AM35" s="53" t="inlineStr">
         <is>
           <t>淡水 Bass / 开阔水远投・缓坡 / light Carolina 与弱波动搜索</t>
         </is>
       </c>
-      <c r="AN35" s="19" t="inlineStr">
+      <c r="AN35" s="53" t="inlineStr">
         <is>
           <t>长尺 UL 远投 finesse</t>
         </is>
       </c>
-      <c r="AO35" s="19" t="inlineStr">
+      <c r="AO35" s="53" t="inlineStr">
         <is>
           <t>Light Carolina 和长 leader Down Shot 适合远处慢拖，No Sinker 与 I-shaped Plug 用来处理清水弱波动鱼。</t>
         </is>
       </c>
-      <c r="AP35" s="19" t="inlineStr">
+      <c r="AP35" s="53" t="inlineStr">
         <is>
           <t>BLUE TREK 10th Anniversary Model 10th Anniversary Model DSTYLE創業10周年に相応しい究極のフィネスロッドモデル。</t>
         </is>
       </c>
-      <c r="AQ35" s="19" t="inlineStr"/>
-      <c r="AR35" s="19" t="inlineStr"/>
+      <c r="AQ35" s="53" t="inlineStr"/>
+      <c r="AR35" s="53" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="52" t="inlineStr">
         <is>
           <t>DSRD10034</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="52" t="inlineStr">
         <is>
           <t>DBTS-60UL-S</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="52" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="52" t="inlineStr">
         <is>
           <t>6’0″</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr"/>
-      <c r="I36" s="22" t="inlineStr"/>
-      <c r="J36" s="22" t="inlineStr">
+      <c r="H36" s="52" t="inlineStr"/>
+      <c r="I36" s="52" t="inlineStr"/>
+      <c r="J36" s="52" t="inlineStr">
         <is>
           <t>78g</t>
         </is>
       </c>
-      <c r="K36" s="22" t="inlineStr"/>
-      <c r="L36" s="22" t="inlineStr"/>
-      <c r="M36" s="22" t="inlineStr">
+      <c r="K36" s="52" t="inlineStr"/>
+      <c r="L36" s="52" t="inlineStr"/>
+      <c r="M36" s="52" t="inlineStr">
         <is>
           <t>2~5</t>
         </is>
       </c>
-      <c r="N36" s="22" t="inlineStr"/>
-      <c r="O36" s="22" t="inlineStr"/>
-      <c r="P36" s="22" t="inlineStr"/>
-      <c r="Q36" s="22" t="inlineStr"/>
-      <c r="R36" s="22" t="inlineStr">
+      <c r="N36" s="52" t="inlineStr"/>
+      <c r="O36" s="52" t="inlineStr"/>
+      <c r="P36" s="52" t="inlineStr"/>
+      <c r="Q36" s="52" t="inlineStr"/>
+      <c r="R36" s="52" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S36" s="22" t="inlineStr">
+      <c r="S36" s="52" t="inlineStr">
         <is>
           <t>4580484756946</t>
         </is>
       </c>
-      <c r="T36" s="22" t="inlineStr"/>
-      <c r="U36" s="22" t="inlineStr"/>
-      <c r="V36" s="22" t="inlineStr"/>
-      <c r="W36" s="22" t="inlineStr"/>
-      <c r="X36" s="22" t="inlineStr"/>
-      <c r="Y36" s="22" t="inlineStr"/>
-      <c r="Z36" s="22" t="inlineStr">
+      <c r="T36" s="52" t="inlineStr"/>
+      <c r="U36" s="52" t="inlineStr"/>
+      <c r="V36" s="52" t="inlineStr"/>
+      <c r="W36" s="52" t="inlineStr"/>
+      <c r="X36" s="52" t="inlineStr"/>
+      <c r="Y36" s="52" t="inlineStr"/>
+      <c r="Z36" s="52" t="inlineStr">
         <is>
           <t>1/48～1/8</t>
         </is>
       </c>
-      <c r="AA36" s="22" t="inlineStr"/>
-      <c r="AB36" s="22" t="inlineStr"/>
-      <c r="AC36" s="22" t="inlineStr"/>
-      <c r="AD36" s="22" t="inlineStr"/>
-      <c r="AE36" s="22" t="inlineStr"/>
-      <c r="AF36" s="22" t="inlineStr"/>
-      <c r="AG36" s="22" t="inlineStr"/>
-      <c r="AH36" s="22" t="inlineStr">
+      <c r="AA36" s="52" t="inlineStr"/>
+      <c r="AB36" s="52" t="inlineStr"/>
+      <c r="AC36" s="52" t="inlineStr"/>
+      <c r="AD36" s="52" t="inlineStr"/>
+      <c r="AE36" s="52" t="inlineStr"/>
+      <c r="AF36" s="52" t="inlineStr"/>
+      <c r="AG36" s="52" t="inlineStr"/>
+      <c r="AH36" s="52" t="inlineStr">
         <is>
           <t>60UL-S 是 super finesse，适合高压短距用 Down Shot、Neko、No Sinker 和 Small Rubber Jig 抢一口；重点是轻量操控和不放过短咬。</t>
         </is>
       </c>
-      <c r="AI36" s="22" t="inlineStr">
+      <c r="AI36" s="52" t="inlineStr">
         <is>
           <t>Down Shot / Neko Rig / No Sinker / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ36" s="22" t="inlineStr"/>
-      <c r="AK36" s="22" t="inlineStr"/>
-      <c r="AL36" s="22" t="inlineStr"/>
-      <c r="AM36" s="22" t="inlineStr">
+      <c r="AJ36" s="52" t="inlineStr"/>
+      <c r="AK36" s="52" t="inlineStr"/>
+      <c r="AL36" s="52" t="inlineStr"/>
+      <c r="AM36" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压野池・近岸 cover 边 / super finesse</t>
         </is>
       </c>
-      <c r="AN36" s="22" t="inlineStr">
+      <c r="AN36" s="52" t="inlineStr">
         <is>
           <t>短距轻量食わせ</t>
         </is>
       </c>
-      <c r="AO36" s="22" t="inlineStr">
+      <c r="AO36" s="52" t="inlineStr">
         <is>
           <t>Down Shot、Neko、No Sinker 和 Small Rubber Jig 都是高压场常用组合，短尺让贴边落点和轻抖更好控制。</t>
         </is>
       </c>
-      <c r="AP36" s="22" t="inlineStr">
+      <c r="AP36" s="52" t="inlineStr">
         <is>
           <t>よりフィネスを簡単に。タフな状況でも１匹を逃さないスーパーフィネスロッド</t>
         </is>
       </c>
-      <c r="AQ36" s="22" t="inlineStr">
+      <c r="AQ36" s="52" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="AR36" s="22" t="inlineStr"/>
+      <c r="AR36" s="52" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="52" t="inlineStr">
         <is>
           <t>DSRD10035</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="52" t="inlineStr">
         <is>
           <t>DBTS-61UL+-S</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="52" t="inlineStr">
         <is>
           <t>UL+</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="52" t="inlineStr">
         <is>
           <t>6’1″</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr"/>
-      <c r="I37" s="22" t="inlineStr"/>
-      <c r="J37" s="22" t="inlineStr">
+      <c r="H37" s="52" t="inlineStr"/>
+      <c r="I37" s="52" t="inlineStr"/>
+      <c r="J37" s="52" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K37" s="22" t="inlineStr"/>
-      <c r="L37" s="22" t="inlineStr"/>
-      <c r="M37" s="22" t="inlineStr">
+      <c r="K37" s="52" t="inlineStr"/>
+      <c r="L37" s="52" t="inlineStr"/>
+      <c r="M37" s="52" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N37" s="22" t="inlineStr"/>
-      <c r="O37" s="22" t="inlineStr"/>
-      <c r="P37" s="22" t="inlineStr"/>
-      <c r="Q37" s="22" t="inlineStr"/>
-      <c r="R37" s="22" t="inlineStr">
+      <c r="N37" s="52" t="inlineStr"/>
+      <c r="O37" s="52" t="inlineStr"/>
+      <c r="P37" s="52" t="inlineStr"/>
+      <c r="Q37" s="52" t="inlineStr"/>
+      <c r="R37" s="52" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S37" s="22" t="inlineStr">
+      <c r="S37" s="52" t="inlineStr">
         <is>
           <t>4580484758339</t>
         </is>
       </c>
-      <c r="T37" s="22" t="inlineStr"/>
-      <c r="U37" s="22" t="inlineStr"/>
-      <c r="V37" s="22" t="inlineStr"/>
-      <c r="W37" s="22" t="inlineStr"/>
-      <c r="X37" s="22" t="inlineStr"/>
-      <c r="Y37" s="22" t="inlineStr"/>
-      <c r="Z37" s="22" t="inlineStr">
+      <c r="T37" s="52" t="inlineStr"/>
+      <c r="U37" s="52" t="inlineStr"/>
+      <c r="V37" s="52" t="inlineStr"/>
+      <c r="W37" s="52" t="inlineStr"/>
+      <c r="X37" s="52" t="inlineStr"/>
+      <c r="Y37" s="52" t="inlineStr"/>
+      <c r="Z37" s="52" t="inlineStr">
         <is>
           <t>1/32〜3/16</t>
         </is>
       </c>
-      <c r="AA37" s="22" t="inlineStr"/>
-      <c r="AB37" s="22" t="inlineStr"/>
-      <c r="AC37" s="22" t="inlineStr"/>
-      <c r="AD37" s="22" t="inlineStr"/>
-      <c r="AE37" s="22" t="inlineStr"/>
-      <c r="AF37" s="22" t="inlineStr"/>
-      <c r="AG37" s="22" t="inlineStr"/>
-      <c r="AH37" s="22" t="inlineStr">
+      <c r="AA37" s="52" t="inlineStr"/>
+      <c r="AB37" s="52" t="inlineStr"/>
+      <c r="AC37" s="52" t="inlineStr"/>
+      <c r="AD37" s="52" t="inlineStr"/>
+      <c r="AE37" s="52" t="inlineStr"/>
+      <c r="AF37" s="52" t="inlineStr"/>
+      <c r="AG37" s="52" t="inlineStr"/>
+      <c r="AH37" s="52" t="inlineStr">
         <is>
           <t>61UL+-S 是进化型 super finesse，UL+ solid 更适合轻量 Down Shot、Neko、Jighead 与 No Sinker；比普通 L power 更重视细节反馈。</t>
         </is>
       </c>
-      <c r="AI37" s="22" t="inlineStr">
+      <c r="AI37" s="52" t="inlineStr">
         <is>
           <t>Down Shot / Neko Rig / Jighead Rig / No Sinker</t>
         </is>
       </c>
-      <c r="AJ37" s="22" t="inlineStr"/>
-      <c r="AK37" s="22" t="inlineStr"/>
-      <c r="AL37" s="22" t="inlineStr"/>
-      <c r="AM37" s="22" t="inlineStr">
+      <c r="AJ37" s="52" t="inlineStr"/>
+      <c r="AK37" s="52" t="inlineStr"/>
+      <c r="AL37" s="52" t="inlineStr"/>
+      <c r="AM37" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 小型湖库・清水高压 / 轻量 finesse</t>
         </is>
       </c>
-      <c r="AN37" s="22" t="inlineStr">
+      <c r="AN37" s="52" t="inlineStr">
         <is>
           <t>UL+ 细线精细操作</t>
         </is>
       </c>
-      <c r="AO37" s="22" t="inlineStr">
+      <c r="AO37" s="52" t="inlineStr">
         <is>
           <t>Down Shot、Neko、Jighead、No Sinker 的轻量操作更稳，适合需要比 XUL 多一点支撑但仍重视细节反馈的玩家。</t>
         </is>
       </c>
-      <c r="AP37" s="22" t="inlineStr">
+      <c r="AP37" s="52" t="inlineStr">
         <is>
           <t>時を捉える事が出来る進化したスーパーフィネスモデル</t>
         </is>
       </c>
-      <c r="AQ37" s="22" t="inlineStr">
+      <c r="AQ37" s="52" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AR37" s="22" t="inlineStr"/>
+      <c r="AR37" s="52" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="52" t="inlineStr">
         <is>
           <t>DSRD10036</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="52" t="inlineStr">
         <is>
           <t>DBTS-61L</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="52" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="52" t="inlineStr">
         <is>
           <t>6’1″</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr"/>
-      <c r="I38" s="22" t="inlineStr"/>
-      <c r="J38" s="22" t="inlineStr">
+      <c r="H38" s="52" t="inlineStr"/>
+      <c r="I38" s="52" t="inlineStr"/>
+      <c r="J38" s="52" t="inlineStr">
         <is>
           <t>82g</t>
         </is>
       </c>
-      <c r="K38" s="22" t="inlineStr"/>
-      <c r="L38" s="22" t="inlineStr"/>
-      <c r="M38" s="22" t="inlineStr">
+      <c r="K38" s="52" t="inlineStr"/>
+      <c r="L38" s="52" t="inlineStr"/>
+      <c r="M38" s="52" t="inlineStr">
         <is>
           <t>2.5~8</t>
         </is>
       </c>
-      <c r="N38" s="22" t="inlineStr"/>
-      <c r="O38" s="22" t="inlineStr"/>
-      <c r="P38" s="22" t="inlineStr"/>
-      <c r="Q38" s="22" t="inlineStr"/>
-      <c r="R38" s="22" t="inlineStr">
+      <c r="N38" s="52" t="inlineStr"/>
+      <c r="O38" s="52" t="inlineStr"/>
+      <c r="P38" s="52" t="inlineStr"/>
+      <c r="Q38" s="52" t="inlineStr"/>
+      <c r="R38" s="52" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S38" s="22" t="inlineStr">
+      <c r="S38" s="52" t="inlineStr">
         <is>
           <t>4580484756953</t>
         </is>
       </c>
-      <c r="T38" s="22" t="inlineStr"/>
-      <c r="U38" s="22" t="inlineStr"/>
-      <c r="V38" s="22" t="inlineStr"/>
-      <c r="W38" s="22" t="inlineStr"/>
-      <c r="X38" s="22" t="inlineStr"/>
-      <c r="Y38" s="22" t="inlineStr"/>
-      <c r="Z38" s="22" t="inlineStr">
+      <c r="T38" s="52" t="inlineStr"/>
+      <c r="U38" s="52" t="inlineStr"/>
+      <c r="V38" s="52" t="inlineStr"/>
+      <c r="W38" s="52" t="inlineStr"/>
+      <c r="X38" s="52" t="inlineStr"/>
+      <c r="Y38" s="52" t="inlineStr"/>
+      <c r="Z38" s="52" t="inlineStr">
         <is>
           <t>1/32～1/4</t>
         </is>
       </c>
-      <c r="AA38" s="22" t="inlineStr"/>
-      <c r="AB38" s="22" t="inlineStr"/>
-      <c r="AC38" s="22" t="inlineStr"/>
-      <c r="AD38" s="22" t="inlineStr"/>
-      <c r="AE38" s="22" t="inlineStr"/>
-      <c r="AF38" s="22" t="inlineStr"/>
-      <c r="AG38" s="22" t="inlineStr"/>
-      <c r="AH38" s="22" t="inlineStr">
+      <c r="AA38" s="52" t="inlineStr"/>
+      <c r="AB38" s="52" t="inlineStr"/>
+      <c r="AC38" s="52" t="inlineStr"/>
+      <c r="AD38" s="52" t="inlineStr"/>
+      <c r="AE38" s="52" t="inlineStr"/>
+      <c r="AF38" s="52" t="inlineStr"/>
+      <c r="AG38" s="52" t="inlineStr"/>
+      <c r="AH38" s="52" t="inlineStr">
         <is>
           <t>61L 是 super all-round spinning，但白名单实钓明确支持 Neko；因此以 Neko、Down Shot、No Sinker 和 Small Rubber Jig 为主，小型 Plug 作为轻量搜索补充。</t>
         </is>
       </c>
-      <c r="AI38" s="22" t="inlineStr">
+      <c r="AI38" s="52" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Plug</t>
         </is>
       </c>
-      <c r="AJ38" s="22" t="inlineStr"/>
-      <c r="AK38" s="22" t="inlineStr"/>
-      <c r="AL38" s="22" t="inlineStr"/>
-      <c r="AM38" s="22" t="inlineStr">
+      <c r="AJ38" s="52" t="inlineStr"/>
+      <c r="AK38" s="52" t="inlineStr"/>
+      <c r="AL38" s="52" t="inlineStr"/>
+      <c r="AM38" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 水库・清水岸钓 / Neko 与细线 light finesse</t>
         </is>
       </c>
-      <c r="AN38" s="22" t="inlineStr">
+      <c r="AN38" s="52" t="inlineStr">
         <is>
           <t>Neko 主轴轻量泛用</t>
         </is>
       </c>
-      <c r="AO38" s="22" t="inlineStr">
+      <c r="AO38" s="52" t="inlineStr">
         <is>
           <t>Neko Rig 实战适配度高，Down Shot、No Sinker、Small Rubber Jig 和 Small Plug 能补齐食わせ到轻搜索的路线。</t>
         </is>
       </c>
-      <c r="AP38" s="22" t="inlineStr">
+      <c r="AP38" s="52" t="inlineStr">
         <is>
           <t>時を捉える事が出来るスーパーオールラウンドモデル</t>
         </is>
       </c>
-      <c r="AQ38" s="22" t="inlineStr">
+      <c r="AQ38" s="52" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AR38" s="22" t="inlineStr"/>
+      <c r="AR38" s="52" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="52" t="inlineStr">
         <is>
           <t>DSRD10037</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
+      <c r="B39" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C39" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D39" s="52" t="inlineStr">
         <is>
           <t>DBTS-63UL-MIDSP</t>
         </is>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+      <c r="E39" s="52" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="52" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G39" s="22" t="inlineStr">
+      <c r="G39" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H39" s="22" t="inlineStr"/>
-      <c r="I39" s="22" t="inlineStr"/>
-      <c r="J39" s="22" t="inlineStr">
+      <c r="H39" s="52" t="inlineStr"/>
+      <c r="I39" s="52" t="inlineStr"/>
+      <c r="J39" s="52" t="inlineStr">
         <is>
           <t>82g</t>
         </is>
       </c>
-      <c r="K39" s="22" t="inlineStr"/>
-      <c r="L39" s="22" t="inlineStr"/>
-      <c r="M39" s="22" t="inlineStr">
+      <c r="K39" s="52" t="inlineStr"/>
+      <c r="L39" s="52" t="inlineStr"/>
+      <c r="M39" s="52" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N39" s="22" t="inlineStr"/>
-      <c r="O39" s="22" t="inlineStr"/>
-      <c r="P39" s="22" t="inlineStr"/>
-      <c r="Q39" s="22" t="inlineStr"/>
-      <c r="R39" s="22" t="inlineStr">
+      <c r="N39" s="52" t="inlineStr"/>
+      <c r="O39" s="52" t="inlineStr"/>
+      <c r="P39" s="52" t="inlineStr"/>
+      <c r="Q39" s="52" t="inlineStr"/>
+      <c r="R39" s="52" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S39" s="22" t="inlineStr">
+      <c r="S39" s="52" t="inlineStr">
         <is>
           <t>4580484758346</t>
         </is>
       </c>
-      <c r="T39" s="22" t="inlineStr"/>
-      <c r="U39" s="22" t="inlineStr"/>
-      <c r="V39" s="22" t="inlineStr"/>
-      <c r="W39" s="22" t="inlineStr"/>
-      <c r="X39" s="22" t="inlineStr"/>
-      <c r="Y39" s="22" t="inlineStr"/>
-      <c r="Z39" s="22" t="inlineStr">
+      <c r="T39" s="52" t="inlineStr"/>
+      <c r="U39" s="52" t="inlineStr"/>
+      <c r="V39" s="52" t="inlineStr"/>
+      <c r="W39" s="52" t="inlineStr"/>
+      <c r="X39" s="52" t="inlineStr"/>
+      <c r="Y39" s="52" t="inlineStr"/>
+      <c r="Z39" s="52" t="inlineStr">
         <is>
           <t>1/32～3/16</t>
         </is>
       </c>
-      <c r="AA39" s="22" t="inlineStr"/>
-      <c r="AB39" s="22" t="inlineStr"/>
-      <c r="AC39" s="22" t="inlineStr"/>
-      <c r="AD39" s="22" t="inlineStr"/>
-      <c r="AE39" s="22" t="inlineStr"/>
-      <c r="AF39" s="22" t="inlineStr"/>
-      <c r="AG39" s="22" t="inlineStr"/>
-      <c r="AH39" s="22" t="inlineStr">
+      <c r="AA39" s="52" t="inlineStr"/>
+      <c r="AB39" s="52" t="inlineStr"/>
+      <c r="AC39" s="52" t="inlineStr"/>
+      <c r="AD39" s="52" t="inlineStr"/>
+      <c r="AE39" s="52" t="inlineStr"/>
+      <c r="AF39" s="52" t="inlineStr"/>
+      <c r="AG39" s="52" t="inlineStr"/>
+      <c r="AH39" s="52" t="inlineStr">
         <is>
           <t>63UL-MIDSP 明确是 mid-strolling rod，Jighead/Hover Strolling 优先，Down Shot 和 No Sinker 只作为同样需要线弧与轻抖的补充。</t>
         </is>
       </c>
-      <c r="AI39" s="22" t="inlineStr">
+      <c r="AI39" s="52" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Hover Strolling / Down Shot / No Sinker</t>
         </is>
       </c>
-      <c r="AJ39" s="22" t="inlineStr"/>
-      <c r="AK39" s="22" t="inlineStr"/>
-      <c r="AL39" s="22" t="inlineStr"/>
-      <c r="AM39" s="22" t="inlineStr">
+      <c r="AJ39" s="52" t="inlineStr"/>
+      <c r="AK39" s="52" t="inlineStr"/>
+      <c r="AL39" s="52" t="inlineStr"/>
+      <c r="AM39" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水・中层悬浮鱼 / mid strolling</t>
         </is>
       </c>
-      <c r="AN39" s="22" t="inlineStr">
+      <c r="AN39" s="52" t="inlineStr">
         <is>
           <t>轻量 Mid Strolling 专向</t>
         </is>
       </c>
-      <c r="AO39" s="22" t="inlineStr">
+      <c r="AO39" s="52" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead 和 Hover Strolling 是主轴，Down Shot、No Sinker 可按同样线弧和轻抖逻辑补充。</t>
         </is>
       </c>
-      <c r="AP39" s="22" t="inlineStr">
+      <c r="AP39" s="52" t="inlineStr">
         <is>
           <t>無双できるミッドストローリングロッド</t>
         </is>
       </c>
-      <c r="AQ39" s="22" t="inlineStr">
+      <c r="AQ39" s="52" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="AR39" s="22" t="inlineStr"/>
+      <c r="AR39" s="52" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="52" t="inlineStr">
         <is>
           <t>DSRD10038</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
+      <c r="B40" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="C40" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D40" s="52" t="inlineStr">
         <is>
           <t>DBTS-65L+</t>
         </is>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="52" t="inlineStr">
         <is>
           <t>L+</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F40" s="52" t="inlineStr">
         <is>
           <t>6’5″</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr">
+      <c r="G40" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H40" s="22" t="inlineStr"/>
-      <c r="I40" s="22" t="inlineStr"/>
-      <c r="J40" s="22" t="inlineStr">
+      <c r="H40" s="52" t="inlineStr"/>
+      <c r="I40" s="52" t="inlineStr"/>
+      <c r="J40" s="52" t="inlineStr">
         <is>
           <t>82g</t>
         </is>
       </c>
-      <c r="K40" s="22" t="inlineStr"/>
-      <c r="L40" s="22" t="inlineStr"/>
-      <c r="M40" s="22" t="inlineStr">
+      <c r="K40" s="52" t="inlineStr"/>
+      <c r="L40" s="52" t="inlineStr"/>
+      <c r="M40" s="52" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N40" s="22" t="inlineStr"/>
-      <c r="O40" s="22" t="inlineStr"/>
-      <c r="P40" s="22" t="inlineStr"/>
-      <c r="Q40" s="22" t="inlineStr"/>
-      <c r="R40" s="22" t="inlineStr">
+      <c r="N40" s="52" t="inlineStr"/>
+      <c r="O40" s="52" t="inlineStr"/>
+      <c r="P40" s="52" t="inlineStr"/>
+      <c r="Q40" s="52" t="inlineStr"/>
+      <c r="R40" s="52" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S40" s="22" t="inlineStr">
+      <c r="S40" s="52" t="inlineStr">
         <is>
           <t>4580484756960</t>
         </is>
       </c>
-      <c r="T40" s="22" t="inlineStr"/>
-      <c r="U40" s="22" t="inlineStr"/>
-      <c r="V40" s="22" t="inlineStr"/>
-      <c r="W40" s="22" t="inlineStr"/>
-      <c r="X40" s="22" t="inlineStr"/>
-      <c r="Y40" s="22" t="inlineStr"/>
-      <c r="Z40" s="22" t="inlineStr">
+      <c r="T40" s="52" t="inlineStr"/>
+      <c r="U40" s="52" t="inlineStr"/>
+      <c r="V40" s="52" t="inlineStr"/>
+      <c r="W40" s="52" t="inlineStr"/>
+      <c r="X40" s="52" t="inlineStr"/>
+      <c r="Y40" s="52" t="inlineStr"/>
+      <c r="Z40" s="52" t="inlineStr">
         <is>
           <t>1/32～1/4</t>
         </is>
       </c>
-      <c r="AA40" s="22" t="inlineStr"/>
-      <c r="AB40" s="22" t="inlineStr"/>
-      <c r="AC40" s="22" t="inlineStr"/>
-      <c r="AD40" s="22" t="inlineStr"/>
-      <c r="AE40" s="22" t="inlineStr"/>
-      <c r="AF40" s="22" t="inlineStr"/>
-      <c r="AG40" s="22" t="inlineStr"/>
-      <c r="AH40" s="22" t="inlineStr">
+      <c r="AA40" s="52" t="inlineStr"/>
+      <c r="AB40" s="52" t="inlineStr"/>
+      <c r="AC40" s="52" t="inlineStr"/>
+      <c r="AD40" s="52" t="inlineStr"/>
+      <c r="AE40" s="52" t="inlineStr"/>
+      <c r="AF40" s="52" t="inlineStr"/>
+      <c r="AG40" s="52" t="inlineStr"/>
+      <c r="AH40" s="52" t="inlineStr">
         <is>
           <t>65L+ 是兼具 long distance 和细致度的 light versatile，Neko、Down Shot、No Sinker 负责食わせ，Small Minnow 负责远处搜索。</t>
         </is>
       </c>
-      <c r="AI40" s="22" t="inlineStr">
+      <c r="AI40" s="52" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / Small Minnow / No Sinker</t>
         </is>
       </c>
-      <c r="AJ40" s="22" t="inlineStr"/>
-      <c r="AK40" s="22" t="inlineStr"/>
-      <c r="AL40" s="22" t="inlineStr"/>
-      <c r="AM40" s="22" t="inlineStr">
+      <c r="AJ40" s="52" t="inlineStr"/>
+      <c r="AK40" s="52" t="inlineStr"/>
+      <c r="AL40" s="52" t="inlineStr"/>
+      <c r="AM40" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓远投・开阔水 / finesse 与 Small Minnow</t>
         </is>
       </c>
-      <c r="AN40" s="22" t="inlineStr">
+      <c r="AN40" s="52" t="inlineStr">
         <is>
           <t>远投轻量软硬饵泛用</t>
         </is>
       </c>
-      <c r="AO40" s="22" t="inlineStr">
+      <c r="AO40" s="52" t="inlineStr">
         <is>
           <t>Neko、Down Shot、No Sinker 用于食わせ，Small Minnow 用于远处搜索；L+ power 让轻量路线多一点距离和控鱼余量。</t>
         </is>
       </c>
-      <c r="AP40" s="22" t="inlineStr">
+      <c r="AP40" s="52" t="inlineStr">
         <is>
           <t>ロングディスタンスと繊細さを併せ持ったバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ40" s="22" t="inlineStr">
+      <c r="AQ40" s="52" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="AR40" s="22" t="inlineStr"/>
+      <c r="AR40" s="52" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="52" t="inlineStr">
         <is>
           <t>DSRD10039</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr">
+      <c r="B41" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C41" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D41" s="52" t="inlineStr">
         <is>
           <t>DBTS-66ML-S-MIDSP</t>
         </is>
       </c>
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E41" s="52" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="52" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
+      <c r="G41" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H41" s="22" t="inlineStr"/>
-      <c r="I41" s="22" t="inlineStr"/>
-      <c r="J41" s="22" t="inlineStr">
+      <c r="H41" s="52" t="inlineStr"/>
+      <c r="I41" s="52" t="inlineStr"/>
+      <c r="J41" s="52" t="inlineStr">
         <is>
           <t>88g</t>
         </is>
       </c>
-      <c r="K41" s="22" t="inlineStr"/>
-      <c r="L41" s="22" t="inlineStr"/>
-      <c r="M41" s="22" t="inlineStr">
+      <c r="K41" s="52" t="inlineStr"/>
+      <c r="L41" s="52" t="inlineStr"/>
+      <c r="M41" s="52" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N41" s="22" t="inlineStr">
+      <c r="N41" s="52" t="inlineStr">
         <is>
           <t>0.4~1</t>
         </is>
       </c>
-      <c r="O41" s="22" t="inlineStr"/>
-      <c r="P41" s="22" t="inlineStr"/>
-      <c r="Q41" s="22" t="inlineStr"/>
-      <c r="R41" s="22" t="inlineStr">
+      <c r="O41" s="52" t="inlineStr"/>
+      <c r="P41" s="52" t="inlineStr"/>
+      <c r="Q41" s="52" t="inlineStr"/>
+      <c r="R41" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S41" s="22" t="inlineStr">
+      <c r="S41" s="52" t="inlineStr">
         <is>
           <t>4571527862120</t>
         </is>
       </c>
-      <c r="T41" s="22" t="inlineStr"/>
-      <c r="U41" s="22" t="inlineStr"/>
-      <c r="V41" s="22" t="inlineStr"/>
-      <c r="W41" s="22" t="inlineStr"/>
-      <c r="X41" s="22" t="inlineStr"/>
-      <c r="Y41" s="22" t="inlineStr"/>
-      <c r="Z41" s="22" t="inlineStr">
+      <c r="T41" s="52" t="inlineStr"/>
+      <c r="U41" s="52" t="inlineStr"/>
+      <c r="V41" s="52" t="inlineStr"/>
+      <c r="W41" s="52" t="inlineStr"/>
+      <c r="X41" s="52" t="inlineStr"/>
+      <c r="Y41" s="52" t="inlineStr"/>
+      <c r="Z41" s="52" t="inlineStr">
         <is>
           <t>1/32～1/4</t>
         </is>
       </c>
-      <c r="AA41" s="22" t="inlineStr"/>
-      <c r="AB41" s="22" t="inlineStr"/>
-      <c r="AC41" s="22" t="inlineStr"/>
-      <c r="AD41" s="22" t="inlineStr"/>
-      <c r="AE41" s="22" t="inlineStr"/>
-      <c r="AF41" s="22" t="inlineStr"/>
-      <c r="AG41" s="22" t="inlineStr"/>
-      <c r="AH41" s="22" t="inlineStr">
+      <c r="AA41" s="52" t="inlineStr"/>
+      <c r="AB41" s="52" t="inlineStr"/>
+      <c r="AC41" s="52" t="inlineStr"/>
+      <c r="AD41" s="52" t="inlineStr"/>
+      <c r="AE41" s="52" t="inlineStr"/>
+      <c r="AF41" s="52" t="inlineStr"/>
+      <c r="AG41" s="52" t="inlineStr"/>
+      <c r="AH41" s="52" t="inlineStr">
         <is>
           <t>66ML-S-MIDSP 以 mid-strolling 为主，白名单 No Sinker 实例可补强中层软饵操作；Small Plug 是远投轻搜索，不应盖过 mid-strolling 主轴。</t>
         </is>
       </c>
-      <c r="AI41" s="22" t="inlineStr">
+      <c r="AI41" s="52" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / No Sinker / Hover Strolling / Small Plug</t>
         </is>
       </c>
-      <c r="AJ41" s="22" t="inlineStr"/>
-      <c r="AK41" s="22" t="inlineStr"/>
-      <c r="AL41" s="22" t="inlineStr"/>
-      <c r="AM41" s="22" t="inlineStr">
+      <c r="AJ41" s="52" t="inlineStr"/>
+      <c r="AK41" s="52" t="inlineStr"/>
+      <c r="AL41" s="52" t="inlineStr"/>
+      <c r="AM41" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 池・野池・开阔水 / mid strolling 与 No Sinker</t>
         </is>
       </c>
-      <c r="AN41" s="22" t="inlineStr">
+      <c r="AN41" s="52" t="inlineStr">
         <is>
           <t>ML solid 中层游动</t>
         </is>
       </c>
-      <c r="AO41" s="22" t="inlineStr">
+      <c r="AO41" s="52" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead 是主线，No Sinker 和 Hover Strolling 能处理更弱波动的中层鱼，小 Plug 只作为轻搜索补充。</t>
         </is>
       </c>
-      <c r="AP41" s="22" t="inlineStr">
+      <c r="AP41" s="52" t="inlineStr">
         <is>
           <t>無双できるミッドストローリングロッド</t>
         </is>
       </c>
-      <c r="AQ41" s="22" t="inlineStr">
+      <c r="AQ41" s="52" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR41" s="22" t="inlineStr"/>
+      <c r="AR41" s="52" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="52" t="inlineStr">
         <is>
           <t>DSRD10040</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B42" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C42" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D42" s="52" t="inlineStr">
         <is>
           <t>DBTS-66M</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E42" s="52" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="52" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="G42" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H42" s="22" t="inlineStr"/>
-      <c r="I42" s="22" t="inlineStr"/>
-      <c r="J42" s="22" t="inlineStr">
+      <c r="H42" s="52" t="inlineStr"/>
+      <c r="I42" s="52" t="inlineStr"/>
+      <c r="J42" s="52" t="inlineStr">
         <is>
           <t>91g</t>
         </is>
       </c>
-      <c r="K42" s="22" t="inlineStr"/>
-      <c r="L42" s="22" t="inlineStr"/>
-      <c r="M42" s="22" t="inlineStr">
+      <c r="K42" s="52" t="inlineStr"/>
+      <c r="L42" s="52" t="inlineStr"/>
+      <c r="M42" s="52" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N42" s="22" t="inlineStr">
+      <c r="N42" s="52" t="inlineStr">
         <is>
           <t>0.6~1.5</t>
         </is>
       </c>
-      <c r="O42" s="22" t="inlineStr"/>
-      <c r="P42" s="22" t="inlineStr"/>
-      <c r="Q42" s="22" t="inlineStr"/>
-      <c r="R42" s="22" t="inlineStr">
+      <c r="O42" s="52" t="inlineStr"/>
+      <c r="P42" s="52" t="inlineStr"/>
+      <c r="Q42" s="52" t="inlineStr"/>
+      <c r="R42" s="52" t="inlineStr">
         <is>
           <t>¥28,500 （税込￥31,350）</t>
         </is>
       </c>
-      <c r="S42" s="22" t="inlineStr">
+      <c r="S42" s="52" t="inlineStr">
         <is>
           <t>4580484756977</t>
         </is>
       </c>
-      <c r="T42" s="22" t="inlineStr"/>
-      <c r="U42" s="22" t="inlineStr"/>
-      <c r="V42" s="22" t="inlineStr"/>
-      <c r="W42" s="22" t="inlineStr"/>
-      <c r="X42" s="22" t="inlineStr"/>
-      <c r="Y42" s="22" t="inlineStr"/>
-      <c r="Z42" s="22" t="inlineStr">
+      <c r="T42" s="52" t="inlineStr"/>
+      <c r="U42" s="52" t="inlineStr"/>
+      <c r="V42" s="52" t="inlineStr"/>
+      <c r="W42" s="52" t="inlineStr"/>
+      <c r="X42" s="52" t="inlineStr"/>
+      <c r="Y42" s="52" t="inlineStr"/>
+      <c r="Z42" s="52" t="inlineStr">
         <is>
           <t>1/16～3/8</t>
         </is>
       </c>
-      <c r="AA42" s="22" t="inlineStr"/>
-      <c r="AB42" s="22" t="inlineStr"/>
-      <c r="AC42" s="22" t="inlineStr"/>
-      <c r="AD42" s="22" t="inlineStr"/>
-      <c r="AE42" s="22" t="inlineStr"/>
-      <c r="AF42" s="22" t="inlineStr"/>
-      <c r="AG42" s="22" t="inlineStr"/>
-      <c r="AH42" s="22" t="inlineStr">
+      <c r="AA42" s="52" t="inlineStr"/>
+      <c r="AB42" s="52" t="inlineStr"/>
+      <c r="AC42" s="52" t="inlineStr"/>
+      <c r="AD42" s="52" t="inlineStr"/>
+      <c r="AE42" s="52" t="inlineStr"/>
+      <c r="AF42" s="52" t="inlineStr"/>
+      <c r="AG42" s="52" t="inlineStr"/>
+      <c r="AH42" s="52" t="inlineStr">
         <is>
           <t>66M 是 power finesse spin，重点是 PE 下的 Cover Neko、Small Rubber Jig 和偏重 No Sinker，把轻量精细推进到 cover 与远投场景。</t>
         </is>
       </c>
-      <c r="AI42" s="22" t="inlineStr">
+      <c r="AI42" s="52" t="inlineStr">
         <is>
           <t>Power Finesse / Cover Neko / Small Rubber Jig / No Sinker</t>
         </is>
       </c>
-      <c r="AJ42" s="22" t="inlineStr"/>
-      <c r="AK42" s="22" t="inlineStr"/>
-      <c r="AL42" s="22" t="inlineStr"/>
-      <c r="AM42" s="22" t="inlineStr">
+      <c r="AJ42" s="52" t="inlineStr"/>
+      <c r="AK42" s="52" t="inlineStr"/>
+      <c r="AL42" s="52" t="inlineStr"/>
+      <c r="AM42" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 边缘・远投点 / spinning power finesse</t>
         </is>
       </c>
-      <c r="AN42" s="22" t="inlineStr">
+      <c r="AN42" s="52" t="inlineStr">
         <is>
           <t>M power finesse spinning</t>
         </is>
       </c>
-      <c r="AO42" s="22" t="inlineStr">
+      <c r="AO42" s="52" t="inlineStr">
         <is>
           <t>Power Finesse、Cover Neko 和 Small Rubber Jig 的控鱼力比轻量 spinning 更充足，适合细线体系下处理更厚的 cover。</t>
         </is>
       </c>
-      <c r="AP42" s="22" t="inlineStr">
+      <c r="AP42" s="52" t="inlineStr">
         <is>
           <t>キャスタビリティーとパワーを追求したパワーフィネススピン</t>
         </is>
       </c>
-      <c r="AQ42" s="22" t="inlineStr">
+      <c r="AQ42" s="52" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR42" s="22" t="inlineStr"/>
+      <c r="AR42" s="52" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="52" t="inlineStr">
         <is>
           <t>DSRD10041</t>
         </is>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B43" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C43" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D43" s="22" t="inlineStr">
+      <c r="D43" s="52" t="inlineStr">
         <is>
           <t>DBTS-68H-S-PF</t>
         </is>
       </c>
-      <c r="E43" s="22" t="inlineStr">
+      <c r="E43" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="52" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G43" s="22" t="inlineStr">
+      <c r="G43" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H43" s="22" t="inlineStr"/>
-      <c r="I43" s="22" t="inlineStr"/>
-      <c r="J43" s="22" t="inlineStr">
+      <c r="H43" s="52" t="inlineStr"/>
+      <c r="I43" s="52" t="inlineStr"/>
+      <c r="J43" s="52" t="inlineStr">
         <is>
           <t>108g</t>
         </is>
       </c>
-      <c r="K43" s="22" t="inlineStr"/>
-      <c r="L43" s="22" t="inlineStr"/>
-      <c r="M43" s="22" t="inlineStr"/>
-      <c r="N43" s="22" t="inlineStr">
+      <c r="K43" s="52" t="inlineStr"/>
+      <c r="L43" s="52" t="inlineStr"/>
+      <c r="M43" s="52" t="inlineStr"/>
+      <c r="N43" s="52" t="inlineStr">
         <is>
           <t>MAX ~2.5</t>
         </is>
       </c>
-      <c r="O43" s="22" t="inlineStr"/>
-      <c r="P43" s="22" t="inlineStr"/>
-      <c r="Q43" s="22" t="inlineStr"/>
-      <c r="R43" s="22" t="inlineStr">
+      <c r="O43" s="52" t="inlineStr"/>
+      <c r="P43" s="52" t="inlineStr"/>
+      <c r="Q43" s="52" t="inlineStr"/>
+      <c r="R43" s="52" t="inlineStr">
         <is>
           <t>¥28,500 （税込￥31,350）</t>
         </is>
       </c>
-      <c r="S43" s="22" t="inlineStr">
+      <c r="S43" s="52" t="inlineStr">
         <is>
           <t>4580484758353</t>
         </is>
       </c>
-      <c r="T43" s="22" t="inlineStr"/>
-      <c r="U43" s="22" t="inlineStr"/>
-      <c r="V43" s="22" t="inlineStr"/>
-      <c r="W43" s="22" t="inlineStr"/>
-      <c r="X43" s="22" t="inlineStr"/>
-      <c r="Y43" s="22" t="inlineStr"/>
-      <c r="Z43" s="22" t="inlineStr">
+      <c r="T43" s="52" t="inlineStr"/>
+      <c r="U43" s="52" t="inlineStr"/>
+      <c r="V43" s="52" t="inlineStr"/>
+      <c r="W43" s="52" t="inlineStr"/>
+      <c r="X43" s="52" t="inlineStr"/>
+      <c r="Y43" s="52" t="inlineStr"/>
+      <c r="Z43" s="52" t="inlineStr">
         <is>
           <t>1/8～3/4</t>
         </is>
       </c>
-      <c r="AA43" s="22" t="inlineStr"/>
-      <c r="AB43" s="22" t="inlineStr"/>
-      <c r="AC43" s="22" t="inlineStr"/>
-      <c r="AD43" s="22" t="inlineStr"/>
-      <c r="AE43" s="22" t="inlineStr"/>
-      <c r="AF43" s="22" t="inlineStr"/>
-      <c r="AG43" s="22" t="inlineStr"/>
-      <c r="AH43" s="22" t="inlineStr">
+      <c r="AA43" s="52" t="inlineStr"/>
+      <c r="AB43" s="52" t="inlineStr"/>
+      <c r="AC43" s="52" t="inlineStr"/>
+      <c r="AD43" s="52" t="inlineStr"/>
+      <c r="AE43" s="52" t="inlineStr"/>
+      <c r="AF43" s="52" t="inlineStr"/>
+      <c r="AG43" s="52" t="inlineStr"/>
+      <c r="AH43" s="52" t="inlineStr">
         <is>
           <t>68H-S-PF 明确面向高压 cover power finesse，H power solid 负责把鱼从 cover 中带出；Cover Neko、Small Rubber Jig 和高比重 No Sinker 是主要用途。</t>
         </is>
       </c>
-      <c r="AI43" s="22" t="inlineStr">
+      <c r="AI43" s="52" t="inlineStr">
         <is>
           <t>Power Finesse / Cover Neko / Small Rubber Jig / High-density No Sinker</t>
         </is>
       </c>
-      <c r="AJ43" s="22" t="inlineStr"/>
-      <c r="AK43" s="22" t="inlineStr"/>
-      <c r="AL43" s="22" t="inlineStr"/>
-      <c r="AM43" s="22" t="inlineStr">
+      <c r="AJ43" s="52" t="inlineStr"/>
+      <c r="AK43" s="52" t="inlineStr"/>
+      <c r="AL43" s="52" t="inlineStr"/>
+      <c r="AM43" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压重 cover・草洞 / heavy power finesse</t>
         </is>
       </c>
-      <c r="AN43" s="22" t="inlineStr">
+      <c r="AN43" s="52" t="inlineStr">
         <is>
           <t>H solid power finesse</t>
         </is>
       </c>
-      <c r="AO43" s="22" t="inlineStr">
+      <c r="AO43" s="52" t="inlineStr">
         <is>
           <t>Cover Neko、Small Rubber Jig 和高比重 No Sinker 进 cover 后有足够竿身支撑，适合 PE 强行控鱼。</t>
         </is>
       </c>
-      <c r="AP43" s="22" t="inlineStr">
+      <c r="AP43" s="52" t="inlineStr">
         <is>
           <t>ハイプレッシャーカバーを侵略せよ！！パワーフィネスモデル</t>
         </is>
       </c>
-      <c r="AQ43" s="22" t="inlineStr">
+      <c r="AQ43" s="52" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR43" s="22" t="inlineStr"/>
+      <c r="AR43" s="52" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="52" t="inlineStr">
         <is>
           <t>DSRD10042</t>
         </is>
       </c>
-      <c r="B44" s="22" t="inlineStr">
+      <c r="B44" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C44" s="22" t="inlineStr">
+      <c r="C44" s="52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D44" s="22" t="inlineStr">
+      <c r="D44" s="52" t="inlineStr">
         <is>
           <t>DBTS-610L-S</t>
         </is>
       </c>
-      <c r="E44" s="22" t="inlineStr">
+      <c r="E44" s="52" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F44" s="22" t="inlineStr">
+      <c r="F44" s="52" t="inlineStr">
         <is>
           <t>6’10”</t>
         </is>
       </c>
-      <c r="G44" s="22" t="inlineStr">
+      <c r="G44" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H44" s="22" t="inlineStr"/>
-      <c r="I44" s="22" t="inlineStr"/>
-      <c r="J44" s="22" t="inlineStr">
+      <c r="H44" s="52" t="inlineStr"/>
+      <c r="I44" s="52" t="inlineStr"/>
+      <c r="J44" s="52" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="K44" s="22" t="inlineStr"/>
-      <c r="L44" s="22" t="inlineStr"/>
-      <c r="M44" s="22" t="inlineStr">
+      <c r="K44" s="52" t="inlineStr"/>
+      <c r="L44" s="52" t="inlineStr"/>
+      <c r="M44" s="52" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N44" s="22" t="inlineStr">
+      <c r="N44" s="52" t="inlineStr">
         <is>
           <t>0.4~1</t>
         </is>
       </c>
-      <c r="O44" s="22" t="inlineStr"/>
-      <c r="P44" s="22" t="inlineStr"/>
-      <c r="Q44" s="22" t="inlineStr"/>
-      <c r="R44" s="22" t="inlineStr">
+      <c r="O44" s="52" t="inlineStr"/>
+      <c r="P44" s="52" t="inlineStr"/>
+      <c r="Q44" s="52" t="inlineStr"/>
+      <c r="R44" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S44" s="22" t="inlineStr">
+      <c r="S44" s="52" t="inlineStr">
         <is>
           <t>4571527860713</t>
         </is>
       </c>
-      <c r="T44" s="22" t="inlineStr"/>
-      <c r="U44" s="22" t="inlineStr"/>
-      <c r="V44" s="22" t="inlineStr"/>
-      <c r="W44" s="22" t="inlineStr"/>
-      <c r="X44" s="22" t="inlineStr"/>
-      <c r="Y44" s="22" t="inlineStr"/>
-      <c r="Z44" s="22" t="inlineStr">
+      <c r="T44" s="52" t="inlineStr"/>
+      <c r="U44" s="52" t="inlineStr"/>
+      <c r="V44" s="52" t="inlineStr"/>
+      <c r="W44" s="52" t="inlineStr"/>
+      <c r="X44" s="52" t="inlineStr"/>
+      <c r="Y44" s="52" t="inlineStr"/>
+      <c r="Z44" s="52" t="inlineStr">
         <is>
           <t>1/16～1/4</t>
         </is>
       </c>
-      <c r="AA44" s="22" t="inlineStr"/>
-      <c r="AB44" s="22" t="inlineStr"/>
-      <c r="AC44" s="22" t="inlineStr"/>
-      <c r="AD44" s="22" t="inlineStr"/>
-      <c r="AE44" s="22" t="inlineStr"/>
-      <c r="AF44" s="22" t="inlineStr"/>
-      <c r="AG44" s="22" t="inlineStr"/>
-      <c r="AH44" s="22" t="inlineStr">
+      <c r="AA44" s="52" t="inlineStr"/>
+      <c r="AB44" s="52" t="inlineStr"/>
+      <c r="AC44" s="52" t="inlineStr"/>
+      <c r="AD44" s="52" t="inlineStr"/>
+      <c r="AE44" s="52" t="inlineStr"/>
+      <c r="AF44" s="52" t="inlineStr"/>
+      <c r="AG44" s="52" t="inlineStr"/>
+      <c r="AH44" s="52" t="inlineStr">
         <is>
           <t>610L-S 是 long shooting special，白名单和描述都支持远投 light finesse 与表层/I-shaped plug；Neko 远投和 Small Rubber Jig 放在精细端。</t>
         </is>
       </c>
-      <c r="AI44" s="22" t="inlineStr">
+      <c r="AI44" s="52" t="inlineStr">
         <is>
           <t>Long Cast Neko Rig / I-shaped Plug / Surface Plug / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ44" s="22" t="inlineStr"/>
-      <c r="AK44" s="22" t="inlineStr"/>
-      <c r="AL44" s="22" t="inlineStr"/>
-      <c r="AM44" s="22" t="inlineStr">
+      <c r="AJ44" s="52" t="inlineStr"/>
+      <c r="AK44" s="52" t="inlineStr"/>
+      <c r="AL44" s="52" t="inlineStr"/>
+      <c r="AM44" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓远投・开放水・表层 / long shooting finesse</t>
         </is>
       </c>
-      <c r="AN44" s="22" t="inlineStr">
+      <c r="AN44" s="52" t="inlineStr">
         <is>
           <t>远投 Neko 与表层轻搜索</t>
         </is>
       </c>
-      <c r="AO44" s="22" t="inlineStr">
+      <c r="AO44" s="52" t="inlineStr">
         <is>
           <t>Long Cast Neko、I-shaped Plug、Surface Plug 和 Small Rubber Jig 都围绕距离展开，适合想把轻量路线送到更远标点的玩家。</t>
         </is>
       </c>
-      <c r="AP44" s="22" t="inlineStr">
+      <c r="AP44" s="52" t="inlineStr">
         <is>
           <t>ロングシューティングスペシャル</t>
         </is>
       </c>
-      <c r="AQ44" s="22" t="inlineStr">
+      <c r="AQ44" s="52" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="AR44" s="22" t="inlineStr"/>
+      <c r="AR44" s="52" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="52" t="inlineStr">
         <is>
           <t>DSRD10043</t>
         </is>
       </c>
-      <c r="B45" s="22" t="inlineStr">
+      <c r="B45" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C45" s="22" t="inlineStr">
+      <c r="C45" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D45" s="22" t="inlineStr">
+      <c r="D45" s="52" t="inlineStr">
         <is>
           <t>DBTC-64ML-FM</t>
         </is>
       </c>
-      <c r="E45" s="22" t="inlineStr">
+      <c r="E45" s="52" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F45" s="22" t="inlineStr">
+      <c r="F45" s="52" t="inlineStr">
         <is>
           <t>6’4″</t>
         </is>
       </c>
-      <c r="G45" s="22" t="inlineStr">
+      <c r="G45" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H45" s="22" t="inlineStr"/>
-      <c r="I45" s="22" t="inlineStr"/>
-      <c r="J45" s="22" t="inlineStr">
+      <c r="H45" s="52" t="inlineStr"/>
+      <c r="I45" s="52" t="inlineStr"/>
+      <c r="J45" s="52" t="inlineStr">
         <is>
           <t>156g</t>
         </is>
       </c>
-      <c r="K45" s="22" t="inlineStr"/>
-      <c r="L45" s="22" t="inlineStr"/>
-      <c r="M45" s="22" t="inlineStr">
+      <c r="K45" s="52" t="inlineStr"/>
+      <c r="L45" s="52" t="inlineStr"/>
+      <c r="M45" s="52" t="inlineStr">
         <is>
           <t>７~16</t>
         </is>
       </c>
-      <c r="N45" s="22" t="inlineStr"/>
-      <c r="O45" s="22" t="inlineStr"/>
-      <c r="P45" s="22" t="inlineStr"/>
-      <c r="Q45" s="22" t="inlineStr"/>
-      <c r="R45" s="22" t="inlineStr">
+      <c r="N45" s="52" t="inlineStr"/>
+      <c r="O45" s="52" t="inlineStr"/>
+      <c r="P45" s="52" t="inlineStr"/>
+      <c r="Q45" s="52" t="inlineStr"/>
+      <c r="R45" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S45" s="22" t="inlineStr">
+      <c r="S45" s="52" t="inlineStr">
         <is>
           <t>4571527860737</t>
         </is>
       </c>
-      <c r="T45" s="22" t="inlineStr"/>
-      <c r="U45" s="22" t="inlineStr"/>
-      <c r="V45" s="22" t="inlineStr"/>
-      <c r="W45" s="22" t="inlineStr"/>
-      <c r="X45" s="22" t="inlineStr"/>
-      <c r="Y45" s="22" t="inlineStr"/>
-      <c r="Z45" s="22" t="inlineStr">
+      <c r="T45" s="52" t="inlineStr"/>
+      <c r="U45" s="52" t="inlineStr"/>
+      <c r="V45" s="52" t="inlineStr"/>
+      <c r="W45" s="52" t="inlineStr"/>
+      <c r="X45" s="52" t="inlineStr"/>
+      <c r="Y45" s="52" t="inlineStr"/>
+      <c r="Z45" s="52" t="inlineStr">
         <is>
           <t>1/16～1/4</t>
         </is>
       </c>
-      <c r="AA45" s="22" t="inlineStr"/>
-      <c r="AB45" s="22" t="inlineStr"/>
-      <c r="AC45" s="22" t="inlineStr"/>
-      <c r="AD45" s="22" t="inlineStr"/>
-      <c r="AE45" s="22" t="inlineStr"/>
-      <c r="AF45" s="22" t="inlineStr"/>
-      <c r="AG45" s="22" t="inlineStr"/>
-      <c r="AH45" s="22" t="inlineStr">
+      <c r="AA45" s="52" t="inlineStr"/>
+      <c r="AB45" s="52" t="inlineStr"/>
+      <c r="AC45" s="52" t="inlineStr"/>
+      <c r="AD45" s="52" t="inlineStr"/>
+      <c r="AE45" s="52" t="inlineStr"/>
+      <c r="AF45" s="52" t="inlineStr"/>
+      <c r="AG45" s="52" t="inlineStr"/>
+      <c r="AH45" s="52" t="inlineStr">
         <is>
           <t>64ML-FM 是 full-glass fast-moving 专用，Crankbait、Shad、Minnow 和 Topwater Plug 的连收、碰障碍与短咬吸收是核心，不应写成软饵底操。</t>
         </is>
       </c>
-      <c r="AI45" s="22" t="inlineStr">
+      <c r="AI45" s="52" t="inlineStr">
         <is>
           <t>Crankbait / Shad / Minnow / Topwater Plug</t>
         </is>
       </c>
-      <c r="AJ45" s="22" t="inlineStr"/>
-      <c r="AK45" s="22" t="inlineStr"/>
-      <c r="AL45" s="22" t="inlineStr"/>
-      <c r="AM45" s="22" t="inlineStr">
+      <c r="AJ45" s="52" t="inlineStr"/>
+      <c r="AK45" s="52" t="inlineStr"/>
+      <c r="AL45" s="52" t="inlineStr"/>
+      <c r="AM45" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 浅场・硬物边・护岸 / fast moving plug</t>
         </is>
       </c>
-      <c r="AN45" s="22" t="inlineStr">
+      <c r="AN45" s="52" t="inlineStr">
         <is>
           <t>Full-glass 卷物硬饵</t>
         </is>
       </c>
-      <c r="AO45" s="22" t="inlineStr">
+      <c r="AO45" s="52" t="inlineStr">
         <is>
           <t>Crankbait、Shad、Minnow、Topwater 连续收线时更容易维持泳姿，Full-glass 调性对碰硬物和短咬承接更宽容。</t>
         </is>
       </c>
-      <c r="AP45" s="22" t="inlineStr">
+      <c r="AP45" s="52" t="inlineStr">
         <is>
           <t>フルグラスブランク採用 ファストムービング専用モデル</t>
         </is>
       </c>
-      <c r="AQ45" s="22" t="inlineStr">
+      <c r="AQ45" s="52" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="AR45" s="22" t="inlineStr"/>
+      <c r="AR45" s="52" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="A46" s="52" t="inlineStr">
         <is>
           <t>DSRD10044</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
+      <c r="B46" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="C46" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D46" s="22" t="inlineStr">
+      <c r="D46" s="52" t="inlineStr">
         <is>
           <t>DBTC-65ML-FM</t>
         </is>
       </c>
-      <c r="E46" s="22" t="inlineStr">
+      <c r="E46" s="52" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F46" s="22" t="inlineStr">
+      <c r="F46" s="52" t="inlineStr">
         <is>
           <t>6’5″</t>
         </is>
       </c>
-      <c r="G46" s="22" t="inlineStr">
+      <c r="G46" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H46" s="22" t="inlineStr"/>
-      <c r="I46" s="22" t="inlineStr"/>
-      <c r="J46" s="22" t="inlineStr">
+      <c r="H46" s="52" t="inlineStr"/>
+      <c r="I46" s="52" t="inlineStr"/>
+      <c r="J46" s="52" t="inlineStr">
         <is>
           <t>117g</t>
         </is>
       </c>
-      <c r="K46" s="22" t="inlineStr"/>
-      <c r="L46" s="22" t="inlineStr"/>
-      <c r="M46" s="22" t="inlineStr">
+      <c r="K46" s="52" t="inlineStr"/>
+      <c r="L46" s="52" t="inlineStr"/>
+      <c r="M46" s="52" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N46" s="22" t="inlineStr"/>
-      <c r="O46" s="22" t="inlineStr"/>
-      <c r="P46" s="22" t="inlineStr"/>
-      <c r="Q46" s="22" t="inlineStr"/>
-      <c r="R46" s="22" t="inlineStr">
+      <c r="N46" s="52" t="inlineStr"/>
+      <c r="O46" s="52" t="inlineStr"/>
+      <c r="P46" s="52" t="inlineStr"/>
+      <c r="Q46" s="52" t="inlineStr"/>
+      <c r="R46" s="52" t="inlineStr">
         <is>
           <t>¥28,500 （税込￥31,350）</t>
         </is>
       </c>
-      <c r="S46" s="22" t="inlineStr">
+      <c r="S46" s="52" t="inlineStr">
         <is>
           <t>4580484756984</t>
         </is>
       </c>
-      <c r="T46" s="22" t="inlineStr"/>
-      <c r="U46" s="22" t="inlineStr"/>
-      <c r="V46" s="22" t="inlineStr"/>
-      <c r="W46" s="22" t="inlineStr"/>
-      <c r="X46" s="22" t="inlineStr"/>
-      <c r="Y46" s="22" t="inlineStr"/>
-      <c r="Z46" s="22" t="inlineStr">
+      <c r="T46" s="52" t="inlineStr"/>
+      <c r="U46" s="52" t="inlineStr"/>
+      <c r="V46" s="52" t="inlineStr"/>
+      <c r="W46" s="52" t="inlineStr"/>
+      <c r="X46" s="52" t="inlineStr"/>
+      <c r="Y46" s="52" t="inlineStr"/>
+      <c r="Z46" s="52" t="inlineStr">
         <is>
           <t>3/16～5/8</t>
         </is>
       </c>
-      <c r="AA46" s="22" t="inlineStr"/>
-      <c r="AB46" s="22" t="inlineStr"/>
-      <c r="AC46" s="22" t="inlineStr"/>
-      <c r="AD46" s="22" t="inlineStr"/>
-      <c r="AE46" s="22" t="inlineStr"/>
-      <c r="AF46" s="22" t="inlineStr"/>
-      <c r="AG46" s="22" t="inlineStr"/>
-      <c r="AH46" s="22" t="inlineStr">
+      <c r="AA46" s="52" t="inlineStr"/>
+      <c r="AB46" s="52" t="inlineStr"/>
+      <c r="AC46" s="52" t="inlineStr"/>
+      <c r="AD46" s="52" t="inlineStr"/>
+      <c r="AE46" s="52" t="inlineStr"/>
+      <c r="AF46" s="52" t="inlineStr"/>
+      <c r="AG46" s="52" t="inlineStr"/>
+      <c r="AH46" s="52" t="inlineStr">
         <is>
           <t>65ML-FM 是低弹性碳布 light-plugging special，适合 Minnow、Shad、轻量 Crankbait 和 Topwater 的控速与停顿；不是普通软硬泛用。</t>
         </is>
       </c>
-      <c r="AI46" s="22" t="inlineStr">
+      <c r="AI46" s="52" t="inlineStr">
         <is>
           <t>Minnow / Shad / Crankbait / Topwater Plug</t>
         </is>
       </c>
-      <c r="AJ46" s="22" t="inlineStr"/>
-      <c r="AK46" s="22" t="inlineStr"/>
-      <c r="AL46" s="22" t="inlineStr"/>
-      <c r="AM46" s="22" t="inlineStr">
+      <c r="AJ46" s="52" t="inlineStr"/>
+      <c r="AK46" s="52" t="inlineStr"/>
+      <c r="AL46" s="52" t="inlineStr"/>
+      <c r="AM46" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 小型河川・野池・清水浅场 / light plugging</t>
         </is>
       </c>
-      <c r="AN46" s="22" t="inlineStr">
+      <c r="AN46" s="52" t="inlineStr">
         <is>
           <t>轻硬饵 plug 专向</t>
         </is>
       </c>
-      <c r="AO46" s="22" t="inlineStr">
+      <c r="AO46" s="52" t="inlineStr">
         <is>
           <t>Minnow、Shad、轻 Crankbait 和 Topwater 的控速、停顿、twitch 更自然，适合用低弹性手感处理轻硬饵。</t>
         </is>
       </c>
-      <c r="AP46" s="22" t="inlineStr">
+      <c r="AP46" s="52" t="inlineStr">
         <is>
           <t>低弾性カーボンブランクス採用 ライトプラッキングスペシャル</t>
         </is>
       </c>
-      <c r="AQ46" s="22" t="inlineStr">
+      <c r="AQ46" s="52" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="AR46" s="22" t="inlineStr"/>
+      <c r="AR46" s="52" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+      <c r="A47" s="52" t="inlineStr">
         <is>
           <t>DSRD10045</t>
         </is>
       </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="B47" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C47" s="22" t="inlineStr">
+      <c r="C47" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D47" s="22" t="inlineStr">
+      <c r="D47" s="52" t="inlineStr">
         <is>
           <t>DBTC-65M+-PF</t>
         </is>
       </c>
-      <c r="E47" s="22" t="inlineStr">
+      <c r="E47" s="52" t="inlineStr">
         <is>
           <t>M+</t>
         </is>
       </c>
-      <c r="F47" s="22" t="inlineStr">
+      <c r="F47" s="52" t="inlineStr">
         <is>
           <t>6’5″</t>
         </is>
       </c>
-      <c r="G47" s="22" t="inlineStr">
+      <c r="G47" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H47" s="22" t="inlineStr"/>
-      <c r="I47" s="22" t="inlineStr"/>
-      <c r="J47" s="22" t="inlineStr">
+      <c r="H47" s="52" t="inlineStr"/>
+      <c r="I47" s="52" t="inlineStr"/>
+      <c r="J47" s="52" t="inlineStr">
         <is>
           <t>93g</t>
         </is>
       </c>
-      <c r="K47" s="22" t="inlineStr"/>
-      <c r="L47" s="22" t="inlineStr"/>
-      <c r="M47" s="22" t="inlineStr">
+      <c r="K47" s="52" t="inlineStr"/>
+      <c r="L47" s="52" t="inlineStr"/>
+      <c r="M47" s="52" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N47" s="22" t="inlineStr">
+      <c r="N47" s="52" t="inlineStr">
         <is>
           <t>0.8~2</t>
         </is>
       </c>
-      <c r="O47" s="22" t="inlineStr"/>
-      <c r="P47" s="22" t="inlineStr"/>
-      <c r="Q47" s="22" t="inlineStr"/>
-      <c r="R47" s="22" t="inlineStr">
+      <c r="O47" s="52" t="inlineStr"/>
+      <c r="P47" s="52" t="inlineStr"/>
+      <c r="Q47" s="52" t="inlineStr"/>
+      <c r="R47" s="52" t="inlineStr">
         <is>
           <t>¥28,500 （税込￥31,350）</t>
         </is>
       </c>
-      <c r="S47" s="22" t="inlineStr">
+      <c r="S47" s="52" t="inlineStr">
         <is>
           <t>4571527863578</t>
         </is>
       </c>
-      <c r="T47" s="22" t="inlineStr"/>
-      <c r="U47" s="22" t="inlineStr"/>
-      <c r="V47" s="22" t="inlineStr"/>
-      <c r="W47" s="22" t="inlineStr"/>
-      <c r="X47" s="22" t="inlineStr"/>
-      <c r="Y47" s="22" t="inlineStr"/>
-      <c r="Z47" s="22" t="inlineStr">
+      <c r="T47" s="52" t="inlineStr"/>
+      <c r="U47" s="52" t="inlineStr"/>
+      <c r="V47" s="52" t="inlineStr"/>
+      <c r="W47" s="52" t="inlineStr"/>
+      <c r="X47" s="52" t="inlineStr"/>
+      <c r="Y47" s="52" t="inlineStr"/>
+      <c r="Z47" s="52" t="inlineStr">
         <is>
           <t>1/8～5/8</t>
         </is>
       </c>
-      <c r="AA47" s="22" t="inlineStr"/>
-      <c r="AB47" s="22" t="inlineStr"/>
-      <c r="AC47" s="22" t="inlineStr"/>
-      <c r="AD47" s="22" t="inlineStr"/>
-      <c r="AE47" s="22" t="inlineStr"/>
-      <c r="AF47" s="22" t="inlineStr"/>
-      <c r="AG47" s="22" t="inlineStr"/>
-      <c r="AH47" s="22" t="inlineStr">
+      <c r="AA47" s="52" t="inlineStr"/>
+      <c r="AB47" s="52" t="inlineStr"/>
+      <c r="AC47" s="52" t="inlineStr"/>
+      <c r="AD47" s="52" t="inlineStr"/>
+      <c r="AE47" s="52" t="inlineStr"/>
+      <c r="AF47" s="52" t="inlineStr"/>
+      <c r="AG47" s="52" t="inlineStr"/>
+      <c r="AH47" s="52" t="inlineStr">
         <is>
           <t>65M+-PF 是 light-cover bait power finesse，PE 时以 Small Rubber Jig、Bait Neko 为主，换 fluorocarbon 后可转 Heavy Down Shot、Free Rig、Texas 和 Football。</t>
         </is>
       </c>
-      <c r="AI47" s="22" t="inlineStr">
+      <c r="AI47" s="52" t="inlineStr">
         <is>
           <t>Bait Power Finesse / Small Rubber Jig / Bait Neko / Heavy Down Shot / Free Rig / Texas Rig / Football Jig</t>
         </is>
       </c>
-      <c r="AJ47" s="22" t="inlineStr"/>
-      <c r="AK47" s="22" t="inlineStr"/>
-      <c r="AL47" s="22" t="inlineStr"/>
-      <c r="AM47" s="22" t="inlineStr">
+      <c r="AJ47" s="52" t="inlineStr"/>
+      <c r="AK47" s="52" t="inlineStr"/>
+      <c r="AL47" s="52" t="inlineStr"/>
+      <c r="AM47" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / light cover・沉木边・草洞 / bait power finesse</t>
         </is>
       </c>
-      <c r="AN47" s="22" t="inlineStr">
+      <c r="AN47" s="52" t="inlineStr">
         <is>
           <t>轻 cover bait power finesse</t>
         </is>
       </c>
-      <c r="AO47" s="22" t="inlineStr">
+      <c r="AO47" s="52" t="inlineStr">
         <is>
           <t>PE 时 Small Rubber Jig 和 Bait Neko 是主轴，换 fluorocarbon 后可用 Heavy Down Shot、Free Rig、Texas、Football 打底。</t>
         </is>
       </c>
-      <c r="AP47" s="22" t="inlineStr">
+      <c r="AP47" s="52" t="inlineStr">
         <is>
           <t>ライトカバー用ベイトパワーフィネスSPモデル</t>
         </is>
       </c>
-      <c r="AQ47" s="22" t="inlineStr">
+      <c r="AQ47" s="52" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="AR47" s="22" t="inlineStr"/>
+      <c r="AR47" s="52" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="52" t="inlineStr">
         <is>
           <t>DSRD10046</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C48" s="22" t="inlineStr">
+      <c r="C48" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D48" s="22" t="inlineStr">
+      <c r="D48" s="52" t="inlineStr">
         <is>
           <t>DBTC-67ML-BF</t>
         </is>
       </c>
-      <c r="E48" s="22" t="inlineStr">
+      <c r="E48" s="52" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="F48" s="52" t="inlineStr">
         <is>
           <t>6’7″</t>
         </is>
       </c>
-      <c r="G48" s="22" t="inlineStr">
+      <c r="G48" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H48" s="22" t="inlineStr"/>
-      <c r="I48" s="22" t="inlineStr"/>
-      <c r="J48" s="22" t="inlineStr">
+      <c r="H48" s="52" t="inlineStr"/>
+      <c r="I48" s="52" t="inlineStr"/>
+      <c r="J48" s="52" t="inlineStr">
         <is>
           <t>111g</t>
         </is>
       </c>
-      <c r="K48" s="22" t="inlineStr"/>
-      <c r="L48" s="22" t="inlineStr"/>
-      <c r="M48" s="22" t="inlineStr">
+      <c r="K48" s="52" t="inlineStr"/>
+      <c r="L48" s="52" t="inlineStr"/>
+      <c r="M48" s="52" t="inlineStr">
         <is>
           <t>6~12</t>
         </is>
       </c>
-      <c r="N48" s="22" t="inlineStr"/>
-      <c r="O48" s="22" t="inlineStr"/>
-      <c r="P48" s="22" t="inlineStr"/>
-      <c r="Q48" s="22" t="inlineStr"/>
-      <c r="R48" s="22" t="inlineStr">
+      <c r="N48" s="52" t="inlineStr"/>
+      <c r="O48" s="52" t="inlineStr"/>
+      <c r="P48" s="52" t="inlineStr"/>
+      <c r="Q48" s="52" t="inlineStr"/>
+      <c r="R48" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S48" s="22" t="inlineStr">
+      <c r="S48" s="52" t="inlineStr">
         <is>
           <t>4580484756991</t>
         </is>
       </c>
-      <c r="T48" s="22" t="inlineStr"/>
-      <c r="U48" s="22" t="inlineStr"/>
-      <c r="V48" s="22" t="inlineStr"/>
-      <c r="W48" s="22" t="inlineStr"/>
-      <c r="X48" s="22" t="inlineStr"/>
-      <c r="Y48" s="22" t="inlineStr"/>
-      <c r="Z48" s="22" t="inlineStr">
+      <c r="T48" s="52" t="inlineStr"/>
+      <c r="U48" s="52" t="inlineStr"/>
+      <c r="V48" s="52" t="inlineStr"/>
+      <c r="W48" s="52" t="inlineStr"/>
+      <c r="X48" s="52" t="inlineStr"/>
+      <c r="Y48" s="52" t="inlineStr"/>
+      <c r="Z48" s="52" t="inlineStr">
         <is>
           <t>1/16～1/4</t>
         </is>
       </c>
-      <c r="AA48" s="22" t="inlineStr"/>
-      <c r="AB48" s="22" t="inlineStr"/>
-      <c r="AC48" s="22" t="inlineStr"/>
-      <c r="AD48" s="22" t="inlineStr"/>
-      <c r="AE48" s="22" t="inlineStr"/>
-      <c r="AF48" s="22" t="inlineStr"/>
-      <c r="AG48" s="22" t="inlineStr"/>
-      <c r="AH48" s="22" t="inlineStr">
+      <c r="AA48" s="52" t="inlineStr"/>
+      <c r="AB48" s="52" t="inlineStr"/>
+      <c r="AC48" s="52" t="inlineStr"/>
+      <c r="AD48" s="52" t="inlineStr"/>
+      <c r="AE48" s="52" t="inlineStr"/>
+      <c r="AF48" s="52" t="inlineStr"/>
+      <c r="AG48" s="52" t="inlineStr"/>
+      <c r="AH48" s="52" t="inlineStr">
         <is>
           <t>67ML-BF 是进攻型 bait finesse，既能投 Small Plug 和小型 Spinnerbait 搜索，也能用 Small Rubber Jig、Neko、Down Shot 做精准软饵操作。</t>
         </is>
       </c>
-      <c r="AI48" s="22" t="inlineStr">
+      <c r="AI48" s="52" t="inlineStr">
         <is>
           <t>Bait Finesse Small Plug / Small Rubber Jig / Neko Rig / Down Shot / Small Spinnerbait</t>
         </is>
       </c>
-      <c r="AJ48" s="22" t="inlineStr"/>
-      <c r="AK48" s="22" t="inlineStr"/>
-      <c r="AL48" s="22" t="inlineStr"/>
-      <c r="AM48" s="22" t="inlineStr">
+      <c r="AJ48" s="52" t="inlineStr"/>
+      <c r="AK48" s="52" t="inlineStr"/>
+      <c r="AL48" s="52" t="inlineStr"/>
+      <c r="AM48" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 野池・护岸・轻 cover / 攻击型 BFS</t>
         </is>
       </c>
-      <c r="AN48" s="22" t="inlineStr">
+      <c r="AN48" s="52" t="inlineStr">
         <is>
           <t>进攻型 bait finesse</t>
         </is>
       </c>
-      <c r="AO48" s="22" t="inlineStr">
+      <c r="AO48" s="52" t="inlineStr">
         <is>
           <t>Small Plug 与 Small Spinnerbait 可快速搜索，Small Rubber Jig、Neko、Down Shot 可补精细打点，适合手返し很高的近中距离作钓。</t>
         </is>
       </c>
-      <c r="AP48" s="22" t="inlineStr">
+      <c r="AP48" s="52" t="inlineStr">
         <is>
           <t>攻めのベイトフィネスモデル</t>
         </is>
       </c>
-      <c r="AQ48" s="22" t="inlineStr">
+      <c r="AQ48" s="52" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="AR48" s="22" t="inlineStr"/>
+      <c r="AR48" s="52" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="inlineStr">
+      <c r="A49" s="52" t="inlineStr">
         <is>
           <t>DSRD10047</t>
         </is>
       </c>
-      <c r="B49" s="22" t="inlineStr">
+      <c r="B49" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C49" s="22" t="inlineStr">
+      <c r="C49" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D49" s="22" t="inlineStr">
+      <c r="D49" s="52" t="inlineStr">
         <is>
           <t>DBTC-68M</t>
         </is>
       </c>
-      <c r="E49" s="22" t="inlineStr">
+      <c r="E49" s="52" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F49" s="22" t="inlineStr">
+      <c r="F49" s="52" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G49" s="22" t="inlineStr">
+      <c r="G49" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H49" s="22" t="inlineStr"/>
-      <c r="I49" s="22" t="inlineStr"/>
-      <c r="J49" s="22" t="inlineStr">
+      <c r="H49" s="52" t="inlineStr"/>
+      <c r="I49" s="52" t="inlineStr"/>
+      <c r="J49" s="52" t="inlineStr">
         <is>
           <t>108g</t>
         </is>
       </c>
-      <c r="K49" s="22" t="inlineStr"/>
-      <c r="L49" s="22" t="inlineStr"/>
-      <c r="M49" s="22" t="inlineStr">
+      <c r="K49" s="52" t="inlineStr"/>
+      <c r="L49" s="52" t="inlineStr"/>
+      <c r="M49" s="52" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N49" s="22" t="inlineStr"/>
-      <c r="O49" s="22" t="inlineStr"/>
-      <c r="P49" s="22" t="inlineStr"/>
-      <c r="Q49" s="22" t="inlineStr"/>
-      <c r="R49" s="22" t="inlineStr">
+      <c r="N49" s="52" t="inlineStr"/>
+      <c r="O49" s="52" t="inlineStr"/>
+      <c r="P49" s="52" t="inlineStr"/>
+      <c r="Q49" s="52" t="inlineStr"/>
+      <c r="R49" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S49" s="22" t="inlineStr">
+      <c r="S49" s="52" t="inlineStr">
         <is>
           <t>4580484757004</t>
         </is>
       </c>
-      <c r="T49" s="22" t="inlineStr"/>
-      <c r="U49" s="22" t="inlineStr"/>
-      <c r="V49" s="22" t="inlineStr"/>
-      <c r="W49" s="22" t="inlineStr"/>
-      <c r="X49" s="22" t="inlineStr"/>
-      <c r="Y49" s="22" t="inlineStr"/>
-      <c r="Z49" s="22" t="inlineStr">
+      <c r="T49" s="52" t="inlineStr"/>
+      <c r="U49" s="52" t="inlineStr"/>
+      <c r="V49" s="52" t="inlineStr"/>
+      <c r="W49" s="52" t="inlineStr"/>
+      <c r="X49" s="52" t="inlineStr"/>
+      <c r="Y49" s="52" t="inlineStr"/>
+      <c r="Z49" s="52" t="inlineStr">
         <is>
           <t>3/16～5/8</t>
         </is>
       </c>
-      <c r="AA49" s="22" t="inlineStr"/>
-      <c r="AB49" s="22" t="inlineStr"/>
-      <c r="AC49" s="22" t="inlineStr"/>
-      <c r="AD49" s="22" t="inlineStr"/>
-      <c r="AE49" s="22" t="inlineStr"/>
-      <c r="AF49" s="22" t="inlineStr"/>
-      <c r="AG49" s="22" t="inlineStr"/>
-      <c r="AH49" s="22" t="inlineStr">
+      <c r="AA49" s="52" t="inlineStr"/>
+      <c r="AB49" s="52" t="inlineStr"/>
+      <c r="AC49" s="52" t="inlineStr"/>
+      <c r="AD49" s="52" t="inlineStr"/>
+      <c r="AE49" s="52" t="inlineStr"/>
+      <c r="AF49" s="52" t="inlineStr"/>
+      <c r="AG49" s="52" t="inlineStr"/>
+      <c r="AH49" s="52" t="inlineStr">
         <is>
           <t>68M 官方为 super versatile，白名单实钓强化 Crankbait/Shad/Jerkbait 搜索端；Spinnerbait/Chatterbait 次之，Texas 作为软饵补充。</t>
         </is>
       </c>
-      <c r="AI49" s="22" t="inlineStr">
+      <c r="AI49" s="52" t="inlineStr">
         <is>
           <t>Crankbait / Shad / Jerkbait / Spinnerbait / Chatterbait / Texas Rig</t>
         </is>
       </c>
-      <c r="AJ49" s="22" t="inlineStr"/>
-      <c r="AK49" s="22" t="inlineStr"/>
-      <c r="AL49" s="22" t="inlineStr"/>
-      <c r="AM49" s="22" t="inlineStr">
+      <c r="AJ49" s="52" t="inlineStr"/>
+      <c r="AK49" s="52" t="inlineStr"/>
+      <c r="AL49" s="52" t="inlineStr"/>
+      <c r="AM49" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 湖泊・船钓・开阔水 / 中量硬饵搜索</t>
         </is>
       </c>
-      <c r="AN49" s="22" t="inlineStr">
+      <c r="AN49" s="52" t="inlineStr">
         <is>
           <t>硬饵搜索兼 bait versatile</t>
         </is>
       </c>
-      <c r="AO49" s="22" t="inlineStr">
+      <c r="AO49" s="52" t="inlineStr">
         <is>
           <t>Crankbait、Shad、Jerkbait 是更强项，Spinnerbait、Chatterbait 可扩展搜索，Texas 作为软饵补充而不是主轴。</t>
         </is>
       </c>
-      <c r="AP49" s="22" t="inlineStr">
+      <c r="AP49" s="52" t="inlineStr">
         <is>
           <t>スーパーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ49" s="22" t="inlineStr">
+      <c r="AQ49" s="52" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR49" s="22" t="inlineStr"/>
+      <c r="AR49" s="52" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="A50" s="52" t="inlineStr">
         <is>
           <t>DSRD10048</t>
         </is>
       </c>
-      <c r="B50" s="22" t="inlineStr">
+      <c r="B50" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C50" s="22" t="inlineStr">
+      <c r="C50" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D50" s="22" t="inlineStr">
+      <c r="D50" s="52" t="inlineStr">
         <is>
           <t>DBTC-610MH</t>
         </is>
       </c>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E50" s="52" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F50" s="22" t="inlineStr">
+      <c r="F50" s="52" t="inlineStr">
         <is>
           <t>6’10”</t>
         </is>
       </c>
-      <c r="G50" s="22" t="inlineStr">
+      <c r="G50" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H50" s="22" t="inlineStr"/>
-      <c r="I50" s="22" t="inlineStr"/>
-      <c r="J50" s="22" t="inlineStr">
+      <c r="H50" s="52" t="inlineStr"/>
+      <c r="I50" s="52" t="inlineStr"/>
+      <c r="J50" s="52" t="inlineStr">
         <is>
           <t>118g</t>
         </is>
       </c>
-      <c r="K50" s="22" t="inlineStr"/>
-      <c r="L50" s="22" t="inlineStr"/>
-      <c r="M50" s="22" t="inlineStr">
+      <c r="K50" s="52" t="inlineStr"/>
+      <c r="L50" s="52" t="inlineStr"/>
+      <c r="M50" s="52" t="inlineStr">
         <is>
           <t>8~20</t>
         </is>
       </c>
-      <c r="N50" s="22" t="inlineStr"/>
-      <c r="O50" s="22" t="inlineStr"/>
-      <c r="P50" s="22" t="inlineStr"/>
-      <c r="Q50" s="22" t="inlineStr"/>
-      <c r="R50" s="22" t="inlineStr">
+      <c r="N50" s="52" t="inlineStr"/>
+      <c r="O50" s="52" t="inlineStr"/>
+      <c r="P50" s="52" t="inlineStr"/>
+      <c r="Q50" s="52" t="inlineStr"/>
+      <c r="R50" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S50" s="22" t="inlineStr">
+      <c r="S50" s="52" t="inlineStr">
         <is>
           <t>4580484757011</t>
         </is>
       </c>
-      <c r="T50" s="22" t="inlineStr"/>
-      <c r="U50" s="22" t="inlineStr"/>
-      <c r="V50" s="22" t="inlineStr"/>
-      <c r="W50" s="22" t="inlineStr"/>
-      <c r="X50" s="22" t="inlineStr"/>
-      <c r="Y50" s="22" t="inlineStr"/>
-      <c r="Z50" s="22" t="inlineStr">
+      <c r="T50" s="52" t="inlineStr"/>
+      <c r="U50" s="52" t="inlineStr"/>
+      <c r="V50" s="52" t="inlineStr"/>
+      <c r="W50" s="52" t="inlineStr"/>
+      <c r="X50" s="52" t="inlineStr"/>
+      <c r="Y50" s="52" t="inlineStr"/>
+      <c r="Z50" s="52" t="inlineStr">
         <is>
           <t>3/16～3/4</t>
         </is>
       </c>
-      <c r="AA50" s="22" t="inlineStr"/>
-      <c r="AB50" s="22" t="inlineStr"/>
-      <c r="AC50" s="22" t="inlineStr"/>
-      <c r="AD50" s="22" t="inlineStr"/>
-      <c r="AE50" s="22" t="inlineStr"/>
-      <c r="AF50" s="22" t="inlineStr"/>
-      <c r="AG50" s="22" t="inlineStr"/>
-      <c r="AH50" s="22" t="inlineStr">
+      <c r="AA50" s="52" t="inlineStr"/>
+      <c r="AB50" s="52" t="inlineStr"/>
+      <c r="AC50" s="52" t="inlineStr"/>
+      <c r="AD50" s="52" t="inlineStr"/>
+      <c r="AE50" s="52" t="inlineStr"/>
+      <c r="AF50" s="52" t="inlineStr"/>
+      <c r="AG50" s="52" t="inlineStr"/>
+      <c r="AH50" s="52" t="inlineStr">
         <is>
           <t>610MH 官方是 middle versatile，白名单明确 bladed jig 实例，因此 Chatterbait 放首位；Spinnerbait 与 Crankbait 负责巻き，Texas/Rubber Jig 负责撃ち。</t>
         </is>
       </c>
-      <c r="AI50" s="22" t="inlineStr">
+      <c r="AI50" s="52" t="inlineStr">
         <is>
           <t>Chatterbait / Spinnerbait / Texas Rig / Rubber Jig / Crankbait</t>
         </is>
       </c>
-      <c r="AJ50" s="22" t="inlineStr"/>
-      <c r="AK50" s="22" t="inlineStr"/>
-      <c r="AL50" s="22" t="inlineStr"/>
-      <c r="AM50" s="22" t="inlineStr">
+      <c r="AJ50" s="52" t="inlineStr"/>
+      <c r="AK50" s="52" t="inlineStr"/>
+      <c r="AL50" s="52" t="inlineStr"/>
+      <c r="AM50" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 野池・草边・浅 cover / Chatterbait 与中量 bait</t>
         </is>
       </c>
-      <c r="AN50" s="22" t="inlineStr">
+      <c r="AN50" s="52" t="inlineStr">
         <is>
           <t>Chatterbait 主轴中量泛用</t>
         </is>
       </c>
-      <c r="AO50" s="22" t="inlineStr">
+      <c r="AO50" s="52" t="inlineStr">
         <is>
           <t>Chatterbait 和 Spinnerbait 的卷动稳定性更突出，Texas、Rubber Jig 可在同一套线组下补打点，适合移动饵和底操来回切。</t>
         </is>
       </c>
-      <c r="AP50" s="22" t="inlineStr">
+      <c r="AP50" s="52" t="inlineStr">
         <is>
           <t>ミドルスーパーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ50" s="22" t="inlineStr">
+      <c r="AQ50" s="52" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="AR50" s="22" t="inlineStr"/>
+      <c r="AR50" s="52" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="A51" s="52" t="inlineStr">
         <is>
           <t>DSRD10049</t>
         </is>
       </c>
-      <c r="B51" s="22" t="inlineStr">
+      <c r="B51" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C51" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D51" s="22" t="inlineStr">
+      <c r="D51" s="52" t="inlineStr">
         <is>
           <t>DBTC-70M+-FM</t>
         </is>
       </c>
-      <c r="E51" s="22" t="inlineStr">
+      <c r="E51" s="52" t="inlineStr">
         <is>
           <t>M+</t>
         </is>
       </c>
-      <c r="F51" s="22" t="inlineStr">
+      <c r="F51" s="52" t="inlineStr">
         <is>
           <t>7’0″</t>
         </is>
       </c>
-      <c r="G51" s="22" t="inlineStr">
+      <c r="G51" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H51" s="22" t="inlineStr"/>
-      <c r="I51" s="22" t="inlineStr"/>
-      <c r="J51" s="22" t="inlineStr">
+      <c r="H51" s="52" t="inlineStr"/>
+      <c r="I51" s="52" t="inlineStr"/>
+      <c r="J51" s="52" t="inlineStr">
         <is>
           <t>152g</t>
         </is>
       </c>
-      <c r="K51" s="22" t="inlineStr"/>
-      <c r="L51" s="22" t="inlineStr"/>
-      <c r="M51" s="22" t="inlineStr">
+      <c r="K51" s="52" t="inlineStr"/>
+      <c r="L51" s="52" t="inlineStr"/>
+      <c r="M51" s="52" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N51" s="22" t="inlineStr"/>
-      <c r="O51" s="22" t="inlineStr"/>
-      <c r="P51" s="22" t="inlineStr"/>
-      <c r="Q51" s="22" t="inlineStr"/>
-      <c r="R51" s="22" t="inlineStr">
+      <c r="N51" s="52" t="inlineStr"/>
+      <c r="O51" s="52" t="inlineStr"/>
+      <c r="P51" s="52" t="inlineStr"/>
+      <c r="Q51" s="52" t="inlineStr"/>
+      <c r="R51" s="52" t="inlineStr">
         <is>
           <t>¥29,500 （税込￥32,450）</t>
         </is>
       </c>
-      <c r="S51" s="22" t="inlineStr">
+      <c r="S51" s="52" t="inlineStr">
         <is>
           <t>4571527860720</t>
         </is>
       </c>
-      <c r="T51" s="22" t="inlineStr"/>
-      <c r="U51" s="22" t="inlineStr"/>
-      <c r="V51" s="22" t="inlineStr"/>
-      <c r="W51" s="22" t="inlineStr"/>
-      <c r="X51" s="22" t="inlineStr"/>
-      <c r="Y51" s="22" t="inlineStr"/>
-      <c r="Z51" s="22" t="inlineStr">
+      <c r="T51" s="52" t="inlineStr"/>
+      <c r="U51" s="52" t="inlineStr"/>
+      <c r="V51" s="52" t="inlineStr"/>
+      <c r="W51" s="52" t="inlineStr"/>
+      <c r="X51" s="52" t="inlineStr"/>
+      <c r="Y51" s="52" t="inlineStr"/>
+      <c r="Z51" s="52" t="inlineStr">
         <is>
           <t>1/4～1</t>
         </is>
       </c>
-      <c r="AA51" s="22" t="inlineStr"/>
-      <c r="AB51" s="22" t="inlineStr"/>
-      <c r="AC51" s="22" t="inlineStr"/>
-      <c r="AD51" s="22" t="inlineStr"/>
-      <c r="AE51" s="22" t="inlineStr"/>
-      <c r="AF51" s="22" t="inlineStr"/>
-      <c r="AG51" s="22" t="inlineStr"/>
-      <c r="AH51" s="22" t="inlineStr">
+      <c r="AA51" s="52" t="inlineStr"/>
+      <c r="AB51" s="52" t="inlineStr"/>
+      <c r="AC51" s="52" t="inlineStr"/>
+      <c r="AD51" s="52" t="inlineStr"/>
+      <c r="AE51" s="52" t="inlineStr"/>
+      <c r="AF51" s="52" t="inlineStr"/>
+      <c r="AG51" s="52" t="inlineStr"/>
+      <c r="AH51" s="52" t="inlineStr">
         <is>
           <t>70M+-FM 是 glass-composite fast-moving 专用，官网明确列出 Crankbait、Big Minnow、中大型 Topwater、Spinnerbait、Buzzbait、Blade Jig 和 Shad Tail，全部属于巻物/移动饵体系。</t>
         </is>
       </c>
-      <c r="AI51" s="22" t="inlineStr">
+      <c r="AI51" s="52" t="inlineStr">
         <is>
           <t>Crankbait / Big Minnow / Topwater Plug / Spinnerbait / Buzzbait / Chatterbait / Shad Tail</t>
         </is>
       </c>
-      <c r="AJ51" s="22" t="inlineStr"/>
-      <c r="AK51" s="22" t="inlineStr"/>
-      <c r="AL51" s="22" t="inlineStr"/>
-      <c r="AM51" s="22" t="inlineStr">
+      <c r="AJ51" s="52" t="inlineStr"/>
+      <c r="AK51" s="52" t="inlineStr"/>
+      <c r="AL51" s="52" t="inlineStr"/>
+      <c r="AM51" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 开阔水・硬物边・风口 / fast moving search</t>
         </is>
       </c>
-      <c r="AN51" s="22" t="inlineStr">
+      <c r="AN51" s="52" t="inlineStr">
         <is>
           <t>Glass-composite 强搜索卷物</t>
         </is>
       </c>
-      <c r="AO51" s="22" t="inlineStr">
+      <c r="AO51" s="52" t="inlineStr">
         <is>
           <t>Crankbait、Big Minnow、Topwater、Spinnerbait、Buzzbait、Chatterbait 和 Shad Tail 都围绕连续搜索，适合覆盖水面和承接追咬。</t>
         </is>
       </c>
-      <c r="AP51" s="22" t="inlineStr">
+      <c r="AP51" s="52" t="inlineStr">
         <is>
           <t>グラスコンポジットブランク採用 ファストムービング専用モデル グラスコンポジットブランク採用のファストムービングモデル。クランクベイト、ビックミノー、中～大型トップウォーターやスピナーベイト、バズベイト、ブレードジグ、シャッドテールなど広く使用する事が可能。キャスタビリティーも非常に良く、狙ったスポットへ正確にアプローチを出来る性能とバイトより深く出来るのがグラスコンポジットの特徴でもあります。ロッド一本で巻物系全般をカバーしたいそんなアングラーに送るオススメの１本です。ストレートグリップモデル。</t>
         </is>
       </c>
-      <c r="AQ51" s="22" t="inlineStr">
+      <c r="AQ51" s="52" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="AR51" s="22" t="inlineStr"/>
+      <c r="AR51" s="52" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="52" t="inlineStr">
         <is>
           <t>DSRD10050</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B52" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C52" s="22" t="inlineStr">
+      <c r="C52" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D52" s="22" t="inlineStr">
+      <c r="D52" s="52" t="inlineStr">
         <is>
           <t>DBTC-70H-S</t>
         </is>
       </c>
-      <c r="E52" s="22" t="inlineStr">
+      <c r="E52" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F52" s="22" t="inlineStr">
+      <c r="F52" s="52" t="inlineStr">
         <is>
           <t>7’0″</t>
         </is>
       </c>
-      <c r="G52" s="22" t="inlineStr">
+      <c r="G52" s="52" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H52" s="22" t="inlineStr"/>
-      <c r="I52" s="22" t="inlineStr"/>
-      <c r="J52" s="22" t="inlineStr">
+      <c r="H52" s="52" t="inlineStr"/>
+      <c r="I52" s="52" t="inlineStr"/>
+      <c r="J52" s="52" t="inlineStr">
         <is>
           <t>126g</t>
         </is>
       </c>
-      <c r="K52" s="22" t="inlineStr"/>
-      <c r="L52" s="22" t="inlineStr"/>
-      <c r="M52" s="22" t="inlineStr">
+      <c r="K52" s="52" t="inlineStr"/>
+      <c r="L52" s="52" t="inlineStr"/>
+      <c r="M52" s="52" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N52" s="22" t="inlineStr"/>
-      <c r="O52" s="22" t="inlineStr"/>
-      <c r="P52" s="22" t="inlineStr"/>
-      <c r="Q52" s="22" t="inlineStr"/>
-      <c r="R52" s="22" t="inlineStr">
+      <c r="N52" s="52" t="inlineStr"/>
+      <c r="O52" s="52" t="inlineStr"/>
+      <c r="P52" s="52" t="inlineStr"/>
+      <c r="Q52" s="52" t="inlineStr"/>
+      <c r="R52" s="52" t="inlineStr">
         <is>
           <t>¥29,500 （税込￥32,450）</t>
         </is>
       </c>
-      <c r="S52" s="22" t="inlineStr">
+      <c r="S52" s="52" t="inlineStr">
         <is>
           <t>4571527863585</t>
         </is>
       </c>
-      <c r="T52" s="22" t="inlineStr"/>
-      <c r="U52" s="22" t="inlineStr"/>
-      <c r="V52" s="22" t="inlineStr"/>
-      <c r="W52" s="22" t="inlineStr"/>
-      <c r="X52" s="22" t="inlineStr"/>
-      <c r="Y52" s="22" t="inlineStr"/>
-      <c r="Z52" s="22" t="inlineStr">
+      <c r="T52" s="52" t="inlineStr"/>
+      <c r="U52" s="52" t="inlineStr"/>
+      <c r="V52" s="52" t="inlineStr"/>
+      <c r="W52" s="52" t="inlineStr"/>
+      <c r="X52" s="52" t="inlineStr"/>
+      <c r="Y52" s="52" t="inlineStr"/>
+      <c r="Z52" s="52" t="inlineStr">
         <is>
           <t>3/16～1</t>
         </is>
       </c>
-      <c r="AA52" s="22" t="inlineStr"/>
-      <c r="AB52" s="22" t="inlineStr"/>
-      <c r="AC52" s="22" t="inlineStr"/>
-      <c r="AD52" s="22" t="inlineStr"/>
-      <c r="AE52" s="22" t="inlineStr"/>
-      <c r="AF52" s="22" t="inlineStr"/>
-      <c r="AG52" s="22" t="inlineStr"/>
-      <c r="AH52" s="22" t="inlineStr">
+      <c r="AA52" s="52" t="inlineStr"/>
+      <c r="AB52" s="52" t="inlineStr"/>
+      <c r="AC52" s="52" t="inlineStr"/>
+      <c r="AD52" s="52" t="inlineStr"/>
+      <c r="AE52" s="52" t="inlineStr"/>
+      <c r="AF52" s="52" t="inlineStr"/>
+      <c r="AG52" s="52" t="inlineStr"/>
+      <c r="AH52" s="52" t="inlineStr">
         <is>
           <t>70H-S 以 heavy cover finesse 为主题，Cover Neko 放首位，Texas、Rubber Jig 和 Heavy Down Shot 用于更重 cover 或更强穿透；不扩写到大型饵。</t>
         </is>
       </c>
-      <c r="AI52" s="22" t="inlineStr">
+      <c r="AI52" s="52" t="inlineStr">
         <is>
           <t>Cover Neko / Texas Rig / Rubber Jig / Heavy Down Shot</t>
         </is>
       </c>
-      <c r="AJ52" s="22" t="inlineStr"/>
-      <c r="AK52" s="22" t="inlineStr"/>
-      <c r="AL52" s="22" t="inlineStr"/>
-      <c r="AM52" s="22" t="inlineStr">
+      <c r="AJ52" s="52" t="inlineStr"/>
+      <c r="AK52" s="52" t="inlineStr"/>
+      <c r="AL52" s="52" t="inlineStr"/>
+      <c r="AM52" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / heavy cover・沉木・厚草 / heavy cover finesse</t>
         </is>
       </c>
-      <c r="AN52" s="22" t="inlineStr">
+      <c r="AN52" s="52" t="inlineStr">
         <is>
           <t>重 cover 软饵控制</t>
         </is>
       </c>
-      <c r="AO52" s="22" t="inlineStr">
+      <c r="AO52" s="52" t="inlineStr">
         <is>
           <t>Cover Neko、Texas、Rubber Jig 和 Heavy Down Shot 都服务于重 cover 内的精细进攻，重点是进得去、挂住后拉得出来。</t>
         </is>
       </c>
-      <c r="AP52" s="22" t="inlineStr">
+      <c r="AP52" s="52" t="inlineStr">
         <is>
           <t>ヘビーカバーをよりフィネスに</t>
         </is>
       </c>
-      <c r="AQ52" s="22" t="inlineStr">
+      <c r="AQ52" s="52" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="AR52" s="22" t="inlineStr"/>
+      <c r="AR52" s="52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="A53" s="52" t="inlineStr">
         <is>
           <t>DSRD10051</t>
         </is>
       </c>
-      <c r="B53" s="22" t="inlineStr">
+      <c r="B53" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C53" s="22" t="inlineStr">
+      <c r="C53" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D53" s="22" t="inlineStr">
+      <c r="D53" s="52" t="inlineStr">
         <is>
           <t>DBTC-71MH-PF</t>
         </is>
       </c>
-      <c r="E53" s="22" t="inlineStr">
+      <c r="E53" s="52" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F53" s="22" t="inlineStr">
+      <c r="F53" s="52" t="inlineStr">
         <is>
           <t>7’1″</t>
         </is>
       </c>
-      <c r="G53" s="22" t="inlineStr">
+      <c r="G53" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H53" s="22" t="inlineStr"/>
-      <c r="I53" s="22" t="inlineStr"/>
-      <c r="J53" s="22" t="inlineStr">
+      <c r="H53" s="52" t="inlineStr"/>
+      <c r="I53" s="52" t="inlineStr"/>
+      <c r="J53" s="52" t="inlineStr">
         <is>
           <t>117g</t>
         </is>
       </c>
-      <c r="K53" s="22" t="inlineStr"/>
-      <c r="L53" s="22" t="inlineStr"/>
-      <c r="M53" s="22" t="inlineStr">
+      <c r="K53" s="52" t="inlineStr"/>
+      <c r="L53" s="52" t="inlineStr"/>
+      <c r="M53" s="52" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N53" s="22" t="inlineStr">
+      <c r="N53" s="52" t="inlineStr">
         <is>
           <t>1~2.5</t>
         </is>
       </c>
-      <c r="O53" s="22" t="inlineStr"/>
-      <c r="P53" s="22" t="inlineStr"/>
-      <c r="Q53" s="22" t="inlineStr"/>
-      <c r="R53" s="22" t="inlineStr">
+      <c r="O53" s="52" t="inlineStr"/>
+      <c r="P53" s="52" t="inlineStr"/>
+      <c r="Q53" s="52" t="inlineStr"/>
+      <c r="R53" s="52" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S53" s="22" t="inlineStr">
+      <c r="S53" s="52" t="inlineStr">
         <is>
           <t>4580484757028</t>
         </is>
       </c>
-      <c r="T53" s="22" t="inlineStr"/>
-      <c r="U53" s="22" t="inlineStr"/>
-      <c r="V53" s="22" t="inlineStr"/>
-      <c r="W53" s="22" t="inlineStr"/>
-      <c r="X53" s="22" t="inlineStr"/>
-      <c r="Y53" s="22" t="inlineStr"/>
-      <c r="Z53" s="22" t="inlineStr">
+      <c r="T53" s="52" t="inlineStr"/>
+      <c r="U53" s="52" t="inlineStr"/>
+      <c r="V53" s="52" t="inlineStr"/>
+      <c r="W53" s="52" t="inlineStr"/>
+      <c r="X53" s="52" t="inlineStr"/>
+      <c r="Y53" s="52" t="inlineStr"/>
+      <c r="Z53" s="52" t="inlineStr">
         <is>
           <t>1/8～3/4</t>
         </is>
       </c>
-      <c r="AA53" s="22" t="inlineStr"/>
-      <c r="AB53" s="22" t="inlineStr"/>
-      <c r="AC53" s="22" t="inlineStr"/>
-      <c r="AD53" s="22" t="inlineStr"/>
-      <c r="AE53" s="22" t="inlineStr"/>
-      <c r="AF53" s="22" t="inlineStr"/>
-      <c r="AG53" s="22" t="inlineStr"/>
-      <c r="AH53" s="22" t="inlineStr">
+      <c r="AA53" s="52" t="inlineStr"/>
+      <c r="AB53" s="52" t="inlineStr"/>
+      <c r="AC53" s="52" t="inlineStr"/>
+      <c r="AD53" s="52" t="inlineStr"/>
+      <c r="AE53" s="52" t="inlineStr"/>
+      <c r="AF53" s="52" t="inlineStr"/>
+      <c r="AG53" s="52" t="inlineStr"/>
+      <c r="AH53" s="52" t="inlineStr">
         <is>
           <t>71MH-PF 官方主轴是 bait power finesse：PE 时 Small Rubber Jig 与 Bait Neko 优先；白名单 Frog 可作为 cover 补强，fluorocarbon 时再切 Heavy Down Shot、Free Rig、Texas、Football。</t>
         </is>
       </c>
-      <c r="AI53" s="22" t="inlineStr">
+      <c r="AI53" s="52" t="inlineStr">
         <is>
           <t>Bait Power Finesse / Small Rubber Jig / Bait Neko / Frog / Heavy Down Shot / Free Rig / Texas Rig / Football Jig</t>
         </is>
       </c>
-      <c r="AJ53" s="22" t="inlineStr"/>
-      <c r="AK53" s="22" t="inlineStr"/>
-      <c r="AL53" s="22" t="inlineStr"/>
-      <c r="AM53" s="22" t="inlineStr">
+      <c r="AJ53" s="52" t="inlineStr"/>
+      <c r="AK53" s="52" t="inlineStr"/>
+      <c r="AL53" s="52" t="inlineStr"/>
+      <c r="AM53" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 池塘・草洞・浮物 / bait power finesse 与 Frog</t>
         </is>
       </c>
-      <c r="AN53" s="22" t="inlineStr">
+      <c r="AN53" s="52" t="inlineStr">
         <is>
           <t>Bait power finesse 兼 Frog cover</t>
         </is>
       </c>
-      <c r="AO53" s="22" t="inlineStr">
+      <c r="AO53" s="52" t="inlineStr">
         <is>
           <t>Small Rubber Jig、Bait Neko 是主轴，Frog 可处理草面或浮物，Heavy Down Shot、Free Rig、Texas、Football 让同一支竿能切到底层强攻。</t>
         </is>
       </c>
-      <c r="AP53" s="22" t="inlineStr">
+      <c r="AP53" s="52" t="inlineStr">
         <is>
           <t>ヘビーカバー用ベイトパワーフィネスSPモデル より手返し良くパワーフィネスをベイトタックルで行う為に生まれたベイトパワーフィネスSPモデル。PEラインを使用したスモラバやベイトネコのパワーフィネスを基軸に、フロロカーボンラインならヘビーダウンショット、フリーリグ、テキサスリグ、フットボールなどマルチに活躍します。カバー負けしないMHパワーのブランクにティップセクションは糸絡みを考慮しLDBガイドを採用。グリップデザインもシェイク疲れを軽減するべくパワーフィネスSP仕様。異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビッグフィッシュでも逃さない粘りを実現。</t>
         </is>
       </c>
-      <c r="AQ53" s="22" t="inlineStr">
+      <c r="AQ53" s="52" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="AR53" s="22" t="inlineStr"/>
+      <c r="AR53" s="52" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="A54" s="52" t="inlineStr">
         <is>
           <t>DSRD10052</t>
         </is>
       </c>
-      <c r="B54" s="22" t="inlineStr">
+      <c r="B54" s="52" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C54" s="22" t="inlineStr">
+      <c r="C54" s="52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D54" s="22" t="inlineStr">
+      <c r="D54" s="52" t="inlineStr">
         <is>
           <t>DBTC-73H</t>
         </is>
       </c>
-      <c r="E54" s="22" t="inlineStr">
+      <c r="E54" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F54" s="22" t="inlineStr">
+      <c r="F54" s="52" t="inlineStr">
         <is>
           <t>7’3″</t>
         </is>
       </c>
-      <c r="G54" s="22" t="inlineStr">
+      <c r="G54" s="52" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H54" s="22" t="inlineStr"/>
-      <c r="I54" s="22" t="inlineStr"/>
-      <c r="J54" s="22" t="inlineStr">
+      <c r="H54" s="52" t="inlineStr"/>
+      <c r="I54" s="52" t="inlineStr"/>
+      <c r="J54" s="52" t="inlineStr">
         <is>
           <t>133g</t>
         </is>
       </c>
-      <c r="K54" s="22" t="inlineStr"/>
-      <c r="L54" s="22" t="inlineStr"/>
-      <c r="M54" s="22" t="inlineStr">
+      <c r="K54" s="52" t="inlineStr"/>
+      <c r="L54" s="52" t="inlineStr"/>
+      <c r="M54" s="52" t="inlineStr">
         <is>
           <t>14~25</t>
         </is>
       </c>
-      <c r="N54" s="22" t="inlineStr"/>
-      <c r="O54" s="22" t="inlineStr"/>
-      <c r="P54" s="22" t="inlineStr"/>
-      <c r="Q54" s="22" t="inlineStr"/>
-      <c r="R54" s="22" t="inlineStr">
+      <c r="N54" s="52" t="inlineStr"/>
+      <c r="O54" s="52" t="inlineStr"/>
+      <c r="P54" s="52" t="inlineStr"/>
+      <c r="Q54" s="52" t="inlineStr"/>
+      <c r="R54" s="52" t="inlineStr">
         <is>
           <t>¥29,500 （税込￥32,450）</t>
         </is>
       </c>
-      <c r="S54" s="22" t="inlineStr">
+      <c r="S54" s="52" t="inlineStr">
         <is>
           <t>4580484757035</t>
         </is>
       </c>
-      <c r="T54" s="22" t="inlineStr"/>
-      <c r="U54" s="22" t="inlineStr"/>
-      <c r="V54" s="22" t="inlineStr"/>
-      <c r="W54" s="22" t="inlineStr"/>
-      <c r="X54" s="22" t="inlineStr"/>
-      <c r="Y54" s="22" t="inlineStr"/>
-      <c r="Z54" s="22" t="inlineStr">
+      <c r="T54" s="52" t="inlineStr"/>
+      <c r="U54" s="52" t="inlineStr"/>
+      <c r="V54" s="52" t="inlineStr"/>
+      <c r="W54" s="52" t="inlineStr"/>
+      <c r="X54" s="52" t="inlineStr"/>
+      <c r="Y54" s="52" t="inlineStr"/>
+      <c r="Z54" s="52" t="inlineStr">
         <is>
           <t>1/4～1・1/4</t>
         </is>
       </c>
-      <c r="AA54" s="22" t="inlineStr"/>
-      <c r="AB54" s="22" t="inlineStr"/>
-      <c r="AC54" s="22" t="inlineStr"/>
-      <c r="AD54" s="22" t="inlineStr"/>
-      <c r="AE54" s="22" t="inlineStr"/>
-      <c r="AF54" s="22" t="inlineStr"/>
-      <c r="AG54" s="22" t="inlineStr"/>
-      <c r="AH54" s="22" t="inlineStr">
+      <c r="AA54" s="52" t="inlineStr"/>
+      <c r="AB54" s="52" t="inlineStr"/>
+      <c r="AC54" s="52" t="inlineStr"/>
+      <c r="AD54" s="52" t="inlineStr"/>
+      <c r="AE54" s="52" t="inlineStr"/>
+      <c r="AF54" s="52" t="inlineStr"/>
+      <c r="AG54" s="52" t="inlineStr"/>
+      <c r="AH54" s="52" t="inlineStr">
         <is>
           <t>73H 是 heavy versatile，适合 Big Bait、Crawler、Swimbait 和 Swim Jig 这类强搜索，也能承担 Heavy Texas 与 Flipping；排序体现大型移动饵和 heavy cover 双线用途。</t>
         </is>
       </c>
-      <c r="AI54" s="22" t="inlineStr">
+      <c r="AI54" s="52" t="inlineStr">
         <is>
           <t>Big Bait / Crawler Bait / Swimbait / Swim Jig / Heavy Texas / Flipping</t>
         </is>
       </c>
-      <c r="AJ54" s="22" t="inlineStr"/>
-      <c r="AK54" s="22" t="inlineStr"/>
-      <c r="AL54" s="22" t="inlineStr"/>
-      <c r="AM54" s="22" t="inlineStr">
+      <c r="AJ54" s="52" t="inlineStr"/>
+      <c r="AK54" s="52" t="inlineStr"/>
+      <c r="AL54" s="52" t="inlineStr"/>
+      <c r="AM54" s="52" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖・草区・重 cover / big bait 与 heavy cover</t>
         </is>
       </c>
-      <c r="AN54" s="22" t="inlineStr">
+      <c r="AN54" s="52" t="inlineStr">
         <is>
           <t>大型移动饵与 heavy cover 双线</t>
         </is>
       </c>
-      <c r="AO54" s="22" t="inlineStr">
+      <c r="AO54" s="52" t="inlineStr">
         <is>
           <t>Big Bait、Crawler、Swimbait、Swim Jig 负责大范围搜索，Heavy Texas 和 Flipping 可处理重 cover，是偏强力路线的一支。</t>
         </is>
       </c>
-      <c r="AP54" s="22" t="inlineStr">
+      <c r="AP54" s="52" t="inlineStr">
         <is>
           <t>ヘビーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ54" s="22" t="inlineStr">
+      <c r="AQ54" s="52" t="inlineStr">
         <is>
           <t>221</t>
         </is>
       </c>
-      <c r="AR54" s="22" t="inlineStr"/>
+      <c r="AR54" s="52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GearSage-client/pkgGear/data_raw/dstyle_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/dstyle_rod_import.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="rod" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="rod_detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rod" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rod_detail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59,8 +59,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -482,6 +490,10 @@
   </sheetPr>
   <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -886,8 +898,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR54"/>
+  <dimension ref="A1:AS54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1102,6628 +1118,6898 @@
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>product_technical</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>Extra Spec 1</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Extra Spec 2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="53" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>DSRD10000</t>
         </is>
       </c>
-      <c r="B2" s="53" t="inlineStr">
+      <c r="B2" s="61" t="inlineStr">
         <is>
           <t>DSR1000</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D2" s="53" t="inlineStr">
+      <c r="D2" s="61" t="inlineStr">
         <is>
           <t>DHRS-GD-64L</t>
         </is>
       </c>
-      <c r="E2" s="53" t="inlineStr">
+      <c r="E2" s="61" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F2" s="53" t="inlineStr">
+      <c r="F2" s="61" t="inlineStr">
         <is>
           <t>6’4″</t>
         </is>
       </c>
-      <c r="G2" s="53" t="inlineStr">
+      <c r="G2" s="61" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H2" s="53" t="inlineStr"/>
-      <c r="I2" s="53" t="inlineStr"/>
-      <c r="J2" s="53" t="inlineStr">
+      <c r="H2" s="61" t="inlineStr"/>
+      <c r="I2" s="61" t="inlineStr"/>
+      <c r="J2" s="61" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K2" s="53" t="inlineStr"/>
-      <c r="L2" s="53" t="inlineStr"/>
-      <c r="M2" s="53" t="inlineStr">
+      <c r="K2" s="61" t="inlineStr"/>
+      <c r="L2" s="61" t="inlineStr"/>
+      <c r="M2" s="61" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N2" s="53" t="inlineStr"/>
-      <c r="O2" s="53" t="inlineStr"/>
-      <c r="P2" s="53" t="inlineStr"/>
-      <c r="Q2" s="53" t="inlineStr"/>
-      <c r="R2" s="53" t="inlineStr">
+      <c r="N2" s="61" t="inlineStr"/>
+      <c r="O2" s="61" t="inlineStr"/>
+      <c r="P2" s="61" t="inlineStr"/>
+      <c r="Q2" s="61" t="inlineStr"/>
+      <c r="R2" s="61" t="inlineStr">
         <is>
           <t>¥60,000 （税込￥66,000）</t>
         </is>
       </c>
-      <c r="S2" s="53" t="inlineStr"/>
-      <c r="T2" s="53" t="inlineStr"/>
-      <c r="U2" s="53" t="inlineStr"/>
-      <c r="V2" s="53" t="inlineStr"/>
-      <c r="W2" s="53" t="inlineStr"/>
-      <c r="X2" s="53" t="inlineStr"/>
-      <c r="Y2" s="53" t="inlineStr"/>
-      <c r="Z2" s="53" t="inlineStr">
+      <c r="S2" s="61" t="inlineStr"/>
+      <c r="T2" s="61" t="inlineStr"/>
+      <c r="U2" s="61" t="inlineStr"/>
+      <c r="V2" s="61" t="inlineStr"/>
+      <c r="W2" s="61" t="inlineStr"/>
+      <c r="X2" s="61" t="inlineStr"/>
+      <c r="Y2" s="61" t="inlineStr"/>
+      <c r="Z2" s="61" t="inlineStr">
         <is>
           <t>1/32〜3/16</t>
         </is>
       </c>
-      <c r="AA2" s="53" t="inlineStr"/>
-      <c r="AB2" s="53" t="inlineStr"/>
-      <c r="AC2" s="53" t="inlineStr">
+      <c r="AA2" s="61" t="inlineStr"/>
+      <c r="AB2" s="61" t="inlineStr"/>
+      <c r="AC2" s="61" t="inlineStr">
         <is>
           <t>RIKU Mk-01</t>
         </is>
       </c>
-      <c r="AD2" s="53" t="inlineStr"/>
-      <c r="AE2" s="53" t="inlineStr"/>
-      <c r="AF2" s="53" t="inlineStr"/>
-      <c r="AG2" s="53" t="inlineStr">
+      <c r="AD2" s="61" t="inlineStr"/>
+      <c r="AE2" s="61" t="inlineStr"/>
+      <c r="AF2" s="61" t="inlineStr"/>
+      <c r="AG2" s="61" t="inlineStr">
         <is>
           <t>不鏽鋼 SiC 導環：兼顧耐用與出線穩定，Bass 多技法拋投和控線更可靠</t>
         </is>
       </c>
-      <c r="AH2" s="53" t="inlineStr">
+      <c r="AH2" s="61" t="inlineStr">
         <is>
           <t>RIKU 是轻量泛用 spinning：先以 Neko、Down Shot、No Sinker 做精细操作，需要搜索时再切到小型 Plug；温和 Fast 调性兼顾远投、控线和中鱼后的牵制。</t>
         </is>
       </c>
-      <c r="AI2" s="53" t="inlineStr">
+      <c r="AI2" s="61" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Plug</t>
         </is>
       </c>
-      <c r="AJ2" s="53" t="inlineStr"/>
-      <c r="AK2" s="53" t="inlineStr"/>
-      <c r="AL2" s="53" t="inlineStr"/>
-      <c r="AM2" s="53" t="inlineStr">
+      <c r="AJ2" s="61" t="inlineStr"/>
+      <c r="AK2" s="61" t="inlineStr"/>
+      <c r="AL2" s="61" t="inlineStr"/>
+      <c r="AM2" s="61" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓与船钓 / 近中距离精细到小型硬饵搜索</t>
         </is>
       </c>
-      <c r="AN2" s="53" t="inlineStr">
+      <c r="AN2" s="61" t="inlineStr">
         <is>
           <t>轻量精细泛用 spinning</t>
         </is>
       </c>
-      <c r="AO2" s="53" t="inlineStr">
+      <c r="AO2" s="61" t="inlineStr">
         <is>
           <t>Neko、Down Shot 和 No Sinker 的控线手感比较自然，小型 Plug 搜索也能兼顾，适合只带一支 spinning 应对高压场。</t>
         </is>
       </c>
-      <c r="AP2" s="53" t="inlineStr">
+      <c r="AP2" s="61" t="inlineStr">
         <is>
           <t>RIKU Mk-01 「RIKU」 ■ 青木大介 × ダイワの融合から生まれた次世代スピニングロッド トップトーナメンター青木大介の理論と経験、そしてダイワの最先端テクノロジーが融合した1本。 それがスピニングロッド 「RIKU」 です。 ■ 届く・操る・獲るを高次元で実現 軽量かつ高強度のブランクス設計により、繊細な近距離アプローチからロングキャストまで対応。 さらに、掛けた魚を確実に寄せ切るバットパワーを備え、アングラーの操作を確実に成果へとつなげます。 ■ 幅広い戦略を支えるマイルドなファストテーパー 極端に用途を限定しないマイルドなファストテーパーを採用。 ライトリグを駆使した繊細な釣りから、小型プラグを用いた巻きの釣りまで柔軟にこなします。 1本で幅広い状況に対応できる懐の深さが、大きなアドバンテージとなります。 ■ 新しい可能性を拓くスピニングロッド 青木大介のこだわりとダイワのテクノロジーが融合した「RIKU」。 多様化する現代フィールドにおいて、次世代の可能性を切り拓くスピニングロッドです。</t>
         </is>
       </c>
-      <c r="AQ2" s="53" t="inlineStr">
+      <c r="AQ2" s="61" t="inlineStr">
+        <is>
+          <t>X45フルシールド / エアセンサーシート / SVFカーボン / ステンレスSICガイド / グルーブドセンターグリップ / ショートコルクグリップ / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR2" s="61" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="AR2" s="53" t="inlineStr"/>
+      <c r="AS2" s="61" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>DSRD10001</t>
         </is>
       </c>
-      <c r="B3" s="53" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>DSR1000</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D3" s="53" t="inlineStr">
+      <c r="D3" s="61" t="inlineStr">
         <is>
           <t>DHRC-GD-68M-LM</t>
         </is>
       </c>
-      <c r="E3" s="53" t="inlineStr">
+      <c r="E3" s="61" t="inlineStr">
         <is>
           <t>M-LM</t>
         </is>
       </c>
-      <c r="F3" s="53" t="inlineStr">
+      <c r="F3" s="61" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G3" s="53" t="inlineStr">
+      <c r="G3" s="61" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H3" s="53" t="inlineStr"/>
-      <c r="I3" s="53" t="inlineStr"/>
-      <c r="J3" s="53" t="inlineStr">
+      <c r="H3" s="61" t="inlineStr"/>
+      <c r="I3" s="61" t="inlineStr"/>
+      <c r="J3" s="61" t="inlineStr">
         <is>
           <t>101g</t>
         </is>
       </c>
-      <c r="K3" s="53" t="inlineStr"/>
-      <c r="L3" s="53" t="inlineStr"/>
-      <c r="M3" s="53" t="inlineStr">
+      <c r="K3" s="61" t="inlineStr"/>
+      <c r="L3" s="61" t="inlineStr"/>
+      <c r="M3" s="61" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N3" s="53" t="inlineStr"/>
-      <c r="O3" s="53" t="inlineStr"/>
-      <c r="P3" s="53" t="inlineStr"/>
-      <c r="Q3" s="53" t="inlineStr"/>
-      <c r="R3" s="53" t="inlineStr">
+      <c r="N3" s="61" t="inlineStr"/>
+      <c r="O3" s="61" t="inlineStr"/>
+      <c r="P3" s="61" t="inlineStr"/>
+      <c r="Q3" s="61" t="inlineStr"/>
+      <c r="R3" s="61" t="inlineStr">
         <is>
           <t>¥62,000 （税込￥68,200）</t>
         </is>
       </c>
-      <c r="S3" s="53" t="inlineStr"/>
-      <c r="T3" s="53" t="inlineStr"/>
-      <c r="U3" s="53" t="inlineStr"/>
-      <c r="V3" s="53" t="inlineStr"/>
-      <c r="W3" s="53" t="inlineStr"/>
-      <c r="X3" s="53" t="inlineStr"/>
-      <c r="Y3" s="53" t="inlineStr"/>
-      <c r="Z3" s="53" t="inlineStr">
+      <c r="S3" s="61" t="inlineStr"/>
+      <c r="T3" s="61" t="inlineStr"/>
+      <c r="U3" s="61" t="inlineStr"/>
+      <c r="V3" s="61" t="inlineStr"/>
+      <c r="W3" s="61" t="inlineStr"/>
+      <c r="X3" s="61" t="inlineStr"/>
+      <c r="Y3" s="61" t="inlineStr"/>
+      <c r="Z3" s="61" t="inlineStr">
         <is>
           <t>3/16〜5/8</t>
         </is>
       </c>
-      <c r="AA3" s="53" t="inlineStr"/>
-      <c r="AB3" s="53" t="inlineStr"/>
-      <c r="AC3" s="53" t="inlineStr">
+      <c r="AA3" s="61" t="inlineStr"/>
+      <c r="AB3" s="61" t="inlineStr"/>
+      <c r="AC3" s="61" t="inlineStr">
         <is>
           <t>THE SUTO Mk-01</t>
         </is>
       </c>
-      <c r="AD3" s="53" t="inlineStr"/>
-      <c r="AE3" s="53" t="inlineStr"/>
-      <c r="AF3" s="53" t="inlineStr"/>
-      <c r="AG3" s="53" t="inlineStr">
+      <c r="AD3" s="61" t="inlineStr"/>
+      <c r="AE3" s="61" t="inlineStr"/>
+      <c r="AF3" s="61" t="inlineStr"/>
+      <c r="AG3" s="61" t="inlineStr">
         <is>
           <t>不鏽鋼 SiC 導環：兼顧耐用與出線穩定，Bass 多技法拋投和控線更可靠</t>
         </is>
       </c>
-      <c r="AH3" s="53" t="inlineStr">
+      <c r="AH3" s="61" t="inlineStr">
         <is>
           <t>THE SUTO 以 bait mid-strolling 为主轴：Jighead 或 Football Jig 自然游动放首位，低弹性碳布让短咬更容易黏住；硬饵和 wire bait 只是副线用途。</t>
         </is>
       </c>
-      <c r="AI3" s="53" t="inlineStr">
+      <c r="AI3" s="61" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Swimming Football Jig / Hover Strolling / Spinnerbait / Crankbait</t>
         </is>
       </c>
-      <c r="AJ3" s="53" t="inlineStr"/>
-      <c r="AK3" s="53" t="inlineStr"/>
-      <c r="AL3" s="53" t="inlineStr"/>
-      <c r="AM3" s="53" t="inlineStr">
+      <c r="AJ3" s="61" t="inlineStr"/>
+      <c r="AK3" s="61" t="inlineStr"/>
+      <c r="AL3" s="61" t="inlineStr"/>
+      <c r="AM3" s="61" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水域・船钓 / 中层游动与轻移动饵</t>
         </is>
       </c>
-      <c r="AN3" s="53" t="inlineStr">
+      <c r="AN3" s="61" t="inlineStr">
         <is>
           <t>Bait mid-strolling 兼轻移动饵</t>
         </is>
       </c>
-      <c r="AO3" s="53" t="inlineStr">
+      <c r="AO3" s="61" t="inlineStr">
         <is>
           <t>用枪柄系统做 Mid Strolling 时更好控线，Swimming Football Jig 也能维持泳姿；需要时可切 Spinnerbait、Crankbait 做弱搜索。</t>
         </is>
       </c>
-      <c r="AP3" s="53" t="inlineStr">
+      <c r="AP3" s="61" t="inlineStr">
         <is>
           <t>THE SUTO Mk-01 『THE SUTO』 ベイトで操る、新時代のミドストロッド。 青木大介が培ってきたミドスト理論と、ダイワの最先端テクノロジーが融合した1本。 その名も 『THE SUTO』。 従来はスピニングでしか実現できなかった繊細な揺らぎを、ベイトタックルで正確かつ快適に再現できるよう設計されています。 ■ オリジナルテーパーが生む操作性と感度 独自のテーパー設計によるしなやかなティップが、ジグヘッドやフットボールジグを自然にスイミング。 ルアーの微細な振動やショートバイトも逃さず、確実に手元へと伝えます。 一方でベリーからバットにかけてはしっかりとした張りを備え、フッキングからランディングまで安定したやり取りを可能にします。 ■ Low Modulusカーボン採用による懐の深さ しなやかさと粘りを兼ね備えた低弾性カーボン“Low Modulus”を採用。 ミドスト専用機としての性能はもちろん、副次的にハードベイトやワイヤーベイトにも幅広く対応。 1本で様々なアプローチを可能にする汎用性を手にしました。 ■ 青木大介 × ダイワの答え 青木大介のこだわりとダイワテクノロジーの融合から生まれた、ベイトミドストという新たな可能性を切り拓くロッド。 それが DHRC-GD-68M-LM “THE SUTO” です。</t>
         </is>
       </c>
-      <c r="AQ3" s="53" t="inlineStr">
+      <c r="AQ3" s="61" t="inlineStr">
+        <is>
+          <t>X45フルシールド / エアセンサーシート / SVFカーボン / Low Modulusカーボン / ステンレスSICガイド / グルーブドセンターグリップ / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR3" s="61" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR3" s="53" t="inlineStr"/>
+      <c r="AS3" s="61" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>DSRD10002</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C4" s="52" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>DHRS-511UL</t>
         </is>
       </c>
-      <c r="E4" s="52" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="F4" s="60" t="inlineStr">
         <is>
           <t>5’11”</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H4" s="52" t="inlineStr"/>
-      <c r="I4" s="52" t="inlineStr"/>
-      <c r="J4" s="52" t="inlineStr">
+      <c r="H4" s="60" t="inlineStr"/>
+      <c r="I4" s="60" t="inlineStr"/>
+      <c r="J4" s="60" t="inlineStr">
         <is>
           <t>70g</t>
         </is>
       </c>
-      <c r="K4" s="52" t="inlineStr"/>
-      <c r="L4" s="52" t="inlineStr"/>
-      <c r="M4" s="52" t="inlineStr">
+      <c r="K4" s="60" t="inlineStr"/>
+      <c r="L4" s="60" t="inlineStr"/>
+      <c r="M4" s="60" t="inlineStr">
         <is>
           <t>2~6</t>
         </is>
       </c>
-      <c r="N4" s="52" t="inlineStr"/>
-      <c r="O4" s="52" t="inlineStr"/>
-      <c r="P4" s="52" t="inlineStr"/>
-      <c r="Q4" s="52" t="inlineStr"/>
-      <c r="R4" s="52" t="inlineStr">
+      <c r="N4" s="60" t="inlineStr"/>
+      <c r="O4" s="60" t="inlineStr"/>
+      <c r="P4" s="60" t="inlineStr"/>
+      <c r="Q4" s="60" t="inlineStr"/>
+      <c r="R4" s="60" t="inlineStr">
         <is>
           <t>￥50,000 （￥55,000）</t>
         </is>
       </c>
-      <c r="S4" s="52" t="inlineStr">
+      <c r="S4" s="60" t="inlineStr">
         <is>
           <t>4571527865183</t>
         </is>
       </c>
-      <c r="T4" s="52" t="inlineStr"/>
-      <c r="U4" s="52" t="inlineStr"/>
-      <c r="V4" s="52" t="inlineStr"/>
-      <c r="W4" s="52" t="inlineStr"/>
-      <c r="X4" s="52" t="inlineStr"/>
-      <c r="Y4" s="52" t="inlineStr"/>
-      <c r="Z4" s="52" t="inlineStr">
+      <c r="T4" s="60" t="inlineStr"/>
+      <c r="U4" s="60" t="inlineStr"/>
+      <c r="V4" s="60" t="inlineStr"/>
+      <c r="W4" s="60" t="inlineStr"/>
+      <c r="X4" s="60" t="inlineStr"/>
+      <c r="Y4" s="60" t="inlineStr"/>
+      <c r="Z4" s="60" t="inlineStr">
         <is>
           <t>1/48～3/16</t>
         </is>
       </c>
-      <c r="AA4" s="52" t="inlineStr"/>
-      <c r="AB4" s="52" t="inlineStr"/>
-      <c r="AC4" s="52" t="inlineStr">
+      <c r="AA4" s="60" t="inlineStr"/>
+      <c r="AB4" s="60" t="inlineStr"/>
+      <c r="AC4" s="60" t="inlineStr">
         <is>
           <t>Finesse Shake 1</t>
         </is>
       </c>
-      <c r="AD4" s="52" t="inlineStr"/>
-      <c r="AE4" s="52" t="inlineStr"/>
-      <c r="AF4" s="52" t="inlineStr"/>
-      <c r="AG4" s="52" t="inlineStr">
+      <c r="AD4" s="60" t="inlineStr"/>
+      <c r="AE4" s="60" t="inlineStr"/>
+      <c r="AF4" s="60" t="inlineStr"/>
+      <c r="AG4" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH4" s="52" t="inlineStr">
+      <c r="AH4" s="60" t="inlineStr">
         <is>
           <t>短竿超精细定位，适合高压近距离用 Neko、Down Shot、No Sinker 和 Small Rubber Jig 做精准落点与细抖；小型 Plug 属补充搜索。</t>
         </is>
       </c>
-      <c r="AI4" s="52" t="inlineStr">
+      <c r="AI4" s="60" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Plug</t>
         </is>
       </c>
-      <c r="AJ4" s="52" t="inlineStr"/>
-      <c r="AK4" s="52" t="inlineStr"/>
-      <c r="AL4" s="52" t="inlineStr"/>
-      <c r="AM4" s="52" t="inlineStr">
+      <c r="AJ4" s="60" t="inlineStr"/>
+      <c r="AK4" s="60" t="inlineStr"/>
+      <c r="AL4" s="60" t="inlineStr"/>
+      <c r="AM4" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压野池・近岸标点 / 短距超精细</t>
         </is>
       </c>
-      <c r="AN4" s="52" t="inlineStr">
+      <c r="AN4" s="60" t="inlineStr">
         <is>
           <t>近距离超精细食わせ</t>
         </is>
       </c>
-      <c r="AO4" s="52" t="inlineStr">
+      <c r="AO4" s="60" t="inlineStr">
         <is>
           <t>短竿在狭小标点更容易压低弹道，Neko、Down Shot、Small Rubber Jig 的轻抖和短咬反馈更直接。</t>
         </is>
       </c>
-      <c r="AP4" s="52" t="inlineStr">
+      <c r="AP4" s="60" t="inlineStr">
         <is>
           <t>Finesse SHAKE 1 Finesse Shake 1 過去の自分を超える為のスーパーフィネスロッド。青木大介が新たに考えた『ショートグリップコンセプト』を色濃く反映させ、正確なキャスト性能とルアーをより繊細に扱える操作性と感度が向上。 ６ft以下まで下げる事で極限のプレッシャーでも攻撃的フィネス展開。よりタイト、よりシビアに進化したウルトラフィネスロッド。 伝統の食わせのファストテーパーからバスの引きに負けないバットパワーを持ち合わせ、ネコリグ、ダウンショットリグ、ノーシンカーリグ、スモラバなどのフィネス全般からスモールプラグまで幅広く対応。</t>
         </is>
       </c>
-      <c r="AQ4" s="52" t="inlineStr">
+      <c r="AQ4" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR4" s="60" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="AR4" s="52" t="inlineStr">
+      <c r="AS4" s="60" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>DSRD10003</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>DHRS-60L</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F5" s="52" t="inlineStr">
+      <c r="F5" s="60" t="inlineStr">
         <is>
           <t>6’0″</t>
         </is>
       </c>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="G5" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr"/>
-      <c r="I5" s="52" t="inlineStr"/>
-      <c r="J5" s="52" t="inlineStr">
+      <c r="H5" s="60" t="inlineStr"/>
+      <c r="I5" s="60" t="inlineStr"/>
+      <c r="J5" s="60" t="inlineStr">
         <is>
           <t>74g</t>
         </is>
       </c>
-      <c r="K5" s="52" t="inlineStr"/>
-      <c r="L5" s="52" t="inlineStr"/>
-      <c r="M5" s="52" t="inlineStr">
+      <c r="K5" s="60" t="inlineStr"/>
+      <c r="L5" s="60" t="inlineStr"/>
+      <c r="M5" s="60" t="inlineStr">
         <is>
           <t>2.5~8</t>
         </is>
       </c>
-      <c r="N5" s="52" t="inlineStr"/>
-      <c r="O5" s="52" t="inlineStr"/>
-      <c r="P5" s="52" t="inlineStr"/>
-      <c r="Q5" s="52" t="inlineStr"/>
-      <c r="R5" s="52" t="inlineStr">
+      <c r="N5" s="60" t="inlineStr"/>
+      <c r="O5" s="60" t="inlineStr"/>
+      <c r="P5" s="60" t="inlineStr"/>
+      <c r="Q5" s="60" t="inlineStr"/>
+      <c r="R5" s="60" t="inlineStr">
         <is>
           <t>￥50,000 （￥55,000）</t>
         </is>
       </c>
-      <c r="S5" s="52" t="inlineStr">
+      <c r="S5" s="60" t="inlineStr">
         <is>
           <t>4571527865190</t>
         </is>
       </c>
-      <c r="T5" s="52" t="inlineStr"/>
-      <c r="U5" s="52" t="inlineStr"/>
-      <c r="V5" s="52" t="inlineStr"/>
-      <c r="W5" s="52" t="inlineStr"/>
-      <c r="X5" s="52" t="inlineStr"/>
-      <c r="Y5" s="52" t="inlineStr"/>
-      <c r="Z5" s="52" t="inlineStr">
+      <c r="T5" s="60" t="inlineStr"/>
+      <c r="U5" s="60" t="inlineStr"/>
+      <c r="V5" s="60" t="inlineStr"/>
+      <c r="W5" s="60" t="inlineStr"/>
+      <c r="X5" s="60" t="inlineStr"/>
+      <c r="Y5" s="60" t="inlineStr"/>
+      <c r="Z5" s="60" t="inlineStr">
         <is>
           <t>1/32〜1/4</t>
         </is>
       </c>
-      <c r="AA5" s="52" t="inlineStr"/>
-      <c r="AB5" s="52" t="inlineStr"/>
-      <c r="AC5" s="52" t="inlineStr">
+      <c r="AA5" s="60" t="inlineStr"/>
+      <c r="AB5" s="60" t="inlineStr"/>
+      <c r="AC5" s="60" t="inlineStr">
         <is>
           <t>Finesse Shake 2</t>
         </is>
       </c>
-      <c r="AD5" s="52" t="inlineStr"/>
-      <c r="AE5" s="52" t="inlineStr"/>
-      <c r="AF5" s="52" t="inlineStr"/>
-      <c r="AG5" s="52" t="inlineStr">
+      <c r="AD5" s="60" t="inlineStr"/>
+      <c r="AE5" s="60" t="inlineStr"/>
+      <c r="AF5" s="60" t="inlineStr"/>
+      <c r="AG5" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH5" s="52" t="inlineStr">
+      <c r="AH5" s="60" t="inlineStr">
         <is>
           <t>Finesse Shake 2 仍以食わせ系 Fast taper 为核心，Neko、Down Shot、No Sinker 和 Small Rubber Jig 是主场；需要拉开距离时可兼顾小型 Plug。</t>
         </is>
       </c>
-      <c r="AI5" s="52" t="inlineStr">
+      <c r="AI5" s="60" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Plug</t>
         </is>
       </c>
-      <c r="AJ5" s="52" t="inlineStr"/>
-      <c r="AK5" s="52" t="inlineStr"/>
-      <c r="AL5" s="52" t="inlineStr"/>
-      <c r="AM5" s="52" t="inlineStr">
+      <c r="AJ5" s="60" t="inlineStr"/>
+      <c r="AK5" s="60" t="inlineStr"/>
+      <c r="AL5" s="60" t="inlineStr"/>
+      <c r="AM5" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压湖库・野池 / 精细软饵到小型 Plug</t>
         </is>
       </c>
-      <c r="AN5" s="52" t="inlineStr">
+      <c r="AN5" s="60" t="inlineStr">
         <is>
           <t>精细食わせ泛用 spinning</t>
         </is>
       </c>
-      <c r="AO5" s="52" t="inlineStr">
+      <c r="AO5" s="60" t="inlineStr">
         <is>
           <t>比 XUL/UL 更有余量，细线软饵仍然好操作，遇到鱼追但不咬时可换小型 Plug 做慢速搜索。</t>
         </is>
       </c>
-      <c r="AP5" s="52" t="inlineStr">
+      <c r="AP5" s="60" t="inlineStr">
         <is>
           <t>Finesse SHAKE 2 Finesse Shake 2 過去の自分を超える為のスーパーフィネスロッド。青木大介が新たに考えた『ショートグリップコンセプト』を色濃く反映させ、正確なキャスト性能とルアーをより繊細に扱える操作性と感度が向上。 伝統の食わせのファストテーパーからバスの引きに負けないバットパワーを持ち合わせ、ネコリグ、ダウンショットリグ、ノーシンカーリグ、スモラバなどのフィネス全般からスモールプラグまで幅広く対応。</t>
         </is>
       </c>
-      <c r="AQ5" s="52" t="inlineStr">
+      <c r="AQ5" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR5" s="60" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="AR5" s="52" t="inlineStr">
+      <c r="AS5" s="60" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="52" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>DSRD10004</t>
         </is>
       </c>
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C6" s="52" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>DHRS-63L</t>
         </is>
       </c>
-      <c r="E6" s="52" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F6" s="52" t="inlineStr">
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G6" s="52" t="inlineStr">
+      <c r="G6" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H6" s="52" t="inlineStr"/>
-      <c r="I6" s="52" t="inlineStr"/>
-      <c r="J6" s="52" t="inlineStr">
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
+      <c r="J6" s="60" t="inlineStr">
         <is>
           <t>74g</t>
         </is>
       </c>
-      <c r="K6" s="52" t="inlineStr"/>
-      <c r="L6" s="52" t="inlineStr"/>
-      <c r="M6" s="52" t="inlineStr">
+      <c r="K6" s="60" t="inlineStr"/>
+      <c r="L6" s="60" t="inlineStr"/>
+      <c r="M6" s="60" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N6" s="52" t="inlineStr"/>
-      <c r="O6" s="52" t="inlineStr"/>
-      <c r="P6" s="52" t="inlineStr"/>
-      <c r="Q6" s="52" t="inlineStr"/>
-      <c r="R6" s="52" t="inlineStr">
+      <c r="N6" s="60" t="inlineStr"/>
+      <c r="O6" s="60" t="inlineStr"/>
+      <c r="P6" s="60" t="inlineStr"/>
+      <c r="Q6" s="60" t="inlineStr"/>
+      <c r="R6" s="60" t="inlineStr">
         <is>
           <t>￥50,000 （￥55,000）</t>
         </is>
       </c>
-      <c r="S6" s="52" t="inlineStr">
+      <c r="S6" s="60" t="inlineStr">
         <is>
           <t>4571527863790</t>
         </is>
       </c>
-      <c r="T6" s="52" t="inlineStr"/>
-      <c r="U6" s="52" t="inlineStr"/>
-      <c r="V6" s="52" t="inlineStr"/>
-      <c r="W6" s="52" t="inlineStr"/>
-      <c r="X6" s="52" t="inlineStr"/>
-      <c r="Y6" s="52" t="inlineStr"/>
-      <c r="Z6" s="52" t="inlineStr">
+      <c r="T6" s="60" t="inlineStr"/>
+      <c r="U6" s="60" t="inlineStr"/>
+      <c r="V6" s="60" t="inlineStr"/>
+      <c r="W6" s="60" t="inlineStr"/>
+      <c r="X6" s="60" t="inlineStr"/>
+      <c r="Y6" s="60" t="inlineStr"/>
+      <c r="Z6" s="60" t="inlineStr">
         <is>
           <t>1/32〜3/16</t>
         </is>
       </c>
-      <c r="AA6" s="52" t="inlineStr"/>
-      <c r="AB6" s="52" t="inlineStr"/>
-      <c r="AC6" s="52" t="inlineStr">
+      <c r="AA6" s="60" t="inlineStr"/>
+      <c r="AB6" s="60" t="inlineStr"/>
+      <c r="AC6" s="60" t="inlineStr">
         <is>
           <t>Finesse Versatile</t>
         </is>
       </c>
-      <c r="AD6" s="52" t="inlineStr"/>
-      <c r="AE6" s="52" t="inlineStr"/>
-      <c r="AF6" s="52" t="inlineStr"/>
-      <c r="AG6" s="52" t="inlineStr">
+      <c r="AD6" s="60" t="inlineStr"/>
+      <c r="AE6" s="60" t="inlineStr"/>
+      <c r="AF6" s="60" t="inlineStr"/>
+      <c r="AG6" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH6" s="52" t="inlineStr">
+      <c r="AH6" s="60" t="inlineStr">
         <is>
           <t>Finesse Versatile 覆盖 spinning light-rig 全段：底层 Neko/Down Shot、无铅软饵、表层 Plug、Shad 和虫系都能切换，重点是轻量多用途而不是强障碍。</t>
         </is>
       </c>
-      <c r="AI6" s="52" t="inlineStr">
+      <c r="AI6" s="60" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Surface Plug / Shad / Bug Lure</t>
         </is>
       </c>
-      <c r="AJ6" s="52" t="inlineStr"/>
-      <c r="AK6" s="52" t="inlineStr"/>
-      <c r="AL6" s="52" t="inlineStr"/>
-      <c r="AM6" s="52" t="inlineStr">
+      <c r="AJ6" s="60" t="inlineStr"/>
+      <c r="AK6" s="60" t="inlineStr"/>
+      <c r="AL6" s="60" t="inlineStr"/>
+      <c r="AM6" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓中距离 / 轻量软饵・表层・Shad 切换</t>
         </is>
       </c>
-      <c r="AN6" s="52" t="inlineStr">
+      <c r="AN6" s="60" t="inlineStr">
         <is>
           <t>轻量多用途 spinning</t>
         </is>
       </c>
-      <c r="AO6" s="52" t="inlineStr">
+      <c r="AO6" s="60" t="inlineStr">
         <is>
           <t>Neko、Down Shot、No Sinker 是主轴，表层 Plug、Shad 和虫系可补搜索；适合一支竿覆盖高压轻量路线。</t>
         </is>
       </c>
-      <c r="AP6" s="52" t="inlineStr">
+      <c r="AP6" s="60" t="inlineStr">
         <is>
           <t>Finesse Versatile Finesse Versatile 癖のないファーストテーパーデザインにより、スピニングにおけるあらゆるライトリグをカバーするフィネスバーサタイルスピン。6’3″で近距離の繊細攻めから中距離の少しディスタンスが必要な釣りまでをこなす。ライトリグ全般から表層系プラグ、シャッド、虫系など幅広く対応。１本であらゆる状況にアジャストできる至高の１本。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ6" s="52" t="inlineStr">
+      <c r="AQ6" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR6" s="60" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="AR6" s="52" t="inlineStr"/>
+      <c r="AS6" s="60" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>DSRD10005</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C7" s="52" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D7" s="52" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>DHRS-63UL-FS</t>
         </is>
       </c>
-      <c r="E7" s="52" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F7" s="52" t="inlineStr">
+      <c r="F7" s="60" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G7" s="52" t="inlineStr">
+      <c r="G7" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H7" s="52" t="inlineStr"/>
-      <c r="I7" s="52" t="inlineStr"/>
-      <c r="J7" s="52" t="inlineStr">
+      <c r="H7" s="60" t="inlineStr"/>
+      <c r="I7" s="60" t="inlineStr"/>
+      <c r="J7" s="60" t="inlineStr">
         <is>
           <t>71g</t>
         </is>
       </c>
-      <c r="K7" s="52" t="inlineStr"/>
-      <c r="L7" s="52" t="inlineStr"/>
-      <c r="M7" s="52" t="inlineStr">
+      <c r="K7" s="60" t="inlineStr"/>
+      <c r="L7" s="60" t="inlineStr"/>
+      <c r="M7" s="60" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N7" s="52" t="inlineStr"/>
-      <c r="O7" s="52" t="inlineStr"/>
-      <c r="P7" s="52" t="inlineStr"/>
-      <c r="Q7" s="52" t="inlineStr"/>
-      <c r="R7" s="52" t="inlineStr">
+      <c r="N7" s="60" t="inlineStr"/>
+      <c r="O7" s="60" t="inlineStr"/>
+      <c r="P7" s="60" t="inlineStr"/>
+      <c r="Q7" s="60" t="inlineStr"/>
+      <c r="R7" s="60" t="inlineStr">
         <is>
           <t>￥51,000 (￥56,100)</t>
         </is>
       </c>
-      <c r="S7" s="52" t="inlineStr">
+      <c r="S7" s="60" t="inlineStr">
         <is>
           <t>4571527863806</t>
         </is>
       </c>
-      <c r="T7" s="52" t="inlineStr"/>
-      <c r="U7" s="52" t="inlineStr"/>
-      <c r="V7" s="52" t="inlineStr"/>
-      <c r="W7" s="52" t="inlineStr"/>
-      <c r="X7" s="52" t="inlineStr"/>
-      <c r="Y7" s="52" t="inlineStr"/>
-      <c r="Z7" s="52" t="inlineStr">
+      <c r="T7" s="60" t="inlineStr"/>
+      <c r="U7" s="60" t="inlineStr"/>
+      <c r="V7" s="60" t="inlineStr"/>
+      <c r="W7" s="60" t="inlineStr"/>
+      <c r="X7" s="60" t="inlineStr"/>
+      <c r="Y7" s="60" t="inlineStr"/>
+      <c r="Z7" s="60" t="inlineStr">
         <is>
           <t>1/32〜3/16</t>
         </is>
       </c>
-      <c r="AA7" s="52" t="inlineStr"/>
-      <c r="AB7" s="52" t="inlineStr"/>
-      <c r="AC7" s="52" t="inlineStr">
+      <c r="AA7" s="60" t="inlineStr"/>
+      <c r="AB7" s="60" t="inlineStr"/>
+      <c r="AC7" s="60" t="inlineStr">
         <is>
           <t>Light Midstroll</t>
         </is>
       </c>
-      <c r="AD7" s="52" t="inlineStr"/>
-      <c r="AE7" s="52" t="inlineStr"/>
-      <c r="AF7" s="52" t="inlineStr"/>
-      <c r="AG7" s="52" t="inlineStr">
+      <c r="AD7" s="60" t="inlineStr"/>
+      <c r="AE7" s="60" t="inlineStr"/>
+      <c r="AF7" s="60" t="inlineStr"/>
+      <c r="AG7" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH7" s="52" t="inlineStr">
+      <c r="AH7" s="60" t="inlineStr">
         <is>
           <t>Finesse Swim 不是普通底操竿，重点是用 Jighead、Neko 或 Down Shot 做中层游动；竿尖和导环设定服务于线弧、抖动节奏和泳姿稳定。</t>
         </is>
       </c>
-      <c r="AI7" s="52" t="inlineStr">
+      <c r="AI7" s="60" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Swimming Neko Rig / Swimming Down Shot / Hover Strolling</t>
         </is>
       </c>
-      <c r="AJ7" s="52" t="inlineStr"/>
-      <c r="AK7" s="52" t="inlineStr"/>
-      <c r="AL7" s="52" t="inlineStr"/>
-      <c r="AM7" s="52" t="inlineStr">
+      <c r="AJ7" s="60" t="inlineStr"/>
+      <c r="AK7" s="60" t="inlineStr"/>
+      <c r="AL7" s="60" t="inlineStr"/>
+      <c r="AM7" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水域・缓坡 / 中层 finesse swim</t>
         </is>
       </c>
-      <c r="AN7" s="52" t="inlineStr">
+      <c r="AN7" s="60" t="inlineStr">
         <is>
           <t>轻量中层游动专向</t>
         </is>
       </c>
-      <c r="AO7" s="52" t="inlineStr">
+      <c r="AO7" s="60" t="inlineStr">
         <is>
           <t>Jighead、Swimming Neko 和 Swimming Down Shot 的线弧更容易维持，适合持续抖动和轻量软饵水平泳姿控制。</t>
         </is>
       </c>
-      <c r="AP7" s="52" t="inlineStr">
+      <c r="AP7" s="60" t="inlineStr">
         <is>
           <t>Finesse Swim Finesse Swim 近年欠かすことの出来ないテクニックの一つミッドストローリングは、より進化をした時代を迎え、ジグヘッドの釣りに限らずネコリグやダウンショットなどあらゆるライトリグでスイミングで使いやすさを求められます。よりタイトに攻める事が出来る操作性とラインスラッグを出しながらシェイクをしやすいテーパーとガイドセッティングを追求することで、最高のフィネススイミングロッドに仕上げた。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ7" s="52" t="inlineStr">
+      <c r="AQ7" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ / フィネススイミング向けガイドセッティング</t>
+        </is>
+      </c>
+      <c r="AR7" s="60" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="AR7" s="52" t="inlineStr"/>
+      <c r="AS7" s="60" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="52" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>DSRD10006</t>
         </is>
       </c>
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C8" s="52" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D8" s="52" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>DHRS-66ML</t>
         </is>
       </c>
-      <c r="E8" s="52" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F8" s="52" t="inlineStr">
+      <c r="F8" s="60" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G8" s="52" t="inlineStr">
+      <c r="G8" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H8" s="52" t="inlineStr"/>
-      <c r="I8" s="52" t="inlineStr"/>
-      <c r="J8" s="52" t="inlineStr">
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr"/>
+      <c r="J8" s="60" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K8" s="52" t="inlineStr"/>
-      <c r="L8" s="52" t="inlineStr"/>
-      <c r="M8" s="52" t="inlineStr">
+      <c r="K8" s="60" t="inlineStr"/>
+      <c r="L8" s="60" t="inlineStr"/>
+      <c r="M8" s="60" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N8" s="52" t="inlineStr">
+      <c r="N8" s="60" t="inlineStr">
         <is>
           <t>0.6~1.5</t>
         </is>
       </c>
-      <c r="O8" s="52" t="inlineStr"/>
-      <c r="P8" s="52" t="inlineStr"/>
-      <c r="Q8" s="52" t="inlineStr"/>
-      <c r="R8" s="52" t="inlineStr">
+      <c r="O8" s="60" t="inlineStr"/>
+      <c r="P8" s="60" t="inlineStr"/>
+      <c r="Q8" s="60" t="inlineStr"/>
+      <c r="R8" s="60" t="inlineStr">
         <is>
           <t>￥51,500 (￥56,650)</t>
         </is>
       </c>
-      <c r="S8" s="52" t="inlineStr">
+      <c r="S8" s="60" t="inlineStr">
         <is>
           <t>4571527865206</t>
         </is>
       </c>
-      <c r="T8" s="52" t="inlineStr"/>
-      <c r="U8" s="52" t="inlineStr"/>
-      <c r="V8" s="52" t="inlineStr"/>
-      <c r="W8" s="52" t="inlineStr"/>
-      <c r="X8" s="52" t="inlineStr"/>
-      <c r="Y8" s="52" t="inlineStr"/>
-      <c r="Z8" s="52" t="inlineStr">
+      <c r="T8" s="60" t="inlineStr"/>
+      <c r="U8" s="60" t="inlineStr"/>
+      <c r="V8" s="60" t="inlineStr"/>
+      <c r="W8" s="60" t="inlineStr"/>
+      <c r="X8" s="60" t="inlineStr"/>
+      <c r="Y8" s="60" t="inlineStr"/>
+      <c r="Z8" s="60" t="inlineStr">
         <is>
           <t>1/32〜3/8</t>
         </is>
       </c>
-      <c r="AA8" s="52" t="inlineStr"/>
-      <c r="AB8" s="52" t="inlineStr"/>
-      <c r="AC8" s="52" t="inlineStr">
+      <c r="AA8" s="60" t="inlineStr"/>
+      <c r="AB8" s="60" t="inlineStr"/>
+      <c r="AC8" s="60" t="inlineStr">
         <is>
           <t>MAX Finesse</t>
         </is>
       </c>
-      <c r="AD8" s="52" t="inlineStr"/>
-      <c r="AE8" s="52" t="inlineStr"/>
-      <c r="AF8" s="52" t="inlineStr"/>
-      <c r="AG8" s="52" t="inlineStr">
+      <c r="AD8" s="60" t="inlineStr"/>
+      <c r="AE8" s="60" t="inlineStr"/>
+      <c r="AF8" s="60" t="inlineStr"/>
+      <c r="AG8" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH8" s="52" t="inlineStr">
+      <c r="AH8" s="60" t="inlineStr">
         <is>
           <t>MAX Finesse 面向 PE cover power finesse：吊挂 Small Rubber Jig、Elastomer dog-walk、Power Mid Strolling 和稍重 Neko/Down Shot 都可用，重点是细致操作后把鱼带出 cover。</t>
         </is>
       </c>
-      <c r="AI8" s="52" t="inlineStr">
+      <c r="AI8" s="60" t="inlineStr">
         <is>
           <t>Power Finesse / Hanging Small Rubber Jig / Elastomer Dog Walk / Power Mid Strolling / Heavy Down Shot</t>
         </is>
       </c>
-      <c r="AJ8" s="52" t="inlineStr"/>
-      <c r="AK8" s="52" t="inlineStr"/>
-      <c r="AL8" s="52" t="inlineStr"/>
-      <c r="AM8" s="52" t="inlineStr">
+      <c r="AJ8" s="60" t="inlineStr"/>
+      <c r="AK8" s="60" t="inlineStr"/>
+      <c r="AL8" s="60" t="inlineStr"/>
+      <c r="AM8" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 边缘・码头・草洞 / PE power finesse</t>
         </is>
       </c>
-      <c r="AN8" s="52" t="inlineStr">
+      <c r="AN8" s="60" t="inlineStr">
         <is>
           <t>PE power finesse 多用途</t>
         </is>
       </c>
-      <c r="AO8" s="52" t="inlineStr">
+      <c r="AO8" s="60" t="inlineStr">
         <is>
           <t>Small Rubber Jig 吊挂、Elastomer dog-walk 和 Power Mid Strolling 都能处理，价值在细操作后仍有把鱼带出 cover 的支撑。</t>
         </is>
       </c>
-      <c r="AP8" s="52" t="inlineStr">
+      <c r="AP8" s="60" t="inlineStr">
         <is>
           <t>MAX Finesse MAX Finesse ミドルバーサタイルフィネスロッド。PEを使用したカバー周りのパワーフィネスから吊るし系、エラストマールアーのドックウォーク、パワーミドスト、やや重量のあるライトリグ全般まで幅広くカバー。 。伝統の食わせのファストテーパーからバスの引きに負けないバットパワーを持ち合わせバスを捉える。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい</t>
         </is>
       </c>
-      <c r="AQ8" s="52" t="inlineStr">
+      <c r="AQ8" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR8" s="60" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR8" s="52" t="inlineStr">
+      <c r="AS8" s="60" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="52" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>DSRD10007</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C9" s="52" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D9" s="52" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>DHRS-66L/ML-FS</t>
         </is>
       </c>
-      <c r="E9" s="52" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>L/ML</t>
         </is>
       </c>
-      <c r="F9" s="52" t="inlineStr">
+      <c r="F9" s="60" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G9" s="52" t="inlineStr">
+      <c r="G9" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H9" s="52" t="inlineStr"/>
-      <c r="I9" s="52" t="inlineStr"/>
-      <c r="J9" s="52" t="inlineStr"/>
-      <c r="K9" s="52" t="inlineStr"/>
-      <c r="L9" s="52" t="inlineStr"/>
-      <c r="M9" s="52" t="inlineStr">
+      <c r="H9" s="60" t="inlineStr"/>
+      <c r="I9" s="60" t="inlineStr"/>
+      <c r="J9" s="60" t="inlineStr"/>
+      <c r="K9" s="60" t="inlineStr"/>
+      <c r="L9" s="60" t="inlineStr"/>
+      <c r="M9" s="60" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N9" s="52" t="inlineStr">
+      <c r="N9" s="60" t="inlineStr">
         <is>
           <t>0.4~1号</t>
         </is>
       </c>
-      <c r="O9" s="52" t="inlineStr"/>
-      <c r="P9" s="52" t="inlineStr"/>
-      <c r="Q9" s="52" t="inlineStr"/>
-      <c r="R9" s="52" t="inlineStr">
+      <c r="O9" s="60" t="inlineStr"/>
+      <c r="P9" s="60" t="inlineStr"/>
+      <c r="Q9" s="60" t="inlineStr"/>
+      <c r="R9" s="60" t="inlineStr">
         <is>
           <t>￥57,500 (￥63,250)</t>
         </is>
       </c>
-      <c r="S9" s="52" t="inlineStr">
+      <c r="S9" s="60" t="inlineStr">
         <is>
           <t>4571527869037</t>
         </is>
       </c>
-      <c r="T9" s="52" t="inlineStr"/>
-      <c r="U9" s="52" t="inlineStr"/>
-      <c r="V9" s="52" t="inlineStr"/>
-      <c r="W9" s="52" t="inlineStr"/>
-      <c r="X9" s="52" t="inlineStr"/>
-      <c r="Y9" s="52" t="inlineStr"/>
-      <c r="Z9" s="52" t="inlineStr">
+      <c r="T9" s="60" t="inlineStr"/>
+      <c r="U9" s="60" t="inlineStr"/>
+      <c r="V9" s="60" t="inlineStr"/>
+      <c r="W9" s="60" t="inlineStr"/>
+      <c r="X9" s="60" t="inlineStr"/>
+      <c r="Y9" s="60" t="inlineStr"/>
+      <c r="Z9" s="60" t="inlineStr">
         <is>
           <t>1/32〜1/4</t>
         </is>
       </c>
-      <c r="AA9" s="52" t="inlineStr"/>
-      <c r="AB9" s="52" t="inlineStr"/>
-      <c r="AC9" s="52" t="inlineStr">
+      <c r="AA9" s="60" t="inlineStr"/>
+      <c r="AB9" s="60" t="inlineStr"/>
+      <c r="AC9" s="60" t="inlineStr">
         <is>
           <t>Power Finesse Swim</t>
         </is>
       </c>
-      <c r="AD9" s="52" t="inlineStr"/>
-      <c r="AE9" s="52" t="inlineStr"/>
-      <c r="AF9" s="52" t="inlineStr"/>
-      <c r="AG9" s="52" t="inlineStr">
+      <c r="AD9" s="60" t="inlineStr"/>
+      <c r="AE9" s="60" t="inlineStr"/>
+      <c r="AF9" s="60" t="inlineStr"/>
+      <c r="AG9" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH9" s="52" t="inlineStr">
+      <c r="AH9" s="60" t="inlineStr">
         <is>
           <t>Power Finesse Swim 是 4-5 寸中型 worm 的 mid-strolling 专用向，导环给线松弛和 blank 震动传递留空间；Power Finesse 只是同一套 PE 系统下的延伸。</t>
         </is>
       </c>
-      <c r="AI9" s="52" t="inlineStr">
+      <c r="AI9" s="60" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Hover Strolling / 4-5in Worm Swim / Power Finesse</t>
         </is>
       </c>
-      <c r="AJ9" s="52" t="inlineStr"/>
-      <c r="AK9" s="52" t="inlineStr"/>
-      <c r="AL9" s="52" t="inlineStr"/>
-      <c r="AM9" s="52" t="inlineStr">
+      <c r="AJ9" s="60" t="inlineStr"/>
+      <c r="AK9" s="60" t="inlineStr"/>
+      <c r="AL9" s="60" t="inlineStr"/>
+      <c r="AM9" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水域・大型湖库 / 4-5 寸 worm 中层游动</t>
         </is>
       </c>
-      <c r="AN9" s="52" t="inlineStr">
+      <c r="AN9" s="60" t="inlineStr">
         <is>
           <t>中型软饵 Mid Strolling</t>
         </is>
       </c>
-      <c r="AO9" s="52" t="inlineStr">
+      <c r="AO9" s="60" t="inlineStr">
         <is>
           <t>4-5 寸 worm 做 Mid Strolling 时不容易被饵重拖垮，远处线弧和 roll 感更好维持，兼顾 PE power finesse。</t>
         </is>
       </c>
-      <c r="AP9" s="52" t="inlineStr">
+      <c r="AP9" s="60" t="inlineStr">
         <is>
           <t>Power Finesse Swim Power Finesse Swim 昨今のハイプレッシャーフィールドにおいて、欠かすことのできないテクニックとなったミッドストローリング。青木大介が求める「理想の振り幅」を具現化したミドスト特化型モデル。 最大の特徴は、独自のガイドセッティング。ラインの遊びを適度に持たせつつ、ブランクスの振動を効率よくルアーへ伝えることで、4〜5インチクラスの中型ワームを誰でも簡単に、かつ正確にロールさせ続けることが可能。微かなバイトを弾かずに絡め取り、ミドスト特有の「重くなるだけのバイト」を確実に手元へ伝える。現場で振り続けてきたからこそ辿り着いた、ミドストの完成形がここにある。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ9" s="52" t="inlineStr">
+      <c r="AQ9" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ / フィネススイミング向けガイドセッティング</t>
+        </is>
+      </c>
+      <c r="AR9" s="60" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR9" s="52" t="inlineStr">
+      <c r="AS9" s="60" t="inlineStr">
         <is>
           <t>2026 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="52" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>DSRD10008</t>
         </is>
       </c>
-      <c r="B10" s="52" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C10" s="52" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="52" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>DHRS-68M</t>
         </is>
       </c>
-      <c r="E10" s="52" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F10" s="52" t="inlineStr">
+      <c r="F10" s="60" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G10" s="52" t="inlineStr">
+      <c r="G10" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H10" s="52" t="inlineStr"/>
-      <c r="I10" s="52" t="inlineStr"/>
-      <c r="J10" s="52" t="inlineStr"/>
-      <c r="K10" s="52" t="inlineStr"/>
-      <c r="L10" s="52" t="inlineStr"/>
-      <c r="M10" s="52" t="inlineStr"/>
-      <c r="N10" s="52" t="inlineStr">
+      <c r="H10" s="60" t="inlineStr"/>
+      <c r="I10" s="60" t="inlineStr"/>
+      <c r="J10" s="60" t="inlineStr"/>
+      <c r="K10" s="60" t="inlineStr"/>
+      <c r="L10" s="60" t="inlineStr"/>
+      <c r="M10" s="60" t="inlineStr"/>
+      <c r="N10" s="60" t="inlineStr">
         <is>
           <t>MAX~2号</t>
         </is>
       </c>
-      <c r="O10" s="52" t="inlineStr"/>
-      <c r="P10" s="52" t="inlineStr"/>
-      <c r="Q10" s="52" t="inlineStr"/>
-      <c r="R10" s="52" t="inlineStr">
+      <c r="O10" s="60" t="inlineStr"/>
+      <c r="P10" s="60" t="inlineStr"/>
+      <c r="Q10" s="60" t="inlineStr"/>
+      <c r="R10" s="60" t="inlineStr">
         <is>
           <t>￥58,500 (￥64,350)</t>
         </is>
       </c>
-      <c r="S10" s="52" t="inlineStr">
+      <c r="S10" s="60" t="inlineStr">
         <is>
           <t>4571527869044</t>
         </is>
       </c>
-      <c r="T10" s="52" t="inlineStr"/>
-      <c r="U10" s="52" t="inlineStr"/>
-      <c r="V10" s="52" t="inlineStr"/>
-      <c r="W10" s="52" t="inlineStr"/>
-      <c r="X10" s="52" t="inlineStr"/>
-      <c r="Y10" s="52" t="inlineStr"/>
-      <c r="Z10" s="52" t="inlineStr">
+      <c r="T10" s="60" t="inlineStr"/>
+      <c r="U10" s="60" t="inlineStr"/>
+      <c r="V10" s="60" t="inlineStr"/>
+      <c r="W10" s="60" t="inlineStr"/>
+      <c r="X10" s="60" t="inlineStr"/>
+      <c r="Y10" s="60" t="inlineStr"/>
+      <c r="Z10" s="60" t="inlineStr">
         <is>
           <t>1/8〜5/8</t>
         </is>
       </c>
-      <c r="AA10" s="52" t="inlineStr"/>
-      <c r="AB10" s="52" t="inlineStr"/>
-      <c r="AC10" s="52" t="inlineStr">
+      <c r="AA10" s="60" t="inlineStr"/>
+      <c r="AB10" s="60" t="inlineStr"/>
+      <c r="AC10" s="60" t="inlineStr">
         <is>
           <t>Power Finesse Shake</t>
         </is>
       </c>
-      <c r="AD10" s="52" t="inlineStr"/>
-      <c r="AE10" s="52" t="inlineStr"/>
-      <c r="AF10" s="52" t="inlineStr"/>
-      <c r="AG10" s="52" t="inlineStr">
+      <c r="AD10" s="60" t="inlineStr"/>
+      <c r="AE10" s="60" t="inlineStr"/>
+      <c r="AF10" s="60" t="inlineStr"/>
+      <c r="AG10" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH10" s="52" t="inlineStr">
+      <c r="AH10" s="60" t="inlineStr">
         <is>
           <t>Power Finesse Shake 以 PE spinning 远投和 cover 拖鱼为核心，Cover Neko、Small Rubber Jig、6 寸以上 worm 的 Mid Strolling 和较重无铅软饵都比普通轻量底操更匹配。</t>
         </is>
       </c>
-      <c r="AI10" s="52" t="inlineStr">
+      <c r="AI10" s="60" t="inlineStr">
         <is>
           <t>Power Finesse / Cover Neko / Small Rubber Jig / 6in+ Mid Strolling / Heavy No Sinker</t>
         </is>
       </c>
-      <c r="AJ10" s="52" t="inlineStr"/>
-      <c r="AK10" s="52" t="inlineStr"/>
-      <c r="AL10" s="52" t="inlineStr"/>
-      <c r="AM10" s="52" t="inlineStr">
+      <c r="AJ10" s="60" t="inlineStr"/>
+      <c r="AK10" s="60" t="inlineStr"/>
+      <c r="AL10" s="60" t="inlineStr"/>
+      <c r="AM10" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖库・远投 cover / 强化 spinning finesse</t>
         </is>
       </c>
-      <c r="AN10" s="52" t="inlineStr">
+      <c r="AN10" s="60" t="inlineStr">
         <is>
           <t>远投型 power finesse spinning</t>
         </is>
       </c>
-      <c r="AO10" s="52" t="inlineStr">
+      <c r="AO10" s="60" t="inlineStr">
         <is>
           <t>Cover Neko、Small Rubber Jig 和 6 寸以上 worm 的远距离操作更有底气，适合细线体系下想兼顾距离和控鱼的人。</t>
         </is>
       </c>
-      <c r="AP10" s="52" t="inlineStr">
+      <c r="AP10" s="60" t="inlineStr">
         <is>
           <t>Power Finesse Shake Power Finesse Shake スピニングタックルでのPEライン使用を前提とした、次世代のマルチフィネスモデル。フィネスロッドの枠を超えたパワーと遠投性能を兼ね備えている。 重量級ワームの抵抗に負けないバットパワーを持ちながら、ティップは繊細なアクションを殺さない。また、ライトリグ全般からカバーネコ、スモラバ、6インチ以上のルアーを使用したミドストをカバーし、PEラインの特性を最大限に活かした「遠くで掛ける」「カバーから引きずり出す」といった強気のフィネスを可能にする。 スピニングだから獲れる魚がいる。Mクラスだから挑める場所がある。青木の右腕として欠かせない、パワーフィネスの新たな基軸。屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ10" s="52" t="inlineStr">
+      <c r="AQ10" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR10" s="60" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR10" s="52" t="inlineStr">
+      <c r="AS10" s="60" t="inlineStr">
         <is>
           <t>2026 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="52" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>DSRD10009</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C11" s="52" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D11" s="52" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>DHRC-66L/ML</t>
         </is>
       </c>
-      <c r="E11" s="52" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>L/ML</t>
         </is>
       </c>
-      <c r="F11" s="52" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G11" s="52" t="inlineStr">
+      <c r="G11" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H11" s="52" t="inlineStr"/>
-      <c r="I11" s="52" t="inlineStr"/>
-      <c r="J11" s="52" t="inlineStr">
+      <c r="H11" s="60" t="inlineStr"/>
+      <c r="I11" s="60" t="inlineStr"/>
+      <c r="J11" s="60" t="inlineStr">
         <is>
           <t>95g</t>
         </is>
       </c>
-      <c r="K11" s="52" t="inlineStr"/>
-      <c r="L11" s="52" t="inlineStr"/>
-      <c r="M11" s="52" t="inlineStr">
+      <c r="K11" s="60" t="inlineStr"/>
+      <c r="L11" s="60" t="inlineStr"/>
+      <c r="M11" s="60" t="inlineStr">
         <is>
           <t>6~12</t>
         </is>
       </c>
-      <c r="N11" s="52" t="inlineStr"/>
-      <c r="O11" s="52" t="inlineStr"/>
-      <c r="P11" s="52" t="inlineStr"/>
-      <c r="Q11" s="52" t="inlineStr"/>
-      <c r="R11" s="52" t="inlineStr">
+      <c r="N11" s="60" t="inlineStr"/>
+      <c r="O11" s="60" t="inlineStr"/>
+      <c r="P11" s="60" t="inlineStr"/>
+      <c r="Q11" s="60" t="inlineStr"/>
+      <c r="R11" s="60" t="inlineStr">
         <is>
           <t>￥50,500 （￥55,550）</t>
         </is>
       </c>
-      <c r="S11" s="52" t="inlineStr">
+      <c r="S11" s="60" t="inlineStr">
         <is>
           <t>4571527863813</t>
         </is>
       </c>
-      <c r="T11" s="52" t="inlineStr"/>
-      <c r="U11" s="52" t="inlineStr"/>
-      <c r="V11" s="52" t="inlineStr"/>
-      <c r="W11" s="52" t="inlineStr"/>
-      <c r="X11" s="52" t="inlineStr"/>
-      <c r="Y11" s="52" t="inlineStr"/>
-      <c r="Z11" s="52" t="inlineStr">
+      <c r="T11" s="60" t="inlineStr"/>
+      <c r="U11" s="60" t="inlineStr"/>
+      <c r="V11" s="60" t="inlineStr"/>
+      <c r="W11" s="60" t="inlineStr"/>
+      <c r="X11" s="60" t="inlineStr"/>
+      <c r="Y11" s="60" t="inlineStr"/>
+      <c r="Z11" s="60" t="inlineStr">
         <is>
           <t>1/16〜1/4</t>
         </is>
       </c>
-      <c r="AA11" s="52" t="inlineStr"/>
-      <c r="AB11" s="52" t="inlineStr"/>
-      <c r="AC11" s="52" t="inlineStr">
+      <c r="AA11" s="60" t="inlineStr"/>
+      <c r="AB11" s="60" t="inlineStr"/>
+      <c r="AC11" s="60" t="inlineStr">
         <is>
           <t>Bait Finesse Versatile</t>
         </is>
       </c>
-      <c r="AD11" s="52" t="inlineStr"/>
-      <c r="AE11" s="52" t="inlineStr"/>
-      <c r="AF11" s="52" t="inlineStr"/>
-      <c r="AG11" s="52" t="inlineStr">
+      <c r="AD11" s="60" t="inlineStr"/>
+      <c r="AE11" s="60" t="inlineStr"/>
+      <c r="AF11" s="60" t="inlineStr"/>
+      <c r="AG11" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH11" s="52" t="inlineStr">
+      <c r="AH11" s="60" t="inlineStr">
         <is>
           <t>Bait Finesse Versatile 适合在 cover 与 open water 间精准投放 No Sinker、Neko、Down Shot 和 Small Rubber Jig；优势是短中距离落点、读底和控线。</t>
         </is>
       </c>
-      <c r="AI11" s="52" t="inlineStr">
+      <c r="AI11" s="60" t="inlineStr">
         <is>
           <t>No Sinker / Neko Rig / Down Shot / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ11" s="52" t="inlineStr"/>
-      <c r="AK11" s="52" t="inlineStr"/>
-      <c r="AL11" s="52" t="inlineStr"/>
-      <c r="AM11" s="52" t="inlineStr">
+      <c r="AJ11" s="60" t="inlineStr"/>
+      <c r="AK11" s="60" t="inlineStr"/>
+      <c r="AL11" s="60" t="inlineStr"/>
+      <c r="AM11" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 边缘・浅场 / BFS 软饵精细</t>
         </is>
       </c>
-      <c r="AN11" s="52" t="inlineStr">
+      <c r="AN11" s="60" t="inlineStr">
         <is>
           <t>软饵向 bait finesse</t>
         </is>
       </c>
-      <c r="AO11" s="52" t="inlineStr">
+      <c r="AO11" s="60" t="inlineStr">
         <is>
           <t>No Sinker、Neko、Down Shot 和 Small Rubber Jig 的落点控制好，适合用枪柄在障碍边缘做低弹道精细投放。</t>
         </is>
       </c>
-      <c r="AP11" s="52" t="inlineStr">
+      <c r="AP11" s="60" t="inlineStr">
         <is>
           <t>Bait Finesse Versatile Bait Finesse Versatile LパワーティップにMLパワーのバット、繊細さと強さを兼ね備えたバーサタイルベイトフィネスロッド。 カバーでもオープンエリアでも取り回しが良い6’6″の長さはカバーへの正確なフィネスアプローチや底の変化をしっかりと感じ取るボトムの釣りでもアドバンテージをもたらします。ノーシンカー、ネコリグ、ダウンショット、スモールラバージグのフィネス系全般に活躍する１本。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ11" s="52" t="inlineStr">
+      <c r="AQ11" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR11" s="60" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR11" s="52" t="inlineStr"/>
+      <c r="AS11" s="60" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>DSRD10010</t>
         </is>
       </c>
-      <c r="B12" s="52" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C12" s="52" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D12" s="52" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr">
         <is>
           <t>DHRC-69L+</t>
         </is>
       </c>
-      <c r="E12" s="52" t="inlineStr">
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>L+</t>
         </is>
       </c>
-      <c r="F12" s="52" t="inlineStr">
+      <c r="F12" s="60" t="inlineStr">
         <is>
           <t>6’9″</t>
         </is>
       </c>
-      <c r="G12" s="52" t="inlineStr">
+      <c r="G12" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H12" s="52" t="inlineStr"/>
-      <c r="I12" s="52" t="inlineStr"/>
-      <c r="J12" s="52" t="inlineStr">
+      <c r="H12" s="60" t="inlineStr"/>
+      <c r="I12" s="60" t="inlineStr"/>
+      <c r="J12" s="60" t="inlineStr">
         <is>
           <t>95g</t>
         </is>
       </c>
-      <c r="K12" s="52" t="inlineStr"/>
-      <c r="L12" s="52" t="inlineStr"/>
-      <c r="M12" s="52" t="inlineStr">
+      <c r="K12" s="60" t="inlineStr"/>
+      <c r="L12" s="60" t="inlineStr"/>
+      <c r="M12" s="60" t="inlineStr">
         <is>
           <t>6~12</t>
         </is>
       </c>
-      <c r="N12" s="52" t="inlineStr"/>
-      <c r="O12" s="52" t="inlineStr"/>
-      <c r="P12" s="52" t="inlineStr"/>
-      <c r="Q12" s="52" t="inlineStr"/>
-      <c r="R12" s="52" t="inlineStr">
+      <c r="N12" s="60" t="inlineStr"/>
+      <c r="O12" s="60" t="inlineStr"/>
+      <c r="P12" s="60" t="inlineStr"/>
+      <c r="Q12" s="60" t="inlineStr"/>
+      <c r="R12" s="60" t="inlineStr">
         <is>
           <t>￥51,500 (￥56,650)</t>
         </is>
       </c>
-      <c r="S12" s="52" t="inlineStr">
+      <c r="S12" s="60" t="inlineStr">
         <is>
           <t>4571527865213</t>
         </is>
       </c>
-      <c r="T12" s="52" t="inlineStr"/>
-      <c r="U12" s="52" t="inlineStr"/>
-      <c r="V12" s="52" t="inlineStr"/>
-      <c r="W12" s="52" t="inlineStr"/>
-      <c r="X12" s="52" t="inlineStr"/>
-      <c r="Y12" s="52" t="inlineStr"/>
-      <c r="Z12" s="52" t="inlineStr">
+      <c r="T12" s="60" t="inlineStr"/>
+      <c r="U12" s="60" t="inlineStr"/>
+      <c r="V12" s="60" t="inlineStr"/>
+      <c r="W12" s="60" t="inlineStr"/>
+      <c r="X12" s="60" t="inlineStr"/>
+      <c r="Y12" s="60" t="inlineStr"/>
+      <c r="Z12" s="60" t="inlineStr">
         <is>
           <t>1/16〜1/4</t>
         </is>
       </c>
-      <c r="AA12" s="52" t="inlineStr"/>
-      <c r="AB12" s="52" t="inlineStr"/>
-      <c r="AC12" s="52" t="inlineStr">
+      <c r="AA12" s="60" t="inlineStr"/>
+      <c r="AB12" s="60" t="inlineStr"/>
+      <c r="AC12" s="60" t="inlineStr">
         <is>
           <t>Cover Finesse</t>
         </is>
       </c>
-      <c r="AD12" s="52" t="inlineStr"/>
-      <c r="AE12" s="52" t="inlineStr"/>
-      <c r="AF12" s="52" t="inlineStr"/>
-      <c r="AG12" s="52" t="inlineStr">
+      <c r="AD12" s="60" t="inlineStr"/>
+      <c r="AE12" s="60" t="inlineStr"/>
+      <c r="AF12" s="60" t="inlineStr"/>
+      <c r="AG12" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH12" s="52" t="inlineStr">
+      <c r="AH12" s="60" t="inlineStr">
         <is>
           <t>Cover Finesse 的重点是把轻量软饵送进 cover：Cover Neko 和 Small Rubber Jig 放首位，No Sinker 与 Light Texas 用于更隐蔽或更抗挂的切换。</t>
         </is>
       </c>
-      <c r="AI12" s="52" t="inlineStr">
+      <c r="AI12" s="60" t="inlineStr">
         <is>
           <t>Cover Neko / Small Rubber Jig / No Sinker / Light Texas</t>
         </is>
       </c>
-      <c r="AJ12" s="52" t="inlineStr"/>
-      <c r="AK12" s="52" t="inlineStr"/>
-      <c r="AL12" s="52" t="inlineStr"/>
-      <c r="AM12" s="52" t="inlineStr">
+      <c r="AJ12" s="60" t="inlineStr"/>
+      <c r="AK12" s="60" t="inlineStr"/>
+      <c r="AL12" s="60" t="inlineStr"/>
+      <c r="AM12" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 轻 cover・芦苇边・浮物 / cover finesse</t>
         </is>
       </c>
-      <c r="AN12" s="52" t="inlineStr">
+      <c r="AN12" s="60" t="inlineStr">
         <is>
           <t>轻 cover 精细软饵</t>
         </is>
       </c>
-      <c r="AO12" s="52" t="inlineStr">
+      <c r="AO12" s="60" t="inlineStr">
         <is>
           <t>Cover Neko 和 Small Rubber Jig 是最自然的搭配，竿长让贴 cover 投放和中鱼后导鱼更有优势。</t>
         </is>
       </c>
-      <c r="AP12" s="52" t="inlineStr">
+      <c r="AP12" s="60" t="inlineStr">
         <is>
           <t>COVER Finesse Cover Finesse 時代が変わっても必要とされる不変のカバーフィネスロッド。 6’９”の長さはカバーへのより正確なフィネスアプローチや掛けた時の優位性、カバーの釣りに必要な性能備えている。カバーネコリグ、スモールラバージグ、ノーシンカーなどフィネス系全般に活躍する１本。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ12" s="52" t="inlineStr">
+      <c r="AQ12" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR12" s="60" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="AR12" s="52" t="inlineStr">
+      <c r="AS12" s="60" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>DSRD10011</t>
         </is>
       </c>
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C13" s="52" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D13" s="52" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>DHRC-68M</t>
         </is>
       </c>
-      <c r="E13" s="52" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F13" s="52" t="inlineStr">
+      <c r="F13" s="60" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G13" s="52" t="inlineStr">
+      <c r="G13" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H13" s="52" t="inlineStr"/>
-      <c r="I13" s="52" t="inlineStr"/>
-      <c r="J13" s="52" t="inlineStr">
+      <c r="H13" s="60" t="inlineStr"/>
+      <c r="I13" s="60" t="inlineStr"/>
+      <c r="J13" s="60" t="inlineStr">
         <is>
           <t>95g</t>
         </is>
       </c>
-      <c r="K13" s="52" t="inlineStr"/>
-      <c r="L13" s="52" t="inlineStr"/>
-      <c r="M13" s="52" t="inlineStr">
+      <c r="K13" s="60" t="inlineStr"/>
+      <c r="L13" s="60" t="inlineStr"/>
+      <c r="M13" s="60" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N13" s="52" t="inlineStr"/>
-      <c r="O13" s="52" t="inlineStr"/>
-      <c r="P13" s="52" t="inlineStr"/>
-      <c r="Q13" s="52" t="inlineStr"/>
-      <c r="R13" s="52" t="inlineStr">
+      <c r="N13" s="60" t="inlineStr"/>
+      <c r="O13" s="60" t="inlineStr"/>
+      <c r="P13" s="60" t="inlineStr"/>
+      <c r="Q13" s="60" t="inlineStr"/>
+      <c r="R13" s="60" t="inlineStr">
         <is>
           <t>￥51,500 (￥56,650)</t>
         </is>
       </c>
-      <c r="S13" s="52" t="inlineStr">
+      <c r="S13" s="60" t="inlineStr">
         <is>
           <t>4571527863820</t>
         </is>
       </c>
-      <c r="T13" s="52" t="inlineStr"/>
-      <c r="U13" s="52" t="inlineStr"/>
-      <c r="V13" s="52" t="inlineStr"/>
-      <c r="W13" s="52" t="inlineStr"/>
-      <c r="X13" s="52" t="inlineStr"/>
-      <c r="Y13" s="52" t="inlineStr"/>
-      <c r="Z13" s="52" t="inlineStr">
+      <c r="T13" s="60" t="inlineStr"/>
+      <c r="U13" s="60" t="inlineStr"/>
+      <c r="V13" s="60" t="inlineStr"/>
+      <c r="W13" s="60" t="inlineStr"/>
+      <c r="X13" s="60" t="inlineStr"/>
+      <c r="Y13" s="60" t="inlineStr"/>
+      <c r="Z13" s="60" t="inlineStr">
         <is>
           <t>3/16〜5/8</t>
         </is>
       </c>
-      <c r="AA13" s="52" t="inlineStr"/>
-      <c r="AB13" s="52" t="inlineStr"/>
-      <c r="AC13" s="52" t="inlineStr">
+      <c r="AA13" s="60" t="inlineStr"/>
+      <c r="AB13" s="60" t="inlineStr"/>
+      <c r="AC13" s="60" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="AD13" s="52" t="inlineStr"/>
-      <c r="AE13" s="52" t="inlineStr"/>
-      <c r="AF13" s="52" t="inlineStr"/>
-      <c r="AG13" s="52" t="inlineStr">
+      <c r="AD13" s="60" t="inlineStr"/>
+      <c r="AE13" s="60" t="inlineStr"/>
+      <c r="AF13" s="60" t="inlineStr"/>
+      <c r="AG13" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH13" s="52" t="inlineStr">
+      <c r="AH13" s="60" t="inlineStr">
         <is>
           <t>FX 是 bait 万用核心竿，描述明确覆盖从撃ち到巻き：软饵端以 No Sinker、Texas、Down Shot、Neko、Football 为主，搜索端再接 Crankbait 和 Spinnerbait。</t>
         </is>
       </c>
-      <c r="AI13" s="52" t="inlineStr">
+      <c r="AI13" s="60" t="inlineStr">
         <is>
           <t>No Sinker / Texas Rig / Down Shot / Neko Rig / Football Jig / Crankbait / Spinnerbait</t>
         </is>
       </c>
-      <c r="AJ13" s="52" t="inlineStr"/>
-      <c r="AK13" s="52" t="inlineStr"/>
-      <c r="AL13" s="52" t="inlineStr"/>
-      <c r="AM13" s="52" t="inlineStr">
+      <c r="AJ13" s="60" t="inlineStr"/>
+      <c r="AK13" s="60" t="inlineStr"/>
+      <c r="AL13" s="60" t="inlineStr"/>
+      <c r="AM13" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓・船钓 / 软饵底操到卷物搜索</t>
         </is>
       </c>
-      <c r="AN13" s="52" t="inlineStr">
+      <c r="AN13" s="60" t="inlineStr">
         <is>
           <t>软硬饵切换型 bait versatile</t>
         </is>
       </c>
-      <c r="AO13" s="52" t="inlineStr">
+      <c r="AO13" s="60" t="inlineStr">
         <is>
           <t>No Sinker、Texas、Down Shot、Neko、Football 可以打点，Crankbait 和 Spinnerbait 可搜索，适合一支竿覆盖日常主力 bait 场景。</t>
         </is>
       </c>
-      <c r="AP13" s="52" t="inlineStr">
+      <c r="AP13" s="60" t="inlineStr">
         <is>
           <t>FX 巻きから撃ちまでマルチにこなせるスーパーバーサタイルモデル。癖のないテーパーから生み出されるキャスト性能とロッドの自由度。ベイトモデルの中核に相応しいバランスを実現。ノーシンカー、テキサス、ダウンショット、ネコリグ、フットボール、プラグ全般、ワイヤーベイトまであらゆるジャンルのタイプが使用可能。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ13" s="52" t="inlineStr">
+      <c r="AQ13" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR13" s="60" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR13" s="52" t="inlineStr"/>
+      <c r="AS13" s="60" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>DSRD10012</t>
         </is>
       </c>
-      <c r="B14" s="52" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C14" s="52" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D14" s="52" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr">
         <is>
           <t>DHRC-610MH</t>
         </is>
       </c>
-      <c r="E14" s="52" t="inlineStr">
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F14" s="52" t="inlineStr">
+      <c r="F14" s="60" t="inlineStr">
         <is>
           <t>6’10”</t>
         </is>
       </c>
-      <c r="G14" s="52" t="inlineStr">
+      <c r="G14" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H14" s="52" t="inlineStr"/>
-      <c r="I14" s="52" t="inlineStr"/>
-      <c r="J14" s="52" t="inlineStr">
+      <c r="H14" s="60" t="inlineStr"/>
+      <c r="I14" s="60" t="inlineStr"/>
+      <c r="J14" s="60" t="inlineStr">
         <is>
           <t>109g</t>
         </is>
       </c>
-      <c r="K14" s="52" t="inlineStr"/>
-      <c r="L14" s="52" t="inlineStr"/>
-      <c r="M14" s="52" t="inlineStr">
+      <c r="K14" s="60" t="inlineStr"/>
+      <c r="L14" s="60" t="inlineStr"/>
+      <c r="M14" s="60" t="inlineStr">
         <is>
           <t>8~20</t>
         </is>
       </c>
-      <c r="N14" s="52" t="inlineStr"/>
-      <c r="O14" s="52" t="inlineStr"/>
-      <c r="P14" s="52" t="inlineStr"/>
-      <c r="Q14" s="52" t="inlineStr"/>
-      <c r="R14" s="52" t="inlineStr">
+      <c r="N14" s="60" t="inlineStr"/>
+      <c r="O14" s="60" t="inlineStr"/>
+      <c r="P14" s="60" t="inlineStr"/>
+      <c r="Q14" s="60" t="inlineStr"/>
+      <c r="R14" s="60" t="inlineStr">
         <is>
           <t>￥52,500 (￥57,750)</t>
         </is>
       </c>
-      <c r="S14" s="52" t="inlineStr">
+      <c r="S14" s="60" t="inlineStr">
         <is>
           <t>4571527865220</t>
         </is>
       </c>
-      <c r="T14" s="52" t="inlineStr"/>
-      <c r="U14" s="52" t="inlineStr"/>
-      <c r="V14" s="52" t="inlineStr"/>
-      <c r="W14" s="52" t="inlineStr"/>
-      <c r="X14" s="52" t="inlineStr"/>
-      <c r="Y14" s="52" t="inlineStr"/>
-      <c r="Z14" s="52" t="inlineStr">
+      <c r="T14" s="60" t="inlineStr"/>
+      <c r="U14" s="60" t="inlineStr"/>
+      <c r="V14" s="60" t="inlineStr"/>
+      <c r="W14" s="60" t="inlineStr"/>
+      <c r="X14" s="60" t="inlineStr"/>
+      <c r="Y14" s="60" t="inlineStr"/>
+      <c r="Z14" s="60" t="inlineStr">
         <is>
           <t>3/16〜3/4</t>
         </is>
       </c>
-      <c r="AA14" s="52" t="inlineStr"/>
-      <c r="AB14" s="52" t="inlineStr"/>
-      <c r="AC14" s="52" t="inlineStr">
+      <c r="AA14" s="60" t="inlineStr"/>
+      <c r="AB14" s="60" t="inlineStr"/>
+      <c r="AC14" s="60" t="inlineStr">
         <is>
           <t>FXR</t>
         </is>
       </c>
-      <c r="AD14" s="52" t="inlineStr"/>
-      <c r="AE14" s="52" t="inlineStr"/>
-      <c r="AF14" s="52" t="inlineStr"/>
-      <c r="AG14" s="52" t="inlineStr">
+      <c r="AD14" s="60" t="inlineStr"/>
+      <c r="AE14" s="60" t="inlineStr"/>
+      <c r="AF14" s="60" t="inlineStr"/>
+      <c r="AG14" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH14" s="52" t="inlineStr">
+      <c r="AH14" s="60" t="inlineStr">
         <is>
           <t>FXR 是中量级 super versatile，先承担 Texas、No Sinker、Down Shot、Neko 和 Football 这类 worm/jig 场景，再扩展到 wire bait 与中型 Big Bait。</t>
         </is>
       </c>
-      <c r="AI14" s="52" t="inlineStr">
+      <c r="AI14" s="60" t="inlineStr">
         <is>
           <t>Texas Rig / No Sinker / Down Shot / Neko Rig / Football Jig / Spinnerbait / Mid-size Big Bait</t>
         </is>
       </c>
-      <c r="AJ14" s="52" t="inlineStr"/>
-      <c r="AK14" s="52" t="inlineStr"/>
-      <c r="AL14" s="52" t="inlineStr"/>
-      <c r="AM14" s="52" t="inlineStr">
+      <c r="AJ14" s="60" t="inlineStr"/>
+      <c r="AK14" s="60" t="inlineStr"/>
+      <c r="AL14" s="60" t="inlineStr"/>
+      <c r="AM14" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 湖库・草边・硬底 / 中量软饵与移动饵</t>
         </is>
       </c>
-      <c r="AN14" s="52" t="inlineStr">
+      <c r="AN14" s="60" t="inlineStr">
         <is>
           <t>中量级强泛用 bait</t>
         </is>
       </c>
-      <c r="AO14" s="52" t="inlineStr">
+      <c r="AO14" s="60" t="inlineStr">
         <is>
           <t>Texas、Football、Neko 和 Spinnerbait 都在合理范围，Mid-size Big Bait 只是扩展用途；更适合中重钓组的连续切换。</t>
         </is>
       </c>
-      <c r="AP14" s="52" t="inlineStr">
+      <c r="AP14" s="60" t="inlineStr">
         <is>
           <t>FXR 巻きから撃ちまでマルチにこなせるスーパーミドルバーサタイルモデル。癖のないテーパーから生み出されるキャスト性能とロッドの自由度。ベイトモデルの中核に相応しいバランスを実現。ノーシンカー、テキサス、ダウンショット、ネコリグ、フットボール、プラグ全般、ワイヤーベイト、ミドルサイズビッグベイトまであらゆるジャンルのタイプが使用可能。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ14" s="52" t="inlineStr">
+      <c r="AQ14" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR14" s="60" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="AR14" s="52" t="inlineStr">
+      <c r="AS14" s="60" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="52" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>DSRD10013</t>
         </is>
       </c>
-      <c r="B15" s="52" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C15" s="52" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D15" s="52" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr">
         <is>
           <t>DHRC-70H</t>
         </is>
       </c>
-      <c r="E15" s="52" t="inlineStr">
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F15" s="52" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr">
         <is>
           <t>7’0″</t>
         </is>
       </c>
-      <c r="G15" s="52" t="inlineStr">
+      <c r="G15" s="60" t="inlineStr">
         <is>
           <t>Regular first</t>
         </is>
       </c>
-      <c r="H15" s="52" t="inlineStr"/>
-      <c r="I15" s="52" t="inlineStr"/>
-      <c r="J15" s="52" t="inlineStr">
+      <c r="H15" s="60" t="inlineStr"/>
+      <c r="I15" s="60" t="inlineStr"/>
+      <c r="J15" s="60" t="inlineStr">
         <is>
           <t>112g</t>
         </is>
       </c>
-      <c r="K15" s="52" t="inlineStr"/>
-      <c r="L15" s="52" t="inlineStr"/>
-      <c r="M15" s="52" t="inlineStr">
+      <c r="K15" s="60" t="inlineStr"/>
+      <c r="L15" s="60" t="inlineStr"/>
+      <c r="M15" s="60" t="inlineStr">
         <is>
           <t>12~25</t>
         </is>
       </c>
-      <c r="N15" s="52" t="inlineStr"/>
-      <c r="O15" s="52" t="inlineStr"/>
-      <c r="P15" s="52" t="inlineStr"/>
-      <c r="Q15" s="52" t="inlineStr"/>
-      <c r="R15" s="52" t="inlineStr">
+      <c r="N15" s="60" t="inlineStr"/>
+      <c r="O15" s="60" t="inlineStr"/>
+      <c r="P15" s="60" t="inlineStr"/>
+      <c r="Q15" s="60" t="inlineStr"/>
+      <c r="R15" s="60" t="inlineStr">
         <is>
           <t>￥52,500 (￥57,750)</t>
         </is>
       </c>
-      <c r="S15" s="52" t="inlineStr">
+      <c r="S15" s="60" t="inlineStr">
         <is>
           <t>4571527863837</t>
         </is>
       </c>
-      <c r="T15" s="52" t="inlineStr"/>
-      <c r="U15" s="52" t="inlineStr"/>
-      <c r="V15" s="52" t="inlineStr"/>
-      <c r="W15" s="52" t="inlineStr"/>
-      <c r="X15" s="52" t="inlineStr"/>
-      <c r="Y15" s="52" t="inlineStr"/>
-      <c r="Z15" s="52" t="inlineStr">
+      <c r="T15" s="60" t="inlineStr"/>
+      <c r="U15" s="60" t="inlineStr"/>
+      <c r="V15" s="60" t="inlineStr"/>
+      <c r="W15" s="60" t="inlineStr"/>
+      <c r="X15" s="60" t="inlineStr"/>
+      <c r="Y15" s="60" t="inlineStr"/>
+      <c r="Z15" s="60" t="inlineStr">
         <is>
           <t>3/16〜1</t>
         </is>
       </c>
-      <c r="AA15" s="52" t="inlineStr"/>
-      <c r="AB15" s="52" t="inlineStr"/>
-      <c r="AC15" s="52" t="inlineStr">
+      <c r="AA15" s="60" t="inlineStr"/>
+      <c r="AB15" s="60" t="inlineStr"/>
+      <c r="AC15" s="60" t="inlineStr">
         <is>
           <t>Power Fishing Versatile</t>
         </is>
       </c>
-      <c r="AD15" s="52" t="inlineStr"/>
-      <c r="AE15" s="52" t="inlineStr"/>
-      <c r="AF15" s="52" t="inlineStr"/>
-      <c r="AG15" s="52" t="inlineStr">
+      <c r="AD15" s="60" t="inlineStr"/>
+      <c r="AE15" s="60" t="inlineStr"/>
+      <c r="AF15" s="60" t="inlineStr"/>
+      <c r="AG15" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH15" s="52" t="inlineStr">
+      <c r="AH15" s="60" t="inlineStr">
         <is>
           <t>Power Fishing Versatile 明确面向重 cover 和重系钓组：Heavy Texas、Rubber Jig、Carolina、Free Rig 是主线，Big Spoon、Big Bait 和 Heavy Spinnerbait 属强力搜索补充。</t>
         </is>
       </c>
-      <c r="AI15" s="52" t="inlineStr">
+      <c r="AI15" s="60" t="inlineStr">
         <is>
           <t>Heavy Texas / Rubber Jig / Carolina Rig / Free Rig / Big Spoon / Big Bait / Heavy Spinnerbait</t>
         </is>
       </c>
-      <c r="AJ15" s="52" t="inlineStr"/>
-      <c r="AK15" s="52" t="inlineStr"/>
-      <c r="AL15" s="52" t="inlineStr"/>
-      <c r="AM15" s="52" t="inlineStr">
+      <c r="AJ15" s="60" t="inlineStr"/>
+      <c r="AK15" s="60" t="inlineStr"/>
+      <c r="AL15" s="60" t="inlineStr"/>
+      <c r="AM15" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 重 cover・深水硬底・大型饵搜索</t>
         </is>
       </c>
-      <c r="AN15" s="52" t="inlineStr">
+      <c r="AN15" s="60" t="inlineStr">
         <is>
           <t>强力底操与重系搜索</t>
         </is>
       </c>
-      <c r="AO15" s="52" t="inlineStr">
+      <c r="AO15" s="60" t="inlineStr">
         <is>
           <t>Heavy Texas、Rubber Jig、Carolina、Free Rig 能打重 cover，Big Spoon、Big Bait 和 Heavy Spinnerbait 可做强搜索，适合需要控鱼余量的场景。</t>
         </is>
       </c>
-      <c r="AP15" s="52" t="inlineStr">
+      <c r="AP15" s="60" t="inlineStr">
         <is>
           <t>Power Fishing Versatile Power Fishing Versatile 難攻不落のカバーを制するヘビーバーサタイルロッド。強靭な強さと繊細さを合わせ持つこのロッドは軽めのリグから重めのリグまでフィールドの状況に応じて幅広い変化に対応。テキサス、ラバージグ、キャロライナリグ、フリーリグ、ビッグスプーン、ビッグベイト、ヘビースピナーベイトなど対応。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ15" s="52" t="inlineStr">
+      <c r="AQ15" s="60" t="inlineStr">
+        <is>
+          <t>異なる弾性率カーボン / グルーブドセンターグリップ / チタンSICガイド / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR15" s="60" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="AR15" s="52" t="inlineStr"/>
+      <c r="AS15" s="60" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="52" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>DSRD10014</t>
         </is>
       </c>
-      <c r="B16" s="52" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C16" s="52" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="52" t="inlineStr">
+      <c r="D16" s="60" t="inlineStr">
         <is>
           <t>DHRS-E-62UL-S</t>
         </is>
       </c>
-      <c r="E16" s="52" t="inlineStr">
+      <c r="E16" s="60" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F16" s="52" t="inlineStr">
+      <c r="F16" s="60" t="inlineStr">
         <is>
           <t>6’2″</t>
         </is>
       </c>
-      <c r="G16" s="52" t="inlineStr">
+      <c r="G16" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H16" s="52" t="inlineStr"/>
-      <c r="I16" s="52" t="inlineStr"/>
-      <c r="J16" s="52" t="inlineStr">
+      <c r="H16" s="60" t="inlineStr"/>
+      <c r="I16" s="60" t="inlineStr"/>
+      <c r="J16" s="60" t="inlineStr">
         <is>
           <t>71g</t>
         </is>
       </c>
-      <c r="K16" s="52" t="inlineStr"/>
-      <c r="L16" s="52" t="inlineStr"/>
-      <c r="M16" s="52" t="inlineStr">
+      <c r="K16" s="60" t="inlineStr"/>
+      <c r="L16" s="60" t="inlineStr"/>
+      <c r="M16" s="60" t="inlineStr">
         <is>
           <t>2.5~8</t>
         </is>
       </c>
-      <c r="N16" s="52" t="inlineStr"/>
-      <c r="O16" s="52" t="inlineStr"/>
-      <c r="P16" s="52" t="inlineStr"/>
-      <c r="Q16" s="52" t="inlineStr"/>
-      <c r="R16" s="52" t="inlineStr">
+      <c r="N16" s="60" t="inlineStr"/>
+      <c r="O16" s="60" t="inlineStr"/>
+      <c r="P16" s="60" t="inlineStr"/>
+      <c r="Q16" s="60" t="inlineStr"/>
+      <c r="R16" s="60" t="inlineStr">
         <is>
           <t>￥62,000 (￥68,200)</t>
         </is>
       </c>
-      <c r="S16" s="52" t="inlineStr">
+      <c r="S16" s="60" t="inlineStr">
         <is>
           <t>4571527863844</t>
         </is>
       </c>
-      <c r="T16" s="52" t="inlineStr"/>
-      <c r="U16" s="52" t="inlineStr"/>
-      <c r="V16" s="52" t="inlineStr"/>
-      <c r="W16" s="52" t="inlineStr"/>
-      <c r="X16" s="52" t="inlineStr"/>
-      <c r="Y16" s="52" t="inlineStr"/>
-      <c r="Z16" s="52" t="inlineStr">
+      <c r="T16" s="60" t="inlineStr"/>
+      <c r="U16" s="60" t="inlineStr"/>
+      <c r="V16" s="60" t="inlineStr"/>
+      <c r="W16" s="60" t="inlineStr"/>
+      <c r="X16" s="60" t="inlineStr"/>
+      <c r="Y16" s="60" t="inlineStr"/>
+      <c r="Z16" s="60" t="inlineStr">
         <is>
           <t>1/32〜1/4</t>
         </is>
       </c>
-      <c r="AA16" s="52" t="inlineStr"/>
-      <c r="AB16" s="52" t="inlineStr"/>
-      <c r="AC16" s="52" t="inlineStr">
+      <c r="AA16" s="60" t="inlineStr"/>
+      <c r="AB16" s="60" t="inlineStr"/>
+      <c r="AC16" s="60" t="inlineStr">
         <is>
           <t>The Finesse Shooting</t>
         </is>
       </c>
-      <c r="AD16" s="52" t="inlineStr"/>
-      <c r="AE16" s="52" t="inlineStr"/>
-      <c r="AF16" s="52" t="inlineStr"/>
-      <c r="AG16" s="52" t="inlineStr">
+      <c r="AD16" s="60" t="inlineStr"/>
+      <c r="AE16" s="60" t="inlineStr"/>
+      <c r="AF16" s="60" t="inlineStr"/>
+      <c r="AG16" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH16" s="52" t="inlineStr">
+      <c r="AH16" s="60" t="inlineStr">
         <is>
           <t>The Finesse Shooting 用长 solid tip 和细 PE 做轻量投射与操作，No Sinker、Down Shot、Neko、Jighead、Small Rubber Jig 和 Hover Strolling 都是官网明确适用。</t>
         </is>
       </c>
-      <c r="AI16" s="52" t="inlineStr">
+      <c r="AI16" s="60" t="inlineStr">
         <is>
           <t>No Sinker / Down Shot / Neko Rig / Jighead Rig / Small Rubber Jig / Hover Strolling</t>
         </is>
       </c>
-      <c r="AJ16" s="52" t="inlineStr"/>
-      <c r="AK16" s="52" t="inlineStr"/>
-      <c r="AL16" s="52" t="inlineStr"/>
-      <c r="AM16" s="52" t="inlineStr">
+      <c r="AJ16" s="60" t="inlineStr"/>
+      <c r="AK16" s="60" t="inlineStr"/>
+      <c r="AL16" s="60" t="inlineStr"/>
+      <c r="AM16" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压开放水・清水 / PE finesse shooting</t>
         </is>
       </c>
-      <c r="AN16" s="52" t="inlineStr">
+      <c r="AN16" s="60" t="inlineStr">
         <is>
           <t>极细线轻量投射 finesse</t>
         </is>
       </c>
-      <c r="AO16" s="52" t="inlineStr">
+      <c r="AO16" s="60" t="inlineStr">
         <is>
           <t>No Sinker、Down Shot、Jighead 和 Hover Strolling 的轻量投射更稳定，长 solid tip 对短咬和细微负重变化更友好。</t>
         </is>
       </c>
-      <c r="AP16" s="52" t="inlineStr">
+      <c r="AP16" s="60" t="inlineStr">
         <is>
           <t>The Finesse Shooting EXTREME SPEC/2024 【EXTREME SPEC/2024 Limited】The Finesse Shooting 過激なまでに追求したエクストリームスペックモデル。ハイクオリティカーボンと中弾性ロングソリッドの極上なまでの操作感で軽量ルアーを意のままに飛ばし、操り、掛ける。極細PEラインに対応。ノーシンカー、ダウンショット、ネコリグ、ジグヘッド、スモラバ、ホバストまで幅広く対応。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ16" s="52" t="inlineStr">
+      <c r="AQ16" s="60" t="inlineStr">
+        <is>
+          <t>ハイクオリティカーボン / 中弾性ロングソリッド / TORZITEガイド / グルーブドセンターグリップ / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR16" s="60" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="AR16" s="52" t="inlineStr"/>
+      <c r="AS16" s="60" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>DSRD10015</t>
         </is>
       </c>
-      <c r="B17" s="52" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>DSR1001</t>
         </is>
       </c>
-      <c r="C17" s="52" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D17" s="52" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr">
         <is>
           <t>DHRS-E-510XUL-S</t>
         </is>
       </c>
-      <c r="E17" s="52" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F17" s="52" t="inlineStr">
+      <c r="F17" s="60" t="inlineStr">
         <is>
           <t>5’10”</t>
         </is>
       </c>
-      <c r="G17" s="52" t="inlineStr">
+      <c r="G17" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H17" s="52" t="inlineStr"/>
-      <c r="I17" s="52" t="inlineStr"/>
-      <c r="J17" s="52" t="inlineStr">
+      <c r="H17" s="60" t="inlineStr"/>
+      <c r="I17" s="60" t="inlineStr"/>
+      <c r="J17" s="60" t="inlineStr">
         <is>
           <t>67g</t>
         </is>
       </c>
-      <c r="K17" s="52" t="inlineStr"/>
-      <c r="L17" s="52" t="inlineStr"/>
-      <c r="M17" s="52" t="inlineStr">
+      <c r="K17" s="60" t="inlineStr"/>
+      <c r="L17" s="60" t="inlineStr"/>
+      <c r="M17" s="60" t="inlineStr">
         <is>
           <t>2~4</t>
         </is>
       </c>
-      <c r="N17" s="52" t="inlineStr">
+      <c r="N17" s="60" t="inlineStr">
         <is>
           <t>0.2~0.6</t>
         </is>
       </c>
-      <c r="O17" s="52" t="inlineStr"/>
-      <c r="P17" s="52" t="inlineStr"/>
-      <c r="Q17" s="52" t="inlineStr"/>
-      <c r="R17" s="52" t="inlineStr">
+      <c r="O17" s="60" t="inlineStr"/>
+      <c r="P17" s="60" t="inlineStr"/>
+      <c r="Q17" s="60" t="inlineStr"/>
+      <c r="R17" s="60" t="inlineStr">
         <is>
           <t>￥62,000 (￥68,200)</t>
         </is>
       </c>
-      <c r="S17" s="52" t="inlineStr">
+      <c r="S17" s="60" t="inlineStr">
         <is>
           <t>4571527865237</t>
         </is>
       </c>
-      <c r="T17" s="52" t="inlineStr"/>
-      <c r="U17" s="52" t="inlineStr"/>
-      <c r="V17" s="52" t="inlineStr"/>
-      <c r="W17" s="52" t="inlineStr"/>
-      <c r="X17" s="52" t="inlineStr"/>
-      <c r="Y17" s="52" t="inlineStr"/>
-      <c r="Z17" s="52" t="inlineStr">
+      <c r="T17" s="60" t="inlineStr"/>
+      <c r="U17" s="60" t="inlineStr"/>
+      <c r="V17" s="60" t="inlineStr"/>
+      <c r="W17" s="60" t="inlineStr"/>
+      <c r="X17" s="60" t="inlineStr"/>
+      <c r="Y17" s="60" t="inlineStr"/>
+      <c r="Z17" s="60" t="inlineStr">
         <is>
           <t>1/48～1/8</t>
         </is>
       </c>
-      <c r="AA17" s="52" t="inlineStr"/>
-      <c r="AB17" s="52" t="inlineStr"/>
-      <c r="AC17" s="52" t="inlineStr">
+      <c r="AA17" s="60" t="inlineStr"/>
+      <c r="AB17" s="60" t="inlineStr"/>
+      <c r="AC17" s="60" t="inlineStr">
         <is>
           <t>Finesse Shake KIWAMI</t>
         </is>
       </c>
-      <c r="AD17" s="52" t="inlineStr"/>
-      <c r="AE17" s="52" t="inlineStr"/>
-      <c r="AF17" s="52" t="inlineStr"/>
-      <c r="AG17" s="52" t="inlineStr">
+      <c r="AD17" s="60" t="inlineStr"/>
+      <c r="AE17" s="60" t="inlineStr"/>
+      <c r="AF17" s="60" t="inlineStr"/>
+      <c r="AG17" s="60" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH17" s="52" t="inlineStr">
+      <c r="AH17" s="60" t="inlineStr">
         <is>
           <t>Finesse Shake KIWAMI 是 XUL solid 的极限食わせ竿，适合短咬明显的 No Sinker、Down Shot、Neko、Jighead 和 Hover Strolling，重点是轻量操控和瞬间挂鱼。</t>
         </is>
       </c>
-      <c r="AI17" s="52" t="inlineStr">
+      <c r="AI17" s="60" t="inlineStr">
         <is>
           <t>No Sinker / Down Shot / Neko Rig / Jighead Rig / Hover Strolling</t>
         </is>
       </c>
-      <c r="AJ17" s="52" t="inlineStr"/>
-      <c r="AK17" s="52" t="inlineStr"/>
-      <c r="AL17" s="52" t="inlineStr"/>
-      <c r="AM17" s="52" t="inlineStr">
+      <c r="AJ17" s="60" t="inlineStr"/>
+      <c r="AK17" s="60" t="inlineStr"/>
+      <c r="AL17" s="60" t="inlineStr"/>
+      <c r="AM17" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 极高压近距・ sight fishing / XUL finesse</t>
         </is>
       </c>
-      <c r="AN17" s="52" t="inlineStr">
+      <c r="AN17" s="60" t="inlineStr">
         <is>
           <t>短距极轻食わせ专向</t>
         </is>
       </c>
-      <c r="AO17" s="52" t="inlineStr">
+      <c r="AO17" s="60" t="inlineStr">
         <is>
           <t>XUL solid 更适合轻 No Sinker、Down Shot、Neko 与 Hover Strolling，优势是轻饵存在感和短咬判断。</t>
         </is>
       </c>
-      <c r="AP17" s="52" t="inlineStr">
+      <c r="AP17" s="60" t="inlineStr">
         <is>
           <t>Finesse SHAKE KIWAMI EXTREME SPEC/2025 【EXTREME SPEC/2025 Limited】 Finesse Shake KIWAMI 過激なまでに追求したエクストリームスペックモデル。ショートバイトを逃さない、瞬間的に掛けられる研ぎ澄まされたフィネスロッド。ロッドを軽量化する事で得られる感度とXULソリッドを採用する事で水中の違和感さえも把握。極上なまでの操作感で軽量ルアーを意のままに飛ばし、操り、掛ける。極細PEラインに対応。ノーシンカー、ダウンショット、ネコリグ、ジグヘッド、ホバストまで幅広く対応。理屈抜きに青木大介の流儀が全て結集した、まさに『The真打』的なプレミアムロッド。違いが分かる人にお届けしたい。</t>
         </is>
       </c>
-      <c r="AQ17" s="52" t="inlineStr">
+      <c r="AQ17" s="60" t="inlineStr">
+        <is>
+          <t>XULソリッドティップ / TORZITEガイド / グルーブドセンターグリップ / フォアグリップデザイン / コンパクトEVAリアグリップ</t>
+        </is>
+      </c>
+      <c r="AR17" s="60" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="AR17" s="52" t="inlineStr">
+      <c r="AS17" s="60" t="inlineStr">
         <is>
           <t>2025 NEW Model</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>DSRD10016</t>
         </is>
       </c>
-      <c r="B18" s="53" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>DSR1002</t>
         </is>
       </c>
-      <c r="C18" s="53" t="inlineStr">
+      <c r="C18" s="61" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D18" s="53" t="inlineStr">
+      <c r="D18" s="61" t="inlineStr">
         <is>
           <t>DBTS-SS-63ML</t>
         </is>
       </c>
-      <c r="E18" s="53" t="inlineStr">
+      <c r="E18" s="61" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F18" s="53" t="inlineStr">
+      <c r="F18" s="61" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G18" s="53" t="inlineStr">
+      <c r="G18" s="61" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H18" s="53" t="inlineStr"/>
-      <c r="I18" s="53" t="inlineStr"/>
-      <c r="J18" s="53" t="inlineStr">
+      <c r="H18" s="61" t="inlineStr"/>
+      <c r="I18" s="61" t="inlineStr"/>
+      <c r="J18" s="61" t="inlineStr">
         <is>
           <t>93g</t>
         </is>
       </c>
-      <c r="K18" s="53" t="inlineStr"/>
-      <c r="L18" s="53" t="inlineStr"/>
-      <c r="M18" s="53" t="inlineStr">
+      <c r="K18" s="61" t="inlineStr"/>
+      <c r="L18" s="61" t="inlineStr"/>
+      <c r="M18" s="61" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N18" s="53" t="inlineStr">
+      <c r="N18" s="61" t="inlineStr">
         <is>
           <t>0.6~1.2</t>
         </is>
       </c>
-      <c r="O18" s="53" t="inlineStr"/>
-      <c r="P18" s="53" t="inlineStr"/>
-      <c r="Q18" s="53" t="inlineStr"/>
-      <c r="R18" s="53" t="inlineStr">
+      <c r="O18" s="61" t="inlineStr"/>
+      <c r="P18" s="61" t="inlineStr"/>
+      <c r="Q18" s="61" t="inlineStr"/>
+      <c r="R18" s="61" t="inlineStr">
         <is>
           <t>¥28,000 （税込み¥30,800）</t>
         </is>
       </c>
-      <c r="S18" s="53" t="inlineStr">
+      <c r="S18" s="61" t="inlineStr">
         <is>
           <t>4571527863554</t>
         </is>
       </c>
-      <c r="T18" s="53" t="inlineStr"/>
-      <c r="U18" s="53" t="inlineStr"/>
-      <c r="V18" s="53" t="inlineStr"/>
-      <c r="W18" s="53" t="inlineStr"/>
-      <c r="X18" s="53" t="inlineStr"/>
-      <c r="Y18" s="53" t="inlineStr"/>
-      <c r="Z18" s="53" t="inlineStr">
+      <c r="T18" s="61" t="inlineStr"/>
+      <c r="U18" s="61" t="inlineStr"/>
+      <c r="V18" s="61" t="inlineStr"/>
+      <c r="W18" s="61" t="inlineStr"/>
+      <c r="X18" s="61" t="inlineStr"/>
+      <c r="Y18" s="61" t="inlineStr"/>
+      <c r="Z18" s="61" t="inlineStr">
         <is>
           <t>1/16~1/4</t>
         </is>
       </c>
-      <c r="AA18" s="53" t="inlineStr"/>
-      <c r="AB18" s="53" t="inlineStr"/>
-      <c r="AC18" s="53" t="inlineStr">
+      <c r="AA18" s="61" t="inlineStr"/>
+      <c r="AB18" s="61" t="inlineStr"/>
+      <c r="AC18" s="61" t="inlineStr">
         <is>
           <t>Lightning</t>
         </is>
       </c>
-      <c r="AD18" s="53" t="inlineStr"/>
-      <c r="AE18" s="53" t="inlineStr"/>
-      <c r="AF18" s="53" t="inlineStr"/>
-      <c r="AG18" s="53" t="inlineStr"/>
-      <c r="AH18" s="53" t="inlineStr">
+      <c r="AD18" s="61" t="inlineStr"/>
+      <c r="AE18" s="61" t="inlineStr"/>
+      <c r="AF18" s="61" t="inlineStr"/>
+      <c r="AG18" s="61" t="inlineStr"/>
+      <c r="AH18" s="61" t="inlineStr">
         <is>
           <t>Lightning 为 big lake finesse pattern 设计，Neko 是核心，Down Shot、Small Rubber Jig 和 No Sinker 承接 light-rig 全般；ML power 用来补足远处中鱼后的牵制。</t>
         </is>
       </c>
-      <c r="AI18" s="53" t="inlineStr">
+      <c r="AI18" s="61" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / Small Rubber Jig / No Sinker / Power Finesse</t>
         </is>
       </c>
-      <c r="AJ18" s="53" t="inlineStr"/>
-      <c r="AK18" s="53" t="inlineStr"/>
-      <c r="AL18" s="53" t="inlineStr"/>
-      <c r="AM18" s="53" t="inlineStr">
+      <c r="AJ18" s="61" t="inlineStr"/>
+      <c r="AK18" s="61" t="inlineStr"/>
+      <c r="AL18" s="61" t="inlineStr"/>
+      <c r="AM18" s="61" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖库・风浪边 / Neko 与 power finesse</t>
         </is>
       </c>
-      <c r="AN18" s="53" t="inlineStr">
+      <c r="AN18" s="61" t="inlineStr">
         <is>
           <t>湖库 Neko power finesse</t>
         </is>
       </c>
-      <c r="AO18" s="53" t="inlineStr">
+      <c r="AO18" s="61" t="inlineStr">
         <is>
           <t>Neko Rig 放在核心，Down Shot、Small Rubber Jig 和 No Sinker 可跟进；ML power 让远处中鱼后更容易保持主动。</t>
         </is>
       </c>
-      <c r="AP18" s="53" t="inlineStr">
+      <c r="AP18" s="61" t="inlineStr">
         <is>
           <t>Lightning BLUE TREKから生まれた個性派SABER SERIES(サーベルシリーズ）。 ビッグレイクのフィネスパターン攻略に主眼を置き、ネコリグを中心としたライトリグ全般をこなせるパワー系フィネスロッド。6.3ftのレングスは操作性とパワーを両立。シェイクをしやすいテーパー設定を採用。グリップデザインはサーベルシリーズ専用設計。 異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビッグフィッシュでも逃さない粘りを実現。Lightning『タフコンディションを切り裂く剣』</t>
         </is>
       </c>
-      <c r="AQ18" s="53" t="inlineStr"/>
-      <c r="AR18" s="53" t="inlineStr"/>
+      <c r="AQ18" s="61" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / SABER SERIES EVAグリップ / セパレートグリップ / 圧縮コルクグリップ</t>
+        </is>
+      </c>
+      <c r="AR18" s="61" t="inlineStr"/>
+      <c r="AS18" s="61" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>DSRD10017</t>
         </is>
       </c>
-      <c r="B19" s="53" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>DSR1002</t>
         </is>
       </c>
-      <c r="C19" s="53" t="inlineStr">
+      <c r="C19" s="61" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D19" s="53" t="inlineStr">
+      <c r="D19" s="61" t="inlineStr">
         <is>
           <t>DBTS-SS-68L</t>
         </is>
       </c>
-      <c r="E19" s="53" t="inlineStr">
+      <c r="E19" s="61" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F19" s="53" t="inlineStr">
+      <c r="F19" s="61" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G19" s="53" t="inlineStr">
+      <c r="G19" s="61" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H19" s="53" t="inlineStr"/>
-      <c r="I19" s="53" t="inlineStr"/>
-      <c r="J19" s="53" t="inlineStr">
+      <c r="H19" s="61" t="inlineStr"/>
+      <c r="I19" s="61" t="inlineStr"/>
+      <c r="J19" s="61" t="inlineStr">
         <is>
           <t>93g</t>
         </is>
       </c>
-      <c r="K19" s="53" t="inlineStr"/>
-      <c r="L19" s="53" t="inlineStr"/>
-      <c r="M19" s="53" t="inlineStr">
+      <c r="K19" s="61" t="inlineStr"/>
+      <c r="L19" s="61" t="inlineStr"/>
+      <c r="M19" s="61" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N19" s="53" t="inlineStr">
+      <c r="N19" s="61" t="inlineStr">
         <is>
           <t>0.4~0.8</t>
         </is>
       </c>
-      <c r="O19" s="53" t="inlineStr"/>
-      <c r="P19" s="53" t="inlineStr"/>
-      <c r="Q19" s="53" t="inlineStr"/>
-      <c r="R19" s="53" t="inlineStr">
+      <c r="O19" s="61" t="inlineStr"/>
+      <c r="P19" s="61" t="inlineStr"/>
+      <c r="Q19" s="61" t="inlineStr"/>
+      <c r="R19" s="61" t="inlineStr">
         <is>
           <t>¥28,500 （税込み¥31,350）</t>
         </is>
       </c>
-      <c r="S19" s="53" t="inlineStr">
+      <c r="S19" s="61" t="inlineStr">
         <is>
           <t>4571527862762</t>
         </is>
       </c>
-      <c r="T19" s="53" t="inlineStr"/>
-      <c r="U19" s="53" t="inlineStr"/>
-      <c r="V19" s="53" t="inlineStr"/>
-      <c r="W19" s="53" t="inlineStr"/>
-      <c r="X19" s="53" t="inlineStr"/>
-      <c r="Y19" s="53" t="inlineStr"/>
-      <c r="Z19" s="53" t="inlineStr">
+      <c r="T19" s="61" t="inlineStr"/>
+      <c r="U19" s="61" t="inlineStr"/>
+      <c r="V19" s="61" t="inlineStr"/>
+      <c r="W19" s="61" t="inlineStr"/>
+      <c r="X19" s="61" t="inlineStr"/>
+      <c r="Y19" s="61" t="inlineStr"/>
+      <c r="Z19" s="61" t="inlineStr">
         <is>
           <t>1/32~1/4</t>
         </is>
       </c>
-      <c r="AA19" s="53" t="inlineStr"/>
-      <c r="AB19" s="53" t="inlineStr"/>
-      <c r="AC19" s="53" t="inlineStr">
+      <c r="AA19" s="61" t="inlineStr"/>
+      <c r="AB19" s="61" t="inlineStr"/>
+      <c r="AC19" s="61" t="inlineStr">
         <is>
           <t>BM1</t>
         </is>
       </c>
-      <c r="AD19" s="53" t="inlineStr"/>
-      <c r="AE19" s="53" t="inlineStr"/>
-      <c r="AF19" s="53" t="inlineStr"/>
-      <c r="AG19" s="53" t="inlineStr"/>
-      <c r="AH19" s="53" t="inlineStr">
+      <c r="AD19" s="61" t="inlineStr"/>
+      <c r="AE19" s="61" t="inlineStr"/>
+      <c r="AF19" s="61" t="inlineStr"/>
+      <c r="AG19" s="61" t="inlineStr"/>
+      <c r="AH19" s="61" t="inlineStr">
         <is>
           <t>BM1 的主轴是 long-cast mid-strolling，6'8 长度和较粗 fluorocarbon/PE 导环设定服务于远投控线；Down Shot、No Sinker 只是 light-rig 侧向扩展。</t>
         </is>
       </c>
-      <c r="AI19" s="53" t="inlineStr">
+      <c r="AI19" s="61" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Long Cast Down Shot / No Sinker / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ19" s="53" t="inlineStr"/>
-      <c r="AK19" s="53" t="inlineStr"/>
-      <c r="AL19" s="53" t="inlineStr"/>
-      <c r="AM19" s="53" t="inlineStr">
+      <c r="AJ19" s="61" t="inlineStr"/>
+      <c r="AK19" s="61" t="inlineStr"/>
+      <c r="AL19" s="61" t="inlineStr"/>
+      <c r="AM19" s="61" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖库・远投开阔水 / long-cast mid strolling</t>
         </is>
       </c>
-      <c r="AN19" s="53" t="inlineStr">
+      <c r="AN19" s="61" t="inlineStr">
         <is>
           <t>远投中层游动 spinning</t>
         </is>
       </c>
-      <c r="AO19" s="53" t="inlineStr">
+      <c r="AO19" s="61" t="inlineStr">
         <is>
           <t>6'8 长度适合把 Jighead Mid Strolling 和 Long Cast Down Shot 送远，PE 或较粗 fluorocarbon 下仍能维持线弧。</t>
         </is>
       </c>
-      <c r="AP19" s="53" t="inlineStr">
+      <c r="AP19" s="61" t="inlineStr">
         <is>
           <t>BM1 BLUE TREKから生まれた個性派SABER SERIES(サーベルシリーズ） ミッドストローリングのロングキャストシューティングを主眼に置き、ライトリグ全般をこなせるロッド。6.8ftのレングスはキャスト性能と操作性を両立。ガイドセッティングは太めのフロロカーボンラインやPEを想定したセッティング。グリップデザインはサーベルシリーズ専用設計。 異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビックフィッシュでも逃さない粘りを実現。BM1『琵琶湖を制するミドストロッド』 https://youtu.be/KUaGHkQiQJY</t>
         </is>
       </c>
-      <c r="AQ19" s="53" t="inlineStr"/>
-      <c r="AR19" s="53" t="inlineStr"/>
+      <c r="AQ19" s="61" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / 太めフロロ/PE対応ガイドセッティング / SABER SERIES EVAグリップ / セパレートグリップ / 圧縮コルクグリップ</t>
+        </is>
+      </c>
+      <c r="AR19" s="61" t="inlineStr"/>
+      <c r="AS19" s="61" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>DSRD10018</t>
         </is>
       </c>
-      <c r="B20" s="53" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>DSR1002</t>
         </is>
       </c>
-      <c r="C20" s="53" t="inlineStr">
+      <c r="C20" s="61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D20" s="53" t="inlineStr">
+      <c r="D20" s="61" t="inlineStr">
         <is>
           <t>DBTC-SS-64MH</t>
         </is>
       </c>
-      <c r="E20" s="53" t="inlineStr">
+      <c r="E20" s="61" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F20" s="53" t="inlineStr">
+      <c r="F20" s="61" t="inlineStr">
         <is>
           <t>6’4″</t>
         </is>
       </c>
-      <c r="G20" s="53" t="inlineStr">
+      <c r="G20" s="61" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H20" s="53" t="inlineStr"/>
-      <c r="I20" s="53" t="inlineStr"/>
-      <c r="J20" s="53" t="inlineStr">
+      <c r="H20" s="61" t="inlineStr"/>
+      <c r="I20" s="61" t="inlineStr"/>
+      <c r="J20" s="61" t="inlineStr">
         <is>
           <t>108g</t>
         </is>
       </c>
-      <c r="K20" s="53" t="inlineStr"/>
-      <c r="L20" s="53" t="inlineStr"/>
-      <c r="M20" s="53" t="inlineStr">
+      <c r="K20" s="61" t="inlineStr"/>
+      <c r="L20" s="61" t="inlineStr"/>
+      <c r="M20" s="61" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N20" s="53" t="inlineStr"/>
-      <c r="O20" s="53" t="inlineStr"/>
-      <c r="P20" s="53" t="inlineStr"/>
-      <c r="Q20" s="53" t="inlineStr"/>
-      <c r="R20" s="53" t="inlineStr">
+      <c r="N20" s="61" t="inlineStr"/>
+      <c r="O20" s="61" t="inlineStr"/>
+      <c r="P20" s="61" t="inlineStr"/>
+      <c r="Q20" s="61" t="inlineStr"/>
+      <c r="R20" s="61" t="inlineStr">
         <is>
           <t>¥29,500 （税込み¥32,450）</t>
         </is>
       </c>
-      <c r="S20" s="53" t="inlineStr">
+      <c r="S20" s="61" t="inlineStr">
         <is>
           <t>4571527862779</t>
         </is>
       </c>
-      <c r="T20" s="53" t="inlineStr"/>
-      <c r="U20" s="53" t="inlineStr"/>
-      <c r="V20" s="53" t="inlineStr"/>
-      <c r="W20" s="53" t="inlineStr"/>
-      <c r="X20" s="53" t="inlineStr"/>
-      <c r="Y20" s="53" t="inlineStr"/>
-      <c r="Z20" s="53" t="inlineStr">
+      <c r="T20" s="61" t="inlineStr"/>
+      <c r="U20" s="61" t="inlineStr"/>
+      <c r="V20" s="61" t="inlineStr"/>
+      <c r="W20" s="61" t="inlineStr"/>
+      <c r="X20" s="61" t="inlineStr"/>
+      <c r="Y20" s="61" t="inlineStr"/>
+      <c r="Z20" s="61" t="inlineStr">
         <is>
           <t>3/16~3/4</t>
         </is>
       </c>
-      <c r="AA20" s="53" t="inlineStr"/>
-      <c r="AB20" s="53" t="inlineStr"/>
-      <c r="AC20" s="53" t="inlineStr">
+      <c r="AA20" s="61" t="inlineStr"/>
+      <c r="AB20" s="61" t="inlineStr"/>
+      <c r="AC20" s="61" t="inlineStr">
         <is>
           <t>Dagger</t>
         </is>
       </c>
-      <c r="AD20" s="53" t="inlineStr"/>
-      <c r="AE20" s="53" t="inlineStr"/>
-      <c r="AF20" s="53" t="inlineStr"/>
-      <c r="AG20" s="53" t="inlineStr"/>
-      <c r="AH20" s="53" t="inlineStr">
+      <c r="AD20" s="61" t="inlineStr"/>
+      <c r="AE20" s="61" t="inlineStr"/>
+      <c r="AF20" s="61" t="inlineStr"/>
+      <c r="AG20" s="61" t="inlineStr"/>
+      <c r="AH20" s="61" t="inlineStr">
         <is>
           <t>Dagger 明确为高比重 worm no-sinker jerking 设计，6'4 长度便于连续 jerk 和控姿；Texas、Free Rig 只是同等重量软饵的补充用法。</t>
         </is>
       </c>
-      <c r="AI20" s="53" t="inlineStr">
+      <c r="AI20" s="61" t="inlineStr">
         <is>
           <t>High-density No Sinker / Jerk Worm / Texas Rig / Free Rig</t>
         </is>
       </c>
-      <c r="AJ20" s="53" t="inlineStr"/>
-      <c r="AK20" s="53" t="inlineStr"/>
-      <c r="AL20" s="53" t="inlineStr"/>
-      <c r="AM20" s="53" t="inlineStr">
+      <c r="AJ20" s="61" t="inlineStr"/>
+      <c r="AK20" s="61" t="inlineStr"/>
+      <c r="AL20" s="61" t="inlineStr"/>
+      <c r="AM20" s="61" t="inlineStr">
         <is>
           <t>淡水 Bass / 浅草边・开口区 / 高比重 worm jerk</t>
         </is>
       </c>
-      <c r="AN20" s="53" t="inlineStr">
+      <c r="AN20" s="61" t="inlineStr">
         <is>
           <t>高比重无铅 jerking 专向</t>
         </is>
       </c>
-      <c r="AO20" s="53" t="inlineStr">
+      <c r="AO20" s="61" t="inlineStr">
         <is>
           <t>短尺 MH 让 High-density No Sinker 和 Jerk Worm 更好做连续抽停，Texas、Free Rig 可作为同重量软饵替代。</t>
         </is>
       </c>
-      <c r="AP20" s="53" t="inlineStr">
+      <c r="AP20" s="61" t="inlineStr">
         <is>
           <t>Dagger BLUE TREKから生まれた個性派SABER SERIES(サーベルシリーズ） 近年流行のノーシンカー高比重ワームのジャーキングメソッドを主眼に置いたモデル。ジャーク時のアクションを考えレングスを6.4ftにする事でジャークのし易さ向上と共に操作性もUP。ブランクはしなやかに曲がりつつもバットはしっかりとビッグバスに耐えれるタフ仕様。グリップデザインはサーベルシリーズ専用設計。異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビックフィッシュでも逃さない粘りを実現。Dagger『バスを脅かす短剣』 https://youtu.be/MVP9z1qGTFE</t>
         </is>
       </c>
-      <c r="AQ20" s="53" t="inlineStr"/>
-      <c r="AR20" s="53" t="inlineStr"/>
+      <c r="AQ20" s="61" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / SABER SERIES EVAグリップ / セパレートグリップ / 圧縮コルクグリップ</t>
+        </is>
+      </c>
+      <c r="AR20" s="61" t="inlineStr"/>
+      <c r="AS20" s="61" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="61" t="inlineStr">
         <is>
           <t>DSRD10019</t>
         </is>
       </c>
-      <c r="B21" s="53" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>DSR1002</t>
         </is>
       </c>
-      <c r="C21" s="53" t="inlineStr">
+      <c r="C21" s="61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D21" s="53" t="inlineStr">
+      <c r="D21" s="61" t="inlineStr">
         <is>
           <t>DBTC-SS-69MH+</t>
         </is>
       </c>
-      <c r="E21" s="53" t="inlineStr">
+      <c r="E21" s="61" t="inlineStr">
         <is>
           <t>MH+</t>
         </is>
       </c>
-      <c r="F21" s="53" t="inlineStr">
+      <c r="F21" s="61" t="inlineStr">
         <is>
           <t>6’9″</t>
         </is>
       </c>
-      <c r="G21" s="53" t="inlineStr">
+      <c r="G21" s="61" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H21" s="53" t="inlineStr"/>
-      <c r="I21" s="53" t="inlineStr"/>
-      <c r="J21" s="53" t="inlineStr">
+      <c r="H21" s="61" t="inlineStr"/>
+      <c r="I21" s="61" t="inlineStr"/>
+      <c r="J21" s="61" t="inlineStr">
         <is>
           <t>131g</t>
         </is>
       </c>
-      <c r="K21" s="53" t="inlineStr"/>
-      <c r="L21" s="53" t="inlineStr"/>
-      <c r="M21" s="53" t="inlineStr">
+      <c r="K21" s="61" t="inlineStr"/>
+      <c r="L21" s="61" t="inlineStr"/>
+      <c r="M21" s="61" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N21" s="53" t="inlineStr"/>
-      <c r="O21" s="53" t="inlineStr"/>
-      <c r="P21" s="53" t="inlineStr"/>
-      <c r="Q21" s="53" t="inlineStr"/>
-      <c r="R21" s="53" t="inlineStr">
+      <c r="N21" s="61" t="inlineStr"/>
+      <c r="O21" s="61" t="inlineStr"/>
+      <c r="P21" s="61" t="inlineStr"/>
+      <c r="Q21" s="61" t="inlineStr"/>
+      <c r="R21" s="61" t="inlineStr">
         <is>
           <t>¥29,500 （税込み¥32,450）</t>
         </is>
       </c>
-      <c r="S21" s="53" t="inlineStr">
+      <c r="S21" s="61" t="inlineStr">
         <is>
           <t>4571527863561</t>
         </is>
       </c>
-      <c r="T21" s="53" t="inlineStr"/>
-      <c r="U21" s="53" t="inlineStr"/>
-      <c r="V21" s="53" t="inlineStr"/>
-      <c r="W21" s="53" t="inlineStr"/>
-      <c r="X21" s="53" t="inlineStr"/>
-      <c r="Y21" s="53" t="inlineStr"/>
-      <c r="Z21" s="53" t="inlineStr">
+      <c r="T21" s="61" t="inlineStr"/>
+      <c r="U21" s="61" t="inlineStr"/>
+      <c r="V21" s="61" t="inlineStr"/>
+      <c r="W21" s="61" t="inlineStr"/>
+      <c r="X21" s="61" t="inlineStr"/>
+      <c r="Y21" s="61" t="inlineStr"/>
+      <c r="Z21" s="61" t="inlineStr">
         <is>
           <t>3/16~3/4</t>
         </is>
       </c>
-      <c r="AA21" s="53" t="inlineStr"/>
-      <c r="AB21" s="53" t="inlineStr"/>
-      <c r="AC21" s="53" t="inlineStr">
+      <c r="AA21" s="61" t="inlineStr"/>
+      <c r="AB21" s="61" t="inlineStr"/>
+      <c r="AC21" s="61" t="inlineStr">
         <is>
           <t>Saber versatile SP</t>
         </is>
       </c>
-      <c r="AD21" s="53" t="inlineStr"/>
-      <c r="AE21" s="53" t="inlineStr"/>
-      <c r="AF21" s="53" t="inlineStr"/>
-      <c r="AG21" s="53" t="inlineStr"/>
-      <c r="AH21" s="53" t="inlineStr">
+      <c r="AD21" s="61" t="inlineStr"/>
+      <c r="AE21" s="61" t="inlineStr"/>
+      <c r="AF21" s="61" t="inlineStr"/>
+      <c r="AG21" s="61" t="inlineStr"/>
+      <c r="AH21" s="61" t="inlineStr">
         <is>
           <t>Saber versatile SP 是琵琶湖向 power versatile，先覆盖 worm 系 rig，再扩展到 wire bait、Chatterbait、Swimbait 和 Big Bait；不是单纯 heavy bottom 竿。</t>
         </is>
       </c>
-      <c r="AI21" s="53" t="inlineStr">
+      <c r="AI21" s="61" t="inlineStr">
         <is>
           <t>Texas Rig / Free Rig / No Sinker / Spinnerbait / Chatterbait / Swimbait / Big Bait</t>
         </is>
       </c>
-      <c r="AJ21" s="53" t="inlineStr"/>
-      <c r="AK21" s="53" t="inlineStr"/>
-      <c r="AL21" s="53" t="inlineStr"/>
-      <c r="AM21" s="53" t="inlineStr">
+      <c r="AJ21" s="61" t="inlineStr"/>
+      <c r="AK21" s="61" t="inlineStr"/>
+      <c r="AL21" s="61" t="inlineStr"/>
+      <c r="AM21" s="61" t="inlineStr">
         <is>
           <t>淡水 Bass / 琵琶湖型大型湖・草区边缘 / power versatile</t>
         </is>
       </c>
-      <c r="AN21" s="53" t="inlineStr">
+      <c r="AN21" s="61" t="inlineStr">
         <is>
           <t>强力软硬饵泛用</t>
         </is>
       </c>
-      <c r="AO21" s="53" t="inlineStr">
+      <c r="AO21" s="61" t="inlineStr">
         <is>
           <t>Texas、Free Rig 和 No Sinker 可打点，Spinnerbait、Chatterbait、Swimbait 和 Big Bait 可搜索，适合大水面重线组切换。</t>
         </is>
       </c>
-      <c r="AP21" s="53" t="inlineStr">
+      <c r="AP21" s="61" t="inlineStr">
         <is>
           <t>Saber versatile SP BLUE TREKから生まれた個性派SABER SERIES(サーベルシリーズ）。 あらゆるワーム系リグを全般にワイヤーベイト、ビッグベイトやスイムベイトまで幅広く対応するパワー系バーサタイルモデル。ブランクスはトルク重視のＭＨアクションを更にパワーをプラス。 グリップデザインはサーベルシリーズ専用設計。異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビッグフィッシュでも逃さない粘りを実現。Saber versatile SP『琵琶湖に求められたバーサタイルロッド』</t>
         </is>
       </c>
-      <c r="AQ21" s="53" t="inlineStr"/>
-      <c r="AR21" s="53" t="inlineStr"/>
+      <c r="AQ21" s="61" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / SABER SERIES EVAグリップ / セパレートグリップ / 圧縮コルクグリップ</t>
+        </is>
+      </c>
+      <c r="AR21" s="61" t="inlineStr"/>
+      <c r="AS21" s="61" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="52" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>DSRD10020</t>
         </is>
       </c>
-      <c r="B22" s="52" t="inlineStr">
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C22" s="52" t="inlineStr">
+      <c r="C22" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D22" s="52" t="inlineStr">
+      <c r="D22" s="60" t="inlineStr">
         <is>
           <t>DBTS-612UL+-S</t>
         </is>
       </c>
-      <c r="E22" s="52" t="inlineStr">
+      <c r="E22" s="60" t="inlineStr">
         <is>
           <t>UL+</t>
         </is>
       </c>
-      <c r="F22" s="52" t="inlineStr">
+      <c r="F22" s="60" t="inlineStr">
         <is>
           <t>6’1″</t>
         </is>
       </c>
-      <c r="G22" s="52" t="inlineStr">
+      <c r="G22" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H22" s="52" t="inlineStr"/>
-      <c r="I22" s="52" t="inlineStr"/>
-      <c r="J22" s="52" t="inlineStr">
+      <c r="H22" s="60" t="inlineStr"/>
+      <c r="I22" s="60" t="inlineStr"/>
+      <c r="J22" s="60" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K22" s="52" t="inlineStr"/>
-      <c r="L22" s="52" t="inlineStr"/>
-      <c r="M22" s="52" t="inlineStr">
+      <c r="K22" s="60" t="inlineStr"/>
+      <c r="L22" s="60" t="inlineStr"/>
+      <c r="M22" s="60" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N22" s="52" t="inlineStr"/>
-      <c r="O22" s="52" t="inlineStr"/>
-      <c r="P22" s="52" t="inlineStr"/>
-      <c r="Q22" s="52" t="inlineStr"/>
-      <c r="R22" s="52" t="inlineStr">
+      <c r="N22" s="60" t="inlineStr"/>
+      <c r="O22" s="60" t="inlineStr"/>
+      <c r="P22" s="60" t="inlineStr"/>
+      <c r="Q22" s="60" t="inlineStr"/>
+      <c r="R22" s="60" t="inlineStr">
         <is>
           <t>¥28,000 （税込み¥30,800）</t>
         </is>
       </c>
-      <c r="S22" s="52" t="inlineStr">
+      <c r="S22" s="60" t="inlineStr">
         <is>
           <t>4571527862540</t>
         </is>
       </c>
-      <c r="T22" s="52" t="inlineStr"/>
-      <c r="U22" s="52" t="inlineStr"/>
-      <c r="V22" s="52" t="inlineStr"/>
-      <c r="W22" s="52" t="inlineStr"/>
-      <c r="X22" s="52" t="inlineStr"/>
-      <c r="Y22" s="52" t="inlineStr"/>
-      <c r="Z22" s="52" t="inlineStr">
+      <c r="T22" s="60" t="inlineStr"/>
+      <c r="U22" s="60" t="inlineStr"/>
+      <c r="V22" s="60" t="inlineStr"/>
+      <c r="W22" s="60" t="inlineStr"/>
+      <c r="X22" s="60" t="inlineStr"/>
+      <c r="Y22" s="60" t="inlineStr"/>
+      <c r="Z22" s="60" t="inlineStr">
         <is>
           <t>1/32~3/16</t>
         </is>
       </c>
-      <c r="AA22" s="52" t="inlineStr"/>
-      <c r="AB22" s="52" t="inlineStr"/>
-      <c r="AC22" s="52" t="inlineStr"/>
-      <c r="AD22" s="52" t="inlineStr"/>
-      <c r="AE22" s="52" t="inlineStr"/>
-      <c r="AF22" s="52" t="inlineStr"/>
-      <c r="AG22" s="52" t="inlineStr"/>
-      <c r="AH22" s="52" t="inlineStr">
+      <c r="AA22" s="60" t="inlineStr"/>
+      <c r="AB22" s="60" t="inlineStr"/>
+      <c r="AC22" s="60" t="inlineStr"/>
+      <c r="AD22" s="60" t="inlineStr"/>
+      <c r="AE22" s="60" t="inlineStr"/>
+      <c r="AF22" s="60" t="inlineStr"/>
+      <c r="AG22" s="60" t="inlineStr"/>
+      <c r="AH22" s="60" t="inlineStr">
         <is>
           <t>2-piece 612UL+-S 是更轻量的 super finesse，solid tip 让 No Sinker、Down Shot、Neko、Jighead、Small Rubber Jig 与 Hover Strolling 的轻咬更容易吃住。</t>
         </is>
       </c>
-      <c r="AI22" s="52" t="inlineStr">
+      <c r="AI22" s="60" t="inlineStr">
         <is>
           <t>No Sinker / Down Shot / Neko Rig / Jighead Rig / Small Rubber Jig / Hover Strolling</t>
         </is>
       </c>
-      <c r="AJ22" s="52" t="inlineStr"/>
-      <c r="AK22" s="52" t="inlineStr"/>
-      <c r="AL22" s="52" t="inlineStr"/>
-      <c r="AM22" s="52" t="inlineStr">
+      <c r="AJ22" s="60" t="inlineStr"/>
+      <c r="AK22" s="60" t="inlineStr"/>
+      <c r="AL22" s="60" t="inlineStr"/>
+      <c r="AM22" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压岸边・小型湖库 / 2pc super finesse</t>
         </is>
       </c>
-      <c r="AN22" s="52" t="inlineStr">
+      <c r="AN22" s="60" t="inlineStr">
         <is>
           <t>便携超精细 spinning</t>
         </is>
       </c>
-      <c r="AO22" s="52" t="inlineStr">
+      <c r="AO22" s="60" t="inlineStr">
         <is>
           <t>No Sinker、Down Shot、Neko、Jighead 和 Hover Strolling 都能细致操作，2pc 适合移动频繁但仍要保持轻饵手感的玩家。</t>
         </is>
       </c>
-      <c r="AP22" s="52" t="inlineStr">
+      <c r="AP22" s="60" t="inlineStr">
         <is>
           <t>時を捉える事が出来る進化したスーパーフィネスモデル DBTS-61Lをベースに、より軽量ルアーを扱えるようチューンニングしたモデル。 ソリッドティップを搭載する事でより軽量ルアーを繊細に扱えるようになり、ショートバイトでもバスを逃しません。ノーシンカー、ダウンショット、ネコリグ、ジグヘッド、スモラバ、ホバストまで幅広く対応。ナノマテリアル配合のBLUE TREKブランクスによりバットパワーでバスを浮かせ主導権を与えません。日々変化するフィールドの時を捉える事が出来る進化した攻撃的フィネスロッドに仕上げました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ22" s="52" t="inlineStr"/>
-      <c r="AR22" s="52" t="inlineStr"/>
+      <c r="AQ22" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / ソリッドティップ / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR22" s="60" t="inlineStr"/>
+      <c r="AS22" s="60" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="52" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>DSRD10021</t>
         </is>
       </c>
-      <c r="B23" s="52" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C23" s="52" t="inlineStr">
+      <c r="C23" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D23" s="52" t="inlineStr">
+      <c r="D23" s="60" t="inlineStr">
         <is>
           <t>DBTS-632UL/L-S</t>
         </is>
       </c>
-      <c r="E23" s="52" t="inlineStr">
+      <c r="E23" s="60" t="inlineStr">
         <is>
           <t>UL/L</t>
         </is>
       </c>
-      <c r="F23" s="52" t="inlineStr">
+      <c r="F23" s="60" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G23" s="52" t="inlineStr">
+      <c r="G23" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H23" s="52" t="inlineStr"/>
-      <c r="I23" s="52" t="inlineStr"/>
-      <c r="J23" s="52" t="inlineStr">
+      <c r="H23" s="60" t="inlineStr"/>
+      <c r="I23" s="60" t="inlineStr"/>
+      <c r="J23" s="60" t="inlineStr">
         <is>
           <t>81g</t>
         </is>
       </c>
-      <c r="K23" s="52" t="inlineStr"/>
-      <c r="L23" s="52" t="inlineStr"/>
-      <c r="M23" s="52" t="inlineStr">
+      <c r="K23" s="60" t="inlineStr"/>
+      <c r="L23" s="60" t="inlineStr"/>
+      <c r="M23" s="60" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N23" s="52" t="inlineStr">
+      <c r="N23" s="60" t="inlineStr">
         <is>
           <t>0.4~1</t>
         </is>
       </c>
-      <c r="O23" s="52" t="inlineStr"/>
-      <c r="P23" s="52" t="inlineStr"/>
-      <c r="Q23" s="52" t="inlineStr"/>
-      <c r="R23" s="52" t="inlineStr">
+      <c r="O23" s="60" t="inlineStr"/>
+      <c r="P23" s="60" t="inlineStr"/>
+      <c r="Q23" s="60" t="inlineStr"/>
+      <c r="R23" s="60" t="inlineStr">
         <is>
           <t>¥28,000 （税込み¥30,800）</t>
         </is>
       </c>
-      <c r="S23" s="52" t="inlineStr">
+      <c r="S23" s="60" t="inlineStr">
         <is>
           <t>4571527863752</t>
         </is>
       </c>
-      <c r="T23" s="52" t="inlineStr"/>
-      <c r="U23" s="52" t="inlineStr"/>
-      <c r="V23" s="52" t="inlineStr"/>
-      <c r="W23" s="52" t="inlineStr"/>
-      <c r="X23" s="52" t="inlineStr"/>
-      <c r="Y23" s="52" t="inlineStr"/>
-      <c r="Z23" s="52" t="inlineStr">
+      <c r="T23" s="60" t="inlineStr"/>
+      <c r="U23" s="60" t="inlineStr"/>
+      <c r="V23" s="60" t="inlineStr"/>
+      <c r="W23" s="60" t="inlineStr"/>
+      <c r="X23" s="60" t="inlineStr"/>
+      <c r="Y23" s="60" t="inlineStr"/>
+      <c r="Z23" s="60" t="inlineStr">
         <is>
           <t>1/32~1/4</t>
         </is>
       </c>
-      <c r="AA23" s="52" t="inlineStr"/>
-      <c r="AB23" s="52" t="inlineStr"/>
-      <c r="AC23" s="52" t="inlineStr"/>
-      <c r="AD23" s="52" t="inlineStr"/>
-      <c r="AE23" s="52" t="inlineStr"/>
-      <c r="AF23" s="52" t="inlineStr"/>
-      <c r="AG23" s="52" t="inlineStr"/>
-      <c r="AH23" s="52" t="inlineStr">
+      <c r="AA23" s="60" t="inlineStr"/>
+      <c r="AB23" s="60" t="inlineStr"/>
+      <c r="AC23" s="60" t="inlineStr"/>
+      <c r="AD23" s="60" t="inlineStr"/>
+      <c r="AE23" s="60" t="inlineStr"/>
+      <c r="AF23" s="60" t="inlineStr"/>
+      <c r="AG23" s="60" t="inlineStr"/>
+      <c r="AH23" s="60" t="inlineStr">
         <is>
           <t>632UL/L-S 用 UL tip 搭配 L butt，官网明确覆盖 No Sinker、Down Shot、Neko、Jighead、Small Rubber Jig、Hover Strolling 与 Elastomer；适合食わせ和控鱼并重。</t>
         </is>
       </c>
-      <c r="AI23" s="52" t="inlineStr">
+      <c r="AI23" s="60" t="inlineStr">
         <is>
           <t>No Sinker / Down Shot / Neko Rig / Jighead Rig / Small Rubber Jig / Hover Strolling / Elastomer Softbait</t>
         </is>
       </c>
-      <c r="AJ23" s="52" t="inlineStr"/>
-      <c r="AK23" s="52" t="inlineStr"/>
-      <c r="AL23" s="52" t="inlineStr"/>
-      <c r="AM23" s="52" t="inlineStr">
+      <c r="AJ23" s="60" t="inlineStr"/>
+      <c r="AK23" s="60" t="inlineStr"/>
+      <c r="AL23" s="60" t="inlineStr"/>
+      <c r="AM23" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压开放水・轻 cover 边 / all-round finesse</t>
         </is>
       </c>
-      <c r="AN23" s="52" t="inlineStr">
+      <c r="AN23" s="60" t="inlineStr">
         <is>
           <t>食わせ与控鱼兼顾 finesse</t>
         </is>
       </c>
-      <c r="AO23" s="52" t="inlineStr">
+      <c r="AO23" s="60" t="inlineStr">
         <is>
           <t>UL tip 负责轻咬承接，L butt 负责控鱼；No Sinker、Down Shot、Small Rubber Jig、Hover 和 Elastomer 都能覆盖。</t>
         </is>
       </c>
-      <c r="AP23" s="52" t="inlineStr">
+      <c r="AP23" s="60" t="inlineStr">
         <is>
           <t>オールマイティーフィネスモデル ULパワーのソリッドティップでバイトを乗せ、Lパワーのバットで魚を制する。食わせとパワーを両立させたオールマイティーフィネスモデル。 ガイドセッティングは近年のPEラインでの使用も考慮したDSTYLEオリジナルセッティング。 ノーシンカー、ダウンショット、ネコリグ、ジグヘッド、スモラバ、ホバスト、エラストマールアーまで幅広く対応。ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビッグフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ23" s="52" t="inlineStr"/>
-      <c r="AR23" s="52" t="inlineStr"/>
+      <c r="AQ23" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / ULパワーソリッドティップ / PE対応DSTYLEオリジナルガイドセッティング / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR23" s="60" t="inlineStr"/>
+      <c r="AS23" s="60" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="52" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>DSRD10022</t>
         </is>
       </c>
-      <c r="B24" s="52" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C24" s="52" t="inlineStr">
+      <c r="C24" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D24" s="52" t="inlineStr">
+      <c r="D24" s="60" t="inlineStr">
         <is>
           <t>DBTS-642UL+-MIDSP</t>
         </is>
       </c>
-      <c r="E24" s="52" t="inlineStr">
+      <c r="E24" s="60" t="inlineStr">
         <is>
           <t>UL+</t>
         </is>
       </c>
-      <c r="F24" s="52" t="inlineStr">
+      <c r="F24" s="60" t="inlineStr">
         <is>
           <t>6’4″</t>
         </is>
       </c>
-      <c r="G24" s="52" t="inlineStr">
+      <c r="G24" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H24" s="52" t="inlineStr"/>
-      <c r="I24" s="52" t="inlineStr"/>
-      <c r="J24" s="52" t="inlineStr">
+      <c r="H24" s="60" t="inlineStr"/>
+      <c r="I24" s="60" t="inlineStr"/>
+      <c r="J24" s="60" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K24" s="52" t="inlineStr"/>
-      <c r="L24" s="52" t="inlineStr"/>
-      <c r="M24" s="52" t="inlineStr">
+      <c r="K24" s="60" t="inlineStr"/>
+      <c r="L24" s="60" t="inlineStr"/>
+      <c r="M24" s="60" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N24" s="52" t="inlineStr"/>
-      <c r="O24" s="52" t="inlineStr"/>
-      <c r="P24" s="52" t="inlineStr"/>
-      <c r="Q24" s="52" t="inlineStr"/>
-      <c r="R24" s="52" t="inlineStr">
+      <c r="N24" s="60" t="inlineStr"/>
+      <c r="O24" s="60" t="inlineStr"/>
+      <c r="P24" s="60" t="inlineStr"/>
+      <c r="Q24" s="60" t="inlineStr"/>
+      <c r="R24" s="60" t="inlineStr">
         <is>
           <t>¥28,000 （税込み¥30,800）</t>
         </is>
       </c>
-      <c r="S24" s="52" t="inlineStr">
+      <c r="S24" s="60" t="inlineStr">
         <is>
           <t>4571527863745</t>
         </is>
       </c>
-      <c r="T24" s="52" t="inlineStr"/>
-      <c r="U24" s="52" t="inlineStr"/>
-      <c r="V24" s="52" t="inlineStr"/>
-      <c r="W24" s="52" t="inlineStr"/>
-      <c r="X24" s="52" t="inlineStr"/>
-      <c r="Y24" s="52" t="inlineStr"/>
-      <c r="Z24" s="52" t="inlineStr">
+      <c r="T24" s="60" t="inlineStr"/>
+      <c r="U24" s="60" t="inlineStr"/>
+      <c r="V24" s="60" t="inlineStr"/>
+      <c r="W24" s="60" t="inlineStr"/>
+      <c r="X24" s="60" t="inlineStr"/>
+      <c r="Y24" s="60" t="inlineStr"/>
+      <c r="Z24" s="60" t="inlineStr">
         <is>
           <t>1/32~3/16</t>
         </is>
       </c>
-      <c r="AA24" s="52" t="inlineStr"/>
-      <c r="AB24" s="52" t="inlineStr"/>
-      <c r="AC24" s="52" t="inlineStr"/>
-      <c r="AD24" s="52" t="inlineStr"/>
-      <c r="AE24" s="52" t="inlineStr"/>
-      <c r="AF24" s="52" t="inlineStr"/>
-      <c r="AG24" s="52" t="inlineStr"/>
-      <c r="AH24" s="52" t="inlineStr">
+      <c r="AA24" s="60" t="inlineStr"/>
+      <c r="AB24" s="60" t="inlineStr"/>
+      <c r="AC24" s="60" t="inlineStr"/>
+      <c r="AD24" s="60" t="inlineStr"/>
+      <c r="AE24" s="60" t="inlineStr"/>
+      <c r="AF24" s="60" t="inlineStr"/>
+      <c r="AG24" s="60" t="inlineStr"/>
+      <c r="AH24" s="60" t="inlineStr">
         <is>
           <t>642UL+-MIDSP 是 mid-strolling 专门项，Jighead 与 Down Shot 的 shake 线弧是核心；Bottom Strolling 是同一调性下的底层游动延伸。</t>
         </is>
       </c>
-      <c r="AI24" s="52" t="inlineStr">
+      <c r="AI24" s="60" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Bottom Strolling / Down Shot / Jighead Rig</t>
         </is>
       </c>
-      <c r="AJ24" s="52" t="inlineStr"/>
-      <c r="AK24" s="52" t="inlineStr"/>
-      <c r="AL24" s="52" t="inlineStr"/>
-      <c r="AM24" s="52" t="inlineStr">
+      <c r="AJ24" s="60" t="inlineStr"/>
+      <c r="AK24" s="60" t="inlineStr"/>
+      <c r="AL24" s="60" t="inlineStr"/>
+      <c r="AM24" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水・缓坡・中层鱼 / 2pc mid strolling</t>
         </is>
       </c>
-      <c r="AN24" s="52" t="inlineStr">
+      <c r="AN24" s="60" t="inlineStr">
         <is>
           <t>便携 mid/bottom strolling 专向</t>
         </is>
       </c>
-      <c r="AO24" s="52" t="inlineStr">
+      <c r="AO24" s="60" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead 和 Bottom Strolling 的节奏更明确，Down Shot 也能按中层或贴底游动思路使用。</t>
         </is>
       </c>
-      <c r="AP24" s="52" t="inlineStr">
+      <c r="AP24" s="60" t="inlineStr">
         <is>
           <t>無双できるミッドストローリングロッド 近年欠かすこと出来ないテクニックの一つミッドストローリング、通称ミドスト。ラインスラッグを出しながらジグヘッドやダウンショットをシェイクしやすいテーパーとガイドセッティングを追求することで、よりミドスト、ボトストの操作性能を高めました。レングスやロッドパワーは２pc専用設計。「ミドストが苦手な方の突破口」になり得る1本。 ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビッグフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ24" s="52" t="inlineStr"/>
-      <c r="AR24" s="52" t="inlineStr"/>
+      <c r="AQ24" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / ミドスト/ボトスト向けガイドセッティング / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR24" s="60" t="inlineStr"/>
+      <c r="AS24" s="60" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="52" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>DSRD10023</t>
         </is>
       </c>
-      <c r="B25" s="52" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C25" s="52" t="inlineStr">
+      <c r="C25" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D25" s="52" t="inlineStr">
+      <c r="D25" s="60" t="inlineStr">
         <is>
           <t>DBTS-662L</t>
         </is>
       </c>
-      <c r="E25" s="52" t="inlineStr">
+      <c r="E25" s="60" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F25" s="52" t="inlineStr">
+      <c r="F25" s="60" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G25" s="52" t="inlineStr">
+      <c r="G25" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H25" s="52" t="inlineStr"/>
-      <c r="I25" s="52" t="inlineStr"/>
-      <c r="J25" s="52" t="inlineStr">
+      <c r="H25" s="60" t="inlineStr"/>
+      <c r="I25" s="60" t="inlineStr"/>
+      <c r="J25" s="60" t="inlineStr">
         <is>
           <t>86g</t>
         </is>
       </c>
-      <c r="K25" s="52" t="inlineStr"/>
-      <c r="L25" s="52" t="inlineStr"/>
-      <c r="M25" s="52" t="inlineStr">
+      <c r="K25" s="60" t="inlineStr"/>
+      <c r="L25" s="60" t="inlineStr"/>
+      <c r="M25" s="60" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N25" s="52" t="inlineStr"/>
-      <c r="O25" s="52" t="inlineStr"/>
-      <c r="P25" s="52" t="inlineStr"/>
-      <c r="Q25" s="52" t="inlineStr"/>
-      <c r="R25" s="52" t="inlineStr">
+      <c r="N25" s="60" t="inlineStr"/>
+      <c r="O25" s="60" t="inlineStr"/>
+      <c r="P25" s="60" t="inlineStr"/>
+      <c r="Q25" s="60" t="inlineStr"/>
+      <c r="R25" s="60" t="inlineStr">
         <is>
           <t>¥28,500 （税込み¥31,350）</t>
         </is>
       </c>
-      <c r="S25" s="52" t="inlineStr">
+      <c r="S25" s="60" t="inlineStr">
         <is>
           <t>4571527862557</t>
         </is>
       </c>
-      <c r="T25" s="52" t="inlineStr"/>
-      <c r="U25" s="52" t="inlineStr"/>
-      <c r="V25" s="52" t="inlineStr"/>
-      <c r="W25" s="52" t="inlineStr"/>
-      <c r="X25" s="52" t="inlineStr"/>
-      <c r="Y25" s="52" t="inlineStr"/>
-      <c r="Z25" s="52" t="inlineStr">
+      <c r="T25" s="60" t="inlineStr"/>
+      <c r="U25" s="60" t="inlineStr"/>
+      <c r="V25" s="60" t="inlineStr"/>
+      <c r="W25" s="60" t="inlineStr"/>
+      <c r="X25" s="60" t="inlineStr"/>
+      <c r="Y25" s="60" t="inlineStr"/>
+      <c r="Z25" s="60" t="inlineStr">
         <is>
           <t>1/32~1/4</t>
         </is>
       </c>
-      <c r="AA25" s="52" t="inlineStr"/>
-      <c r="AB25" s="52" t="inlineStr"/>
-      <c r="AC25" s="52" t="inlineStr"/>
-      <c r="AD25" s="52" t="inlineStr"/>
-      <c r="AE25" s="52" t="inlineStr"/>
-      <c r="AF25" s="52" t="inlineStr"/>
-      <c r="AG25" s="52" t="inlineStr"/>
-      <c r="AH25" s="52" t="inlineStr">
+      <c r="AA25" s="60" t="inlineStr"/>
+      <c r="AB25" s="60" t="inlineStr"/>
+      <c r="AC25" s="60" t="inlineStr"/>
+      <c r="AD25" s="60" t="inlineStr"/>
+      <c r="AE25" s="60" t="inlineStr"/>
+      <c r="AF25" s="60" t="inlineStr"/>
+      <c r="AG25" s="60" t="inlineStr"/>
+      <c r="AH25" s="60" t="inlineStr">
         <is>
           <t>662L 是 finesse 到小型 plug 的多用途 spinning，食わせ端以 Neko、Down Shot、No Sinker 为主；远投搜索时更适合 Small Minnow 与 Shad，而不是重 cover。</t>
         </is>
       </c>
-      <c r="AI25" s="52" t="inlineStr">
+      <c r="AI25" s="60" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Minnow / Shad</t>
         </is>
       </c>
-      <c r="AJ25" s="52" t="inlineStr"/>
-      <c r="AK25" s="52" t="inlineStr"/>
-      <c r="AL25" s="52" t="inlineStr"/>
-      <c r="AM25" s="52" t="inlineStr">
+      <c r="AJ25" s="60" t="inlineStr"/>
+      <c r="AK25" s="60" t="inlineStr"/>
+      <c r="AL25" s="60" t="inlineStr"/>
+      <c r="AM25" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓远近切换 / finesse 到小型 Minnow・Shad</t>
         </is>
       </c>
-      <c r="AN25" s="52" t="inlineStr">
+      <c r="AN25" s="60" t="inlineStr">
         <is>
           <t>轻量软饵兼小硬饵</t>
         </is>
       </c>
-      <c r="AO25" s="52" t="inlineStr">
+      <c r="AO25" s="60" t="inlineStr">
         <is>
           <t>Neko、Down Shot、No Sinker 可以食わせ，Small Minnow 和 Shad 能补搜索，适合岸边只带一支 spinning 时拉开距离。</t>
         </is>
       </c>
-      <c r="AP25" s="52" t="inlineStr">
+      <c r="AP25" s="60" t="inlineStr">
         <is>
           <t>マルチバーサタイルモデル 1本でフィネス全般からプラグ系までアングラーの求める要素を詰め込んだマルチバーサタイルモデル 食わせが必要なフィネスアプローチから距離を求められる小型プラグのロングキャストまでセッティング次第で幅広く対応する事が可能。おかっぱりでもボートでも、持ち出せるタックルが限られた条件でこそ活躍する１本。。 ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビックフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ25" s="52" t="inlineStr"/>
-      <c r="AR25" s="52" t="inlineStr"/>
+      <c r="AQ25" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR25" s="60" t="inlineStr"/>
+      <c r="AS25" s="60" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>DSRD10024</t>
         </is>
       </c>
-      <c r="B26" s="52" t="inlineStr">
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C26" s="52" t="inlineStr">
+      <c r="C26" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D26" s="52" t="inlineStr">
+      <c r="D26" s="60" t="inlineStr">
         <is>
           <t>DBTS-662M</t>
         </is>
       </c>
-      <c r="E26" s="52" t="inlineStr">
+      <c r="E26" s="60" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F26" s="52" t="inlineStr">
+      <c r="F26" s="60" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G26" s="52" t="inlineStr">
+      <c r="G26" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H26" s="52" t="inlineStr"/>
-      <c r="I26" s="52" t="inlineStr"/>
-      <c r="J26" s="52" t="inlineStr">
+      <c r="H26" s="60" t="inlineStr"/>
+      <c r="I26" s="60" t="inlineStr"/>
+      <c r="J26" s="60" t="inlineStr">
         <is>
           <t>91g</t>
         </is>
       </c>
-      <c r="K26" s="52" t="inlineStr"/>
-      <c r="L26" s="52" t="inlineStr"/>
-      <c r="M26" s="52" t="inlineStr">
+      <c r="K26" s="60" t="inlineStr"/>
+      <c r="L26" s="60" t="inlineStr"/>
+      <c r="M26" s="60" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N26" s="52" t="inlineStr">
+      <c r="N26" s="60" t="inlineStr">
         <is>
           <t>0.6~1.5</t>
         </is>
       </c>
-      <c r="O26" s="52" t="inlineStr"/>
-      <c r="P26" s="52" t="inlineStr"/>
-      <c r="Q26" s="52" t="inlineStr"/>
-      <c r="R26" s="52" t="inlineStr">
+      <c r="O26" s="60" t="inlineStr"/>
+      <c r="P26" s="60" t="inlineStr"/>
+      <c r="Q26" s="60" t="inlineStr"/>
+      <c r="R26" s="60" t="inlineStr">
         <is>
           <t>¥28,500 （税込み¥31,350）</t>
         </is>
       </c>
-      <c r="S26" s="52" t="inlineStr">
+      <c r="S26" s="60" t="inlineStr">
         <is>
           <t>4571527862564</t>
         </is>
       </c>
-      <c r="T26" s="52" t="inlineStr"/>
-      <c r="U26" s="52" t="inlineStr"/>
-      <c r="V26" s="52" t="inlineStr"/>
-      <c r="W26" s="52" t="inlineStr"/>
-      <c r="X26" s="52" t="inlineStr"/>
-      <c r="Y26" s="52" t="inlineStr"/>
-      <c r="Z26" s="52" t="inlineStr">
+      <c r="T26" s="60" t="inlineStr"/>
+      <c r="U26" s="60" t="inlineStr"/>
+      <c r="V26" s="60" t="inlineStr"/>
+      <c r="W26" s="60" t="inlineStr"/>
+      <c r="X26" s="60" t="inlineStr"/>
+      <c r="Y26" s="60" t="inlineStr"/>
+      <c r="Z26" s="60" t="inlineStr">
         <is>
           <t>1/16~3/8</t>
         </is>
       </c>
-      <c r="AA26" s="52" t="inlineStr"/>
-      <c r="AB26" s="52" t="inlineStr"/>
-      <c r="AC26" s="52" t="inlineStr"/>
-      <c r="AD26" s="52" t="inlineStr"/>
-      <c r="AE26" s="52" t="inlineStr"/>
-      <c r="AF26" s="52" t="inlineStr"/>
-      <c r="AG26" s="52" t="inlineStr"/>
-      <c r="AH26" s="52" t="inlineStr">
+      <c r="AA26" s="60" t="inlineStr"/>
+      <c r="AB26" s="60" t="inlineStr"/>
+      <c r="AC26" s="60" t="inlineStr"/>
+      <c r="AD26" s="60" t="inlineStr"/>
+      <c r="AE26" s="60" t="inlineStr"/>
+      <c r="AF26" s="60" t="inlineStr"/>
+      <c r="AG26" s="60" t="inlineStr"/>
+      <c r="AH26" s="60" t="inlineStr">
         <is>
           <t>662M 是 PE power finesse spinning，重点是 Guarded Small Rubber Jig、Cover Neko 和虫系打浓 cover；big lake 远投 Down Shot/Neko 可用，但不是第一定位。</t>
         </is>
       </c>
-      <c r="AI26" s="52" t="inlineStr">
+      <c r="AI26" s="60" t="inlineStr">
         <is>
           <t>Cover Neko / Guarded Small Rubber Jig / Bug Lure / Power Finesse / Long Cast Down Shot</t>
         </is>
       </c>
-      <c r="AJ26" s="52" t="inlineStr"/>
-      <c r="AK26" s="52" t="inlineStr"/>
-      <c r="AL26" s="52" t="inlineStr"/>
-      <c r="AM26" s="52" t="inlineStr">
+      <c r="AJ26" s="60" t="inlineStr"/>
+      <c r="AK26" s="60" t="inlineStr"/>
+      <c r="AL26" s="60" t="inlineStr"/>
+      <c r="AM26" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 浓 cover・虫系・大型湖 light rig / PE power finesse</t>
         </is>
       </c>
-      <c r="AN26" s="52" t="inlineStr">
+      <c r="AN26" s="60" t="inlineStr">
         <is>
           <t>cover power finesse spinning</t>
         </is>
       </c>
-      <c r="AO26" s="52" t="inlineStr">
+      <c r="AO26" s="60" t="inlineStr">
         <is>
           <t>Cover Neko、Guarded Small Rubber Jig 和 Bug Lure 适合打 cover，Long Cast Down Shot 可作为大型湖远投精细补充。</t>
         </is>
       </c>
-      <c r="AP26" s="52" t="inlineStr">
+      <c r="AP26" s="60" t="inlineStr">
         <is>
           <t>キャスタビリティーとパワーを追求したパワーフィネススピン 近年の釣りで不可欠な存在になっているPEを用いたパワーフィネス。6’6″のレングスにする事でキャスタビリティー性能を重視。食わせの「間」を与える硬すぎないティップアクションとナノマテリアル配合のBLUE TREKブランクスを採用した強靭なバットがバスをカバーから引きはがします。ガード付きのスモラバやカバーネコ、濃いめのカバーを虫系で攻める場合にアドバンテージを与えてくれる仕様。また琵琶湖等のビックレイクでのライトリグにもおススメです。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ26" s="52" t="inlineStr"/>
-      <c r="AR26" s="52" t="inlineStr"/>
+      <c r="AQ26" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR26" s="60" t="inlineStr"/>
+      <c r="AS26" s="60" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>DSRD10025</t>
         </is>
       </c>
-      <c r="B27" s="52" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C27" s="52" t="inlineStr">
+      <c r="C27" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D27" s="52" t="inlineStr">
+      <c r="D27" s="60" t="inlineStr">
         <is>
           <t>DBTS-6102ML-S</t>
         </is>
       </c>
-      <c r="E27" s="52" t="inlineStr">
+      <c r="E27" s="60" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F27" s="52" t="inlineStr">
+      <c r="F27" s="60" t="inlineStr">
         <is>
           <t>6’10″</t>
         </is>
       </c>
-      <c r="G27" s="52" t="inlineStr">
+      <c r="G27" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H27" s="52" t="inlineStr"/>
-      <c r="I27" s="52" t="inlineStr"/>
-      <c r="J27" s="52" t="inlineStr">
+      <c r="H27" s="60" t="inlineStr"/>
+      <c r="I27" s="60" t="inlineStr"/>
+      <c r="J27" s="60" t="inlineStr">
         <is>
           <t>85g</t>
         </is>
       </c>
-      <c r="K27" s="52" t="inlineStr"/>
-      <c r="L27" s="52" t="inlineStr"/>
-      <c r="M27" s="52" t="inlineStr">
+      <c r="K27" s="60" t="inlineStr"/>
+      <c r="L27" s="60" t="inlineStr"/>
+      <c r="M27" s="60" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N27" s="52" t="inlineStr">
+      <c r="N27" s="60" t="inlineStr">
         <is>
           <t>0.4~1</t>
         </is>
       </c>
-      <c r="O27" s="52" t="inlineStr"/>
-      <c r="P27" s="52" t="inlineStr"/>
-      <c r="Q27" s="52" t="inlineStr"/>
-      <c r="R27" s="52" t="inlineStr">
+      <c r="O27" s="60" t="inlineStr"/>
+      <c r="P27" s="60" t="inlineStr"/>
+      <c r="Q27" s="60" t="inlineStr"/>
+      <c r="R27" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込み¥31,900）</t>
         </is>
       </c>
-      <c r="S27" s="52" t="inlineStr">
+      <c r="S27" s="60" t="inlineStr">
         <is>
           <t>4571527862571</t>
         </is>
       </c>
-      <c r="T27" s="52" t="inlineStr"/>
-      <c r="U27" s="52" t="inlineStr"/>
-      <c r="V27" s="52" t="inlineStr"/>
-      <c r="W27" s="52" t="inlineStr"/>
-      <c r="X27" s="52" t="inlineStr"/>
-      <c r="Y27" s="52" t="inlineStr"/>
-      <c r="Z27" s="52" t="inlineStr">
+      <c r="T27" s="60" t="inlineStr"/>
+      <c r="U27" s="60" t="inlineStr"/>
+      <c r="V27" s="60" t="inlineStr"/>
+      <c r="W27" s="60" t="inlineStr"/>
+      <c r="X27" s="60" t="inlineStr"/>
+      <c r="Y27" s="60" t="inlineStr"/>
+      <c r="Z27" s="60" t="inlineStr">
         <is>
           <t>1/16~3/8</t>
         </is>
       </c>
-      <c r="AA27" s="52" t="inlineStr"/>
-      <c r="AB27" s="52" t="inlineStr"/>
-      <c r="AC27" s="52" t="inlineStr"/>
-      <c r="AD27" s="52" t="inlineStr"/>
-      <c r="AE27" s="52" t="inlineStr"/>
-      <c r="AF27" s="52" t="inlineStr"/>
-      <c r="AG27" s="52" t="inlineStr"/>
-      <c r="AH27" s="52" t="inlineStr">
+      <c r="AA27" s="60" t="inlineStr"/>
+      <c r="AB27" s="60" t="inlineStr"/>
+      <c r="AC27" s="60" t="inlineStr"/>
+      <c r="AD27" s="60" t="inlineStr"/>
+      <c r="AE27" s="60" t="inlineStr"/>
+      <c r="AF27" s="60" t="inlineStr"/>
+      <c r="AG27" s="60" t="inlineStr"/>
+      <c r="AH27" s="60" t="inlineStr">
         <is>
           <t>6102ML-S 是 long-shooting special，ML solid tip 和 PE 导环适合把 Down Shot/Neko、I-shaped、虫系和表层 Plug 送远；核心价值是距离下仍保留操作感。</t>
         </is>
       </c>
-      <c r="AI27" s="52" t="inlineStr">
+      <c r="AI27" s="60" t="inlineStr">
         <is>
           <t>Long Cast Down Shot / Neko Rig / I-shaped Plug / Bug Lure / Surface Plug</t>
         </is>
       </c>
-      <c r="AJ27" s="52" t="inlineStr"/>
-      <c r="AK27" s="52" t="inlineStr"/>
-      <c r="AL27" s="52" t="inlineStr"/>
-      <c r="AM27" s="52" t="inlineStr">
+      <c r="AJ27" s="60" t="inlineStr"/>
+      <c r="AK27" s="60" t="inlineStr"/>
+      <c r="AL27" s="60" t="inlineStr"/>
+      <c r="AM27" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓远投・开阔水 / light rig 与表层搜索</t>
         </is>
       </c>
-      <c r="AN27" s="52" t="inlineStr">
+      <c r="AN27" s="60" t="inlineStr">
         <is>
           <t>远投轻量泛用 spinning</t>
         </is>
       </c>
-      <c r="AO27" s="52" t="inlineStr">
+      <c r="AO27" s="60" t="inlineStr">
         <is>
           <t>Long Cast Down Shot 和 Neko 能保持距离下的操作感，I-shaped、Bug、Surface Plug 用来处理表层或清水弱波动搜索。</t>
         </is>
       </c>
-      <c r="AP27" s="52" t="inlineStr">
+      <c r="AP27" s="60" t="inlineStr">
         <is>
           <t>パワフルロングシューティングスペシャル ロングキャストが必要な状況でキャスタビリティーと操作性の両立を実現させたおかっぱりやボートで重宝するモデル。MLパワーソリッドティップを採用することでライトリグ全般から表層系プラグ、i字系、虫系など幅広く対応。ガイドもPEライン仕様の専用セッティング。ナノマテリアル配合のBLUE TREKブランクは不意なビックフィッシュでも逃さない粘りを実現しました。軽量ルアーをもっと遠くへ、未開の領域へ飛ばしたいアングラーに。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ27" s="52" t="inlineStr"/>
-      <c r="AR27" s="52" t="inlineStr"/>
+      <c r="AQ27" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / MLパワーソリッドティップ / PEライン仕様ガイド / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR27" s="60" t="inlineStr"/>
+      <c r="AS27" s="60" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr">
         <is>
           <t>DSRD10026</t>
         </is>
       </c>
-      <c r="B28" s="52" t="inlineStr">
+      <c r="B28" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C28" s="52" t="inlineStr">
+      <c r="C28" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D28" s="52" t="inlineStr">
+      <c r="D28" s="60" t="inlineStr">
         <is>
           <t>DBTC-662ML-BF</t>
         </is>
       </c>
-      <c r="E28" s="52" t="inlineStr">
+      <c r="E28" s="60" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F28" s="52" t="inlineStr">
+      <c r="F28" s="60" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G28" s="52" t="inlineStr">
+      <c r="G28" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H28" s="52" t="inlineStr"/>
-      <c r="I28" s="52" t="inlineStr"/>
-      <c r="J28" s="52" t="inlineStr">
+      <c r="H28" s="60" t="inlineStr"/>
+      <c r="I28" s="60" t="inlineStr"/>
+      <c r="J28" s="60" t="inlineStr">
         <is>
           <t>110g</t>
         </is>
       </c>
-      <c r="K28" s="52" t="inlineStr"/>
-      <c r="L28" s="52" t="inlineStr"/>
-      <c r="M28" s="52" t="inlineStr">
+      <c r="K28" s="60" t="inlineStr"/>
+      <c r="L28" s="60" t="inlineStr"/>
+      <c r="M28" s="60" t="inlineStr">
         <is>
           <t>6~12</t>
         </is>
       </c>
-      <c r="N28" s="52" t="inlineStr"/>
-      <c r="O28" s="52" t="inlineStr"/>
-      <c r="P28" s="52" t="inlineStr"/>
-      <c r="Q28" s="52" t="inlineStr"/>
-      <c r="R28" s="52" t="inlineStr">
+      <c r="N28" s="60" t="inlineStr"/>
+      <c r="O28" s="60" t="inlineStr"/>
+      <c r="P28" s="60" t="inlineStr"/>
+      <c r="Q28" s="60" t="inlineStr"/>
+      <c r="R28" s="60" t="inlineStr">
         <is>
           <t>¥28,500 （税込み¥31,350）</t>
         </is>
       </c>
-      <c r="S28" s="52" t="inlineStr">
+      <c r="S28" s="60" t="inlineStr">
         <is>
           <t>4571527863769</t>
         </is>
       </c>
-      <c r="T28" s="52" t="inlineStr"/>
-      <c r="U28" s="52" t="inlineStr"/>
-      <c r="V28" s="52" t="inlineStr"/>
-      <c r="W28" s="52" t="inlineStr"/>
-      <c r="X28" s="52" t="inlineStr"/>
-      <c r="Y28" s="52" t="inlineStr"/>
-      <c r="Z28" s="52" t="inlineStr">
+      <c r="T28" s="60" t="inlineStr"/>
+      <c r="U28" s="60" t="inlineStr"/>
+      <c r="V28" s="60" t="inlineStr"/>
+      <c r="W28" s="60" t="inlineStr"/>
+      <c r="X28" s="60" t="inlineStr"/>
+      <c r="Y28" s="60" t="inlineStr"/>
+      <c r="Z28" s="60" t="inlineStr">
         <is>
           <t>1/8~1/2</t>
         </is>
       </c>
-      <c r="AA28" s="52" t="inlineStr"/>
-      <c r="AB28" s="52" t="inlineStr"/>
-      <c r="AC28" s="52" t="inlineStr"/>
-      <c r="AD28" s="52" t="inlineStr"/>
-      <c r="AE28" s="52" t="inlineStr"/>
-      <c r="AF28" s="52" t="inlineStr"/>
-      <c r="AG28" s="52" t="inlineStr"/>
-      <c r="AH28" s="52" t="inlineStr">
+      <c r="AA28" s="60" t="inlineStr"/>
+      <c r="AB28" s="60" t="inlineStr"/>
+      <c r="AC28" s="60" t="inlineStr"/>
+      <c r="AD28" s="60" t="inlineStr"/>
+      <c r="AE28" s="60" t="inlineStr"/>
+      <c r="AF28" s="60" t="inlineStr"/>
+      <c r="AG28" s="60" t="inlineStr"/>
+      <c r="AH28" s="60" t="inlineStr">
         <is>
           <t>662ML-BF 是 multi bait finesse，小型 Plug 与小型 wire bait 可以搜索，Small Rubber Jig、Neko、Down Shot 用于精细投放；优势是近中距离准确和手返し。</t>
         </is>
       </c>
-      <c r="AI28" s="52" t="inlineStr">
+      <c r="AI28" s="60" t="inlineStr">
         <is>
           <t>Bait Finesse Small Plug / Small Spinnerbait / Small Rubber Jig / Neko Rig / Down Shot</t>
         </is>
       </c>
-      <c r="AJ28" s="52" t="inlineStr"/>
-      <c r="AK28" s="52" t="inlineStr"/>
-      <c r="AL28" s="52" t="inlineStr"/>
-      <c r="AM28" s="52" t="inlineStr">
+      <c r="AJ28" s="60" t="inlineStr"/>
+      <c r="AK28" s="60" t="inlineStr"/>
+      <c r="AL28" s="60" t="inlineStr"/>
+      <c r="AM28" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸边障碍・小型河川・野池 / multi BFS</t>
         </is>
       </c>
-      <c r="AN28" s="52" t="inlineStr">
+      <c r="AN28" s="60" t="inlineStr">
         <is>
           <t>小硬饵与精细软饵 BFS</t>
         </is>
       </c>
-      <c r="AO28" s="52" t="inlineStr">
+      <c r="AO28" s="60" t="inlineStr">
         <is>
           <t>Small Plug、Small Spinnerbait 能搜索，Small Rubber Jig、Neko、Down Shot 可打点；适合近中距离精准抛投和手返し。</t>
         </is>
       </c>
-      <c r="AP28" s="52" t="inlineStr">
+      <c r="AP28" s="60" t="inlineStr">
         <is>
           <t>マルチベイトフィネスモデル ベイトフィネスモデルでありながらこの１本で幅広くルアーを扱えるマルチベイトフィネスモデル。スモールプラグや小型ワイヤーベイト、スモールラバージグやネコリグ、ダウンショットまでこなせる汎用性があります。おっかぱりやボートでも重宝する１本。ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビッグフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ28" s="52" t="inlineStr"/>
-      <c r="AR28" s="52" t="inlineStr"/>
+      <c r="AQ28" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR28" s="60" t="inlineStr"/>
+      <c r="AS28" s="60" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="52" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr">
         <is>
           <t>DSRD10027</t>
         </is>
       </c>
-      <c r="B29" s="52" t="inlineStr">
+      <c r="B29" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C29" s="52" t="inlineStr">
+      <c r="C29" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D29" s="52" t="inlineStr">
+      <c r="D29" s="60" t="inlineStr">
         <is>
           <t>DBTC-672MH-S</t>
         </is>
       </c>
-      <c r="E29" s="52" t="inlineStr">
+      <c r="E29" s="60" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F29" s="52" t="inlineStr">
+      <c r="F29" s="60" t="inlineStr">
         <is>
           <t>6’7″</t>
         </is>
       </c>
-      <c r="G29" s="52" t="inlineStr">
+      <c r="G29" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H29" s="52" t="inlineStr"/>
-      <c r="I29" s="52" t="inlineStr"/>
-      <c r="J29" s="52" t="inlineStr">
+      <c r="H29" s="60" t="inlineStr"/>
+      <c r="I29" s="60" t="inlineStr"/>
+      <c r="J29" s="60" t="inlineStr">
         <is>
           <t>117g</t>
         </is>
       </c>
-      <c r="K29" s="52" t="inlineStr"/>
-      <c r="L29" s="52" t="inlineStr"/>
-      <c r="M29" s="52" t="inlineStr">
+      <c r="K29" s="60" t="inlineStr"/>
+      <c r="L29" s="60" t="inlineStr"/>
+      <c r="M29" s="60" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N29" s="52" t="inlineStr"/>
-      <c r="O29" s="52" t="inlineStr"/>
-      <c r="P29" s="52" t="inlineStr"/>
-      <c r="Q29" s="52" t="inlineStr"/>
-      <c r="R29" s="52" t="inlineStr">
+      <c r="N29" s="60" t="inlineStr"/>
+      <c r="O29" s="60" t="inlineStr"/>
+      <c r="P29" s="60" t="inlineStr"/>
+      <c r="Q29" s="60" t="inlineStr"/>
+      <c r="R29" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込み¥31,900）</t>
         </is>
       </c>
-      <c r="S29" s="52" t="inlineStr">
+      <c r="S29" s="60" t="inlineStr">
         <is>
           <t>4571527863776</t>
         </is>
       </c>
-      <c r="T29" s="52" t="inlineStr"/>
-      <c r="U29" s="52" t="inlineStr"/>
-      <c r="V29" s="52" t="inlineStr"/>
-      <c r="W29" s="52" t="inlineStr"/>
-      <c r="X29" s="52" t="inlineStr"/>
-      <c r="Y29" s="52" t="inlineStr"/>
-      <c r="Z29" s="52" t="inlineStr">
+      <c r="T29" s="60" t="inlineStr"/>
+      <c r="U29" s="60" t="inlineStr"/>
+      <c r="V29" s="60" t="inlineStr"/>
+      <c r="W29" s="60" t="inlineStr"/>
+      <c r="X29" s="60" t="inlineStr"/>
+      <c r="Y29" s="60" t="inlineStr"/>
+      <c r="Z29" s="60" t="inlineStr">
         <is>
           <t>3/16~3/4</t>
         </is>
       </c>
-      <c r="AA29" s="52" t="inlineStr"/>
-      <c r="AB29" s="52" t="inlineStr"/>
-      <c r="AC29" s="52" t="inlineStr"/>
-      <c r="AD29" s="52" t="inlineStr"/>
-      <c r="AE29" s="52" t="inlineStr"/>
-      <c r="AF29" s="52" t="inlineStr"/>
-      <c r="AG29" s="52" t="inlineStr"/>
-      <c r="AH29" s="52" t="inlineStr">
+      <c r="AA29" s="60" t="inlineStr"/>
+      <c r="AB29" s="60" t="inlineStr"/>
+      <c r="AC29" s="60" t="inlineStr"/>
+      <c r="AD29" s="60" t="inlineStr"/>
+      <c r="AE29" s="60" t="inlineStr"/>
+      <c r="AF29" s="60" t="inlineStr"/>
+      <c r="AG29" s="60" t="inlineStr"/>
+      <c r="AH29" s="60" t="inlineStr">
         <is>
           <t>672MH-S 描述虽短，但明确是 tough-cover rod；推荐只保守落在 Cover Neko、Heavy Down Shot、Texas 与 Rubber Jig，不外扩到 Big Bait。</t>
         </is>
       </c>
-      <c r="AI29" s="52" t="inlineStr">
+      <c r="AI29" s="60" t="inlineStr">
         <is>
           <t>Cover Neko / Heavy Down Shot / Texas Rig / Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ29" s="52" t="inlineStr"/>
-      <c r="AK29" s="52" t="inlineStr"/>
-      <c r="AL29" s="52" t="inlineStr"/>
-      <c r="AM29" s="52" t="inlineStr">
+      <c r="AJ29" s="60" t="inlineStr"/>
+      <c r="AK29" s="60" t="inlineStr"/>
+      <c r="AL29" s="60" t="inlineStr"/>
+      <c r="AM29" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / tough cover・沉木・草边 / cover soft rig</t>
         </is>
       </c>
-      <c r="AN29" s="52" t="inlineStr">
+      <c r="AN29" s="60" t="inlineStr">
         <is>
           <t>cover 底操与 heavy finesse</t>
         </is>
       </c>
-      <c r="AO29" s="52" t="inlineStr">
+      <c r="AO29" s="60" t="inlineStr">
         <is>
           <t>Cover Neko、Heavy Down Shot、Texas 和 Rubber Jig 都围绕 cover 展开，定位保守清晰，不把 MH 误扩成大型饵竿。</t>
         </is>
       </c>
-      <c r="AP29" s="52" t="inlineStr">
+      <c r="AP29" s="60" t="inlineStr">
         <is>
           <t>タフタイムを制するカバーロッド</t>
         </is>
       </c>
-      <c r="AQ29" s="52" t="inlineStr"/>
-      <c r="AR29" s="52" t="inlineStr"/>
+      <c r="AQ29" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / ソリッドティップ / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR29" s="60" t="inlineStr"/>
+      <c r="AS29" s="60" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="52" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>DSRD10028</t>
         </is>
       </c>
-      <c r="B30" s="52" t="inlineStr">
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C30" s="52" t="inlineStr">
+      <c r="C30" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D30" s="52" t="inlineStr">
+      <c r="D30" s="60" t="inlineStr">
         <is>
           <t>DBTC-6102M</t>
         </is>
       </c>
-      <c r="E30" s="52" t="inlineStr">
+      <c r="E30" s="60" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F30" s="52" t="inlineStr">
+      <c r="F30" s="60" t="inlineStr">
         <is>
           <t>6’10″</t>
         </is>
       </c>
-      <c r="G30" s="52" t="inlineStr">
+      <c r="G30" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H30" s="52" t="inlineStr"/>
-      <c r="I30" s="52" t="inlineStr"/>
-      <c r="J30" s="52" t="inlineStr">
+      <c r="H30" s="60" t="inlineStr"/>
+      <c r="I30" s="60" t="inlineStr"/>
+      <c r="J30" s="60" t="inlineStr">
         <is>
           <t>113g</t>
         </is>
       </c>
-      <c r="K30" s="52" t="inlineStr"/>
-      <c r="L30" s="52" t="inlineStr"/>
-      <c r="M30" s="52" t="inlineStr">
+      <c r="K30" s="60" t="inlineStr"/>
+      <c r="L30" s="60" t="inlineStr"/>
+      <c r="M30" s="60" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N30" s="52" t="inlineStr"/>
-      <c r="O30" s="52" t="inlineStr"/>
-      <c r="P30" s="52" t="inlineStr"/>
-      <c r="Q30" s="52" t="inlineStr"/>
-      <c r="R30" s="52" t="inlineStr">
+      <c r="N30" s="60" t="inlineStr"/>
+      <c r="O30" s="60" t="inlineStr"/>
+      <c r="P30" s="60" t="inlineStr"/>
+      <c r="Q30" s="60" t="inlineStr"/>
+      <c r="R30" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込み¥31,900）</t>
         </is>
       </c>
-      <c r="S30" s="52" t="inlineStr">
+      <c r="S30" s="60" t="inlineStr">
         <is>
           <t>4571527862588</t>
         </is>
       </c>
-      <c r="T30" s="52" t="inlineStr"/>
-      <c r="U30" s="52" t="inlineStr"/>
-      <c r="V30" s="52" t="inlineStr"/>
-      <c r="W30" s="52" t="inlineStr"/>
-      <c r="X30" s="52" t="inlineStr"/>
-      <c r="Y30" s="52" t="inlineStr"/>
-      <c r="Z30" s="52" t="inlineStr">
+      <c r="T30" s="60" t="inlineStr"/>
+      <c r="U30" s="60" t="inlineStr"/>
+      <c r="V30" s="60" t="inlineStr"/>
+      <c r="W30" s="60" t="inlineStr"/>
+      <c r="X30" s="60" t="inlineStr"/>
+      <c r="Y30" s="60" t="inlineStr"/>
+      <c r="Z30" s="60" t="inlineStr">
         <is>
           <t>3/16~5/8</t>
         </is>
       </c>
-      <c r="AA30" s="52" t="inlineStr"/>
-      <c r="AB30" s="52" t="inlineStr"/>
-      <c r="AC30" s="52" t="inlineStr"/>
-      <c r="AD30" s="52" t="inlineStr"/>
-      <c r="AE30" s="52" t="inlineStr"/>
-      <c r="AF30" s="52" t="inlineStr"/>
-      <c r="AG30" s="52" t="inlineStr"/>
-      <c r="AH30" s="52" t="inlineStr">
+      <c r="AA30" s="60" t="inlineStr"/>
+      <c r="AB30" s="60" t="inlineStr"/>
+      <c r="AC30" s="60" t="inlineStr"/>
+      <c r="AD30" s="60" t="inlineStr"/>
+      <c r="AE30" s="60" t="inlineStr"/>
+      <c r="AF30" s="60" t="inlineStr"/>
+      <c r="AG30" s="60" t="inlineStr"/>
+      <c r="AH30" s="60" t="inlineStr">
         <is>
           <t>6102M 是岸钓到船钓都能带的一支 super versatile，worm 系 rig 负责撃ち，Crankbait、Spinnerbait、Chatterbait 负责巻き；适合软硬饵切换。</t>
         </is>
       </c>
-      <c r="AI30" s="52" t="inlineStr">
+      <c r="AI30" s="60" t="inlineStr">
         <is>
           <t>Texas Rig / Free Rig / No Sinker / Crankbait / Spinnerbait / Chatterbait</t>
         </is>
       </c>
-      <c r="AJ30" s="52" t="inlineStr"/>
-      <c r="AK30" s="52" t="inlineStr"/>
-      <c r="AL30" s="52" t="inlineStr"/>
-      <c r="AM30" s="52" t="inlineStr">
+      <c r="AJ30" s="60" t="inlineStr"/>
+      <c r="AK30" s="60" t="inlineStr"/>
+      <c r="AL30" s="60" t="inlineStr"/>
+      <c r="AM30" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓・船钓通用 / worm rig 到 Chatterbait</t>
         </is>
       </c>
-      <c r="AN30" s="52" t="inlineStr">
+      <c r="AN30" s="60" t="inlineStr">
         <is>
           <t>软硬饵日常主力 bait</t>
         </is>
       </c>
-      <c r="AO30" s="52" t="inlineStr">
+      <c r="AO30" s="60" t="inlineStr">
         <is>
           <t>Texas、Free Rig、No Sinker 负责打点，Crankbait、Spinnerbait、Chatterbait 负责搜索，适合一支竿快速切换路线。</t>
         </is>
       </c>
-      <c r="AP30" s="52" t="inlineStr">
+      <c r="AP30" s="60" t="inlineStr">
         <is>
           <t>スーパーバーサタイルモデル 巻きから撃ちまでマルチにこなせるスーパーバーサタイルモデル。おかっぱりからボートまでどこへ行くにも手放せない１本。癖のないレギュラーファーストテーパーにすることで投げて楽しい、掛けて楽しいロッドに仕上がっています。ワーム系リグ全般、プラグやワイヤーベイトまであらゆるジャンルのタイプが使用可能です。「迷ったら」「1本しか持ち出せないなら」この1本をおススメします。 ナノマテリアル配合のBLUE TREKブランクスを採用する事で不意なビックフィッシュでも逃さない粘りを実現しました。『自分らしいフィッシングライフを支える２ピースモデル。』</t>
         </is>
       </c>
-      <c r="AQ30" s="52" t="inlineStr"/>
-      <c r="AR30" s="52" t="inlineStr"/>
+      <c r="AQ30" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR30" s="60" t="inlineStr"/>
+      <c r="AS30" s="60" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="52" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>DSRD10029</t>
         </is>
       </c>
-      <c r="B31" s="52" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C31" s="52" t="inlineStr">
+      <c r="C31" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D31" s="52" t="inlineStr">
+      <c r="D31" s="60" t="inlineStr">
         <is>
           <t>DBTC-6102MH</t>
         </is>
       </c>
-      <c r="E31" s="52" t="inlineStr">
+      <c r="E31" s="60" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F31" s="52" t="inlineStr">
+      <c r="F31" s="60" t="inlineStr">
         <is>
           <t>6’10″</t>
         </is>
       </c>
-      <c r="G31" s="52" t="inlineStr">
+      <c r="G31" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H31" s="52" t="inlineStr"/>
-      <c r="I31" s="52" t="inlineStr"/>
-      <c r="J31" s="52" t="inlineStr">
+      <c r="H31" s="60" t="inlineStr"/>
+      <c r="I31" s="60" t="inlineStr"/>
+      <c r="J31" s="60" t="inlineStr">
         <is>
           <t>123g</t>
         </is>
       </c>
-      <c r="K31" s="52" t="inlineStr"/>
-      <c r="L31" s="52" t="inlineStr"/>
-      <c r="M31" s="52" t="inlineStr">
+      <c r="K31" s="60" t="inlineStr"/>
+      <c r="L31" s="60" t="inlineStr"/>
+      <c r="M31" s="60" t="inlineStr">
         <is>
           <t>8~20</t>
         </is>
       </c>
-      <c r="N31" s="52" t="inlineStr"/>
-      <c r="O31" s="52" t="inlineStr"/>
-      <c r="P31" s="52" t="inlineStr"/>
-      <c r="Q31" s="52" t="inlineStr"/>
-      <c r="R31" s="52" t="inlineStr">
+      <c r="N31" s="60" t="inlineStr"/>
+      <c r="O31" s="60" t="inlineStr"/>
+      <c r="P31" s="60" t="inlineStr"/>
+      <c r="Q31" s="60" t="inlineStr"/>
+      <c r="R31" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込み¥31,900）</t>
         </is>
       </c>
-      <c r="S31" s="52" t="inlineStr">
+      <c r="S31" s="60" t="inlineStr">
         <is>
           <t>4571527862595</t>
         </is>
       </c>
-      <c r="T31" s="52" t="inlineStr"/>
-      <c r="U31" s="52" t="inlineStr"/>
-      <c r="V31" s="52" t="inlineStr"/>
-      <c r="W31" s="52" t="inlineStr"/>
-      <c r="X31" s="52" t="inlineStr"/>
-      <c r="Y31" s="52" t="inlineStr"/>
-      <c r="Z31" s="52" t="inlineStr">
+      <c r="T31" s="60" t="inlineStr"/>
+      <c r="U31" s="60" t="inlineStr"/>
+      <c r="V31" s="60" t="inlineStr"/>
+      <c r="W31" s="60" t="inlineStr"/>
+      <c r="X31" s="60" t="inlineStr"/>
+      <c r="Y31" s="60" t="inlineStr"/>
+      <c r="Z31" s="60" t="inlineStr">
         <is>
           <t>3/16~3/4</t>
         </is>
       </c>
-      <c r="AA31" s="52" t="inlineStr"/>
-      <c r="AB31" s="52" t="inlineStr"/>
-      <c r="AC31" s="52" t="inlineStr"/>
-      <c r="AD31" s="52" t="inlineStr"/>
-      <c r="AE31" s="52" t="inlineStr"/>
-      <c r="AF31" s="52" t="inlineStr"/>
-      <c r="AG31" s="52" t="inlineStr"/>
-      <c r="AH31" s="52" t="inlineStr">
+      <c r="AA31" s="60" t="inlineStr"/>
+      <c r="AB31" s="60" t="inlineStr"/>
+      <c r="AC31" s="60" t="inlineStr"/>
+      <c r="AD31" s="60" t="inlineStr"/>
+      <c r="AE31" s="60" t="inlineStr"/>
+      <c r="AF31" s="60" t="inlineStr"/>
+      <c r="AG31" s="60" t="inlineStr"/>
+      <c r="AH31" s="60" t="inlineStr">
         <is>
           <t>6102MH 只有中量级 versatile 描述，按 MH 规格保守放在 Texas、Free Rig、Rubber Jig 与中量移动饵；不因 MH 自动扩写到大型饵。</t>
         </is>
       </c>
-      <c r="AI31" s="52" t="inlineStr">
+      <c r="AI31" s="60" t="inlineStr">
         <is>
           <t>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait / Crankbait</t>
         </is>
       </c>
-      <c r="AJ31" s="52" t="inlineStr"/>
-      <c r="AK31" s="52" t="inlineStr"/>
-      <c r="AL31" s="52" t="inlineStr"/>
-      <c r="AM31" s="52" t="inlineStr">
+      <c r="AJ31" s="60" t="inlineStr"/>
+      <c r="AK31" s="60" t="inlineStr"/>
+      <c r="AL31" s="60" t="inlineStr"/>
+      <c r="AM31" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 中重 cover・硬底・浅草 / middle-heavy versatile</t>
         </is>
       </c>
-      <c r="AN31" s="52" t="inlineStr">
+      <c r="AN31" s="60" t="inlineStr">
         <is>
           <t>中重软饵与卷物泛用</t>
         </is>
       </c>
-      <c r="AO31" s="52" t="inlineStr">
+      <c r="AO31" s="60" t="inlineStr">
         <is>
           <t>Texas、Free Rig、Rubber Jig 可读底和穿 cover，Spinnerbait、Chatterbait、Crankbait 能做中量搜索；不把用途夸大到纯大饵。</t>
         </is>
       </c>
-      <c r="AP31" s="52" t="inlineStr">
+      <c r="AP31" s="60" t="inlineStr">
         <is>
           <t>ミドルスーパーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ31" s="52" t="inlineStr"/>
-      <c r="AR31" s="52" t="inlineStr"/>
+      <c r="AQ31" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR31" s="60" t="inlineStr"/>
+      <c r="AS31" s="60" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="52" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr">
         <is>
           <t>DSRD10030</t>
         </is>
       </c>
-      <c r="B32" s="52" t="inlineStr">
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C32" s="52" t="inlineStr">
+      <c r="C32" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D32" s="52" t="inlineStr">
+      <c r="D32" s="60" t="inlineStr">
         <is>
           <t>DBTC-6102XH</t>
         </is>
       </c>
-      <c r="E32" s="52" t="inlineStr">
+      <c r="E32" s="60" t="inlineStr">
         <is>
           <t>XH</t>
         </is>
       </c>
-      <c r="F32" s="52" t="inlineStr">
+      <c r="F32" s="60" t="inlineStr">
         <is>
           <t>6’10″</t>
         </is>
       </c>
-      <c r="G32" s="52" t="inlineStr">
+      <c r="G32" s="60" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="H32" s="52" t="inlineStr"/>
-      <c r="I32" s="52" t="inlineStr"/>
-      <c r="J32" s="52" t="inlineStr">
+      <c r="H32" s="60" t="inlineStr"/>
+      <c r="I32" s="60" t="inlineStr"/>
+      <c r="J32" s="60" t="inlineStr">
         <is>
           <t>172g</t>
         </is>
       </c>
-      <c r="K32" s="52" t="inlineStr"/>
-      <c r="L32" s="52" t="inlineStr"/>
-      <c r="M32" s="52" t="inlineStr">
+      <c r="K32" s="60" t="inlineStr"/>
+      <c r="L32" s="60" t="inlineStr"/>
+      <c r="M32" s="60" t="inlineStr">
         <is>
           <t>max 30</t>
         </is>
       </c>
-      <c r="N32" s="52" t="inlineStr"/>
-      <c r="O32" s="52" t="inlineStr"/>
-      <c r="P32" s="52" t="inlineStr"/>
-      <c r="Q32" s="52" t="inlineStr"/>
-      <c r="R32" s="52" t="inlineStr">
+      <c r="N32" s="60" t="inlineStr"/>
+      <c r="O32" s="60" t="inlineStr"/>
+      <c r="P32" s="60" t="inlineStr"/>
+      <c r="Q32" s="60" t="inlineStr"/>
+      <c r="R32" s="60" t="inlineStr">
         <is>
           <t>¥29,500 （税込み¥32,450）</t>
         </is>
       </c>
-      <c r="S32" s="52" t="inlineStr">
+      <c r="S32" s="60" t="inlineStr">
         <is>
           <t>4571527863783</t>
         </is>
       </c>
-      <c r="T32" s="52" t="inlineStr"/>
-      <c r="U32" s="52" t="inlineStr"/>
-      <c r="V32" s="52" t="inlineStr"/>
-      <c r="W32" s="52" t="inlineStr"/>
-      <c r="X32" s="52" t="inlineStr"/>
-      <c r="Y32" s="52" t="inlineStr"/>
-      <c r="Z32" s="52" t="inlineStr">
+      <c r="T32" s="60" t="inlineStr"/>
+      <c r="U32" s="60" t="inlineStr"/>
+      <c r="V32" s="60" t="inlineStr"/>
+      <c r="W32" s="60" t="inlineStr"/>
+      <c r="X32" s="60" t="inlineStr"/>
+      <c r="Y32" s="60" t="inlineStr"/>
+      <c r="Z32" s="60" t="inlineStr">
         <is>
           <t>max4oz</t>
         </is>
       </c>
-      <c r="AA32" s="52" t="inlineStr"/>
-      <c r="AB32" s="52" t="inlineStr"/>
-      <c r="AC32" s="52" t="inlineStr"/>
-      <c r="AD32" s="52" t="inlineStr"/>
-      <c r="AE32" s="52" t="inlineStr"/>
-      <c r="AF32" s="52" t="inlineStr"/>
-      <c r="AG32" s="52" t="inlineStr"/>
-      <c r="AH32" s="52" t="inlineStr">
+      <c r="AA32" s="60" t="inlineStr"/>
+      <c r="AB32" s="60" t="inlineStr"/>
+      <c r="AC32" s="60" t="inlineStr"/>
+      <c r="AD32" s="60" t="inlineStr"/>
+      <c r="AE32" s="60" t="inlineStr"/>
+      <c r="AF32" s="60" t="inlineStr"/>
+      <c r="AG32" s="60" t="inlineStr"/>
+      <c r="AH32" s="60" t="inlineStr">
         <is>
           <t>6102XH 的描述明确是操作系 Big Bait 竿，优先服务 Big Bait、Swimbait、Crawler 和 Glide 系的操控与承接，不再套用普通 Texas/Jig 泛用逻辑。</t>
         </is>
       </c>
-      <c r="AI32" s="52" t="inlineStr">
+      <c r="AI32" s="60" t="inlineStr">
         <is>
           <t>Big Bait / Swimbait / Crawler Bait / Glide Bait</t>
         </is>
       </c>
-      <c r="AJ32" s="52" t="inlineStr"/>
-      <c r="AK32" s="52" t="inlineStr"/>
-      <c r="AL32" s="52" t="inlineStr"/>
-      <c r="AM32" s="52" t="inlineStr">
+      <c r="AJ32" s="60" t="inlineStr"/>
+      <c r="AK32" s="60" t="inlineStr"/>
+      <c r="AL32" s="60" t="inlineStr"/>
+      <c r="AM32" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖・开阔水・大型鱼标点 / big bait 操作</t>
         </is>
       </c>
-      <c r="AN32" s="52" t="inlineStr">
+      <c r="AN32" s="60" t="inlineStr">
         <is>
           <t>操作系大型饵专向</t>
         </is>
       </c>
-      <c r="AO32" s="52" t="inlineStr">
+      <c r="AO32" s="60" t="inlineStr">
         <is>
           <t>Big Bait、Swimbait、Crawler 和 Glide Bait 的抽停与承接是核心，适合需要明确操控大型饵而不是单纯重底操的玩家。</t>
         </is>
       </c>
-      <c r="AP32" s="52" t="inlineStr">
+      <c r="AP32" s="60" t="inlineStr">
         <is>
           <t>XHパワーの操作系ビックベイトロッド</t>
         </is>
       </c>
-      <c r="AQ32" s="52" t="inlineStr"/>
-      <c r="AR32" s="52" t="inlineStr"/>
+      <c r="AQ32" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR32" s="60" t="inlineStr"/>
+      <c r="AS32" s="60" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="52" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr">
         <is>
           <t>DSRD10031</t>
         </is>
       </c>
-      <c r="B33" s="52" t="inlineStr">
+      <c r="B33" s="60" t="inlineStr">
         <is>
           <t>DSR1003</t>
         </is>
       </c>
-      <c r="C33" s="52" t="inlineStr">
+      <c r="C33" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D33" s="52" t="inlineStr">
+      <c r="D33" s="60" t="inlineStr">
         <is>
           <t>DBTC-702H</t>
         </is>
       </c>
-      <c r="E33" s="52" t="inlineStr">
+      <c r="E33" s="60" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F33" s="52" t="inlineStr">
+      <c r="F33" s="60" t="inlineStr">
         <is>
           <t>7’0″</t>
         </is>
       </c>
-      <c r="G33" s="52" t="inlineStr">
+      <c r="G33" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H33" s="52" t="inlineStr"/>
-      <c r="I33" s="52" t="inlineStr"/>
-      <c r="J33" s="52" t="inlineStr">
+      <c r="H33" s="60" t="inlineStr"/>
+      <c r="I33" s="60" t="inlineStr"/>
+      <c r="J33" s="60" t="inlineStr">
         <is>
           <t>128g</t>
         </is>
       </c>
-      <c r="K33" s="52" t="inlineStr"/>
-      <c r="L33" s="52" t="inlineStr"/>
-      <c r="M33" s="52" t="inlineStr">
+      <c r="K33" s="60" t="inlineStr"/>
+      <c r="L33" s="60" t="inlineStr"/>
+      <c r="M33" s="60" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N33" s="52" t="inlineStr"/>
-      <c r="O33" s="52" t="inlineStr"/>
-      <c r="P33" s="52" t="inlineStr"/>
-      <c r="Q33" s="52" t="inlineStr"/>
-      <c r="R33" s="52" t="inlineStr">
+      <c r="N33" s="60" t="inlineStr"/>
+      <c r="O33" s="60" t="inlineStr"/>
+      <c r="P33" s="60" t="inlineStr"/>
+      <c r="Q33" s="60" t="inlineStr"/>
+      <c r="R33" s="60" t="inlineStr">
         <is>
           <t>¥29,500 （税込み¥32,450）</t>
         </is>
       </c>
-      <c r="S33" s="52" t="inlineStr">
+      <c r="S33" s="60" t="inlineStr">
         <is>
           <t>4571527862601</t>
         </is>
       </c>
-      <c r="T33" s="52" t="inlineStr"/>
-      <c r="U33" s="52" t="inlineStr"/>
-      <c r="V33" s="52" t="inlineStr"/>
-      <c r="W33" s="52" t="inlineStr"/>
-      <c r="X33" s="52" t="inlineStr"/>
-      <c r="Y33" s="52" t="inlineStr"/>
-      <c r="Z33" s="52" t="inlineStr">
+      <c r="T33" s="60" t="inlineStr"/>
+      <c r="U33" s="60" t="inlineStr"/>
+      <c r="V33" s="60" t="inlineStr"/>
+      <c r="W33" s="60" t="inlineStr"/>
+      <c r="X33" s="60" t="inlineStr"/>
+      <c r="Y33" s="60" t="inlineStr"/>
+      <c r="Z33" s="60" t="inlineStr">
         <is>
           <t>3/16~1</t>
         </is>
       </c>
-      <c r="AA33" s="52" t="inlineStr"/>
-      <c r="AB33" s="52" t="inlineStr"/>
-      <c r="AC33" s="52" t="inlineStr"/>
-      <c r="AD33" s="52" t="inlineStr"/>
-      <c r="AE33" s="52" t="inlineStr"/>
-      <c r="AF33" s="52" t="inlineStr"/>
-      <c r="AG33" s="52" t="inlineStr"/>
-      <c r="AH33" s="52" t="inlineStr">
+      <c r="AA33" s="60" t="inlineStr"/>
+      <c r="AB33" s="60" t="inlineStr"/>
+      <c r="AC33" s="60" t="inlineStr"/>
+      <c r="AD33" s="60" t="inlineStr"/>
+      <c r="AE33" s="60" t="inlineStr"/>
+      <c r="AF33" s="60" t="inlineStr"/>
+      <c r="AG33" s="60" t="inlineStr"/>
+      <c r="AH33" s="60" t="inlineStr">
         <is>
           <t>702H 仅有 heavy super versatile 描述，按 H power 保守覆盖 Heavy Texas、Rubber Jig、Frog 与中大型移动饵；具体大型饵排序低于底操和 cover 用途。</t>
         </is>
       </c>
-      <c r="AI33" s="52" t="inlineStr">
+      <c r="AI33" s="60" t="inlineStr">
         <is>
           <t>Heavy Texas / Rubber Jig / Frog / Big Bait / Swimbait</t>
         </is>
       </c>
-      <c r="AJ33" s="52" t="inlineStr"/>
-      <c r="AK33" s="52" t="inlineStr"/>
-      <c r="AL33" s="52" t="inlineStr"/>
-      <c r="AM33" s="52" t="inlineStr">
+      <c r="AJ33" s="60" t="inlineStr"/>
+      <c r="AK33" s="60" t="inlineStr"/>
+      <c r="AL33" s="60" t="inlineStr"/>
+      <c r="AM33" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 重 cover・草区・大型饵补充搜索 / heavy versatile</t>
         </is>
       </c>
-      <c r="AN33" s="52" t="inlineStr">
+      <c r="AN33" s="60" t="inlineStr">
         <is>
           <t>强力 cover 与大型饵补充</t>
         </is>
       </c>
-      <c r="AO33" s="52" t="inlineStr">
+      <c r="AO33" s="60" t="inlineStr">
         <is>
           <t>Heavy Texas、Rubber Jig 和 Frog 是主要场景，Big Bait、Swimbait 属副线搜索；适合重线组和控鱼优先的玩家。</t>
         </is>
       </c>
-      <c r="AP33" s="52" t="inlineStr">
+      <c r="AP33" s="60" t="inlineStr">
         <is>
           <t>ヘビースーパーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ33" s="52" t="inlineStr"/>
-      <c r="AR33" s="52" t="inlineStr"/>
+      <c r="AQ33" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / 2ピース構造 / EVAグリップ / ジョイントマーカー</t>
+        </is>
+      </c>
+      <c r="AR33" s="60" t="inlineStr"/>
+      <c r="AS33" s="60" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="53" t="inlineStr">
+      <c r="A34" s="61" t="inlineStr">
         <is>
           <t>DSRD10032</t>
         </is>
       </c>
-      <c r="B34" s="53" t="inlineStr">
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t>DSR1004</t>
         </is>
       </c>
-      <c r="C34" s="53" t="inlineStr">
+      <c r="C34" s="61" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D34" s="53" t="inlineStr">
+      <c r="D34" s="61" t="inlineStr">
         <is>
           <t>DBTS-60XUL-S</t>
         </is>
       </c>
-      <c r="E34" s="53" t="inlineStr">
+      <c r="E34" s="61" t="inlineStr">
         <is>
           <t>XUL</t>
         </is>
       </c>
-      <c r="F34" s="53" t="inlineStr">
+      <c r="F34" s="61" t="inlineStr">
         <is>
           <t>6’0″</t>
         </is>
       </c>
-      <c r="G34" s="53" t="inlineStr">
+      <c r="G34" s="61" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H34" s="53" t="inlineStr"/>
-      <c r="I34" s="53" t="inlineStr"/>
-      <c r="J34" s="53" t="inlineStr">
+      <c r="H34" s="61" t="inlineStr"/>
+      <c r="I34" s="61" t="inlineStr"/>
+      <c r="J34" s="61" t="inlineStr">
         <is>
           <t>72g</t>
         </is>
       </c>
-      <c r="K34" s="53" t="inlineStr"/>
-      <c r="L34" s="53" t="inlineStr"/>
-      <c r="M34" s="53" t="inlineStr">
+      <c r="K34" s="61" t="inlineStr"/>
+      <c r="L34" s="61" t="inlineStr"/>
+      <c r="M34" s="61" t="inlineStr">
         <is>
           <t>2~5</t>
         </is>
       </c>
-      <c r="N34" s="53" t="inlineStr"/>
-      <c r="O34" s="53" t="inlineStr"/>
-      <c r="P34" s="53" t="inlineStr"/>
-      <c r="Q34" s="53" t="inlineStr"/>
-      <c r="R34" s="53" t="inlineStr">
+      <c r="N34" s="61" t="inlineStr"/>
+      <c r="O34" s="61" t="inlineStr"/>
+      <c r="P34" s="61" t="inlineStr"/>
+      <c r="Q34" s="61" t="inlineStr"/>
+      <c r="R34" s="61" t="inlineStr">
         <is>
           <t>¥39,500 （税込み¥43,450）</t>
         </is>
       </c>
-      <c r="S34" s="53" t="inlineStr">
+      <c r="S34" s="61" t="inlineStr">
         <is>
           <t>4571527862106</t>
         </is>
       </c>
-      <c r="T34" s="53" t="inlineStr"/>
-      <c r="U34" s="53" t="inlineStr"/>
-      <c r="V34" s="53" t="inlineStr"/>
-      <c r="W34" s="53" t="inlineStr"/>
-      <c r="X34" s="53" t="inlineStr"/>
-      <c r="Y34" s="53" t="inlineStr"/>
-      <c r="Z34" s="53" t="inlineStr">
+      <c r="T34" s="61" t="inlineStr"/>
+      <c r="U34" s="61" t="inlineStr"/>
+      <c r="V34" s="61" t="inlineStr"/>
+      <c r="W34" s="61" t="inlineStr"/>
+      <c r="X34" s="61" t="inlineStr"/>
+      <c r="Y34" s="61" t="inlineStr"/>
+      <c r="Z34" s="61" t="inlineStr">
         <is>
           <t>1/48~1/8</t>
         </is>
       </c>
-      <c r="AA34" s="53" t="inlineStr"/>
-      <c r="AB34" s="53" t="inlineStr"/>
-      <c r="AC34" s="53" t="inlineStr"/>
-      <c r="AD34" s="53" t="inlineStr"/>
-      <c r="AE34" s="53" t="inlineStr"/>
-      <c r="AF34" s="53" t="inlineStr"/>
-      <c r="AG34" s="53" t="inlineStr">
+      <c r="AA34" s="61" t="inlineStr"/>
+      <c r="AB34" s="61" t="inlineStr"/>
+      <c r="AC34" s="61" t="inlineStr"/>
+      <c r="AD34" s="61" t="inlineStr"/>
+      <c r="AE34" s="61" t="inlineStr"/>
+      <c r="AF34" s="61" t="inlineStr"/>
+      <c r="AG34" s="61" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH34" s="53" t="inlineStr">
+      <c r="AH34" s="61" t="inlineStr">
         <is>
           <t>60XUL-S 是 10th ultimate finesse 的短尺 XUL solid，适合 Down Shot、Neko、Hover Strolling 和轻 No Sinker；强调极轻饵控制和短咬承接。</t>
         </is>
       </c>
-      <c r="AI34" s="53" t="inlineStr">
+      <c r="AI34" s="61" t="inlineStr">
         <is>
           <t>Down Shot / Neko Rig / Hover Strolling / No Sinker</t>
         </is>
       </c>
-      <c r="AJ34" s="53" t="inlineStr"/>
-      <c r="AK34" s="53" t="inlineStr"/>
-      <c r="AL34" s="53" t="inlineStr"/>
-      <c r="AM34" s="53" t="inlineStr">
+      <c r="AJ34" s="61" t="inlineStr"/>
+      <c r="AK34" s="61" t="inlineStr"/>
+      <c r="AL34" s="61" t="inlineStr"/>
+      <c r="AM34" s="61" t="inlineStr">
         <is>
           <t>淡水 Bass / 极高压近岸・清水 / ultimate finesse</t>
         </is>
       </c>
-      <c r="AN34" s="53" t="inlineStr">
+      <c r="AN34" s="61" t="inlineStr">
         <is>
           <t>短尺 XUL 食わせ finesse</t>
         </is>
       </c>
-      <c r="AO34" s="53" t="inlineStr">
+      <c r="AO34" s="61" t="inlineStr">
         <is>
           <t>Down Shot、Neko、Hover Strolling 和轻 No Sinker 更容易做细节动作，适合轻咬口多、鱼不愿追饵的场景。</t>
         </is>
       </c>
-      <c r="AP34" s="53" t="inlineStr">
+      <c r="AP34" s="61" t="inlineStr">
         <is>
           <t>BLUE TREK 10th Anniversary Model 10th Anniversary Model DSTYLE創業10周年に相応しい究極のフィネスロッドモデル。</t>
         </is>
       </c>
-      <c r="AQ34" s="53" t="inlineStr"/>
-      <c r="AR34" s="53" t="inlineStr"/>
+      <c r="AQ34" s="61" t="inlineStr">
+        <is>
+          <t>XULソリッドティップ / ナノマテリアル配合BLUE TREKブランクス / 高弾性ブランクス / チタンSiCガイド / カラースレッド</t>
+        </is>
+      </c>
+      <c r="AR34" s="61" t="inlineStr"/>
+      <c r="AS34" s="61" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="53" t="inlineStr">
+      <c r="A35" s="61" t="inlineStr">
         <is>
           <t>DSRD10033</t>
         </is>
       </c>
-      <c r="B35" s="53" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>DSR1004</t>
         </is>
       </c>
-      <c r="C35" s="53" t="inlineStr">
+      <c r="C35" s="61" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D35" s="53" t="inlineStr">
+      <c r="D35" s="61" t="inlineStr">
         <is>
           <t>DBTS-67UL-S</t>
         </is>
       </c>
-      <c r="E35" s="53" t="inlineStr">
+      <c r="E35" s="61" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F35" s="53" t="inlineStr">
+      <c r="F35" s="61" t="inlineStr">
         <is>
           <t>6’7″</t>
         </is>
       </c>
-      <c r="G35" s="53" t="inlineStr">
+      <c r="G35" s="61" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H35" s="53" t="inlineStr"/>
-      <c r="I35" s="53" t="inlineStr"/>
-      <c r="J35" s="53" t="inlineStr">
+      <c r="H35" s="61" t="inlineStr"/>
+      <c r="I35" s="61" t="inlineStr"/>
+      <c r="J35" s="61" t="inlineStr">
         <is>
           <t>78g</t>
         </is>
       </c>
-      <c r="K35" s="53" t="inlineStr"/>
-      <c r="L35" s="53" t="inlineStr"/>
-      <c r="M35" s="53" t="inlineStr">
+      <c r="K35" s="61" t="inlineStr"/>
+      <c r="L35" s="61" t="inlineStr"/>
+      <c r="M35" s="61" t="inlineStr">
         <is>
           <t>2~5</t>
         </is>
       </c>
-      <c r="N35" s="53" t="inlineStr"/>
-      <c r="O35" s="53" t="inlineStr"/>
-      <c r="P35" s="53" t="inlineStr"/>
-      <c r="Q35" s="53" t="inlineStr"/>
-      <c r="R35" s="53" t="inlineStr">
+      <c r="N35" s="61" t="inlineStr"/>
+      <c r="O35" s="61" t="inlineStr"/>
+      <c r="P35" s="61" t="inlineStr"/>
+      <c r="Q35" s="61" t="inlineStr"/>
+      <c r="R35" s="61" t="inlineStr">
         <is>
           <t>¥39,500 （税込み¥43,450）</t>
         </is>
       </c>
-      <c r="S35" s="53" t="inlineStr">
+      <c r="S35" s="61" t="inlineStr">
         <is>
           <t>4571527862113</t>
         </is>
       </c>
-      <c r="T35" s="53" t="inlineStr"/>
-      <c r="U35" s="53" t="inlineStr"/>
-      <c r="V35" s="53" t="inlineStr"/>
-      <c r="W35" s="53" t="inlineStr"/>
-      <c r="X35" s="53" t="inlineStr"/>
-      <c r="Y35" s="53" t="inlineStr"/>
-      <c r="Z35" s="53" t="inlineStr">
+      <c r="T35" s="61" t="inlineStr"/>
+      <c r="U35" s="61" t="inlineStr"/>
+      <c r="V35" s="61" t="inlineStr"/>
+      <c r="W35" s="61" t="inlineStr"/>
+      <c r="X35" s="61" t="inlineStr"/>
+      <c r="Y35" s="61" t="inlineStr"/>
+      <c r="Z35" s="61" t="inlineStr">
         <is>
           <t>1/48~1/8</t>
         </is>
       </c>
-      <c r="AA35" s="53" t="inlineStr"/>
-      <c r="AB35" s="53" t="inlineStr"/>
-      <c r="AC35" s="53" t="inlineStr"/>
-      <c r="AD35" s="53" t="inlineStr"/>
-      <c r="AE35" s="53" t="inlineStr"/>
-      <c r="AF35" s="53" t="inlineStr"/>
-      <c r="AG35" s="53" t="inlineStr">
+      <c r="AA35" s="61" t="inlineStr"/>
+      <c r="AB35" s="61" t="inlineStr"/>
+      <c r="AC35" s="61" t="inlineStr"/>
+      <c r="AD35" s="61" t="inlineStr"/>
+      <c r="AE35" s="61" t="inlineStr"/>
+      <c r="AF35" s="61" t="inlineStr"/>
+      <c r="AG35" s="61" t="inlineStr">
         <is>
           <t>鈦框 SiC 導環：降低前端重量，細線操作與咬口回饋更清楚</t>
         </is>
       </c>
-      <c r="AH35" s="53" t="inlineStr">
+      <c r="AH35" s="61" t="inlineStr">
         <is>
           <t>67UL-S 是 10th 长尺 finesse，Light Carolina 与长 leader Down Shot 放首位，No Sinker 和 I-shaped Plug 用于需要距离和弱波动搜索的场景。</t>
         </is>
       </c>
-      <c r="AI35" s="53" t="inlineStr">
+      <c r="AI35" s="61" t="inlineStr">
         <is>
           <t>Light Carolina Rig / Long Leader Down Shot / No Sinker / I-shaped Plug</t>
         </is>
       </c>
-      <c r="AJ35" s="53" t="inlineStr"/>
-      <c r="AK35" s="53" t="inlineStr"/>
-      <c r="AL35" s="53" t="inlineStr"/>
-      <c r="AM35" s="53" t="inlineStr">
+      <c r="AJ35" s="61" t="inlineStr"/>
+      <c r="AK35" s="61" t="inlineStr"/>
+      <c r="AL35" s="61" t="inlineStr"/>
+      <c r="AM35" s="61" t="inlineStr">
         <is>
           <t>淡水 Bass / 开阔水远投・缓坡 / light Carolina 与弱波动搜索</t>
         </is>
       </c>
-      <c r="AN35" s="53" t="inlineStr">
+      <c r="AN35" s="61" t="inlineStr">
         <is>
           <t>长尺 UL 远投 finesse</t>
         </is>
       </c>
-      <c r="AO35" s="53" t="inlineStr">
+      <c r="AO35" s="61" t="inlineStr">
         <is>
           <t>Light Carolina 和长 leader Down Shot 适合远处慢拖，No Sinker 与 I-shaped Plug 用来处理清水弱波动鱼。</t>
         </is>
       </c>
-      <c r="AP35" s="53" t="inlineStr">
+      <c r="AP35" s="61" t="inlineStr">
         <is>
           <t>BLUE TREK 10th Anniversary Model 10th Anniversary Model DSTYLE創業10周年に相応しい究極のフィネスロッドモデル。</t>
         </is>
       </c>
-      <c r="AQ35" s="53" t="inlineStr"/>
-      <c r="AR35" s="53" t="inlineStr"/>
+      <c r="AQ35" s="61" t="inlineStr">
+        <is>
+          <t>ULソリッドティップ / ナノマテリアル配合BLUE TREKブランクス / 高弾性ブランクス / チタンSiCガイド / カラースレッド</t>
+        </is>
+      </c>
+      <c r="AR35" s="61" t="inlineStr"/>
+      <c r="AS35" s="61" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="52" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr">
         <is>
           <t>DSRD10034</t>
         </is>
       </c>
-      <c r="B36" s="52" t="inlineStr">
+      <c r="B36" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C36" s="52" t="inlineStr">
+      <c r="C36" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D36" s="52" t="inlineStr">
+      <c r="D36" s="60" t="inlineStr">
         <is>
           <t>DBTS-60UL-S</t>
         </is>
       </c>
-      <c r="E36" s="52" t="inlineStr">
+      <c r="E36" s="60" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F36" s="52" t="inlineStr">
+      <c r="F36" s="60" t="inlineStr">
         <is>
           <t>6’0″</t>
         </is>
       </c>
-      <c r="G36" s="52" t="inlineStr">
+      <c r="G36" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H36" s="52" t="inlineStr"/>
-      <c r="I36" s="52" t="inlineStr"/>
-      <c r="J36" s="52" t="inlineStr">
+      <c r="H36" s="60" t="inlineStr"/>
+      <c r="I36" s="60" t="inlineStr"/>
+      <c r="J36" s="60" t="inlineStr">
         <is>
           <t>78g</t>
         </is>
       </c>
-      <c r="K36" s="52" t="inlineStr"/>
-      <c r="L36" s="52" t="inlineStr"/>
-      <c r="M36" s="52" t="inlineStr">
+      <c r="K36" s="60" t="inlineStr"/>
+      <c r="L36" s="60" t="inlineStr"/>
+      <c r="M36" s="60" t="inlineStr">
         <is>
           <t>2~5</t>
         </is>
       </c>
-      <c r="N36" s="52" t="inlineStr"/>
-      <c r="O36" s="52" t="inlineStr"/>
-      <c r="P36" s="52" t="inlineStr"/>
-      <c r="Q36" s="52" t="inlineStr"/>
-      <c r="R36" s="52" t="inlineStr">
+      <c r="N36" s="60" t="inlineStr"/>
+      <c r="O36" s="60" t="inlineStr"/>
+      <c r="P36" s="60" t="inlineStr"/>
+      <c r="Q36" s="60" t="inlineStr"/>
+      <c r="R36" s="60" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S36" s="52" t="inlineStr">
+      <c r="S36" s="60" t="inlineStr">
         <is>
           <t>4580484756946</t>
         </is>
       </c>
-      <c r="T36" s="52" t="inlineStr"/>
-      <c r="U36" s="52" t="inlineStr"/>
-      <c r="V36" s="52" t="inlineStr"/>
-      <c r="W36" s="52" t="inlineStr"/>
-      <c r="X36" s="52" t="inlineStr"/>
-      <c r="Y36" s="52" t="inlineStr"/>
-      <c r="Z36" s="52" t="inlineStr">
+      <c r="T36" s="60" t="inlineStr"/>
+      <c r="U36" s="60" t="inlineStr"/>
+      <c r="V36" s="60" t="inlineStr"/>
+      <c r="W36" s="60" t="inlineStr"/>
+      <c r="X36" s="60" t="inlineStr"/>
+      <c r="Y36" s="60" t="inlineStr"/>
+      <c r="Z36" s="60" t="inlineStr">
         <is>
           <t>1/48～1/8</t>
         </is>
       </c>
-      <c r="AA36" s="52" t="inlineStr"/>
-      <c r="AB36" s="52" t="inlineStr"/>
-      <c r="AC36" s="52" t="inlineStr"/>
-      <c r="AD36" s="52" t="inlineStr"/>
-      <c r="AE36" s="52" t="inlineStr"/>
-      <c r="AF36" s="52" t="inlineStr"/>
-      <c r="AG36" s="52" t="inlineStr"/>
-      <c r="AH36" s="52" t="inlineStr">
+      <c r="AA36" s="60" t="inlineStr"/>
+      <c r="AB36" s="60" t="inlineStr"/>
+      <c r="AC36" s="60" t="inlineStr"/>
+      <c r="AD36" s="60" t="inlineStr"/>
+      <c r="AE36" s="60" t="inlineStr"/>
+      <c r="AF36" s="60" t="inlineStr"/>
+      <c r="AG36" s="60" t="inlineStr"/>
+      <c r="AH36" s="60" t="inlineStr">
         <is>
           <t>60UL-S 是 super finesse，适合高压短距用 Down Shot、Neko、No Sinker 和 Small Rubber Jig 抢一口；重点是轻量操控和不放过短咬。</t>
         </is>
       </c>
-      <c r="AI36" s="52" t="inlineStr">
+      <c r="AI36" s="60" t="inlineStr">
         <is>
           <t>Down Shot / Neko Rig / No Sinker / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ36" s="52" t="inlineStr"/>
-      <c r="AK36" s="52" t="inlineStr"/>
-      <c r="AL36" s="52" t="inlineStr"/>
-      <c r="AM36" s="52" t="inlineStr">
+      <c r="AJ36" s="60" t="inlineStr"/>
+      <c r="AK36" s="60" t="inlineStr"/>
+      <c r="AL36" s="60" t="inlineStr"/>
+      <c r="AM36" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压野池・近岸 cover 边 / super finesse</t>
         </is>
       </c>
-      <c r="AN36" s="52" t="inlineStr">
+      <c r="AN36" s="60" t="inlineStr">
         <is>
           <t>短距轻量食わせ</t>
         </is>
       </c>
-      <c r="AO36" s="52" t="inlineStr">
+      <c r="AO36" s="60" t="inlineStr">
         <is>
           <t>Down Shot、Neko、No Sinker 和 Small Rubber Jig 都是高压场常用组合，短尺让贴边落点和轻抖更好控制。</t>
         </is>
       </c>
-      <c r="AP36" s="52" t="inlineStr">
+      <c r="AP36" s="60" t="inlineStr">
         <is>
           <t>よりフィネスを簡単に。タフな状況でも１匹を逃さないスーパーフィネスロッド</t>
         </is>
       </c>
-      <c r="AQ36" s="52" t="inlineStr">
+      <c r="AQ36" s="60" t="inlineStr">
+        <is>
+          <t>ULパワーソリッドティップ / ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR36" s="60" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="AR36" s="52" t="inlineStr"/>
+      <c r="AS36" s="60" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="52" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>DSRD10035</t>
         </is>
       </c>
-      <c r="B37" s="52" t="inlineStr">
+      <c r="B37" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C37" s="52" t="inlineStr">
+      <c r="C37" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D37" s="52" t="inlineStr">
+      <c r="D37" s="60" t="inlineStr">
         <is>
           <t>DBTS-61UL+-S</t>
         </is>
       </c>
-      <c r="E37" s="52" t="inlineStr">
+      <c r="E37" s="60" t="inlineStr">
         <is>
           <t>UL+</t>
         </is>
       </c>
-      <c r="F37" s="52" t="inlineStr">
+      <c r="F37" s="60" t="inlineStr">
         <is>
           <t>6’1″</t>
         </is>
       </c>
-      <c r="G37" s="52" t="inlineStr">
+      <c r="G37" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H37" s="52" t="inlineStr"/>
-      <c r="I37" s="52" t="inlineStr"/>
-      <c r="J37" s="52" t="inlineStr">
+      <c r="H37" s="60" t="inlineStr"/>
+      <c r="I37" s="60" t="inlineStr"/>
+      <c r="J37" s="60" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="K37" s="52" t="inlineStr"/>
-      <c r="L37" s="52" t="inlineStr"/>
-      <c r="M37" s="52" t="inlineStr">
+      <c r="K37" s="60" t="inlineStr"/>
+      <c r="L37" s="60" t="inlineStr"/>
+      <c r="M37" s="60" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N37" s="52" t="inlineStr"/>
-      <c r="O37" s="52" t="inlineStr"/>
-      <c r="P37" s="52" t="inlineStr"/>
-      <c r="Q37" s="52" t="inlineStr"/>
-      <c r="R37" s="52" t="inlineStr">
+      <c r="N37" s="60" t="inlineStr"/>
+      <c r="O37" s="60" t="inlineStr"/>
+      <c r="P37" s="60" t="inlineStr"/>
+      <c r="Q37" s="60" t="inlineStr"/>
+      <c r="R37" s="60" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S37" s="52" t="inlineStr">
+      <c r="S37" s="60" t="inlineStr">
         <is>
           <t>4580484758339</t>
         </is>
       </c>
-      <c r="T37" s="52" t="inlineStr"/>
-      <c r="U37" s="52" t="inlineStr"/>
-      <c r="V37" s="52" t="inlineStr"/>
-      <c r="W37" s="52" t="inlineStr"/>
-      <c r="X37" s="52" t="inlineStr"/>
-      <c r="Y37" s="52" t="inlineStr"/>
-      <c r="Z37" s="52" t="inlineStr">
+      <c r="T37" s="60" t="inlineStr"/>
+      <c r="U37" s="60" t="inlineStr"/>
+      <c r="V37" s="60" t="inlineStr"/>
+      <c r="W37" s="60" t="inlineStr"/>
+      <c r="X37" s="60" t="inlineStr"/>
+      <c r="Y37" s="60" t="inlineStr"/>
+      <c r="Z37" s="60" t="inlineStr">
         <is>
           <t>1/32〜3/16</t>
         </is>
       </c>
-      <c r="AA37" s="52" t="inlineStr"/>
-      <c r="AB37" s="52" t="inlineStr"/>
-      <c r="AC37" s="52" t="inlineStr"/>
-      <c r="AD37" s="52" t="inlineStr"/>
-      <c r="AE37" s="52" t="inlineStr"/>
-      <c r="AF37" s="52" t="inlineStr"/>
-      <c r="AG37" s="52" t="inlineStr"/>
-      <c r="AH37" s="52" t="inlineStr">
+      <c r="AA37" s="60" t="inlineStr"/>
+      <c r="AB37" s="60" t="inlineStr"/>
+      <c r="AC37" s="60" t="inlineStr"/>
+      <c r="AD37" s="60" t="inlineStr"/>
+      <c r="AE37" s="60" t="inlineStr"/>
+      <c r="AF37" s="60" t="inlineStr"/>
+      <c r="AG37" s="60" t="inlineStr"/>
+      <c r="AH37" s="60" t="inlineStr">
         <is>
           <t>61UL+-S 是进化型 super finesse，UL+ solid 更适合轻量 Down Shot、Neko、Jighead 与 No Sinker；比普通 L power 更重视细节反馈。</t>
         </is>
       </c>
-      <c r="AI37" s="52" t="inlineStr">
+      <c r="AI37" s="60" t="inlineStr">
         <is>
           <t>Down Shot / Neko Rig / Jighead Rig / No Sinker</t>
         </is>
       </c>
-      <c r="AJ37" s="52" t="inlineStr"/>
-      <c r="AK37" s="52" t="inlineStr"/>
-      <c r="AL37" s="52" t="inlineStr"/>
-      <c r="AM37" s="52" t="inlineStr">
+      <c r="AJ37" s="60" t="inlineStr"/>
+      <c r="AK37" s="60" t="inlineStr"/>
+      <c r="AL37" s="60" t="inlineStr"/>
+      <c r="AM37" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 小型湖库・清水高压 / 轻量 finesse</t>
         </is>
       </c>
-      <c r="AN37" s="52" t="inlineStr">
+      <c r="AN37" s="60" t="inlineStr">
         <is>
           <t>UL+ 细线精细操作</t>
         </is>
       </c>
-      <c r="AO37" s="52" t="inlineStr">
+      <c r="AO37" s="60" t="inlineStr">
         <is>
           <t>Down Shot、Neko、Jighead、No Sinker 的轻量操作更稳，适合需要比 XUL 多一点支撑但仍重视细节反馈的玩家。</t>
         </is>
       </c>
-      <c r="AP37" s="52" t="inlineStr">
+      <c r="AP37" s="60" t="inlineStr">
         <is>
           <t>時を捉える事が出来る進化したスーパーフィネスモデル</t>
         </is>
       </c>
-      <c r="AQ37" s="52" t="inlineStr">
+      <c r="AQ37" s="60" t="inlineStr">
+        <is>
+          <t>ソリッドティップ / ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR37" s="60" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AR37" s="52" t="inlineStr"/>
+      <c r="AS37" s="60" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="52" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr">
         <is>
           <t>DSRD10036</t>
         </is>
       </c>
-      <c r="B38" s="52" t="inlineStr">
+      <c r="B38" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C38" s="52" t="inlineStr">
+      <c r="C38" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D38" s="52" t="inlineStr">
+      <c r="D38" s="60" t="inlineStr">
         <is>
           <t>DBTS-61L</t>
         </is>
       </c>
-      <c r="E38" s="52" t="inlineStr">
+      <c r="E38" s="60" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F38" s="52" t="inlineStr">
+      <c r="F38" s="60" t="inlineStr">
         <is>
           <t>6’1″</t>
         </is>
       </c>
-      <c r="G38" s="52" t="inlineStr">
+      <c r="G38" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H38" s="52" t="inlineStr"/>
-      <c r="I38" s="52" t="inlineStr"/>
-      <c r="J38" s="52" t="inlineStr">
+      <c r="H38" s="60" t="inlineStr"/>
+      <c r="I38" s="60" t="inlineStr"/>
+      <c r="J38" s="60" t="inlineStr">
         <is>
           <t>82g</t>
         </is>
       </c>
-      <c r="K38" s="52" t="inlineStr"/>
-      <c r="L38" s="52" t="inlineStr"/>
-      <c r="M38" s="52" t="inlineStr">
+      <c r="K38" s="60" t="inlineStr"/>
+      <c r="L38" s="60" t="inlineStr"/>
+      <c r="M38" s="60" t="inlineStr">
         <is>
           <t>2.5~8</t>
         </is>
       </c>
-      <c r="N38" s="52" t="inlineStr"/>
-      <c r="O38" s="52" t="inlineStr"/>
-      <c r="P38" s="52" t="inlineStr"/>
-      <c r="Q38" s="52" t="inlineStr"/>
-      <c r="R38" s="52" t="inlineStr">
+      <c r="N38" s="60" t="inlineStr"/>
+      <c r="O38" s="60" t="inlineStr"/>
+      <c r="P38" s="60" t="inlineStr"/>
+      <c r="Q38" s="60" t="inlineStr"/>
+      <c r="R38" s="60" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S38" s="52" t="inlineStr">
+      <c r="S38" s="60" t="inlineStr">
         <is>
           <t>4580484756953</t>
         </is>
       </c>
-      <c r="T38" s="52" t="inlineStr"/>
-      <c r="U38" s="52" t="inlineStr"/>
-      <c r="V38" s="52" t="inlineStr"/>
-      <c r="W38" s="52" t="inlineStr"/>
-      <c r="X38" s="52" t="inlineStr"/>
-      <c r="Y38" s="52" t="inlineStr"/>
-      <c r="Z38" s="52" t="inlineStr">
+      <c r="T38" s="60" t="inlineStr"/>
+      <c r="U38" s="60" t="inlineStr"/>
+      <c r="V38" s="60" t="inlineStr"/>
+      <c r="W38" s="60" t="inlineStr"/>
+      <c r="X38" s="60" t="inlineStr"/>
+      <c r="Y38" s="60" t="inlineStr"/>
+      <c r="Z38" s="60" t="inlineStr">
         <is>
           <t>1/32～1/4</t>
         </is>
       </c>
-      <c r="AA38" s="52" t="inlineStr"/>
-      <c r="AB38" s="52" t="inlineStr"/>
-      <c r="AC38" s="52" t="inlineStr"/>
-      <c r="AD38" s="52" t="inlineStr"/>
-      <c r="AE38" s="52" t="inlineStr"/>
-      <c r="AF38" s="52" t="inlineStr"/>
-      <c r="AG38" s="52" t="inlineStr"/>
-      <c r="AH38" s="52" t="inlineStr">
+      <c r="AA38" s="60" t="inlineStr"/>
+      <c r="AB38" s="60" t="inlineStr"/>
+      <c r="AC38" s="60" t="inlineStr"/>
+      <c r="AD38" s="60" t="inlineStr"/>
+      <c r="AE38" s="60" t="inlineStr"/>
+      <c r="AF38" s="60" t="inlineStr"/>
+      <c r="AG38" s="60" t="inlineStr"/>
+      <c r="AH38" s="60" t="inlineStr">
         <is>
           <t>61L 是 super all-round spinning，但白名单实钓明确支持 Neko；因此以 Neko、Down Shot、No Sinker 和 Small Rubber Jig 为主，小型 Plug 作为轻量搜索补充。</t>
         </is>
       </c>
-      <c r="AI38" s="52" t="inlineStr">
+      <c r="AI38" s="60" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Plug</t>
         </is>
       </c>
-      <c r="AJ38" s="52" t="inlineStr"/>
-      <c r="AK38" s="52" t="inlineStr"/>
-      <c r="AL38" s="52" t="inlineStr"/>
-      <c r="AM38" s="52" t="inlineStr">
+      <c r="AJ38" s="60" t="inlineStr"/>
+      <c r="AK38" s="60" t="inlineStr"/>
+      <c r="AL38" s="60" t="inlineStr"/>
+      <c r="AM38" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 水库・清水岸钓 / Neko 与细线 light finesse</t>
         </is>
       </c>
-      <c r="AN38" s="52" t="inlineStr">
+      <c r="AN38" s="60" t="inlineStr">
         <is>
           <t>Neko 主轴轻量泛用</t>
         </is>
       </c>
-      <c r="AO38" s="52" t="inlineStr">
+      <c r="AO38" s="60" t="inlineStr">
         <is>
           <t>Neko Rig 实战适配度高，Down Shot、No Sinker、Small Rubber Jig 和 Small Plug 能补齐食わせ到轻搜索的路线。</t>
         </is>
       </c>
-      <c r="AP38" s="52" t="inlineStr">
+      <c r="AP38" s="60" t="inlineStr">
         <is>
           <t>時を捉える事が出来るスーパーオールラウンドモデル</t>
         </is>
       </c>
-      <c r="AQ38" s="52" t="inlineStr">
+      <c r="AQ38" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR38" s="60" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AR38" s="52" t="inlineStr"/>
+      <c r="AS38" s="60" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="52" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>DSRD10037</t>
         </is>
       </c>
-      <c r="B39" s="52" t="inlineStr">
+      <c r="B39" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C39" s="52" t="inlineStr">
+      <c r="C39" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D39" s="52" t="inlineStr">
+      <c r="D39" s="60" t="inlineStr">
         <is>
           <t>DBTS-63UL-MIDSP</t>
         </is>
       </c>
-      <c r="E39" s="52" t="inlineStr">
+      <c r="E39" s="60" t="inlineStr">
         <is>
           <t>UL</t>
         </is>
       </c>
-      <c r="F39" s="52" t="inlineStr">
+      <c r="F39" s="60" t="inlineStr">
         <is>
           <t>6’3″</t>
         </is>
       </c>
-      <c r="G39" s="52" t="inlineStr">
+      <c r="G39" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H39" s="52" t="inlineStr"/>
-      <c r="I39" s="52" t="inlineStr"/>
-      <c r="J39" s="52" t="inlineStr">
+      <c r="H39" s="60" t="inlineStr"/>
+      <c r="I39" s="60" t="inlineStr"/>
+      <c r="J39" s="60" t="inlineStr">
         <is>
           <t>82g</t>
         </is>
       </c>
-      <c r="K39" s="52" t="inlineStr"/>
-      <c r="L39" s="52" t="inlineStr"/>
-      <c r="M39" s="52" t="inlineStr">
+      <c r="K39" s="60" t="inlineStr"/>
+      <c r="L39" s="60" t="inlineStr"/>
+      <c r="M39" s="60" t="inlineStr">
         <is>
           <t>2.5~6</t>
         </is>
       </c>
-      <c r="N39" s="52" t="inlineStr"/>
-      <c r="O39" s="52" t="inlineStr"/>
-      <c r="P39" s="52" t="inlineStr"/>
-      <c r="Q39" s="52" t="inlineStr"/>
-      <c r="R39" s="52" t="inlineStr">
+      <c r="N39" s="60" t="inlineStr"/>
+      <c r="O39" s="60" t="inlineStr"/>
+      <c r="P39" s="60" t="inlineStr"/>
+      <c r="Q39" s="60" t="inlineStr"/>
+      <c r="R39" s="60" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S39" s="52" t="inlineStr">
+      <c r="S39" s="60" t="inlineStr">
         <is>
           <t>4580484758346</t>
         </is>
       </c>
-      <c r="T39" s="52" t="inlineStr"/>
-      <c r="U39" s="52" t="inlineStr"/>
-      <c r="V39" s="52" t="inlineStr"/>
-      <c r="W39" s="52" t="inlineStr"/>
-      <c r="X39" s="52" t="inlineStr"/>
-      <c r="Y39" s="52" t="inlineStr"/>
-      <c r="Z39" s="52" t="inlineStr">
+      <c r="T39" s="60" t="inlineStr"/>
+      <c r="U39" s="60" t="inlineStr"/>
+      <c r="V39" s="60" t="inlineStr"/>
+      <c r="W39" s="60" t="inlineStr"/>
+      <c r="X39" s="60" t="inlineStr"/>
+      <c r="Y39" s="60" t="inlineStr"/>
+      <c r="Z39" s="60" t="inlineStr">
         <is>
           <t>1/32～3/16</t>
         </is>
       </c>
-      <c r="AA39" s="52" t="inlineStr"/>
-      <c r="AB39" s="52" t="inlineStr"/>
-      <c r="AC39" s="52" t="inlineStr"/>
-      <c r="AD39" s="52" t="inlineStr"/>
-      <c r="AE39" s="52" t="inlineStr"/>
-      <c r="AF39" s="52" t="inlineStr"/>
-      <c r="AG39" s="52" t="inlineStr"/>
-      <c r="AH39" s="52" t="inlineStr">
+      <c r="AA39" s="60" t="inlineStr"/>
+      <c r="AB39" s="60" t="inlineStr"/>
+      <c r="AC39" s="60" t="inlineStr"/>
+      <c r="AD39" s="60" t="inlineStr"/>
+      <c r="AE39" s="60" t="inlineStr"/>
+      <c r="AF39" s="60" t="inlineStr"/>
+      <c r="AG39" s="60" t="inlineStr"/>
+      <c r="AH39" s="60" t="inlineStr">
         <is>
           <t>63UL-MIDSP 明确是 mid-strolling rod，Jighead/Hover Strolling 优先，Down Shot 和 No Sinker 只作为同样需要线弧与轻抖的补充。</t>
         </is>
       </c>
-      <c r="AI39" s="52" t="inlineStr">
+      <c r="AI39" s="60" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / Hover Strolling / Down Shot / No Sinker</t>
         </is>
       </c>
-      <c r="AJ39" s="52" t="inlineStr"/>
-      <c r="AK39" s="52" t="inlineStr"/>
-      <c r="AL39" s="52" t="inlineStr"/>
-      <c r="AM39" s="52" t="inlineStr">
+      <c r="AJ39" s="60" t="inlineStr"/>
+      <c r="AK39" s="60" t="inlineStr"/>
+      <c r="AL39" s="60" t="inlineStr"/>
+      <c r="AM39" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 开放水・中层悬浮鱼 / mid strolling</t>
         </is>
       </c>
-      <c r="AN39" s="52" t="inlineStr">
+      <c r="AN39" s="60" t="inlineStr">
         <is>
           <t>轻量 Mid Strolling 专向</t>
         </is>
       </c>
-      <c r="AO39" s="52" t="inlineStr">
+      <c r="AO39" s="60" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead 和 Hover Strolling 是主轴，Down Shot、No Sinker 可按同样线弧和轻抖逻辑补充。</t>
         </is>
       </c>
-      <c r="AP39" s="52" t="inlineStr">
+      <c r="AP39" s="60" t="inlineStr">
         <is>
           <t>無双できるミッドストローリングロッド</t>
         </is>
       </c>
-      <c r="AQ39" s="52" t="inlineStr">
+      <c r="AQ39" s="60" t="inlineStr">
+        <is>
+          <t>ミドスト/ボトスト向けガイドセッティング / ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR39" s="60" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="AR39" s="52" t="inlineStr"/>
+      <c r="AS39" s="60" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="52" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>DSRD10038</t>
         </is>
       </c>
-      <c r="B40" s="52" t="inlineStr">
+      <c r="B40" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C40" s="52" t="inlineStr">
+      <c r="C40" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D40" s="52" t="inlineStr">
+      <c r="D40" s="60" t="inlineStr">
         <is>
           <t>DBTS-65L+</t>
         </is>
       </c>
-      <c r="E40" s="52" t="inlineStr">
+      <c r="E40" s="60" t="inlineStr">
         <is>
           <t>L+</t>
         </is>
       </c>
-      <c r="F40" s="52" t="inlineStr">
+      <c r="F40" s="60" t="inlineStr">
         <is>
           <t>6’5″</t>
         </is>
       </c>
-      <c r="G40" s="52" t="inlineStr">
+      <c r="G40" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H40" s="52" t="inlineStr"/>
-      <c r="I40" s="52" t="inlineStr"/>
-      <c r="J40" s="52" t="inlineStr">
+      <c r="H40" s="60" t="inlineStr"/>
+      <c r="I40" s="60" t="inlineStr"/>
+      <c r="J40" s="60" t="inlineStr">
         <is>
           <t>82g</t>
         </is>
       </c>
-      <c r="K40" s="52" t="inlineStr"/>
-      <c r="L40" s="52" t="inlineStr"/>
-      <c r="M40" s="52" t="inlineStr">
+      <c r="K40" s="60" t="inlineStr"/>
+      <c r="L40" s="60" t="inlineStr"/>
+      <c r="M40" s="60" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N40" s="52" t="inlineStr"/>
-      <c r="O40" s="52" t="inlineStr"/>
-      <c r="P40" s="52" t="inlineStr"/>
-      <c r="Q40" s="52" t="inlineStr"/>
-      <c r="R40" s="52" t="inlineStr">
+      <c r="N40" s="60" t="inlineStr"/>
+      <c r="O40" s="60" t="inlineStr"/>
+      <c r="P40" s="60" t="inlineStr"/>
+      <c r="Q40" s="60" t="inlineStr"/>
+      <c r="R40" s="60" t="inlineStr">
         <is>
           <t>¥28,000 （税込￥30,800）</t>
         </is>
       </c>
-      <c r="S40" s="52" t="inlineStr">
+      <c r="S40" s="60" t="inlineStr">
         <is>
           <t>4580484756960</t>
         </is>
       </c>
-      <c r="T40" s="52" t="inlineStr"/>
-      <c r="U40" s="52" t="inlineStr"/>
-      <c r="V40" s="52" t="inlineStr"/>
-      <c r="W40" s="52" t="inlineStr"/>
-      <c r="X40" s="52" t="inlineStr"/>
-      <c r="Y40" s="52" t="inlineStr"/>
-      <c r="Z40" s="52" t="inlineStr">
+      <c r="T40" s="60" t="inlineStr"/>
+      <c r="U40" s="60" t="inlineStr"/>
+      <c r="V40" s="60" t="inlineStr"/>
+      <c r="W40" s="60" t="inlineStr"/>
+      <c r="X40" s="60" t="inlineStr"/>
+      <c r="Y40" s="60" t="inlineStr"/>
+      <c r="Z40" s="60" t="inlineStr">
         <is>
           <t>1/32～1/4</t>
         </is>
       </c>
-      <c r="AA40" s="52" t="inlineStr"/>
-      <c r="AB40" s="52" t="inlineStr"/>
-      <c r="AC40" s="52" t="inlineStr"/>
-      <c r="AD40" s="52" t="inlineStr"/>
-      <c r="AE40" s="52" t="inlineStr"/>
-      <c r="AF40" s="52" t="inlineStr"/>
-      <c r="AG40" s="52" t="inlineStr"/>
-      <c r="AH40" s="52" t="inlineStr">
+      <c r="AA40" s="60" t="inlineStr"/>
+      <c r="AB40" s="60" t="inlineStr"/>
+      <c r="AC40" s="60" t="inlineStr"/>
+      <c r="AD40" s="60" t="inlineStr"/>
+      <c r="AE40" s="60" t="inlineStr"/>
+      <c r="AF40" s="60" t="inlineStr"/>
+      <c r="AG40" s="60" t="inlineStr"/>
+      <c r="AH40" s="60" t="inlineStr">
         <is>
           <t>65L+ 是兼具 long distance 和细致度的 light versatile，Neko、Down Shot、No Sinker 负责食わせ，Small Minnow 负责远处搜索。</t>
         </is>
       </c>
-      <c r="AI40" s="52" t="inlineStr">
+      <c r="AI40" s="60" t="inlineStr">
         <is>
           <t>Neko Rig / Down Shot / Small Minnow / No Sinker</t>
         </is>
       </c>
-      <c r="AJ40" s="52" t="inlineStr"/>
-      <c r="AK40" s="52" t="inlineStr"/>
-      <c r="AL40" s="52" t="inlineStr"/>
-      <c r="AM40" s="52" t="inlineStr">
+      <c r="AJ40" s="60" t="inlineStr"/>
+      <c r="AK40" s="60" t="inlineStr"/>
+      <c r="AL40" s="60" t="inlineStr"/>
+      <c r="AM40" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓远投・开阔水 / finesse 与 Small Minnow</t>
         </is>
       </c>
-      <c r="AN40" s="52" t="inlineStr">
+      <c r="AN40" s="60" t="inlineStr">
         <is>
           <t>远投轻量软硬饵泛用</t>
         </is>
       </c>
-      <c r="AO40" s="52" t="inlineStr">
+      <c r="AO40" s="60" t="inlineStr">
         <is>
           <t>Neko、Down Shot、No Sinker 用于食わせ，Small Minnow 用于远处搜索；L+ power 让轻量路线多一点距离和控鱼余量。</t>
         </is>
       </c>
-      <c r="AP40" s="52" t="inlineStr">
+      <c r="AP40" s="60" t="inlineStr">
         <is>
           <t>ロングディスタンスと繊細さを併せ持ったバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ40" s="52" t="inlineStr">
+      <c r="AQ40" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR40" s="60" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="AR40" s="52" t="inlineStr"/>
+      <c r="AS40" s="60" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="52" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>DSRD10039</t>
         </is>
       </c>
-      <c r="B41" s="52" t="inlineStr">
+      <c r="B41" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C41" s="52" t="inlineStr">
+      <c r="C41" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D41" s="52" t="inlineStr">
+      <c r="D41" s="60" t="inlineStr">
         <is>
           <t>DBTS-66ML-S-MIDSP</t>
         </is>
       </c>
-      <c r="E41" s="52" t="inlineStr">
+      <c r="E41" s="60" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F41" s="52" t="inlineStr">
+      <c r="F41" s="60" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G41" s="52" t="inlineStr">
+      <c r="G41" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H41" s="52" t="inlineStr"/>
-      <c r="I41" s="52" t="inlineStr"/>
-      <c r="J41" s="52" t="inlineStr">
+      <c r="H41" s="60" t="inlineStr"/>
+      <c r="I41" s="60" t="inlineStr"/>
+      <c r="J41" s="60" t="inlineStr">
         <is>
           <t>88g</t>
         </is>
       </c>
-      <c r="K41" s="52" t="inlineStr"/>
-      <c r="L41" s="52" t="inlineStr"/>
-      <c r="M41" s="52" t="inlineStr">
+      <c r="K41" s="60" t="inlineStr"/>
+      <c r="L41" s="60" t="inlineStr"/>
+      <c r="M41" s="60" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N41" s="52" t="inlineStr">
+      <c r="N41" s="60" t="inlineStr">
         <is>
           <t>0.4~1</t>
         </is>
       </c>
-      <c r="O41" s="52" t="inlineStr"/>
-      <c r="P41" s="52" t="inlineStr"/>
-      <c r="Q41" s="52" t="inlineStr"/>
-      <c r="R41" s="52" t="inlineStr">
+      <c r="O41" s="60" t="inlineStr"/>
+      <c r="P41" s="60" t="inlineStr"/>
+      <c r="Q41" s="60" t="inlineStr"/>
+      <c r="R41" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S41" s="52" t="inlineStr">
+      <c r="S41" s="60" t="inlineStr">
         <is>
           <t>4571527862120</t>
         </is>
       </c>
-      <c r="T41" s="52" t="inlineStr"/>
-      <c r="U41" s="52" t="inlineStr"/>
-      <c r="V41" s="52" t="inlineStr"/>
-      <c r="W41" s="52" t="inlineStr"/>
-      <c r="X41" s="52" t="inlineStr"/>
-      <c r="Y41" s="52" t="inlineStr"/>
-      <c r="Z41" s="52" t="inlineStr">
+      <c r="T41" s="60" t="inlineStr"/>
+      <c r="U41" s="60" t="inlineStr"/>
+      <c r="V41" s="60" t="inlineStr"/>
+      <c r="W41" s="60" t="inlineStr"/>
+      <c r="X41" s="60" t="inlineStr"/>
+      <c r="Y41" s="60" t="inlineStr"/>
+      <c r="Z41" s="60" t="inlineStr">
         <is>
           <t>1/32～1/4</t>
         </is>
       </c>
-      <c r="AA41" s="52" t="inlineStr"/>
-      <c r="AB41" s="52" t="inlineStr"/>
-      <c r="AC41" s="52" t="inlineStr"/>
-      <c r="AD41" s="52" t="inlineStr"/>
-      <c r="AE41" s="52" t="inlineStr"/>
-      <c r="AF41" s="52" t="inlineStr"/>
-      <c r="AG41" s="52" t="inlineStr"/>
-      <c r="AH41" s="52" t="inlineStr">
+      <c r="AA41" s="60" t="inlineStr"/>
+      <c r="AB41" s="60" t="inlineStr"/>
+      <c r="AC41" s="60" t="inlineStr"/>
+      <c r="AD41" s="60" t="inlineStr"/>
+      <c r="AE41" s="60" t="inlineStr"/>
+      <c r="AF41" s="60" t="inlineStr"/>
+      <c r="AG41" s="60" t="inlineStr"/>
+      <c r="AH41" s="60" t="inlineStr">
         <is>
           <t>66ML-S-MIDSP 以 mid-strolling 为主，白名单 No Sinker 实例可补强中层软饵操作；Small Plug 是远投轻搜索，不应盖过 mid-strolling 主轴。</t>
         </is>
       </c>
-      <c r="AI41" s="52" t="inlineStr">
+      <c r="AI41" s="60" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead / No Sinker / Hover Strolling / Small Plug</t>
         </is>
       </c>
-      <c r="AJ41" s="52" t="inlineStr"/>
-      <c r="AK41" s="52" t="inlineStr"/>
-      <c r="AL41" s="52" t="inlineStr"/>
-      <c r="AM41" s="52" t="inlineStr">
+      <c r="AJ41" s="60" t="inlineStr"/>
+      <c r="AK41" s="60" t="inlineStr"/>
+      <c r="AL41" s="60" t="inlineStr"/>
+      <c r="AM41" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 池・野池・开阔水 / mid strolling 与 No Sinker</t>
         </is>
       </c>
-      <c r="AN41" s="52" t="inlineStr">
+      <c r="AN41" s="60" t="inlineStr">
         <is>
           <t>ML solid 中层游动</t>
         </is>
       </c>
-      <c r="AO41" s="52" t="inlineStr">
+      <c r="AO41" s="60" t="inlineStr">
         <is>
           <t>Mid Strolling Jighead 是主线，No Sinker 和 Hover Strolling 能处理更弱波动的中层鱼，小 Plug 只作为轻搜索补充。</t>
         </is>
       </c>
-      <c r="AP41" s="52" t="inlineStr">
+      <c r="AP41" s="60" t="inlineStr">
         <is>
           <t>無双できるミッドストローリングロッド</t>
         </is>
       </c>
-      <c r="AQ41" s="52" t="inlineStr">
+      <c r="AQ41" s="60" t="inlineStr">
+        <is>
+          <t>ソリッドティップ / ミドスト/PE対応ガイドセッティング / ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR41" s="60" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR41" s="52" t="inlineStr"/>
+      <c r="AS41" s="60" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="52" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr">
         <is>
           <t>DSRD10040</t>
         </is>
       </c>
-      <c r="B42" s="52" t="inlineStr">
+      <c r="B42" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C42" s="52" t="inlineStr">
+      <c r="C42" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D42" s="52" t="inlineStr">
+      <c r="D42" s="60" t="inlineStr">
         <is>
           <t>DBTS-66M</t>
         </is>
       </c>
-      <c r="E42" s="52" t="inlineStr">
+      <c r="E42" s="60" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F42" s="52" t="inlineStr">
+      <c r="F42" s="60" t="inlineStr">
         <is>
           <t>6’6″</t>
         </is>
       </c>
-      <c r="G42" s="52" t="inlineStr">
+      <c r="G42" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H42" s="52" t="inlineStr"/>
-      <c r="I42" s="52" t="inlineStr"/>
-      <c r="J42" s="52" t="inlineStr">
+      <c r="H42" s="60" t="inlineStr"/>
+      <c r="I42" s="60" t="inlineStr"/>
+      <c r="J42" s="60" t="inlineStr">
         <is>
           <t>91g</t>
         </is>
       </c>
-      <c r="K42" s="52" t="inlineStr"/>
-      <c r="L42" s="52" t="inlineStr"/>
-      <c r="M42" s="52" t="inlineStr">
+      <c r="K42" s="60" t="inlineStr"/>
+      <c r="L42" s="60" t="inlineStr"/>
+      <c r="M42" s="60" t="inlineStr">
         <is>
           <t>4~8</t>
         </is>
       </c>
-      <c r="N42" s="52" t="inlineStr">
+      <c r="N42" s="60" t="inlineStr">
         <is>
           <t>0.6~1.5</t>
         </is>
       </c>
-      <c r="O42" s="52" t="inlineStr"/>
-      <c r="P42" s="52" t="inlineStr"/>
-      <c r="Q42" s="52" t="inlineStr"/>
-      <c r="R42" s="52" t="inlineStr">
+      <c r="O42" s="60" t="inlineStr"/>
+      <c r="P42" s="60" t="inlineStr"/>
+      <c r="Q42" s="60" t="inlineStr"/>
+      <c r="R42" s="60" t="inlineStr">
         <is>
           <t>¥28,500 （税込￥31,350）</t>
         </is>
       </c>
-      <c r="S42" s="52" t="inlineStr">
+      <c r="S42" s="60" t="inlineStr">
         <is>
           <t>4580484756977</t>
         </is>
       </c>
-      <c r="T42" s="52" t="inlineStr"/>
-      <c r="U42" s="52" t="inlineStr"/>
-      <c r="V42" s="52" t="inlineStr"/>
-      <c r="W42" s="52" t="inlineStr"/>
-      <c r="X42" s="52" t="inlineStr"/>
-      <c r="Y42" s="52" t="inlineStr"/>
-      <c r="Z42" s="52" t="inlineStr">
+      <c r="T42" s="60" t="inlineStr"/>
+      <c r="U42" s="60" t="inlineStr"/>
+      <c r="V42" s="60" t="inlineStr"/>
+      <c r="W42" s="60" t="inlineStr"/>
+      <c r="X42" s="60" t="inlineStr"/>
+      <c r="Y42" s="60" t="inlineStr"/>
+      <c r="Z42" s="60" t="inlineStr">
         <is>
           <t>1/16～3/8</t>
         </is>
       </c>
-      <c r="AA42" s="52" t="inlineStr"/>
-      <c r="AB42" s="52" t="inlineStr"/>
-      <c r="AC42" s="52" t="inlineStr"/>
-      <c r="AD42" s="52" t="inlineStr"/>
-      <c r="AE42" s="52" t="inlineStr"/>
-      <c r="AF42" s="52" t="inlineStr"/>
-      <c r="AG42" s="52" t="inlineStr"/>
-      <c r="AH42" s="52" t="inlineStr">
+      <c r="AA42" s="60" t="inlineStr"/>
+      <c r="AB42" s="60" t="inlineStr"/>
+      <c r="AC42" s="60" t="inlineStr"/>
+      <c r="AD42" s="60" t="inlineStr"/>
+      <c r="AE42" s="60" t="inlineStr"/>
+      <c r="AF42" s="60" t="inlineStr"/>
+      <c r="AG42" s="60" t="inlineStr"/>
+      <c r="AH42" s="60" t="inlineStr">
         <is>
           <t>66M 是 power finesse spin，重点是 PE 下的 Cover Neko、Small Rubber Jig 和偏重 No Sinker，把轻量精细推进到 cover 与远投场景。</t>
         </is>
       </c>
-      <c r="AI42" s="52" t="inlineStr">
+      <c r="AI42" s="60" t="inlineStr">
         <is>
           <t>Power Finesse / Cover Neko / Small Rubber Jig / No Sinker</t>
         </is>
       </c>
-      <c r="AJ42" s="52" t="inlineStr"/>
-      <c r="AK42" s="52" t="inlineStr"/>
-      <c r="AL42" s="52" t="inlineStr"/>
-      <c r="AM42" s="52" t="inlineStr">
+      <c r="AJ42" s="60" t="inlineStr"/>
+      <c r="AK42" s="60" t="inlineStr"/>
+      <c r="AL42" s="60" t="inlineStr"/>
+      <c r="AM42" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 边缘・远投点 / spinning power finesse</t>
         </is>
       </c>
-      <c r="AN42" s="52" t="inlineStr">
+      <c r="AN42" s="60" t="inlineStr">
         <is>
           <t>M power finesse spinning</t>
         </is>
       </c>
-      <c r="AO42" s="52" t="inlineStr">
+      <c r="AO42" s="60" t="inlineStr">
         <is>
           <t>Power Finesse、Cover Neko 和 Small Rubber Jig 的控鱼力比轻量 spinning 更充足，适合细线体系下处理更厚的 cover。</t>
         </is>
       </c>
-      <c r="AP42" s="52" t="inlineStr">
+      <c r="AP42" s="60" t="inlineStr">
         <is>
           <t>キャスタビリティーとパワーを追求したパワーフィネススピン</t>
         </is>
       </c>
-      <c r="AQ42" s="52" t="inlineStr">
+      <c r="AQ42" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR42" s="60" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="AR42" s="52" t="inlineStr"/>
+      <c r="AS42" s="60" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="52" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr">
         <is>
           <t>DSRD10041</t>
         </is>
       </c>
-      <c r="B43" s="52" t="inlineStr">
+      <c r="B43" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C43" s="52" t="inlineStr">
+      <c r="C43" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D43" s="52" t="inlineStr">
+      <c r="D43" s="60" t="inlineStr">
         <is>
           <t>DBTS-68H-S-PF</t>
         </is>
       </c>
-      <c r="E43" s="52" t="inlineStr">
+      <c r="E43" s="60" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F43" s="52" t="inlineStr">
+      <c r="F43" s="60" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G43" s="52" t="inlineStr">
+      <c r="G43" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H43" s="52" t="inlineStr"/>
-      <c r="I43" s="52" t="inlineStr"/>
-      <c r="J43" s="52" t="inlineStr">
+      <c r="H43" s="60" t="inlineStr"/>
+      <c r="I43" s="60" t="inlineStr"/>
+      <c r="J43" s="60" t="inlineStr">
         <is>
           <t>108g</t>
         </is>
       </c>
-      <c r="K43" s="52" t="inlineStr"/>
-      <c r="L43" s="52" t="inlineStr"/>
-      <c r="M43" s="52" t="inlineStr"/>
-      <c r="N43" s="52" t="inlineStr">
+      <c r="K43" s="60" t="inlineStr"/>
+      <c r="L43" s="60" t="inlineStr"/>
+      <c r="M43" s="60" t="inlineStr"/>
+      <c r="N43" s="60" t="inlineStr">
         <is>
           <t>MAX ~2.5</t>
         </is>
       </c>
-      <c r="O43" s="52" t="inlineStr"/>
-      <c r="P43" s="52" t="inlineStr"/>
-      <c r="Q43" s="52" t="inlineStr"/>
-      <c r="R43" s="52" t="inlineStr">
+      <c r="O43" s="60" t="inlineStr"/>
+      <c r="P43" s="60" t="inlineStr"/>
+      <c r="Q43" s="60" t="inlineStr"/>
+      <c r="R43" s="60" t="inlineStr">
         <is>
           <t>¥28,500 （税込￥31,350）</t>
         </is>
       </c>
-      <c r="S43" s="52" t="inlineStr">
+      <c r="S43" s="60" t="inlineStr">
         <is>
           <t>4580484758353</t>
         </is>
       </c>
-      <c r="T43" s="52" t="inlineStr"/>
-      <c r="U43" s="52" t="inlineStr"/>
-      <c r="V43" s="52" t="inlineStr"/>
-      <c r="W43" s="52" t="inlineStr"/>
-      <c r="X43" s="52" t="inlineStr"/>
-      <c r="Y43" s="52" t="inlineStr"/>
-      <c r="Z43" s="52" t="inlineStr">
+      <c r="T43" s="60" t="inlineStr"/>
+      <c r="U43" s="60" t="inlineStr"/>
+      <c r="V43" s="60" t="inlineStr"/>
+      <c r="W43" s="60" t="inlineStr"/>
+      <c r="X43" s="60" t="inlineStr"/>
+      <c r="Y43" s="60" t="inlineStr"/>
+      <c r="Z43" s="60" t="inlineStr">
         <is>
           <t>1/8～3/4</t>
         </is>
       </c>
-      <c r="AA43" s="52" t="inlineStr"/>
-      <c r="AB43" s="52" t="inlineStr"/>
-      <c r="AC43" s="52" t="inlineStr"/>
-      <c r="AD43" s="52" t="inlineStr"/>
-      <c r="AE43" s="52" t="inlineStr"/>
-      <c r="AF43" s="52" t="inlineStr"/>
-      <c r="AG43" s="52" t="inlineStr"/>
-      <c r="AH43" s="52" t="inlineStr">
+      <c r="AA43" s="60" t="inlineStr"/>
+      <c r="AB43" s="60" t="inlineStr"/>
+      <c r="AC43" s="60" t="inlineStr"/>
+      <c r="AD43" s="60" t="inlineStr"/>
+      <c r="AE43" s="60" t="inlineStr"/>
+      <c r="AF43" s="60" t="inlineStr"/>
+      <c r="AG43" s="60" t="inlineStr"/>
+      <c r="AH43" s="60" t="inlineStr">
         <is>
           <t>68H-S-PF 明确面向高压 cover power finesse，H power solid 负责把鱼从 cover 中带出；Cover Neko、Small Rubber Jig 和高比重 No Sinker 是主要用途。</t>
         </is>
       </c>
-      <c r="AI43" s="52" t="inlineStr">
+      <c r="AI43" s="60" t="inlineStr">
         <is>
           <t>Power Finesse / Cover Neko / Small Rubber Jig / High-density No Sinker</t>
         </is>
       </c>
-      <c r="AJ43" s="52" t="inlineStr"/>
-      <c r="AK43" s="52" t="inlineStr"/>
-      <c r="AL43" s="52" t="inlineStr"/>
-      <c r="AM43" s="52" t="inlineStr">
+      <c r="AJ43" s="60" t="inlineStr"/>
+      <c r="AK43" s="60" t="inlineStr"/>
+      <c r="AL43" s="60" t="inlineStr"/>
+      <c r="AM43" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 高压重 cover・草洞 / heavy power finesse</t>
         </is>
       </c>
-      <c r="AN43" s="52" t="inlineStr">
+      <c r="AN43" s="60" t="inlineStr">
         <is>
           <t>H solid power finesse</t>
         </is>
       </c>
-      <c r="AO43" s="52" t="inlineStr">
+      <c r="AO43" s="60" t="inlineStr">
         <is>
           <t>Cover Neko、Small Rubber Jig 和高比重 No Sinker 进 cover 后有足够竿身支撑，适合 PE 强行控鱼。</t>
         </is>
       </c>
-      <c r="AP43" s="52" t="inlineStr">
+      <c r="AP43" s="60" t="inlineStr">
         <is>
           <t>ハイプレッシャーカバーを侵略せよ！！パワーフィネスモデル</t>
         </is>
       </c>
-      <c r="AQ43" s="52" t="inlineStr">
+      <c r="AQ43" s="60" t="inlineStr">
+        <is>
+          <t>Hパワーソリッドティップ / PE対応ガイドセッティング / ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR43" s="60" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR43" s="52" t="inlineStr"/>
+      <c r="AS43" s="60" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="52" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr">
         <is>
           <t>DSRD10042</t>
         </is>
       </c>
-      <c r="B44" s="52" t="inlineStr">
+      <c r="B44" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C44" s="52" t="inlineStr">
+      <c r="C44" s="60" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D44" s="52" t="inlineStr">
+      <c r="D44" s="60" t="inlineStr">
         <is>
           <t>DBTS-610L-S</t>
         </is>
       </c>
-      <c r="E44" s="52" t="inlineStr">
+      <c r="E44" s="60" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F44" s="52" t="inlineStr">
+      <c r="F44" s="60" t="inlineStr">
         <is>
           <t>6’10”</t>
         </is>
       </c>
-      <c r="G44" s="52" t="inlineStr">
+      <c r="G44" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H44" s="52" t="inlineStr"/>
-      <c r="I44" s="52" t="inlineStr"/>
-      <c r="J44" s="52" t="inlineStr">
+      <c r="H44" s="60" t="inlineStr"/>
+      <c r="I44" s="60" t="inlineStr"/>
+      <c r="J44" s="60" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="K44" s="52" t="inlineStr"/>
-      <c r="L44" s="52" t="inlineStr"/>
-      <c r="M44" s="52" t="inlineStr">
+      <c r="K44" s="60" t="inlineStr"/>
+      <c r="L44" s="60" t="inlineStr"/>
+      <c r="M44" s="60" t="inlineStr">
         <is>
           <t>3~8</t>
         </is>
       </c>
-      <c r="N44" s="52" t="inlineStr">
+      <c r="N44" s="60" t="inlineStr">
         <is>
           <t>0.4~1</t>
         </is>
       </c>
-      <c r="O44" s="52" t="inlineStr"/>
-      <c r="P44" s="52" t="inlineStr"/>
-      <c r="Q44" s="52" t="inlineStr"/>
-      <c r="R44" s="52" t="inlineStr">
+      <c r="O44" s="60" t="inlineStr"/>
+      <c r="P44" s="60" t="inlineStr"/>
+      <c r="Q44" s="60" t="inlineStr"/>
+      <c r="R44" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S44" s="52" t="inlineStr">
+      <c r="S44" s="60" t="inlineStr">
         <is>
           <t>4571527860713</t>
         </is>
       </c>
-      <c r="T44" s="52" t="inlineStr"/>
-      <c r="U44" s="52" t="inlineStr"/>
-      <c r="V44" s="52" t="inlineStr"/>
-      <c r="W44" s="52" t="inlineStr"/>
-      <c r="X44" s="52" t="inlineStr"/>
-      <c r="Y44" s="52" t="inlineStr"/>
-      <c r="Z44" s="52" t="inlineStr">
+      <c r="T44" s="60" t="inlineStr"/>
+      <c r="U44" s="60" t="inlineStr"/>
+      <c r="V44" s="60" t="inlineStr"/>
+      <c r="W44" s="60" t="inlineStr"/>
+      <c r="X44" s="60" t="inlineStr"/>
+      <c r="Y44" s="60" t="inlineStr"/>
+      <c r="Z44" s="60" t="inlineStr">
         <is>
           <t>1/16～1/4</t>
         </is>
       </c>
-      <c r="AA44" s="52" t="inlineStr"/>
-      <c r="AB44" s="52" t="inlineStr"/>
-      <c r="AC44" s="52" t="inlineStr"/>
-      <c r="AD44" s="52" t="inlineStr"/>
-      <c r="AE44" s="52" t="inlineStr"/>
-      <c r="AF44" s="52" t="inlineStr"/>
-      <c r="AG44" s="52" t="inlineStr"/>
-      <c r="AH44" s="52" t="inlineStr">
+      <c r="AA44" s="60" t="inlineStr"/>
+      <c r="AB44" s="60" t="inlineStr"/>
+      <c r="AC44" s="60" t="inlineStr"/>
+      <c r="AD44" s="60" t="inlineStr"/>
+      <c r="AE44" s="60" t="inlineStr"/>
+      <c r="AF44" s="60" t="inlineStr"/>
+      <c r="AG44" s="60" t="inlineStr"/>
+      <c r="AH44" s="60" t="inlineStr">
         <is>
           <t>610L-S 是 long shooting special，白名单和描述都支持远投 light finesse 与表层/I-shaped plug；Neko 远投和 Small Rubber Jig 放在精细端。</t>
         </is>
       </c>
-      <c r="AI44" s="52" t="inlineStr">
+      <c r="AI44" s="60" t="inlineStr">
         <is>
           <t>Long Cast Neko Rig / I-shaped Plug / Surface Plug / Small Rubber Jig</t>
         </is>
       </c>
-      <c r="AJ44" s="52" t="inlineStr"/>
-      <c r="AK44" s="52" t="inlineStr"/>
-      <c r="AL44" s="52" t="inlineStr"/>
-      <c r="AM44" s="52" t="inlineStr">
+      <c r="AJ44" s="60" t="inlineStr"/>
+      <c r="AK44" s="60" t="inlineStr"/>
+      <c r="AL44" s="60" t="inlineStr"/>
+      <c r="AM44" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 岸钓远投・开放水・表层 / long shooting finesse</t>
         </is>
       </c>
-      <c r="AN44" s="52" t="inlineStr">
+      <c r="AN44" s="60" t="inlineStr">
         <is>
           <t>远投 Neko 与表层轻搜索</t>
         </is>
       </c>
-      <c r="AO44" s="52" t="inlineStr">
+      <c r="AO44" s="60" t="inlineStr">
         <is>
           <t>Long Cast Neko、I-shaped Plug、Surface Plug 和 Small Rubber Jig 都围绕距离展开，适合想把轻量路线送到更远标点的玩家。</t>
         </is>
       </c>
-      <c r="AP44" s="52" t="inlineStr">
+      <c r="AP44" s="60" t="inlineStr">
         <is>
           <t>ロングシューティングスペシャル</t>
         </is>
       </c>
-      <c r="AQ44" s="52" t="inlineStr">
+      <c r="AQ44" s="60" t="inlineStr">
+        <is>
+          <t>Lパワーソリッドティップ / PEライン仕様ガイド / ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR44" s="60" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="AR44" s="52" t="inlineStr"/>
+      <c r="AS44" s="60" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="52" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr">
         <is>
           <t>DSRD10043</t>
         </is>
       </c>
-      <c r="B45" s="52" t="inlineStr">
+      <c r="B45" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C45" s="52" t="inlineStr">
+      <c r="C45" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D45" s="52" t="inlineStr">
+      <c r="D45" s="60" t="inlineStr">
         <is>
           <t>DBTC-64ML-FM</t>
         </is>
       </c>
-      <c r="E45" s="52" t="inlineStr">
+      <c r="E45" s="60" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F45" s="52" t="inlineStr">
+      <c r="F45" s="60" t="inlineStr">
         <is>
           <t>6’4″</t>
         </is>
       </c>
-      <c r="G45" s="52" t="inlineStr">
+      <c r="G45" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H45" s="52" t="inlineStr"/>
-      <c r="I45" s="52" t="inlineStr"/>
-      <c r="J45" s="52" t="inlineStr">
+      <c r="H45" s="60" t="inlineStr"/>
+      <c r="I45" s="60" t="inlineStr"/>
+      <c r="J45" s="60" t="inlineStr">
         <is>
           <t>156g</t>
         </is>
       </c>
-      <c r="K45" s="52" t="inlineStr"/>
-      <c r="L45" s="52" t="inlineStr"/>
-      <c r="M45" s="52" t="inlineStr">
+      <c r="K45" s="60" t="inlineStr"/>
+      <c r="L45" s="60" t="inlineStr"/>
+      <c r="M45" s="60" t="inlineStr">
         <is>
           <t>７~16</t>
         </is>
       </c>
-      <c r="N45" s="52" t="inlineStr"/>
-      <c r="O45" s="52" t="inlineStr"/>
-      <c r="P45" s="52" t="inlineStr"/>
-      <c r="Q45" s="52" t="inlineStr"/>
-      <c r="R45" s="52" t="inlineStr">
+      <c r="N45" s="60" t="inlineStr"/>
+      <c r="O45" s="60" t="inlineStr"/>
+      <c r="P45" s="60" t="inlineStr"/>
+      <c r="Q45" s="60" t="inlineStr"/>
+      <c r="R45" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S45" s="52" t="inlineStr">
+      <c r="S45" s="60" t="inlineStr">
         <is>
           <t>4571527860737</t>
         </is>
       </c>
-      <c r="T45" s="52" t="inlineStr"/>
-      <c r="U45" s="52" t="inlineStr"/>
-      <c r="V45" s="52" t="inlineStr"/>
-      <c r="W45" s="52" t="inlineStr"/>
-      <c r="X45" s="52" t="inlineStr"/>
-      <c r="Y45" s="52" t="inlineStr"/>
-      <c r="Z45" s="52" t="inlineStr">
+      <c r="T45" s="60" t="inlineStr"/>
+      <c r="U45" s="60" t="inlineStr"/>
+      <c r="V45" s="60" t="inlineStr"/>
+      <c r="W45" s="60" t="inlineStr"/>
+      <c r="X45" s="60" t="inlineStr"/>
+      <c r="Y45" s="60" t="inlineStr"/>
+      <c r="Z45" s="60" t="inlineStr">
         <is>
           <t>1/16～1/4</t>
         </is>
       </c>
-      <c r="AA45" s="52" t="inlineStr"/>
-      <c r="AB45" s="52" t="inlineStr"/>
-      <c r="AC45" s="52" t="inlineStr"/>
-      <c r="AD45" s="52" t="inlineStr"/>
-      <c r="AE45" s="52" t="inlineStr"/>
-      <c r="AF45" s="52" t="inlineStr"/>
-      <c r="AG45" s="52" t="inlineStr"/>
-      <c r="AH45" s="52" t="inlineStr">
+      <c r="AA45" s="60" t="inlineStr"/>
+      <c r="AB45" s="60" t="inlineStr"/>
+      <c r="AC45" s="60" t="inlineStr"/>
+      <c r="AD45" s="60" t="inlineStr"/>
+      <c r="AE45" s="60" t="inlineStr"/>
+      <c r="AF45" s="60" t="inlineStr"/>
+      <c r="AG45" s="60" t="inlineStr"/>
+      <c r="AH45" s="60" t="inlineStr">
         <is>
           <t>64ML-FM 是 full-glass fast-moving 专用，Crankbait、Shad、Minnow 和 Topwater Plug 的连收、碰障碍与短咬吸收是核心，不应写成软饵底操。</t>
         </is>
       </c>
-      <c r="AI45" s="52" t="inlineStr">
+      <c r="AI45" s="60" t="inlineStr">
         <is>
           <t>Crankbait / Shad / Minnow / Topwater Plug</t>
         </is>
       </c>
-      <c r="AJ45" s="52" t="inlineStr"/>
-      <c r="AK45" s="52" t="inlineStr"/>
-      <c r="AL45" s="52" t="inlineStr"/>
-      <c r="AM45" s="52" t="inlineStr">
+      <c r="AJ45" s="60" t="inlineStr"/>
+      <c r="AK45" s="60" t="inlineStr"/>
+      <c r="AL45" s="60" t="inlineStr"/>
+      <c r="AM45" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 浅场・硬物边・护岸 / fast moving plug</t>
         </is>
       </c>
-      <c r="AN45" s="52" t="inlineStr">
+      <c r="AN45" s="60" t="inlineStr">
         <is>
           <t>Full-glass 卷物硬饵</t>
         </is>
       </c>
-      <c r="AO45" s="52" t="inlineStr">
+      <c r="AO45" s="60" t="inlineStr">
         <is>
           <t>Crankbait、Shad、Minnow、Topwater 连续收线时更容易维持泳姿，Full-glass 调性对碰硬物和短咬承接更宽容。</t>
         </is>
       </c>
-      <c r="AP45" s="52" t="inlineStr">
+      <c r="AP45" s="60" t="inlineStr">
         <is>
           <t>フルグラスブランク採用 ファストムービング専用モデル</t>
         </is>
       </c>
-      <c r="AQ45" s="52" t="inlineStr">
+      <c r="AQ45" s="60" t="inlineStr">
+        <is>
+          <t>フルグラスブランク / ストレートグリップ</t>
+        </is>
+      </c>
+      <c r="AR45" s="60" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="AR45" s="52" t="inlineStr"/>
+      <c r="AS45" s="60" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="52" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>DSRD10044</t>
         </is>
       </c>
-      <c r="B46" s="52" t="inlineStr">
+      <c r="B46" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C46" s="52" t="inlineStr">
+      <c r="C46" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D46" s="52" t="inlineStr">
+      <c r="D46" s="60" t="inlineStr">
         <is>
           <t>DBTC-65ML-FM</t>
         </is>
       </c>
-      <c r="E46" s="52" t="inlineStr">
+      <c r="E46" s="60" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F46" s="52" t="inlineStr">
+      <c r="F46" s="60" t="inlineStr">
         <is>
           <t>6’5″</t>
         </is>
       </c>
-      <c r="G46" s="52" t="inlineStr">
+      <c r="G46" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H46" s="52" t="inlineStr"/>
-      <c r="I46" s="52" t="inlineStr"/>
-      <c r="J46" s="52" t="inlineStr">
+      <c r="H46" s="60" t="inlineStr"/>
+      <c r="I46" s="60" t="inlineStr"/>
+      <c r="J46" s="60" t="inlineStr">
         <is>
           <t>117g</t>
         </is>
       </c>
-      <c r="K46" s="52" t="inlineStr"/>
-      <c r="L46" s="52" t="inlineStr"/>
-      <c r="M46" s="52" t="inlineStr">
+      <c r="K46" s="60" t="inlineStr"/>
+      <c r="L46" s="60" t="inlineStr"/>
+      <c r="M46" s="60" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N46" s="52" t="inlineStr"/>
-      <c r="O46" s="52" t="inlineStr"/>
-      <c r="P46" s="52" t="inlineStr"/>
-      <c r="Q46" s="52" t="inlineStr"/>
-      <c r="R46" s="52" t="inlineStr">
+      <c r="N46" s="60" t="inlineStr"/>
+      <c r="O46" s="60" t="inlineStr"/>
+      <c r="P46" s="60" t="inlineStr"/>
+      <c r="Q46" s="60" t="inlineStr"/>
+      <c r="R46" s="60" t="inlineStr">
         <is>
           <t>¥28,500 （税込￥31,350）</t>
         </is>
       </c>
-      <c r="S46" s="52" t="inlineStr">
+      <c r="S46" s="60" t="inlineStr">
         <is>
           <t>4580484756984</t>
         </is>
       </c>
-      <c r="T46" s="52" t="inlineStr"/>
-      <c r="U46" s="52" t="inlineStr"/>
-      <c r="V46" s="52" t="inlineStr"/>
-      <c r="W46" s="52" t="inlineStr"/>
-      <c r="X46" s="52" t="inlineStr"/>
-      <c r="Y46" s="52" t="inlineStr"/>
-      <c r="Z46" s="52" t="inlineStr">
+      <c r="T46" s="60" t="inlineStr"/>
+      <c r="U46" s="60" t="inlineStr"/>
+      <c r="V46" s="60" t="inlineStr"/>
+      <c r="W46" s="60" t="inlineStr"/>
+      <c r="X46" s="60" t="inlineStr"/>
+      <c r="Y46" s="60" t="inlineStr"/>
+      <c r="Z46" s="60" t="inlineStr">
         <is>
           <t>3/16～5/8</t>
         </is>
       </c>
-      <c r="AA46" s="52" t="inlineStr"/>
-      <c r="AB46" s="52" t="inlineStr"/>
-      <c r="AC46" s="52" t="inlineStr"/>
-      <c r="AD46" s="52" t="inlineStr"/>
-      <c r="AE46" s="52" t="inlineStr"/>
-      <c r="AF46" s="52" t="inlineStr"/>
-      <c r="AG46" s="52" t="inlineStr"/>
-      <c r="AH46" s="52" t="inlineStr">
+      <c r="AA46" s="60" t="inlineStr"/>
+      <c r="AB46" s="60" t="inlineStr"/>
+      <c r="AC46" s="60" t="inlineStr"/>
+      <c r="AD46" s="60" t="inlineStr"/>
+      <c r="AE46" s="60" t="inlineStr"/>
+      <c r="AF46" s="60" t="inlineStr"/>
+      <c r="AG46" s="60" t="inlineStr"/>
+      <c r="AH46" s="60" t="inlineStr">
         <is>
           <t>65ML-FM 是低弹性碳布 light-plugging special，适合 Minnow、Shad、轻量 Crankbait 和 Topwater 的控速与停顿；不是普通软硬泛用。</t>
         </is>
       </c>
-      <c r="AI46" s="52" t="inlineStr">
+      <c r="AI46" s="60" t="inlineStr">
         <is>
           <t>Minnow / Shad / Crankbait / Topwater Plug</t>
         </is>
       </c>
-      <c r="AJ46" s="52" t="inlineStr"/>
-      <c r="AK46" s="52" t="inlineStr"/>
-      <c r="AL46" s="52" t="inlineStr"/>
-      <c r="AM46" s="52" t="inlineStr">
+      <c r="AJ46" s="60" t="inlineStr"/>
+      <c r="AK46" s="60" t="inlineStr"/>
+      <c r="AL46" s="60" t="inlineStr"/>
+      <c r="AM46" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 小型河川・野池・清水浅场 / light plugging</t>
         </is>
       </c>
-      <c r="AN46" s="52" t="inlineStr">
+      <c r="AN46" s="60" t="inlineStr">
         <is>
           <t>轻硬饵 plug 专向</t>
         </is>
       </c>
-      <c r="AO46" s="52" t="inlineStr">
+      <c r="AO46" s="60" t="inlineStr">
         <is>
           <t>Minnow、Shad、轻 Crankbait 和 Topwater 的控速、停顿、twitch 更自然，适合用低弹性手感处理轻硬饵。</t>
         </is>
       </c>
-      <c r="AP46" s="52" t="inlineStr">
+      <c r="AP46" s="60" t="inlineStr">
         <is>
           <t>低弾性カーボンブランクス採用 ライトプラッキングスペシャル</t>
         </is>
       </c>
-      <c r="AQ46" s="52" t="inlineStr">
+      <c r="AQ46" s="60" t="inlineStr">
+        <is>
+          <t>BLUE TREK独自配合低弾性カーボンブランクス / ストレートグリップ</t>
+        </is>
+      </c>
+      <c r="AR46" s="60" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="AR46" s="52" t="inlineStr"/>
+      <c r="AS46" s="60" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="52" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr">
         <is>
           <t>DSRD10045</t>
         </is>
       </c>
-      <c r="B47" s="52" t="inlineStr">
+      <c r="B47" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C47" s="52" t="inlineStr">
+      <c r="C47" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D47" s="52" t="inlineStr">
+      <c r="D47" s="60" t="inlineStr">
         <is>
           <t>DBTC-65M+-PF</t>
         </is>
       </c>
-      <c r="E47" s="52" t="inlineStr">
+      <c r="E47" s="60" t="inlineStr">
         <is>
           <t>M+</t>
         </is>
       </c>
-      <c r="F47" s="52" t="inlineStr">
+      <c r="F47" s="60" t="inlineStr">
         <is>
           <t>6’5″</t>
         </is>
       </c>
-      <c r="G47" s="52" t="inlineStr">
+      <c r="G47" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H47" s="52" t="inlineStr"/>
-      <c r="I47" s="52" t="inlineStr"/>
-      <c r="J47" s="52" t="inlineStr">
+      <c r="H47" s="60" t="inlineStr"/>
+      <c r="I47" s="60" t="inlineStr"/>
+      <c r="J47" s="60" t="inlineStr">
         <is>
           <t>93g</t>
         </is>
       </c>
-      <c r="K47" s="52" t="inlineStr"/>
-      <c r="L47" s="52" t="inlineStr"/>
-      <c r="M47" s="52" t="inlineStr">
+      <c r="K47" s="60" t="inlineStr"/>
+      <c r="L47" s="60" t="inlineStr"/>
+      <c r="M47" s="60" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N47" s="52" t="inlineStr">
+      <c r="N47" s="60" t="inlineStr">
         <is>
           <t>0.8~2</t>
         </is>
       </c>
-      <c r="O47" s="52" t="inlineStr"/>
-      <c r="P47" s="52" t="inlineStr"/>
-      <c r="Q47" s="52" t="inlineStr"/>
-      <c r="R47" s="52" t="inlineStr">
+      <c r="O47" s="60" t="inlineStr"/>
+      <c r="P47" s="60" t="inlineStr"/>
+      <c r="Q47" s="60" t="inlineStr"/>
+      <c r="R47" s="60" t="inlineStr">
         <is>
           <t>¥28,500 （税込￥31,350）</t>
         </is>
       </c>
-      <c r="S47" s="52" t="inlineStr">
+      <c r="S47" s="60" t="inlineStr">
         <is>
           <t>4571527863578</t>
         </is>
       </c>
-      <c r="T47" s="52" t="inlineStr"/>
-      <c r="U47" s="52" t="inlineStr"/>
-      <c r="V47" s="52" t="inlineStr"/>
-      <c r="W47" s="52" t="inlineStr"/>
-      <c r="X47" s="52" t="inlineStr"/>
-      <c r="Y47" s="52" t="inlineStr"/>
-      <c r="Z47" s="52" t="inlineStr">
+      <c r="T47" s="60" t="inlineStr"/>
+      <c r="U47" s="60" t="inlineStr"/>
+      <c r="V47" s="60" t="inlineStr"/>
+      <c r="W47" s="60" t="inlineStr"/>
+      <c r="X47" s="60" t="inlineStr"/>
+      <c r="Y47" s="60" t="inlineStr"/>
+      <c r="Z47" s="60" t="inlineStr">
         <is>
           <t>1/8～5/8</t>
         </is>
       </c>
-      <c r="AA47" s="52" t="inlineStr"/>
-      <c r="AB47" s="52" t="inlineStr"/>
-      <c r="AC47" s="52" t="inlineStr"/>
-      <c r="AD47" s="52" t="inlineStr"/>
-      <c r="AE47" s="52" t="inlineStr"/>
-      <c r="AF47" s="52" t="inlineStr"/>
-      <c r="AG47" s="52" t="inlineStr"/>
-      <c r="AH47" s="52" t="inlineStr">
+      <c r="AA47" s="60" t="inlineStr"/>
+      <c r="AB47" s="60" t="inlineStr"/>
+      <c r="AC47" s="60" t="inlineStr"/>
+      <c r="AD47" s="60" t="inlineStr"/>
+      <c r="AE47" s="60" t="inlineStr"/>
+      <c r="AF47" s="60" t="inlineStr"/>
+      <c r="AG47" s="60" t="inlineStr"/>
+      <c r="AH47" s="60" t="inlineStr">
         <is>
           <t>65M+-PF 是 light-cover bait power finesse，PE 时以 Small Rubber Jig、Bait Neko 为主，换 fluorocarbon 后可转 Heavy Down Shot、Free Rig、Texas 和 Football。</t>
         </is>
       </c>
-      <c r="AI47" s="52" t="inlineStr">
+      <c r="AI47" s="60" t="inlineStr">
         <is>
           <t>Bait Power Finesse / Small Rubber Jig / Bait Neko / Heavy Down Shot / Free Rig / Texas Rig / Football Jig</t>
         </is>
       </c>
-      <c r="AJ47" s="52" t="inlineStr"/>
-      <c r="AK47" s="52" t="inlineStr"/>
-      <c r="AL47" s="52" t="inlineStr"/>
-      <c r="AM47" s="52" t="inlineStr">
+      <c r="AJ47" s="60" t="inlineStr"/>
+      <c r="AK47" s="60" t="inlineStr"/>
+      <c r="AL47" s="60" t="inlineStr"/>
+      <c r="AM47" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / light cover・沉木边・草洞 / bait power finesse</t>
         </is>
       </c>
-      <c r="AN47" s="52" t="inlineStr">
+      <c r="AN47" s="60" t="inlineStr">
         <is>
           <t>轻 cover bait power finesse</t>
         </is>
       </c>
-      <c r="AO47" s="52" t="inlineStr">
+      <c r="AO47" s="60" t="inlineStr">
         <is>
           <t>PE 时 Small Rubber Jig 和 Bait Neko 是主轴，换 fluorocarbon 后可用 Heavy Down Shot、Free Rig、Texas、Football 打底。</t>
         </is>
       </c>
-      <c r="AP47" s="52" t="inlineStr">
+      <c r="AP47" s="60" t="inlineStr">
         <is>
           <t>ライトカバー用ベイトパワーフィネスSPモデル</t>
         </is>
       </c>
-      <c r="AQ47" s="52" t="inlineStr">
+      <c r="AQ47" s="60" t="inlineStr">
+        <is>
+          <t>LDBガイド / パワーフィネスSPグリップ / ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR47" s="60" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="AR47" s="52" t="inlineStr"/>
+      <c r="AS47" s="60" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="52" t="inlineStr">
+      <c r="A48" s="60" t="inlineStr">
         <is>
           <t>DSRD10046</t>
         </is>
       </c>
-      <c r="B48" s="52" t="inlineStr">
+      <c r="B48" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C48" s="52" t="inlineStr">
+      <c r="C48" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D48" s="52" t="inlineStr">
+      <c r="D48" s="60" t="inlineStr">
         <is>
           <t>DBTC-67ML-BF</t>
         </is>
       </c>
-      <c r="E48" s="52" t="inlineStr">
+      <c r="E48" s="60" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="F48" s="52" t="inlineStr">
+      <c r="F48" s="60" t="inlineStr">
         <is>
           <t>6’7″</t>
         </is>
       </c>
-      <c r="G48" s="52" t="inlineStr">
+      <c r="G48" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H48" s="52" t="inlineStr"/>
-      <c r="I48" s="52" t="inlineStr"/>
-      <c r="J48" s="52" t="inlineStr">
+      <c r="H48" s="60" t="inlineStr"/>
+      <c r="I48" s="60" t="inlineStr"/>
+      <c r="J48" s="60" t="inlineStr">
         <is>
           <t>111g</t>
         </is>
       </c>
-      <c r="K48" s="52" t="inlineStr"/>
-      <c r="L48" s="52" t="inlineStr"/>
-      <c r="M48" s="52" t="inlineStr">
+      <c r="K48" s="60" t="inlineStr"/>
+      <c r="L48" s="60" t="inlineStr"/>
+      <c r="M48" s="60" t="inlineStr">
         <is>
           <t>6~12</t>
         </is>
       </c>
-      <c r="N48" s="52" t="inlineStr"/>
-      <c r="O48" s="52" t="inlineStr"/>
-      <c r="P48" s="52" t="inlineStr"/>
-      <c r="Q48" s="52" t="inlineStr"/>
-      <c r="R48" s="52" t="inlineStr">
+      <c r="N48" s="60" t="inlineStr"/>
+      <c r="O48" s="60" t="inlineStr"/>
+      <c r="P48" s="60" t="inlineStr"/>
+      <c r="Q48" s="60" t="inlineStr"/>
+      <c r="R48" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S48" s="52" t="inlineStr">
+      <c r="S48" s="60" t="inlineStr">
         <is>
           <t>4580484756991</t>
         </is>
       </c>
-      <c r="T48" s="52" t="inlineStr"/>
-      <c r="U48" s="52" t="inlineStr"/>
-      <c r="V48" s="52" t="inlineStr"/>
-      <c r="W48" s="52" t="inlineStr"/>
-      <c r="X48" s="52" t="inlineStr"/>
-      <c r="Y48" s="52" t="inlineStr"/>
-      <c r="Z48" s="52" t="inlineStr">
+      <c r="T48" s="60" t="inlineStr"/>
+      <c r="U48" s="60" t="inlineStr"/>
+      <c r="V48" s="60" t="inlineStr"/>
+      <c r="W48" s="60" t="inlineStr"/>
+      <c r="X48" s="60" t="inlineStr"/>
+      <c r="Y48" s="60" t="inlineStr"/>
+      <c r="Z48" s="60" t="inlineStr">
         <is>
           <t>1/16～1/4</t>
         </is>
       </c>
-      <c r="AA48" s="52" t="inlineStr"/>
-      <c r="AB48" s="52" t="inlineStr"/>
-      <c r="AC48" s="52" t="inlineStr"/>
-      <c r="AD48" s="52" t="inlineStr"/>
-      <c r="AE48" s="52" t="inlineStr"/>
-      <c r="AF48" s="52" t="inlineStr"/>
-      <c r="AG48" s="52" t="inlineStr"/>
-      <c r="AH48" s="52" t="inlineStr">
+      <c r="AA48" s="60" t="inlineStr"/>
+      <c r="AB48" s="60" t="inlineStr"/>
+      <c r="AC48" s="60" t="inlineStr"/>
+      <c r="AD48" s="60" t="inlineStr"/>
+      <c r="AE48" s="60" t="inlineStr"/>
+      <c r="AF48" s="60" t="inlineStr"/>
+      <c r="AG48" s="60" t="inlineStr"/>
+      <c r="AH48" s="60" t="inlineStr">
         <is>
           <t>67ML-BF 是进攻型 bait finesse，既能投 Small Plug 和小型 Spinnerbait 搜索，也能用 Small Rubber Jig、Neko、Down Shot 做精准软饵操作。</t>
         </is>
       </c>
-      <c r="AI48" s="52" t="inlineStr">
+      <c r="AI48" s="60" t="inlineStr">
         <is>
           <t>Bait Finesse Small Plug / Small Rubber Jig / Neko Rig / Down Shot / Small Spinnerbait</t>
         </is>
       </c>
-      <c r="AJ48" s="52" t="inlineStr"/>
-      <c r="AK48" s="52" t="inlineStr"/>
-      <c r="AL48" s="52" t="inlineStr"/>
-      <c r="AM48" s="52" t="inlineStr">
+      <c r="AJ48" s="60" t="inlineStr"/>
+      <c r="AK48" s="60" t="inlineStr"/>
+      <c r="AL48" s="60" t="inlineStr"/>
+      <c r="AM48" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 野池・护岸・轻 cover / 攻击型 BFS</t>
         </is>
       </c>
-      <c r="AN48" s="52" t="inlineStr">
+      <c r="AN48" s="60" t="inlineStr">
         <is>
           <t>进攻型 bait finesse</t>
         </is>
       </c>
-      <c r="AO48" s="52" t="inlineStr">
+      <c r="AO48" s="60" t="inlineStr">
         <is>
           <t>Small Plug 与 Small Spinnerbait 可快速搜索，Small Rubber Jig、Neko、Down Shot 可补精细打点，适合手返し很高的近中距离作钓。</t>
         </is>
       </c>
-      <c r="AP48" s="52" t="inlineStr">
+      <c r="AP48" s="60" t="inlineStr">
         <is>
           <t>攻めのベイトフィネスモデル</t>
         </is>
       </c>
-      <c r="AQ48" s="52" t="inlineStr">
+      <c r="AQ48" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR48" s="60" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="AR48" s="52" t="inlineStr"/>
+      <c r="AS48" s="60" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="52" t="inlineStr">
+      <c r="A49" s="60" t="inlineStr">
         <is>
           <t>DSRD10047</t>
         </is>
       </c>
-      <c r="B49" s="52" t="inlineStr">
+      <c r="B49" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C49" s="52" t="inlineStr">
+      <c r="C49" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D49" s="52" t="inlineStr">
+      <c r="D49" s="60" t="inlineStr">
         <is>
           <t>DBTC-68M</t>
         </is>
       </c>
-      <c r="E49" s="52" t="inlineStr">
+      <c r="E49" s="60" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F49" s="52" t="inlineStr">
+      <c r="F49" s="60" t="inlineStr">
         <is>
           <t>6’8″</t>
         </is>
       </c>
-      <c r="G49" s="52" t="inlineStr">
+      <c r="G49" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H49" s="52" t="inlineStr"/>
-      <c r="I49" s="52" t="inlineStr"/>
-      <c r="J49" s="52" t="inlineStr">
+      <c r="H49" s="60" t="inlineStr"/>
+      <c r="I49" s="60" t="inlineStr"/>
+      <c r="J49" s="60" t="inlineStr">
         <is>
           <t>108g</t>
         </is>
       </c>
-      <c r="K49" s="52" t="inlineStr"/>
-      <c r="L49" s="52" t="inlineStr"/>
-      <c r="M49" s="52" t="inlineStr">
+      <c r="K49" s="60" t="inlineStr"/>
+      <c r="L49" s="60" t="inlineStr"/>
+      <c r="M49" s="60" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N49" s="52" t="inlineStr"/>
-      <c r="O49" s="52" t="inlineStr"/>
-      <c r="P49" s="52" t="inlineStr"/>
-      <c r="Q49" s="52" t="inlineStr"/>
-      <c r="R49" s="52" t="inlineStr">
+      <c r="N49" s="60" t="inlineStr"/>
+      <c r="O49" s="60" t="inlineStr"/>
+      <c r="P49" s="60" t="inlineStr"/>
+      <c r="Q49" s="60" t="inlineStr"/>
+      <c r="R49" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S49" s="52" t="inlineStr">
+      <c r="S49" s="60" t="inlineStr">
         <is>
           <t>4580484757004</t>
         </is>
       </c>
-      <c r="T49" s="52" t="inlineStr"/>
-      <c r="U49" s="52" t="inlineStr"/>
-      <c r="V49" s="52" t="inlineStr"/>
-      <c r="W49" s="52" t="inlineStr"/>
-      <c r="X49" s="52" t="inlineStr"/>
-      <c r="Y49" s="52" t="inlineStr"/>
-      <c r="Z49" s="52" t="inlineStr">
+      <c r="T49" s="60" t="inlineStr"/>
+      <c r="U49" s="60" t="inlineStr"/>
+      <c r="V49" s="60" t="inlineStr"/>
+      <c r="W49" s="60" t="inlineStr"/>
+      <c r="X49" s="60" t="inlineStr"/>
+      <c r="Y49" s="60" t="inlineStr"/>
+      <c r="Z49" s="60" t="inlineStr">
         <is>
           <t>3/16～5/8</t>
         </is>
       </c>
-      <c r="AA49" s="52" t="inlineStr"/>
-      <c r="AB49" s="52" t="inlineStr"/>
-      <c r="AC49" s="52" t="inlineStr"/>
-      <c r="AD49" s="52" t="inlineStr"/>
-      <c r="AE49" s="52" t="inlineStr"/>
-      <c r="AF49" s="52" t="inlineStr"/>
-      <c r="AG49" s="52" t="inlineStr"/>
-      <c r="AH49" s="52" t="inlineStr">
+      <c r="AA49" s="60" t="inlineStr"/>
+      <c r="AB49" s="60" t="inlineStr"/>
+      <c r="AC49" s="60" t="inlineStr"/>
+      <c r="AD49" s="60" t="inlineStr"/>
+      <c r="AE49" s="60" t="inlineStr"/>
+      <c r="AF49" s="60" t="inlineStr"/>
+      <c r="AG49" s="60" t="inlineStr"/>
+      <c r="AH49" s="60" t="inlineStr">
         <is>
           <t>68M 官方为 super versatile，白名单实钓强化 Crankbait/Shad/Jerkbait 搜索端；Spinnerbait/Chatterbait 次之，Texas 作为软饵补充。</t>
         </is>
       </c>
-      <c r="AI49" s="52" t="inlineStr">
+      <c r="AI49" s="60" t="inlineStr">
         <is>
           <t>Crankbait / Shad / Jerkbait / Spinnerbait / Chatterbait / Texas Rig</t>
         </is>
       </c>
-      <c r="AJ49" s="52" t="inlineStr"/>
-      <c r="AK49" s="52" t="inlineStr"/>
-      <c r="AL49" s="52" t="inlineStr"/>
-      <c r="AM49" s="52" t="inlineStr">
+      <c r="AJ49" s="60" t="inlineStr"/>
+      <c r="AK49" s="60" t="inlineStr"/>
+      <c r="AL49" s="60" t="inlineStr"/>
+      <c r="AM49" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 湖泊・船钓・开阔水 / 中量硬饵搜索</t>
         </is>
       </c>
-      <c r="AN49" s="52" t="inlineStr">
+      <c r="AN49" s="60" t="inlineStr">
         <is>
           <t>硬饵搜索兼 bait versatile</t>
         </is>
       </c>
-      <c r="AO49" s="52" t="inlineStr">
+      <c r="AO49" s="60" t="inlineStr">
         <is>
           <t>Crankbait、Shad、Jerkbait 是更强项，Spinnerbait、Chatterbait 可扩展搜索，Texas 作为软饵补充而不是主轴。</t>
         </is>
       </c>
-      <c r="AP49" s="52" t="inlineStr">
+      <c r="AP49" s="60" t="inlineStr">
         <is>
           <t>スーパーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ49" s="52" t="inlineStr">
+      <c r="AQ49" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR49" s="60" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AR49" s="52" t="inlineStr"/>
+      <c r="AS49" s="60" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="52" t="inlineStr">
+      <c r="A50" s="60" t="inlineStr">
         <is>
           <t>DSRD10048</t>
         </is>
       </c>
-      <c r="B50" s="52" t="inlineStr">
+      <c r="B50" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C50" s="52" t="inlineStr">
+      <c r="C50" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D50" s="52" t="inlineStr">
+      <c r="D50" s="60" t="inlineStr">
         <is>
           <t>DBTC-610MH</t>
         </is>
       </c>
-      <c r="E50" s="52" t="inlineStr">
+      <c r="E50" s="60" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F50" s="52" t="inlineStr">
+      <c r="F50" s="60" t="inlineStr">
         <is>
           <t>6’10”</t>
         </is>
       </c>
-      <c r="G50" s="52" t="inlineStr">
+      <c r="G50" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H50" s="52" t="inlineStr"/>
-      <c r="I50" s="52" t="inlineStr"/>
-      <c r="J50" s="52" t="inlineStr">
+      <c r="H50" s="60" t="inlineStr"/>
+      <c r="I50" s="60" t="inlineStr"/>
+      <c r="J50" s="60" t="inlineStr">
         <is>
           <t>118g</t>
         </is>
       </c>
-      <c r="K50" s="52" t="inlineStr"/>
-      <c r="L50" s="52" t="inlineStr"/>
-      <c r="M50" s="52" t="inlineStr">
+      <c r="K50" s="60" t="inlineStr"/>
+      <c r="L50" s="60" t="inlineStr"/>
+      <c r="M50" s="60" t="inlineStr">
         <is>
           <t>8~20</t>
         </is>
       </c>
-      <c r="N50" s="52" t="inlineStr"/>
-      <c r="O50" s="52" t="inlineStr"/>
-      <c r="P50" s="52" t="inlineStr"/>
-      <c r="Q50" s="52" t="inlineStr"/>
-      <c r="R50" s="52" t="inlineStr">
+      <c r="N50" s="60" t="inlineStr"/>
+      <c r="O50" s="60" t="inlineStr"/>
+      <c r="P50" s="60" t="inlineStr"/>
+      <c r="Q50" s="60" t="inlineStr"/>
+      <c r="R50" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S50" s="52" t="inlineStr">
+      <c r="S50" s="60" t="inlineStr">
         <is>
           <t>4580484757011</t>
         </is>
       </c>
-      <c r="T50" s="52" t="inlineStr"/>
-      <c r="U50" s="52" t="inlineStr"/>
-      <c r="V50" s="52" t="inlineStr"/>
-      <c r="W50" s="52" t="inlineStr"/>
-      <c r="X50" s="52" t="inlineStr"/>
-      <c r="Y50" s="52" t="inlineStr"/>
-      <c r="Z50" s="52" t="inlineStr">
+      <c r="T50" s="60" t="inlineStr"/>
+      <c r="U50" s="60" t="inlineStr"/>
+      <c r="V50" s="60" t="inlineStr"/>
+      <c r="W50" s="60" t="inlineStr"/>
+      <c r="X50" s="60" t="inlineStr"/>
+      <c r="Y50" s="60" t="inlineStr"/>
+      <c r="Z50" s="60" t="inlineStr">
         <is>
           <t>3/16～3/4</t>
         </is>
       </c>
-      <c r="AA50" s="52" t="inlineStr"/>
-      <c r="AB50" s="52" t="inlineStr"/>
-      <c r="AC50" s="52" t="inlineStr"/>
-      <c r="AD50" s="52" t="inlineStr"/>
-      <c r="AE50" s="52" t="inlineStr"/>
-      <c r="AF50" s="52" t="inlineStr"/>
-      <c r="AG50" s="52" t="inlineStr"/>
-      <c r="AH50" s="52" t="inlineStr">
+      <c r="AA50" s="60" t="inlineStr"/>
+      <c r="AB50" s="60" t="inlineStr"/>
+      <c r="AC50" s="60" t="inlineStr"/>
+      <c r="AD50" s="60" t="inlineStr"/>
+      <c r="AE50" s="60" t="inlineStr"/>
+      <c r="AF50" s="60" t="inlineStr"/>
+      <c r="AG50" s="60" t="inlineStr"/>
+      <c r="AH50" s="60" t="inlineStr">
         <is>
           <t>610MH 官方是 middle versatile，白名单明确 bladed jig 实例，因此 Chatterbait 放首位；Spinnerbait 与 Crankbait 负责巻き，Texas/Rubber Jig 负责撃ち。</t>
         </is>
       </c>
-      <c r="AI50" s="52" t="inlineStr">
+      <c r="AI50" s="60" t="inlineStr">
         <is>
           <t>Chatterbait / Spinnerbait / Texas Rig / Rubber Jig / Crankbait</t>
         </is>
       </c>
-      <c r="AJ50" s="52" t="inlineStr"/>
-      <c r="AK50" s="52" t="inlineStr"/>
-      <c r="AL50" s="52" t="inlineStr"/>
-      <c r="AM50" s="52" t="inlineStr">
+      <c r="AJ50" s="60" t="inlineStr"/>
+      <c r="AK50" s="60" t="inlineStr"/>
+      <c r="AL50" s="60" t="inlineStr"/>
+      <c r="AM50" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 野池・草边・浅 cover / Chatterbait 与中量 bait</t>
         </is>
       </c>
-      <c r="AN50" s="52" t="inlineStr">
+      <c r="AN50" s="60" t="inlineStr">
         <is>
           <t>Chatterbait 主轴中量泛用</t>
         </is>
       </c>
-      <c r="AO50" s="52" t="inlineStr">
+      <c r="AO50" s="60" t="inlineStr">
         <is>
           <t>Chatterbait 和 Spinnerbait 的卷动稳定性更突出，Texas、Rubber Jig 可在同一套线组下补打点，适合移动饵和底操来回切。</t>
         </is>
       </c>
-      <c r="AP50" s="52" t="inlineStr">
+      <c r="AP50" s="60" t="inlineStr">
         <is>
           <t>ミドルスーパーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ50" s="52" t="inlineStr">
+      <c r="AQ50" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR50" s="60" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="AR50" s="52" t="inlineStr"/>
+      <c r="AS50" s="60" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="52" t="inlineStr">
+      <c r="A51" s="60" t="inlineStr">
         <is>
           <t>DSRD10049</t>
         </is>
       </c>
-      <c r="B51" s="52" t="inlineStr">
+      <c r="B51" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C51" s="52" t="inlineStr">
+      <c r="C51" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D51" s="52" t="inlineStr">
+      <c r="D51" s="60" t="inlineStr">
         <is>
           <t>DBTC-70M+-FM</t>
         </is>
       </c>
-      <c r="E51" s="52" t="inlineStr">
+      <c r="E51" s="60" t="inlineStr">
         <is>
           <t>M+</t>
         </is>
       </c>
-      <c r="F51" s="52" t="inlineStr">
+      <c r="F51" s="60" t="inlineStr">
         <is>
           <t>7’0″</t>
         </is>
       </c>
-      <c r="G51" s="52" t="inlineStr">
+      <c r="G51" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H51" s="52" t="inlineStr"/>
-      <c r="I51" s="52" t="inlineStr"/>
-      <c r="J51" s="52" t="inlineStr">
+      <c r="H51" s="60" t="inlineStr"/>
+      <c r="I51" s="60" t="inlineStr"/>
+      <c r="J51" s="60" t="inlineStr">
         <is>
           <t>152g</t>
         </is>
       </c>
-      <c r="K51" s="52" t="inlineStr"/>
-      <c r="L51" s="52" t="inlineStr"/>
-      <c r="M51" s="52" t="inlineStr">
+      <c r="K51" s="60" t="inlineStr"/>
+      <c r="L51" s="60" t="inlineStr"/>
+      <c r="M51" s="60" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N51" s="52" t="inlineStr"/>
-      <c r="O51" s="52" t="inlineStr"/>
-      <c r="P51" s="52" t="inlineStr"/>
-      <c r="Q51" s="52" t="inlineStr"/>
-      <c r="R51" s="52" t="inlineStr">
+      <c r="N51" s="60" t="inlineStr"/>
+      <c r="O51" s="60" t="inlineStr"/>
+      <c r="P51" s="60" t="inlineStr"/>
+      <c r="Q51" s="60" t="inlineStr"/>
+      <c r="R51" s="60" t="inlineStr">
         <is>
           <t>¥29,500 （税込￥32,450）</t>
         </is>
       </c>
-      <c r="S51" s="52" t="inlineStr">
+      <c r="S51" s="60" t="inlineStr">
         <is>
           <t>4571527860720</t>
         </is>
       </c>
-      <c r="T51" s="52" t="inlineStr"/>
-      <c r="U51" s="52" t="inlineStr"/>
-      <c r="V51" s="52" t="inlineStr"/>
-      <c r="W51" s="52" t="inlineStr"/>
-      <c r="X51" s="52" t="inlineStr"/>
-      <c r="Y51" s="52" t="inlineStr"/>
-      <c r="Z51" s="52" t="inlineStr">
+      <c r="T51" s="60" t="inlineStr"/>
+      <c r="U51" s="60" t="inlineStr"/>
+      <c r="V51" s="60" t="inlineStr"/>
+      <c r="W51" s="60" t="inlineStr"/>
+      <c r="X51" s="60" t="inlineStr"/>
+      <c r="Y51" s="60" t="inlineStr"/>
+      <c r="Z51" s="60" t="inlineStr">
         <is>
           <t>1/4～1</t>
         </is>
       </c>
-      <c r="AA51" s="52" t="inlineStr"/>
-      <c r="AB51" s="52" t="inlineStr"/>
-      <c r="AC51" s="52" t="inlineStr"/>
-      <c r="AD51" s="52" t="inlineStr"/>
-      <c r="AE51" s="52" t="inlineStr"/>
-      <c r="AF51" s="52" t="inlineStr"/>
-      <c r="AG51" s="52" t="inlineStr"/>
-      <c r="AH51" s="52" t="inlineStr">
+      <c r="AA51" s="60" t="inlineStr"/>
+      <c r="AB51" s="60" t="inlineStr"/>
+      <c r="AC51" s="60" t="inlineStr"/>
+      <c r="AD51" s="60" t="inlineStr"/>
+      <c r="AE51" s="60" t="inlineStr"/>
+      <c r="AF51" s="60" t="inlineStr"/>
+      <c r="AG51" s="60" t="inlineStr"/>
+      <c r="AH51" s="60" t="inlineStr">
         <is>
           <t>70M+-FM 是 glass-composite fast-moving 专用，官网明确列出 Crankbait、Big Minnow、中大型 Topwater、Spinnerbait、Buzzbait、Blade Jig 和 Shad Tail，全部属于巻物/移动饵体系。</t>
         </is>
       </c>
-      <c r="AI51" s="52" t="inlineStr">
+      <c r="AI51" s="60" t="inlineStr">
         <is>
           <t>Crankbait / Big Minnow / Topwater Plug / Spinnerbait / Buzzbait / Chatterbait / Shad Tail</t>
         </is>
       </c>
-      <c r="AJ51" s="52" t="inlineStr"/>
-      <c r="AK51" s="52" t="inlineStr"/>
-      <c r="AL51" s="52" t="inlineStr"/>
-      <c r="AM51" s="52" t="inlineStr">
+      <c r="AJ51" s="60" t="inlineStr"/>
+      <c r="AK51" s="60" t="inlineStr"/>
+      <c r="AL51" s="60" t="inlineStr"/>
+      <c r="AM51" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 开阔水・硬物边・风口 / fast moving search</t>
         </is>
       </c>
-      <c r="AN51" s="52" t="inlineStr">
+      <c r="AN51" s="60" t="inlineStr">
         <is>
           <t>Glass-composite 强搜索卷物</t>
         </is>
       </c>
-      <c r="AO51" s="52" t="inlineStr">
+      <c r="AO51" s="60" t="inlineStr">
         <is>
           <t>Crankbait、Big Minnow、Topwater、Spinnerbait、Buzzbait、Chatterbait 和 Shad Tail 都围绕连续搜索，适合覆盖水面和承接追咬。</t>
         </is>
       </c>
-      <c r="AP51" s="52" t="inlineStr">
+      <c r="AP51" s="60" t="inlineStr">
         <is>
           <t>グラスコンポジットブランク採用 ファストムービング専用モデル グラスコンポジットブランク採用のファストムービングモデル。クランクベイト、ビックミノー、中～大型トップウォーターやスピナーベイト、バズベイト、ブレードジグ、シャッドテールなど広く使用する事が可能。キャスタビリティーも非常に良く、狙ったスポットへ正確にアプローチを出来る性能とバイトより深く出来るのがグラスコンポジットの特徴でもあります。ロッド一本で巻物系全般をカバーしたいそんなアングラーに送るオススメの１本です。ストレートグリップモデル。</t>
         </is>
       </c>
-      <c r="AQ51" s="52" t="inlineStr">
+      <c r="AQ51" s="60" t="inlineStr">
+        <is>
+          <t>グラスコンポジットブランク / ストレートグリップ</t>
+        </is>
+      </c>
+      <c r="AR51" s="60" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="AR51" s="52" t="inlineStr"/>
+      <c r="AS51" s="60" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="52" t="inlineStr">
+      <c r="A52" s="60" t="inlineStr">
         <is>
           <t>DSRD10050</t>
         </is>
       </c>
-      <c r="B52" s="52" t="inlineStr">
+      <c r="B52" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C52" s="52" t="inlineStr">
+      <c r="C52" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D52" s="52" t="inlineStr">
+      <c r="D52" s="60" t="inlineStr">
         <is>
           <t>DBTC-70H-S</t>
         </is>
       </c>
-      <c r="E52" s="52" t="inlineStr">
+      <c r="E52" s="60" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F52" s="52" t="inlineStr">
+      <c r="F52" s="60" t="inlineStr">
         <is>
           <t>7’0″</t>
         </is>
       </c>
-      <c r="G52" s="52" t="inlineStr">
+      <c r="G52" s="60" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H52" s="52" t="inlineStr"/>
-      <c r="I52" s="52" t="inlineStr"/>
-      <c r="J52" s="52" t="inlineStr">
+      <c r="H52" s="60" t="inlineStr"/>
+      <c r="I52" s="60" t="inlineStr"/>
+      <c r="J52" s="60" t="inlineStr">
         <is>
           <t>126g</t>
         </is>
       </c>
-      <c r="K52" s="52" t="inlineStr"/>
-      <c r="L52" s="52" t="inlineStr"/>
-      <c r="M52" s="52" t="inlineStr">
+      <c r="K52" s="60" t="inlineStr"/>
+      <c r="L52" s="60" t="inlineStr"/>
+      <c r="M52" s="60" t="inlineStr">
         <is>
           <t>10~20</t>
         </is>
       </c>
-      <c r="N52" s="52" t="inlineStr"/>
-      <c r="O52" s="52" t="inlineStr"/>
-      <c r="P52" s="52" t="inlineStr"/>
-      <c r="Q52" s="52" t="inlineStr"/>
-      <c r="R52" s="52" t="inlineStr">
+      <c r="N52" s="60" t="inlineStr"/>
+      <c r="O52" s="60" t="inlineStr"/>
+      <c r="P52" s="60" t="inlineStr"/>
+      <c r="Q52" s="60" t="inlineStr"/>
+      <c r="R52" s="60" t="inlineStr">
         <is>
           <t>¥29,500 （税込￥32,450）</t>
         </is>
       </c>
-      <c r="S52" s="52" t="inlineStr">
+      <c r="S52" s="60" t="inlineStr">
         <is>
           <t>4571527863585</t>
         </is>
       </c>
-      <c r="T52" s="52" t="inlineStr"/>
-      <c r="U52" s="52" t="inlineStr"/>
-      <c r="V52" s="52" t="inlineStr"/>
-      <c r="W52" s="52" t="inlineStr"/>
-      <c r="X52" s="52" t="inlineStr"/>
-      <c r="Y52" s="52" t="inlineStr"/>
-      <c r="Z52" s="52" t="inlineStr">
+      <c r="T52" s="60" t="inlineStr"/>
+      <c r="U52" s="60" t="inlineStr"/>
+      <c r="V52" s="60" t="inlineStr"/>
+      <c r="W52" s="60" t="inlineStr"/>
+      <c r="X52" s="60" t="inlineStr"/>
+      <c r="Y52" s="60" t="inlineStr"/>
+      <c r="Z52" s="60" t="inlineStr">
         <is>
           <t>3/16～1</t>
         </is>
       </c>
-      <c r="AA52" s="52" t="inlineStr"/>
-      <c r="AB52" s="52" t="inlineStr"/>
-      <c r="AC52" s="52" t="inlineStr"/>
-      <c r="AD52" s="52" t="inlineStr"/>
-      <c r="AE52" s="52" t="inlineStr"/>
-      <c r="AF52" s="52" t="inlineStr"/>
-      <c r="AG52" s="52" t="inlineStr"/>
-      <c r="AH52" s="52" t="inlineStr">
+      <c r="AA52" s="60" t="inlineStr"/>
+      <c r="AB52" s="60" t="inlineStr"/>
+      <c r="AC52" s="60" t="inlineStr"/>
+      <c r="AD52" s="60" t="inlineStr"/>
+      <c r="AE52" s="60" t="inlineStr"/>
+      <c r="AF52" s="60" t="inlineStr"/>
+      <c r="AG52" s="60" t="inlineStr"/>
+      <c r="AH52" s="60" t="inlineStr">
         <is>
           <t>70H-S 以 heavy cover finesse 为主题，Cover Neko 放首位，Texas、Rubber Jig 和 Heavy Down Shot 用于更重 cover 或更强穿透；不扩写到大型饵。</t>
         </is>
       </c>
-      <c r="AI52" s="52" t="inlineStr">
+      <c r="AI52" s="60" t="inlineStr">
         <is>
           <t>Cover Neko / Texas Rig / Rubber Jig / Heavy Down Shot</t>
         </is>
       </c>
-      <c r="AJ52" s="52" t="inlineStr"/>
-      <c r="AK52" s="52" t="inlineStr"/>
-      <c r="AL52" s="52" t="inlineStr"/>
-      <c r="AM52" s="52" t="inlineStr">
+      <c r="AJ52" s="60" t="inlineStr"/>
+      <c r="AK52" s="60" t="inlineStr"/>
+      <c r="AL52" s="60" t="inlineStr"/>
+      <c r="AM52" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / heavy cover・沉木・厚草 / heavy cover finesse</t>
         </is>
       </c>
-      <c r="AN52" s="52" t="inlineStr">
+      <c r="AN52" s="60" t="inlineStr">
         <is>
           <t>重 cover 软饵控制</t>
         </is>
       </c>
-      <c r="AO52" s="52" t="inlineStr">
+      <c r="AO52" s="60" t="inlineStr">
         <is>
           <t>Cover Neko、Texas、Rubber Jig 和 Heavy Down Shot 都服务于重 cover 内的精细进攻，重点是进得去、挂住后拉得出来。</t>
         </is>
       </c>
-      <c r="AP52" s="52" t="inlineStr">
+      <c r="AP52" s="60" t="inlineStr">
         <is>
           <t>ヘビーカバーをよりフィネスに</t>
         </is>
       </c>
-      <c r="AQ52" s="52" t="inlineStr">
+      <c r="AQ52" s="60" t="inlineStr">
+        <is>
+          <t>ヘビーアクションソリッドティップ / ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR52" s="60" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="AR52" s="52" t="inlineStr"/>
+      <c r="AS52" s="60" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="52" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr">
         <is>
           <t>DSRD10051</t>
         </is>
       </c>
-      <c r="B53" s="52" t="inlineStr">
+      <c r="B53" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C53" s="52" t="inlineStr">
+      <c r="C53" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D53" s="52" t="inlineStr">
+      <c r="D53" s="60" t="inlineStr">
         <is>
           <t>DBTC-71MH-PF</t>
         </is>
       </c>
-      <c r="E53" s="52" t="inlineStr">
+      <c r="E53" s="60" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="F53" s="52" t="inlineStr">
+      <c r="F53" s="60" t="inlineStr">
         <is>
           <t>7’1″</t>
         </is>
       </c>
-      <c r="G53" s="52" t="inlineStr">
+      <c r="G53" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H53" s="52" t="inlineStr"/>
-      <c r="I53" s="52" t="inlineStr"/>
-      <c r="J53" s="52" t="inlineStr">
+      <c r="H53" s="60" t="inlineStr"/>
+      <c r="I53" s="60" t="inlineStr"/>
+      <c r="J53" s="60" t="inlineStr">
         <is>
           <t>117g</t>
         </is>
       </c>
-      <c r="K53" s="52" t="inlineStr"/>
-      <c r="L53" s="52" t="inlineStr"/>
-      <c r="M53" s="52" t="inlineStr">
+      <c r="K53" s="60" t="inlineStr"/>
+      <c r="L53" s="60" t="inlineStr"/>
+      <c r="M53" s="60" t="inlineStr">
         <is>
           <t>8~16</t>
         </is>
       </c>
-      <c r="N53" s="52" t="inlineStr">
+      <c r="N53" s="60" t="inlineStr">
         <is>
           <t>1~2.5</t>
         </is>
       </c>
-      <c r="O53" s="52" t="inlineStr"/>
-      <c r="P53" s="52" t="inlineStr"/>
-      <c r="Q53" s="52" t="inlineStr"/>
-      <c r="R53" s="52" t="inlineStr">
+      <c r="O53" s="60" t="inlineStr"/>
+      <c r="P53" s="60" t="inlineStr"/>
+      <c r="Q53" s="60" t="inlineStr"/>
+      <c r="R53" s="60" t="inlineStr">
         <is>
           <t>¥29,000 （税込￥31,900）</t>
         </is>
       </c>
-      <c r="S53" s="52" t="inlineStr">
+      <c r="S53" s="60" t="inlineStr">
         <is>
           <t>4580484757028</t>
         </is>
       </c>
-      <c r="T53" s="52" t="inlineStr"/>
-      <c r="U53" s="52" t="inlineStr"/>
-      <c r="V53" s="52" t="inlineStr"/>
-      <c r="W53" s="52" t="inlineStr"/>
-      <c r="X53" s="52" t="inlineStr"/>
-      <c r="Y53" s="52" t="inlineStr"/>
-      <c r="Z53" s="52" t="inlineStr">
+      <c r="T53" s="60" t="inlineStr"/>
+      <c r="U53" s="60" t="inlineStr"/>
+      <c r="V53" s="60" t="inlineStr"/>
+      <c r="W53" s="60" t="inlineStr"/>
+      <c r="X53" s="60" t="inlineStr"/>
+      <c r="Y53" s="60" t="inlineStr"/>
+      <c r="Z53" s="60" t="inlineStr">
         <is>
           <t>1/8～3/4</t>
         </is>
       </c>
-      <c r="AA53" s="52" t="inlineStr"/>
-      <c r="AB53" s="52" t="inlineStr"/>
-      <c r="AC53" s="52" t="inlineStr"/>
-      <c r="AD53" s="52" t="inlineStr"/>
-      <c r="AE53" s="52" t="inlineStr"/>
-      <c r="AF53" s="52" t="inlineStr"/>
-      <c r="AG53" s="52" t="inlineStr"/>
-      <c r="AH53" s="52" t="inlineStr">
+      <c r="AA53" s="60" t="inlineStr"/>
+      <c r="AB53" s="60" t="inlineStr"/>
+      <c r="AC53" s="60" t="inlineStr"/>
+      <c r="AD53" s="60" t="inlineStr"/>
+      <c r="AE53" s="60" t="inlineStr"/>
+      <c r="AF53" s="60" t="inlineStr"/>
+      <c r="AG53" s="60" t="inlineStr"/>
+      <c r="AH53" s="60" t="inlineStr">
         <is>
           <t>71MH-PF 官方主轴是 bait power finesse：PE 时 Small Rubber Jig 与 Bait Neko 优先；白名单 Frog 可作为 cover 补强，fluorocarbon 时再切 Heavy Down Shot、Free Rig、Texas、Football。</t>
         </is>
       </c>
-      <c r="AI53" s="52" t="inlineStr">
+      <c r="AI53" s="60" t="inlineStr">
         <is>
           <t>Bait Power Finesse / Small Rubber Jig / Bait Neko / Frog / Heavy Down Shot / Free Rig / Texas Rig / Football Jig</t>
         </is>
       </c>
-      <c r="AJ53" s="52" t="inlineStr"/>
-      <c r="AK53" s="52" t="inlineStr"/>
-      <c r="AL53" s="52" t="inlineStr"/>
-      <c r="AM53" s="52" t="inlineStr">
+      <c r="AJ53" s="60" t="inlineStr"/>
+      <c r="AK53" s="60" t="inlineStr"/>
+      <c r="AL53" s="60" t="inlineStr"/>
+      <c r="AM53" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / cover 池塘・草洞・浮物 / bait power finesse 与 Frog</t>
         </is>
       </c>
-      <c r="AN53" s="52" t="inlineStr">
+      <c r="AN53" s="60" t="inlineStr">
         <is>
           <t>Bait power finesse 兼 Frog cover</t>
         </is>
       </c>
-      <c r="AO53" s="52" t="inlineStr">
+      <c r="AO53" s="60" t="inlineStr">
         <is>
           <t>Small Rubber Jig、Bait Neko 是主轴，Frog 可处理草面或浮物，Heavy Down Shot、Free Rig、Texas、Football 让同一支竿能切到底层强攻。</t>
         </is>
       </c>
-      <c r="AP53" s="52" t="inlineStr">
+      <c r="AP53" s="60" t="inlineStr">
         <is>
           <t>ヘビーカバー用ベイトパワーフィネスSPモデル より手返し良くパワーフィネスをベイトタックルで行う為に生まれたベイトパワーフィネスSPモデル。PEラインを使用したスモラバやベイトネコのパワーフィネスを基軸に、フロロカーボンラインならヘビーダウンショット、フリーリグ、テキサスリグ、フットボールなどマルチに活躍します。カバー負けしないMHパワーのブランクにティップセクションは糸絡みを考慮しLDBガイドを採用。グリップデザインもシェイク疲れを軽減するべくパワーフィネスSP仕様。異なる弾性のカーボンで構成したナノマテリアル配合のBLUE TREKブランクスは、不意なビッグフィッシュでも逃さない粘りを実現。</t>
         </is>
       </c>
-      <c r="AQ53" s="52" t="inlineStr">
+      <c r="AQ53" s="60" t="inlineStr">
+        <is>
+          <t>LDBガイド / パワーフィネスSPグリップ / ナノマテリアル配合BLUE TREKブランクス</t>
+        </is>
+      </c>
+      <c r="AR53" s="60" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="AR53" s="52" t="inlineStr"/>
+      <c r="AS53" s="60" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="52" t="inlineStr">
+      <c r="A54" s="60" t="inlineStr">
         <is>
           <t>DSRD10052</t>
         </is>
       </c>
-      <c r="B54" s="52" t="inlineStr">
+      <c r="B54" s="60" t="inlineStr">
         <is>
           <t>DSR1005</t>
         </is>
       </c>
-      <c r="C54" s="52" t="inlineStr">
+      <c r="C54" s="60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D54" s="52" t="inlineStr">
+      <c r="D54" s="60" t="inlineStr">
         <is>
           <t>DBTC-73H</t>
         </is>
       </c>
-      <c r="E54" s="52" t="inlineStr">
+      <c r="E54" s="60" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="F54" s="52" t="inlineStr">
+      <c r="F54" s="60" t="inlineStr">
         <is>
           <t>7’3″</t>
         </is>
       </c>
-      <c r="G54" s="52" t="inlineStr">
+      <c r="G54" s="60" t="inlineStr">
         <is>
           <t>Regular Fast</t>
         </is>
       </c>
-      <c r="H54" s="52" t="inlineStr"/>
-      <c r="I54" s="52" t="inlineStr"/>
-      <c r="J54" s="52" t="inlineStr">
+      <c r="H54" s="60" t="inlineStr"/>
+      <c r="I54" s="60" t="inlineStr"/>
+      <c r="J54" s="60" t="inlineStr">
         <is>
           <t>133g</t>
         </is>
       </c>
-      <c r="K54" s="52" t="inlineStr"/>
-      <c r="L54" s="52" t="inlineStr"/>
-      <c r="M54" s="52" t="inlineStr">
+      <c r="K54" s="60" t="inlineStr"/>
+      <c r="L54" s="60" t="inlineStr"/>
+      <c r="M54" s="60" t="inlineStr">
         <is>
           <t>14~25</t>
         </is>
       </c>
-      <c r="N54" s="52" t="inlineStr"/>
-      <c r="O54" s="52" t="inlineStr"/>
-      <c r="P54" s="52" t="inlineStr"/>
-      <c r="Q54" s="52" t="inlineStr"/>
-      <c r="R54" s="52" t="inlineStr">
+      <c r="N54" s="60" t="inlineStr"/>
+      <c r="O54" s="60" t="inlineStr"/>
+      <c r="P54" s="60" t="inlineStr"/>
+      <c r="Q54" s="60" t="inlineStr"/>
+      <c r="R54" s="60" t="inlineStr">
         <is>
           <t>¥29,500 （税込￥32,450）</t>
         </is>
       </c>
-      <c r="S54" s="52" t="inlineStr">
+      <c r="S54" s="60" t="inlineStr">
         <is>
           <t>4580484757035</t>
         </is>
       </c>
-      <c r="T54" s="52" t="inlineStr"/>
-      <c r="U54" s="52" t="inlineStr"/>
-      <c r="V54" s="52" t="inlineStr"/>
-      <c r="W54" s="52" t="inlineStr"/>
-      <c r="X54" s="52" t="inlineStr"/>
-      <c r="Y54" s="52" t="inlineStr"/>
-      <c r="Z54" s="52" t="inlineStr">
+      <c r="T54" s="60" t="inlineStr"/>
+      <c r="U54" s="60" t="inlineStr"/>
+      <c r="V54" s="60" t="inlineStr"/>
+      <c r="W54" s="60" t="inlineStr"/>
+      <c r="X54" s="60" t="inlineStr"/>
+      <c r="Y54" s="60" t="inlineStr"/>
+      <c r="Z54" s="60" t="inlineStr">
         <is>
           <t>1/4～1・1/4</t>
         </is>
       </c>
-      <c r="AA54" s="52" t="inlineStr"/>
-      <c r="AB54" s="52" t="inlineStr"/>
-      <c r="AC54" s="52" t="inlineStr"/>
-      <c r="AD54" s="52" t="inlineStr"/>
-      <c r="AE54" s="52" t="inlineStr"/>
-      <c r="AF54" s="52" t="inlineStr"/>
-      <c r="AG54" s="52" t="inlineStr"/>
-      <c r="AH54" s="52" t="inlineStr">
+      <c r="AA54" s="60" t="inlineStr"/>
+      <c r="AB54" s="60" t="inlineStr"/>
+      <c r="AC54" s="60" t="inlineStr"/>
+      <c r="AD54" s="60" t="inlineStr"/>
+      <c r="AE54" s="60" t="inlineStr"/>
+      <c r="AF54" s="60" t="inlineStr"/>
+      <c r="AG54" s="60" t="inlineStr"/>
+      <c r="AH54" s="60" t="inlineStr">
         <is>
           <t>73H 是 heavy versatile，适合 Big Bait、Crawler、Swimbait 和 Swim Jig 这类强搜索，也能承担 Heavy Texas 与 Flipping；排序体现大型移动饵和 heavy cover 双线用途。</t>
         </is>
       </c>
-      <c r="AI54" s="52" t="inlineStr">
+      <c r="AI54" s="60" t="inlineStr">
         <is>
           <t>Big Bait / Crawler Bait / Swimbait / Swim Jig / Heavy Texas / Flipping</t>
         </is>
       </c>
-      <c r="AJ54" s="52" t="inlineStr"/>
-      <c r="AK54" s="52" t="inlineStr"/>
-      <c r="AL54" s="52" t="inlineStr"/>
-      <c r="AM54" s="52" t="inlineStr">
+      <c r="AJ54" s="60" t="inlineStr"/>
+      <c r="AK54" s="60" t="inlineStr"/>
+      <c r="AL54" s="60" t="inlineStr"/>
+      <c r="AM54" s="60" t="inlineStr">
         <is>
           <t>淡水 Bass / 大型湖・草区・重 cover / big bait 与 heavy cover</t>
         </is>
       </c>
-      <c r="AN54" s="52" t="inlineStr">
+      <c r="AN54" s="60" t="inlineStr">
         <is>
           <t>大型移动饵与 heavy cover 双线</t>
         </is>
       </c>
-      <c r="AO54" s="52" t="inlineStr">
+      <c r="AO54" s="60" t="inlineStr">
         <is>
           <t>Big Bait、Crawler、Swimbait、Swim Jig 负责大范围搜索，Heavy Texas 和 Flipping 可处理重 cover，是偏强力路线的一支。</t>
         </is>
       </c>
-      <c r="AP54" s="52" t="inlineStr">
+      <c r="AP54" s="60" t="inlineStr">
         <is>
           <t>ヘビーバーサタイルモデル</t>
         </is>
       </c>
-      <c r="AQ54" s="52" t="inlineStr">
+      <c r="AQ54" s="60" t="inlineStr">
+        <is>
+          <t>ナノマテリアル配合BLUE TREKブランクス / オールWフットガイド</t>
+        </is>
+      </c>
+      <c r="AR54" s="60" t="inlineStr">
         <is>
           <t>221</t>
         </is>
       </c>
-      <c r="AR54" s="52" t="inlineStr"/>
+      <c r="AS54" s="60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
